--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B487"/>
+  <dimension ref="A1:B488"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,108 +527,108 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed as working state President of Maharashtra BJP</t>
+          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-devendra-fadnavis-11736609352903.html</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president/articleshow/117155260.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
+          <t>Ravindra Chavan appointed as working state President of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president/articleshow/117155260.cms</t>
+          <t>https://www.livemint.com/politics/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-devendra-fadnavis-11736609352903.html</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BJP mayor needed to remove the stagnation in Kalyan-Dombivli’s development, says BJP Maharashtra presiden</t>
+          <t>Ravindra Chavan appointed as Maharashtra unit BJP president</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
+          <t>https://english.gujaratsamachar.com/news/mumbai/ravindra-chavan-appointed-as-maharashtra-unit-bjp-president</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Maharashtra: Ravindra Chavan to be declared state BJP chief Tuesday, files nomination</t>
+          <t>BJP mayor needed to remove the stagnation in Kalyan-Dombivli’s development, says BJP Maharashtra presiden</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ravindra-chavan-to-be-declared-state-bjp-chief-tuesday-files-nomination-10098263/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BJP appoints Maratha face as its next Maharashtra president: Who is Ravindra Chavan?</t>
+          <t>Maharashtra: Ravindra Chavan to be declared state BJP chief Tuesday, files nomination</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/bjp-appoints-maratha-maharashtra-president-ravindra-chavan-10099887/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ravindra-chavan-to-be-declared-state-bjp-chief-tuesday-files-nomination-10098263/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Three-language policy was withdrawn to avoid law and order problems: Ravindra Chavan</t>
+          <t>Maharashtra BJP to get new chief? Ex-minister Ravindra Chavan joins the race; CM says ‘happy he filed nomination’</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/three-language-policy-was-withdrawn-to-avoid-law-and-order-problems-ravindra-chavan-10117229/</t>
+          <t>https://www.livemint.com/politics/news/maharashtra-bjp-to-get-new-chief-ex-minister-ravindra-chavan-joins-the-race-cm-says-happy-he-filed-nomination-11751293697889.html</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed working president of Maharashtra BJP</t>
+          <t>BJP appoints Maratha face as its next Maharashtra president: Who is Ravindra Chavan?</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/ravindra-chavan-appointed-working-president-of-maharashtra-bjp-9773761/</t>
+          <t>https://indianexpress.com/article/political-pulse/bjp-appoints-maratha-maharashtra-president-ravindra-chavan-10099887/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Maharashtra BJP to get new chief? Ex-minister Ravindra Chavan joins the race; CM says ‘happy he filed nomination’</t>
+          <t>Three-language policy was withdrawn to avoid law and order problems: Ravindra Chavan</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/maharashtra-bjp-to-get-new-chief-ex-minister-ravindra-chavan-joins-the-race-cm-says-happy-he-filed-nomination-11751293697889.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/three-language-policy-was-withdrawn-to-avoid-law-and-order-problems-ravindra-chavan-10117229/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed as Maharashtra unit BJP president</t>
+          <t>Ravindra Chavan appointed working president of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://english.gujaratsamachar.com/news/mumbai/ravindra-chavan-appointed-as-maharashtra-unit-bjp-president</t>
+          <t>https://indianexpress.com/article/cities/mumbai/ravindra-chavan-appointed-working-president-of-maharashtra-bjp-9773761/</t>
         </is>
       </c>
     </row>
@@ -659,48 +659,48 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Newly Appointed Working President Ravindra Chavan Can Be Next Maharashtra BJP Chief—Here's Why</t>
+          <t>Dombivli MLA Ravindra Chavan to be appointed Maharashtra BJP prez</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/newly-appointed-working-president-ravindra-chavan-can-be-next-maharashtra-bjp-chiefheres-why</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez-23582620</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP president ahead of crucial MMR polls</t>
+          <t>Newly Appointed Working President Ravindra Chavan Can Be Next Maharashtra BJP Chief—Here's Why</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-polls-2025-07-01-996989</t>
+          <t>https://swarajyamag.com/news-brief/newly-appointed-working-president-ravindra-chavan-can-be-next-maharashtra-bjp-chiefheres-why</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Why BJP is keen to go solo in local body polls in most of Maharashtra</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP president ahead of crucial MMR polls</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/why-bjp-keen-to-go-solo-local-body-polls-maharashtra-10153064/</t>
+          <t>https://www.indiatvnews.com/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-polls-2025-07-01-996989</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Dombivli MLA Ravindra Chavan to be appointed Maharashtra BJP prez</t>
+          <t>Why BJP is keen to go solo in local body polls in most of Maharashtra</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez-23582620</t>
+          <t>https://indianexpress.com/article/political-pulse/why-bjp-keen-to-go-solo-local-body-polls-maharashtra-10153064/</t>
         </is>
       </c>
     </row>
@@ -935,300 +935,300 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Viral list of dist chiefs fake: BJP; warns of police action</t>
+          <t>Ex-Minister Ravindra Chavan Appointed As Working President of BJP in Maharashtra</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/viral-list-of-dist-chiefs-fake-bjp-warns-of-police-action/articleshow/121252533.cms</t>
+          <t>https://www.republicworld.com/india/ex-minister-ravindra-chavan-appointed-as-working-state-president-of-bjp-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ex-Minister Ravindra Chavan Appointed As Working President of BJP in Maharashtra</t>
+          <t>Justice Chavan Calls For National Judicial Service, Reforms To Address Vacancies In Judiciary</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/ex-minister-ravindra-chavan-appointed-as-working-state-president-of-bjp-in-maharashtra</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Justice Chavan Calls For National Judicial Service, Reforms To Address Vacancies In Judiciary</t>
+          <t>Ex-minister Ravindra Chavan files nomination for post of Maharashtra BJP president</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan files nomination for post of Maharashtra BJP president</t>
+          <t>Ravindra Chavan Elected Maharashtra BJP President Unanimously</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
+          <t>https://www.republicworld.com/india/ravindra-chavan-elected-maharashtra-bjp-president-unanimously</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Elected Maharashtra BJP President Unanimously</t>
+          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/ravindra-chavan-elected-maharashtra-bjp-president-unanimously</t>
+          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
+          <t>How Ravindra Chavan brought Congress's Kunal Patil into BJP fold the day he became Maharashtra party chief</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
+          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Money lender booked for suicide abetment of debtor</t>
+          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/money-lender-booked-for-suicide-abetment-of-debtor/articleshow/121603123.cms</t>
+          <t>https://www.inkl.com/news/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Ravindra Chavan files nomination as BJP Maharashtra state president</t>
+          <t>Indian Political Highlights | Former minister Ravindra Chavan appointed as Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.editorji.com/india-news/chavan-eyes-maharashtra-bjp-presidency-1751290384908</t>
+          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>How Ravindra Chavan brought Congress's Kunal Patil into BJP fold the day he became Maharashtra party chief</t>
+          <t>Amit Shah’s Maharashtra Visit: BJP Gears Up for Local Body Polls with Key Outreach</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP President</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.inkl.com/news/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
+          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Indian Political Highlights | Former minister Ravindra Chavan appointed as Maharashtra BJP working president</t>
+          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ahead of Thackeray reunion, BJP’s Rane claims Uddhav harassed Raj, blames him for Shiv Sena’s downfall</t>
+          <t>58 BJP chiefs of districts named | Mumbai News</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jul/01/ahead-of-thackeray-reunion-bjps-rane-claims-uddhav-harassed-raj-blames-him-for-shiv-senas-downfall</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amit Shah’s Maharashtra Visit: BJP Gears Up for Local Body Polls with Key Outreach</t>
+          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
+          <t>https://www.dynamitenews.com/story/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Once UAPA accused over Dawood ‘links’, Sena (UBT) leader finds place in BJP ahead of Nashik civic polls</t>
+          <t>Former Congress MLA Kunal Patil joins BJP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/uapa-accused-dawood-links-sena-ubt-leader-in-bjp-nashik-civic-polls-10074232/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/former-congress-mla-kunal-patil-joins-bjp-10100556/</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>58 BJP chiefs of districts named | Mumbai News</t>
+          <t>Ravindra Chavan Becomes Maharashtra BJP Chief Unopposed</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
+          <t>https://english.dainikjagranmpcg.com/politics/ravindra-chavan-becomes-maharashtra-bjp-chief-unopposed/article-2343</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
+          <t>BJP chief in Maharashtra brings MNS union workers into party</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://www.dynamitenews.com/story/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Former Congress MLA Kunal Patil joins BJP</t>
+          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/former-congress-mla-kunal-patil-joins-bjp-10100556/</t>
+          <t>https://www.msn.com/en-in/news/India/ameet-satam-becomes-bjp-s-new-mumbai-chief-ahead-of-bmc-polls-who-is-he/ar-AA1L9t6x</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP President</t>
+          <t>Pune bridge collapse: Ex-minister Chavan demands probe into delay in construction of new structure</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
+          <t>https://theprint.in/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/2660671/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Becomes Maharashtra BJP Chief Unopposed</t>
+          <t>Mumbai Confidential: Wait for the new chief</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://english.dainikjagranmpcg.com/politics/ravindra-chavan-becomes-maharashtra-bjp-chief-unopposed/article-2343</t>
+          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-bjp-maharashtra-new-chief-10055191/</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BJP chief in Maharashtra brings MNS union workers into party</t>
+          <t>Indrayani river bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
+          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Pune bridge collapse: Ex-minister Chavan demands probe into delay in construction of new structure</t>
+          <t>Dombivli residents demand clarity as railways issue eviction notices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://theprint.in/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/2660671/</t>
+          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mumbai Confidential: Wait for the new chief</t>
+          <t>Mumbai Confidential: Brother trouble</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-bjp-maharashtra-new-chief-10055191/</t>
+          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Indrayani river bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
+          <t>BJP’s Sankalp to Siddhi campaign to begin this week</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjps-sankalp-to-siddhi-campaign-to-begin-this-week/articleshow/121606429.cms</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Dombivli residents demand clarity as railways issue eviction notices</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
+          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Mumbai Confidential: Brother trouble</t>
+          <t>Pune Congress leader Sanjay Jagtap joins BJP</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
+          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
         </is>
       </c>
     </row>
@@ -1271,432 +1271,432 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ex-Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
+          <t>Ravindra Chavan, Trusted Lieutenant Of Maharashtra CM Devendra Fadnavis, Appointed BJP State Unit President</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-trusted-lieutenant-of-maharashtra-cm-devendra-fadnavis-appointed-bjp-state-unit-president</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>BJP holds meeting of former MPs and MLAs ahead of local body polls in Maharashtra</t>
+          <t>Ravindra Chavan Meets PM Modi In New Delhi After Taking Charge As Maharashtra State BJP Chief</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
+          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-meets-pm-modi-in-new-delhi-after-taking-charge-as-maharashtra-state-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Dombivli MLA Ravindra Chavan Takes Charge as New Maharashtra BJP President, Replacing Chandrashekhar Bawankule</t>
+          <t>BJP’s idea of nationalism will be taken to the common man: Ravindra Chavan</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/dombivli-mla-ravindra-chavan-takes-charge-as-new-maharashtra-bjp-president-replacing-chandrashekhar-bawankule-a475/</t>
+          <t>https://www.lokmattimes.com/national/bjps-idea-of-nationalism-will-be-taken-to-the-common-man-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP State Chief Ravindra Chavan Meets PM Modi, Outlines Party’s Expansion Plan</t>
+          <t>27-Year-Old Flight Attendant from Dombivli Among Victims of Ahmedabad Plane Crash Confirms Maharashtra MLA Ravindra Chavan</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-state-chief-ravindra-chavan-meets-pm-modi-outlines-partys-expansion-plan</t>
+          <t>https://www.lokmattimes.com/thane/27-year-old-flight-attendant-from-dombivli-among-victims-of-ahmedabad-plane-crash-confirms-maharashtra-mla-ravindra-chavan-a475/</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: A Visionary Leader Strengthening Maharashtra BJP's Political Landscape</t>
+          <t>Ravindra Chavan To Lead Maharashtra BJP Telangana, Andhra, Uttarakhand Unit Chiefs To Be Named Tomorrow</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
+          <t>https://news.abplive.com/news/india/ravindra-chavan-to-lead-maharashtra-bjp-telangana-andhra-uttarakhand-unit-chiefs-to-be-named-tomorrow-1784254</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ravindra Chavan, Trusted Lieutenant Of Maharashtra CM Devendra Fadnavis, Appointed BJP State Unit President</t>
+          <t>Ravindra Chavan Files Nomination for Maharashtra BJP President #Gallery</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-trusted-lieutenant-of-maharashtra-cm-devendra-fadnavis-appointed-bjp-state-unit-president</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Meets PM Modi In New Delhi After Taking Charge As Maharashtra State BJP Chief</t>
+          <t>Maharashtra Politics: Former Congress MLA Kailas Gorantyal Joins BJP With Supporters In Mumbai; Ravindra</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-meets-pm-modi-in-new-delhi-after-taking-charge-as-maharashtra-state-bjp-chief</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-mla-kailas-gorantyal-joins-bjp-with-supporters-in-mumbai-ravindra-chavan-welcomes-induction</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BJP’s idea of nationalism will be taken to the common man: Ravindra Chavan</t>
+          <t>BJP-Mahayuti Govt Committed To Farmers’ Progress &amp; Dairy Sector Growth: Ravindra Chavan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjps-idea-of-nationalism-will-be-taken-to-the-common-man-ravindra-chavan/</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>27-Year-Old Flight Attendant from Dombivli Among Victims of Ahmedabad Plane Crash Confirms Maharashtra MLA Ravindra Chavan</t>
+          <t>Punes Kundmala Bridge Collapse: Opposition Alleges Corruption, Demands Culpable Homicide Charges</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/thane/27-year-old-flight-attendant-from-dombivli-among-victims-of-ahmedabad-plane-crash-confirms-maharashtra-mla-ravindra-chavan-a475/</t>
+          <t>https://www.freepressjournal.in/mumbai/punes-kundmala-bridge-collapse-opposition-alleges-corruption-demands-culpable-homicide-charges</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ravindra Chavan To Lead Maharashtra BJP Telangana, Andhra, Uttarakhand Unit Chiefs To Be Named Tomorrow</t>
+          <t>Read Ravindra Chavan bane BJP ke naye Maharashtra President</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ravindra-chavan-to-lead-maharashtra-bjp-telangana-andhra-uttarakhand-unit-chiefs-to-be-named-tomorrow-1784254</t>
+          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Files Nomination for Maharashtra BJP President #Gallery</t>
+          <t>Ravindra Chavan Files Nomination For BJP Maharashtra President Post</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-files-nomination-for-bjp-maharashtra-president-post</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Former Congress MLA Kailas Gorantyal Joins BJP With Supporters In Mumbai; Ravindra</t>
+          <t>BJP Picks Ravindra Chavan As Maharashtra Chief Ahead Of Key Civic Polls</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-mla-kailas-gorantyal-joins-bjp-with-supporters-in-mumbai-ravindra-chavan-welcomes-induction</t>
+          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>BJP-Mahayuti Govt Committed To Farmers’ Progress &amp; Dairy Sector Growth: Ravindra Chavan</t>
+          <t>Double-Engine Govt Working In Peoples Best Interests: New Maharashtra BJP Chief Ravindra Chavan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
+          <t>https://www.freepressjournal.in/mumbai/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Punes Kundmala Bridge Collapse: Opposition Alleges Corruption, Demands Culpable Homicide Charges</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/punes-kundmala-bridge-collapse-opposition-alleges-corruption-demands-culpable-homicide-charges</t>
+          <t>https://www.sakshipost.com/news/ravindra-chavan-set-take-over-maharashtra-unit-bjp-chief-tomorrow-424218</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Files Nomination For BJP Maharashtra President Post</t>
+          <t>Ravindra Chavan, Ex-Minister, Files Nomination For Maharashtra BJP Chief Election, Likely To Win Unopposed</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-files-nomination-for-bjp-maharashtra-president-post</t>
+          <t>https://www.thedailyjagran.com/maharashtra/ravindra-chavan-exminister-files-nomination-for-maharashtra-bjp-chief-election-likely-to-win-unopposed-10249053</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BJP Picks Ravindra Chavan As Maharashtra Chief Ahead Of Key Civic Polls</t>
+          <t>Mumbai: Over 2,000 IndiGo Airline Employees Join BJP Ahead Of BMC Election</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-over-2000-indigo-airline-employees-join-bjp-ahead-of-bmc-election</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Double-Engine Govt Working In Peoples Best Interests: New Maharashtra BJP Chief Ravindra Chavan</t>
+          <t>BJP Appoints Former Minister Ravindra Chavan As Maharashtra Units Working President</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-appoints-former-minister-ravindra-chavan-as-maharashtra-units-working-president</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ravindra Chavan, Ex-Minister, Files Nomination For Maharashtra BJP Chief Election, Likely To Win Unopposed</t>
+          <t>Maharashtra: BJP Poaches Key Leaders From Rival Parties In Palghar, Strengthens Hold Ahead Of Upcoming</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/ravindra-chavan-exminister-files-nomination-for-maharashtra-bjp-chief-election-likely-to-win-unopposed-10249053</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-poaches-key-leaders-from-rival-parties-in-palghar-strengthens-hold-ahead-of-upcoming-elections</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Mumbai: Over 2,000 IndiGo Airline Employees Join BJP Ahead Of BMC Election</t>
+          <t>Ravindra Chavan appointed as BJP state president of Maharashtra</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-over-2000-indigo-airline-employees-join-bjp-ahead-of-bmc-election</t>
+          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/ravindra-chavan-set-take-over-maharashtra-unit-bjp-chief-tomorrow-424218</t>
+          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>BJP Appoints Former Minister Ravindra Chavan As Maharashtra Units Working President</t>
+          <t>Public Gave Us Landslide Victory: Deputy CM Eknath Shinde Exerts Confidence On Win Of Mahayuti In</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-appoints-former-minister-ravindra-chavan-as-maharashtra-units-working-president</t>
+          <t>https://www.freepressjournal.in/mumbai/public-gave-us-landslide-victory-deputy-cm-eknath-shinde-exerts-confidence-on-win-of-mahayuti-in-maharashtra-elections</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP Poaches Key Leaders From Rival Parties In Palghar, Strengthens Hold Ahead Of Upcoming</t>
+          <t>Who Is Ameet Satam? Three-Term MLA From Andheri West Appointed As President Of Mumbai BJP Unit</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-poaches-key-leaders-from-rival-parties-in-palghar-strengthens-hold-ahead-of-upcoming-elections</t>
+          <t>https://www.freepressjournal.in/mumbai/who-is-ameet-satam-three-term-mla-from-andheri-west-appointed-as-president-of-mumbai-bjp-unit</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed as BJP state president of Maharashtra</t>
+          <t>Maharashtra News: BJP Sets Up 1,221 Mandals Across State, Appoints 963 Presidents Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-sets-up-1221-mandals-across-state-appoints-963-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
+          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Public Gave Us Landslide Victory: Deputy CM Eknath Shinde Exerts Confidence On Win Of Mahayuti In</t>
+          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/public-gave-us-landslide-victory-deputy-cm-eknath-shinde-exerts-confidence-on-win-of-mahayuti-in-maharashtra-elections</t>
+          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Who Is Ameet Satam? Three-Term MLA From Andheri West Appointed As President Of Mumbai BJP Unit</t>
+          <t>Pune: Kundmala Bridge Collapses 5 Days After Rs 8 Crore Renovation Approval; Sanjay Raut Alleges Corruption, Claims Only Rs 80,000 Was Actually Sanctioned</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/who-is-ameet-satam-three-term-mla-from-andheri-west-appointed-as-president-of-mumbai-bjp-unit</t>
+          <t>https://www.punekarnews.in/pune-kundmala-bridge-collapses-5-days-after-rs-8-crore-renovation-approval-sanjay-raut-alleges-corruption-claims-only-rs-80000-was-actually-sanctioned/</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Maharashtra News: BJP Sets Up 1,221 Mandals Across State, Appoints 963 Presidents Ahead Of Local Body Polls</t>
+          <t>Maharashtra News: BJP Warns Of Legal Action Over Fake List Of 81 District Presidents Circulating On Social</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-sets-up-1221-mandals-across-state-appoints-963-presidents-ahead-of-local-body-polls</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-warns-of-legal-action-over-fake-list-of-81-district-presidents-circulating-on-social-media</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
+          <t>Maha: Sudhakar Badgujar, who faced charges of 'links' with underworld, joins BJP</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
+          <t>https://www.thehawk.in/news/india/maha-sudhakar-badgujar-who-faced-charges-of-links-with-underworld-joins-bjp</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Nanded-Pune Vande Bharat Express to Start by December 2025</t>
+          <t>Over 2,000 IndiGo employees join BJP ahead of BMC elections in Mumbai</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/nanded-pune-vande-bharat-express-to-start-by-december-2025-a517/</t>
+          <t>https://english.varthabharati.in/india/over-2000-indigo-employees-join-bjp-ahead-of-bmc-elections-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Maharashtra News: BJP Warns Of Legal Action Over Fake List Of 81 District Presidents Circulating On Social</t>
+          <t>महाराष्ट्र में निकाय चुनाव से पहले BJP का बड़ा प्लान, पूर्व सांसदों और विधायकों</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-warns-of-legal-action-over-fake-list-of-81-district-presidents-circulating-on-social-media</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में निकाय चुनाव से पहले BJP का बड़ा प्लान, पूर्व सांसदों और विधायकों</t>
+          <t>Ravindra Chavan: बीजेपी ने पूर्व मंत्री रवींद्र चव्हाण को बनाया महाराष्ट्र का कार्यकारी अध्यक्ष, जानें पूरा सफर</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: बीजेपी ने पूर्व मंत्री रवींद्र चव्हाण को बनाया महाराष्ट्र का कार्यकारी अध्यक्ष, जानें पूरा सफर</t>
+          <t>महाराष्ट्र: BJP ने मराठा फेस रवींद्र चव्हाण पर क्यों जताया भरोसा? जानें पूरा सफर</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-why-did-bjp-express-confidence-in-maratha-face-ravindra-chavan-know-journey-3054753.html</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: BJP ने मराठा फेस रवींद्र चव्हाण पर क्यों जताया भरोसा? जानें पूरा सफर</t>
+          <t>Ravindra Chavan Latest News, Updates in Hindi | रवींद्र चव्हाण के समाचार और अपडेट</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-why-did-bjp-express-confidence-in-maratha-face-ravindra-chavan-know-journey-3054753.html</t>
+          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Latest News, Updates in Hindi | रवींद्र चव्हाण के समाचार और अपडेट</t>
+          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए बॉस, CM फडणवीस के साथ भरा नामांकन, जानें कौन हैं?</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-bjp-will-get-new-president-filed-nomination-know-who-is-ravindra-chavan-19711885</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए बॉस, CM फडणवीस के साथ भरा नामांकन, जानें कौन हैं?</t>
+          <t>मराठा चेहरा, कोंकण में पलटी बाजी; बीजेपी ने क्यों जताया रवींद्र चव्हाण पर भरोसा</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-bjp-will-get-new-president-filed-nomination-know-who-is-ravindra-chavan-19711885</t>
+          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
         </is>
       </c>
     </row>
@@ -1715,288 +1715,288 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>मराठा चेहरा, कोंकण में पलटी बाजी; बीजेपी ने क्यों जताया रवींद्र चव्हाण पर भरोसा</t>
+          <t>महाराष्ट्र बीजेपी अध्यक्ष के लिए ये नाम लगभग तय, जानें क्यों माने जाते हैं प्रबल</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी अध्यक्ष के लिए ये नाम लगभग तय, जानें क्यों माने जाते हैं प्रबल</t>
+          <t>महाराष्ट्र से रविंद्र चव्हाण तो एमपी से खंडेलवाल बने बीजेपी के नए प्रदेश अध्यक्ष, यहां जानें सारी डिटेल्स</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
+          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>महाराष्ट्र से रविंद्र चव्हाण तो एमपी से खंडेलवाल बने बीजेपी के नए प्रदेश अध्यक्ष, यहां जानें सारी डिटेल्स</t>
+          <t>Maharashtra BJP Politics: महाराष्ट्र में बड़ी जीत के बाद इस नेता को प्रदेश अध्यक्ष बना सकती है BJP, फडणवीस के हैं करीबी</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
+          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Maharashtra BJP Politics: महाराष्ट्र में बड़ी जीत के बाद इस नेता को प्रदेश अध्यक्ष बना सकती है BJP, फडणवीस के हैं करीबी</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र भाजपा के कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा ने किया एलान</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
+          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-23865140.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र भाजपा के कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा ने किया एलान</t>
+          <t>Maharashtra: पूर्व मंत्री रवीन्द्र चव्हाण बने महाराष्ट्र भाजपा के नए अध्यक्ष, सीएम देवेंद्र फडणवीस के हैं करीब</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-23865140.html</t>
+          <t>https://www.amarujala.com/india-news/ex-minister-ravindra-chavan-is-bjp-s-new-maharashtra-chief-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Maharashtra: पूर्व मंत्री रवीन्द्र चव्हाण बने महाराष्ट्र भाजपा के नए अध्यक्ष, सीएम देवेंद्र फडणवीस के हैं करीब</t>
+          <t>Maharashtra BJP President: रवींद्र चव्हाण बने महाराष्‍ट्र भाजपा के नए अध्‍यक्ष, पद संभालते के बाद क्‍या बोले?</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/ex-minister-ravindra-chavan-is-bjp-s-new-maharashtra-chief-2025-07-01</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: रवींद्र चव्हाण बने महाराष्‍ट्र भाजपा के नए अध्‍यक्ष, पद संभालते के बाद क्‍या बोले?</t>
+          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के नए प्रदेश अध्यक्ष, जानें उनका राजनीतिक सफर</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के नए प्रदेश अध्यक्ष, जानें उनका राजनीतिक सफर</t>
+          <t>Ravindra Chavan: 4 बार के विधायक, मराठा नेता, नतीजे देने की क्षमता, महाराष्ट्र BJP के नए कार्यकारी अध्यक्ष रवींद्र चव्हाण कौन?</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 4 बार के विधायक, मराठा नेता, नतीजे देने की क्षमता, महाराष्ट्र BJP के नए कार्यकारी अध्यक्ष रवींद्र चव्हाण कौन?</t>
+          <t>महाराष्ट्र भाजपा को मिला नया ‘कप्तान’, जानें कौन हैं प्रदेश अध्यक्ष रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
+          <t>https://www.patrika.com/mumbai-news/ravindra-chavan-became-maharashtra-bjp-president-know-who-is-he-19715228</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा को मिला नया ‘कप्तान’, जानें कौन हैं प्रदेश अध्यक्ष रवींद्र चव्हाण?</t>
+          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए अध्यक्ष, किरेन रिजिजू की मौजूदगी में भरा नामांकन - Ravindra Chavan will be the new president of Maharashtra BJP nomination filed in the presence of Kiren Rijiju</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/ravindra-chavan-became-maharashtra-bjp-president-know-who-is-he-19715228</t>
+          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए अध्यक्ष, किरेन रिजिजू की मौजूदगी में भरा नामांकन - Ravindra Chavan will be the new president of Maharashtra BJP nomination filed in the presence of Kiren Rijiju</t>
+          <t>सीएम देवेंद्र फडणवीस के करीबी रवींद्र चव्हाण बने महाराष्ट्र BJP के अध्यक्ष, जानें</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-elected-maharashtra-bjp-president-ann-2972075</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>सीएम देवेंद्र फडणवीस के करीबी रवींद्र चव्हाण बने महाराष्ट्र BJP के अध्यक्ष, जानें</t>
+          <t>महाराष्ट्र BJP प्रदेश अध्यक्ष का नाम हो गया तय, कल शाम 5 बजे होगी घोषणा</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-elected-maharashtra-bjp-president-ann-2972075</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP प्रदेश अध्यक्ष का नाम हो गया तय, कल शाम 5 बजे होगी घोषणा</t>
+          <t>महाराष्ट्र: रवींद्र चव्हाण बने BJP कार्यकारी प्रदेश अध्यक्ष, क्या छिन गई चंद्रशेखर</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: रवींद्र चव्हाण बने BJP कार्यकारी प्रदेश अध्यक्ष, क्या छिन गई चंद्रशेखर</t>
+          <t>कौन हैं रविंद्र चव्हाण जिन्हें बीजेपी ने पूरा महाराष्ट्र 'सौंप' दिया है? | The Lallantop</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
+          <t>https://www.thelallantop.com/india/post/bjp-appoints-maratha-face-as-its-next-maharashtra-president-who-is-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>कौन हैं रविंद्र चव्हाण जिन्हें बीजेपी ने पूरा महाराष्ट्र 'सौंप' दिया है?</t>
+          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, मुंबई महानगर क्षेत्र चुनाव में बदल सकते हैं समीकरण</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.thelallantop.com/india/post/bjp-appoints-maratha-face-as-its-next-maharashtra-president-who-is-ravindra-chavan</t>
+          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, मुंबई महानगर क्षेत्र चुनाव में बदल सकते हैं समीकरण</t>
+          <t>भाजपच्या 81 जिल्हाध्यक्षांची ती यादी फेक, व्हायरल करू नका रविंद्र चव्हाणांकडून इशारा</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>भाजपच्या 81 जिल्हाध्यक्षांची ती यादी फेक, व्हायरल करू नका रविंद्र चव्हाणांकडून इशारा</t>
+          <t>पार्षद से भाजपा प्रदेश अध्यक्ष तक… कैसा है महाराष्ट्र बीजेपी के नए अध्यक्ष रवींद्र चव्हाण का...</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
+          <t>https://www.tv9hindi.com/india/ravindra-chavan-new-bjp-maharashtra-president-profile-and-political-career-3369773.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>पार्षद से भाजपा प्रदेश अध्यक्ष तक… कैसा है महाराष्ट्र बीजेपी के नए अध्यक्ष रवींद्र चव्हाण का...</t>
+          <t>Maharashtra BJP President: कौन हैं रविंद्र चव्‍हाण? जिनका महाराष्ट्र BJP प्रदेश अध्यक्ष बनना तय है</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/ravindra-chavan-new-bjp-maharashtra-president-profile-and-political-career-3369773.html</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-bjp-president-who-is-ravindra-chavan-going-to-take-over-bjp-state-president-post-1328621.html</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: कौन हैं रविंद्र चव्‍हाण? जिनका महाराष्ट्र BJP प्रदेश अध्यक्ष बनना तय है</t>
+          <t>WHO IS Ravindra Chavan: कौन हैं रवींद्र चव्हाण?, भाजपा ने क्यों खेला दांव, चंद्रशेखर बावनकुले की जगह ले सकते हैं</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-bjp-president-who-is-ravindra-chavan-going-to-take-over-bjp-state-president-post-1328621.html</t>
+          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Kalyan : 'माझी कपिल पाटील आणि रविंद्र चव्हाण यांच्याशी लढाई' कल्याणच्या माजी भाजपा आमदाराची क्लीप Viral</t>
+          <t>बीजेपी प्रदेश अध्यक्ष बनते ही कांग्रेस में सेंध... पहले ही दिन रवींद्र चव्हाण ने कराई कुणाल पाटिल की जॉइनिंग</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>WHO IS Ravindra Chavan: कौन हैं रवींद्र चव्हाण?, भाजपा ने क्यों खेला दांव, चंद्रशेखर बावनकुले की जगह ले सकते हैं</t>
+          <t>Kalyan : 'माझी कपिल पाटील आणि रविंद्र चव्हाण यांच्याशी लढाई' कल्याणच्या माजी भाजपा आमदाराची क्लीप Viral</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
+          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>बीजेपी प्रदेश अध्यक्ष बनते ही कांग्रेस में सेंध... पहले ही दिन रवींद्र चव्हाण ने कराई कुणाल पाटिल की जॉइनिंग</t>
+          <t>महाराष्ट्र बीजेपी की कमान अब रवींद्र चव्हाण के हाथ में, निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
+          <t>https://www.tv9hindi.com/india/ravindra-chavan-elected-unopposed-as-maharashtra-bjp-president-3369508.html</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी की कमान अब रवींद्र चव्हाण के हाथ में, निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
+          <t>भाजपा महाराष्ट्र प्रदेश अध्यक्ष पद पर रविंद्र चौहान</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/ravindra-chavan-elected-unopposed-as-maharashtra-bjp-president-3369508.html</t>
+          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>भाजपा महाराष्ट्र प्रदेश अध्यक्ष पद पर रविंद्र चौहान</t>
+          <t>BJP News : रवींद्र चव्हाण यांची भाजपच्या महाराष्ट्र कार्यकारी अध्यक्षपदी नियुक्ती</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
+          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
         </is>
       </c>
     </row>
@@ -2111,240 +2111,240 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>BJP News : रवींद्र चव्हाण यांची भाजपच्या महाराष्ट्र कार्यकारी अध्यक्षपदी नियुक्ती</t>
+          <t>इंदापूर तालुक्यातील प्रवीण माने यांचा रविंद्र चव्हाण यांच्या उपस्थितीत भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
+          <t>https://www.loksatta.com/maharashtra/praveen-mane-from-indapur-tehsil-joined-bjp-in-the-presence-of-ravindra-chavan-svk-88-phm-00-5199118/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>इंदापूर तालुक्यातील प्रवीण माने यांचा रविंद्र चव्हाण यांच्या उपस्थितीत भाजपात प्रवेश</t>
+          <t>रविंद्र चव्हाण लवकरच भाजपचे नवे प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/praveen-mane-from-indapur-tehsil-joined-bjp-in-the-presence-of-ravindra-chavan-svk-88-phm-00-5199118/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-politics-ravindra-chavan-set-to-be-new-bjp-maharashtra-president-mumbai-print-news-vsd-99-5188808/</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>रविंद्र चव्हाण लवकरच भाजपचे नवे प्रदेशाध्यक्ष</t>
+          <t>भाजपचा नवा प्रदेशाध्यक्ष कोण? ‘या’ बड्या नेत्याचं नाव निश्चित, उद्या नावाची घोषणा होणार!</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-politics-ravindra-chavan-set-to-be-new-bjp-maharashtra-president-mumbai-print-news-vsd-99-5188808/</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-will-be-maharashtra-state-president-of-bjp-name-will-announce-1st-july-1435245.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>भाजपचा नवा प्रदेशाध्यक्ष कोण? ‘या’ बड्या नेत्याचं नाव निश्चित, उद्या नावाची घोषणा होणार!</t>
+          <t>Ravindra Chavan | रविंद्र चव्हाण यांची भाजप महाराष्‍ट्र प्रदेशाध्यक्षपदी निवड!</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-will-be-maharashtra-state-president-of-bjp-name-will-announce-1st-july-1435245.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-appointed-jp-maharashtra-president</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Ravindra Chavan | रविंद्र चव्हाण यांची भाजप महाराष्‍ट्र प्रदेशाध्यक्षपदी निवड!</t>
+          <t>ब्राह्मण, OBC और मराठा... देवेंद्र फडणवीस का अकाट्य फॉर्मूला, कांग्रेस ही नहीं सहयोगी भी चित!</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-appointed-jp-maharashtra-president</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>ब्राह्मण, OBC और मराठा... देवेंद्र फडणवीस का अकाट्य फॉर्मूला, कांग्रेस ही नहीं सहयोगी भी चित!</t>
+          <t>Ravindra Chavan : मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>Ravindra Chavan : फडणवीसांची औरंगजेबाशी तुलना करताच रविंद्र चव्हाण संतापले, काँग्रेस प्रदेशाध्यक्षांना दिलं उत्तर</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : फडणवीसांची औरंगजेबाशी तुलना करताच रविंद्र चव्हाण संतापले, काँग्रेस प्रदेशाध्यक्षांना दिलं उत्तर</t>
+          <t>सांगलीचा आगामी महापौर महायुतीचाच – रविंद्र चव्हाण</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-bjp-ravindra-chavan-confident-next-mayor-in-upcoming-civic-poll-will-be-from-mahayuti-rds-00-5299211/</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>सांगलीचा आगामी महापौर महायुतीचाच – रविंद्र चव्हाण</t>
+          <t>BJP News : शहराध्यक्ष कसा असावा ? भाजपा कार्याध्यक्ष रविंद्र चव्हाण यांनी पदाधिकारी-कार्यकर्त्यांचे कान टोचले!</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-bjp-ravindra-chavan-confident-next-mayor-in-upcoming-civic-poll-will-be-from-mahayuti-rds-00-5299211/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-expresses-expectations-from-bjp-city-district-presidents-jp75</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BJP News : शहराध्यक्ष कसा असावा ? भाजपा कार्याध्यक्ष रविंद्र चव्हाण यांनी पदाधिकारी-कार्यकर्त्यांचे कान टोचले!</t>
+          <t>Ravindra Chavan : रविंद्र चव्हाण यांनी प्रदेशाध्यक्ष पदाचा पदभार स्विकारला</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-expresses-expectations-from-bjp-city-district-presidents-jp75</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रविंद्र चव्हाण यांनी प्रदेशाध्यक्ष पदाचा पदभार स्विकारला</t>
+          <t>नगरसेवक ते थेट भाजपचे प्रदेशाध्यक्ष… रवींद्र चव्हाण यांच्या कारकिर्दीतील हे टप्पे माहीत आहेत...</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-new-maharashtra-bjp-presdent-know-his-journey-1436161.html</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>नगरसेवक ते थेट भाजपचे प्रदेशाध्यक्ष… रवींद्र चव्हाण यांच्या कारकिर्दीतील हे टप्पे माहीत आहेत...</t>
+          <t>महाराष्ट्र भाजपची धुरा रवींद्र चव्हाण सांभाळणार, कार्यकारी प्रदेशाध्यक्ष म्हणून नियुक्ती</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-new-maharashtra-bjp-presdent-know-his-journey-1436161.html</t>
+          <t>https://pudhari.news/national/raviindra-chavhan-appointed-maharashtra-bjp-executive-state-president</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>फेमस यूट्यूबर ने 33 साल की उम्र में दुनिया को कहा अलविदा, किस बीमारी से थे पीड़ित?</t>
+          <t>अण्णासाहेब डांगे दो बेटों के साथ BJP में शामिल, CM देवेंद्र फडणवीस की मौजूदगी में</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/youtuber-shirish-gavas-passed-away-red-soil-stories-channel-33-year-old-founder-died-19834284</t>
+          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपची धुरा रवींद्र चव्हाण सांभाळणार, कार्यकारी प्रदेशाध्यक्ष म्हणून नियुक्ती</t>
+          <t>Maharashtra Politics: कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण, एकमताने निवड, वाचा सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/raviindra-chavhan-appointed-maharashtra-bjp-executive-state-president</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>अण्णासाहेब डांगे दो बेटों के साथ BJP में शामिल, CM देवेंद्र फडणवीस की मौजूदगी में</t>
+          <t>RSS स्वयंसेवक ते BJP प्रदेशाध्यक्ष; ‘अशी’ आहे रवींद्र चव्हाण यांची राजकीय कारकीर्द</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
+          <t>https://www.lokmat.com/maharashtra/from-rss-volunteer-to-bjp-state-president-know-about-ravindra-chavan-political-career-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण, एकमताने निवड, वाचा सविस्तर माहिती</t>
+          <t>भाजपच्या महाराष्ट्र प्रदेश कार्यकारी अध्यक्षपदी रविंद्र चव्हाण यांची नियुक्ती</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
+          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>RSS स्वयंसेवक ते BJP प्रदेशाध्यक्ष; ‘अशी’ आहे रवींद्र चव्हाण यांची राजकीय कारकीर्द</t>
+          <t>Ravindra Chavan : महापालिका आयुक्तांनी प्रोटोकॉल पाळावा, हक्कभंगाची नोटीस देणार, नांदेडचे</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/from-rss-volunteer-to-bjp-state-president-know-about-ravindra-chavan-political-career-a-a719/</t>
+          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>भाजपच्या महाराष्ट्र प्रदेश कार्यकारी अध्यक्षपदी रविंद्र चव्हाण यांची नियुक्ती</t>
+          <t>Ravindra Chavan : ‘उपरा’ डोंबिवलीकर ते भाजप प्रदेश कार्याध्यक्ष</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
+          <t>https://www.loksatta.com/thane/bjp-leader-ravindra-chavan-political-journey-started-as-a-worker-to-maharashtra-bjp-chief-zws-70-4821598/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महापालिका आयुक्तांनी प्रोटोकॉल पाळावा, हक्कभंगाची नोटीस देणार, नांदेडचे</t>
+          <t>BJP Politics : कल्याण-डोंबिवलीत भाजप ठाकरेंना धक्का देणार! शिंदेंचीही अडचण वाढवणार; इन्कमिंग सुरू, महापौरपदासाठी स्वबळाचे संकेत</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
+          <t>https://sarkarnama.esakal.com/mumbai/jatin-prajapati-joins-kalyan-dombivli-bjp-welcomed-by-ravindra-chavan-rm89</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>BJP Politics : कल्याण-डोंबिवलीत भाजप ठाकरेंना धक्का देणार! शिंदेंचीही अडचण वाढवणार; इन्कमिंग सुरू, महापौरपदासाठी स्वबळाचे संकेत</t>
+          <t>Congress News : काँग्रेस खासदार रविंद्र चव्हाण संतापले, महापालिका आयुक्तांना हक्कभंग कारवाईचा इशारा!</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/jatin-prajapati-joins-kalyan-dombivli-bjp-welcomed-by-ravindra-chavan-rm89</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/congress-mp-ravindra-chavan-warns-action-against-commissioner-over-amit-shah-event-jp75</t>
         </is>
       </c>
     </row>
@@ -2363,336 +2363,336 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Congress News : काँग्रेस खासदार रविंद्र चव्हाण संतापले, महापालिका आयुक्तांना हक्कभंग कारवाईचा इशारा!</t>
+          <t>संयमी भूमिका फळली! भाजपच्या कार्यकारी प्रदेशाध्यक्षपदी रविंद्र चव्हाणांची नियुक्ती</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/congress-mp-ravindra-chavan-warns-action-against-commissioner-over-amit-shah-event-jp75</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>संयमी भूमिका फळली! भाजपच्या कार्यकारी प्रदेशाध्यक्षपदी रविंद्र चव्हाणांची नियुक्ती</t>
+          <t>Ravindra Chavan: भाजप नेते रविंद्र चव्हाण यांच्यावर पक्षाची महत्वाची जबाबदारी; कार्यकारी अध्यक्षपदी नियुक्ती</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
+          <t>https://www.esakal.com/desh/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-aau85</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>इंतजार खत्म... बीजेपी ने चार राज्यों में अपने प्रदेश अध्यक्षों के नाम फाइनल किए, जानें कौन है लिस्ट में</t>
+          <t>Ravindra Chavan BJP: रवींद्र चव्हाण भाजपाचे नवे 'कॅप्टन'! महाराष्ट्र प्रदेशाध्यक्षपदी बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-elected-unopposed-as-bjp-maharashtra-state-president-in-mumbai-event-devendra-fadnavis-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजप नेते रविंद्र चव्हाण यांच्यावर पक्षाची महत्वाची जबाबदारी; कार्यकारी अध्यक्षपदी नियुक्ती</t>
+          <t>Maharashtra Updates : भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण, जलसंधारण विभागात 8 हजारांहून अधिक पदांची भरती...</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/desh/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-aau85</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-01-june-2025-live-updates-assembly-session-live-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-raj-thackeray-uddhav-thackeray-devendra-fadnavis-shivsena-rm82</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ravindra Chavan BJP: रवींद्र चव्हाण भाजपाचे नवे 'कॅप्टन'! महाराष्ट्र प्रदेशाध्यक्षपदी बिनविरोध निवड</t>
+          <t>Maharashtra BJP State President: उत्सुकता संपली; भाजपला मिळणार नवा प्रदेशाध्यक्ष! चंद्रशेखर बावनकुळेंच्या जागी रविंद्र चव्हाणांची नियुक्ती होणार</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-elected-unopposed-as-bjp-maharashtra-state-president-in-mumbai-event-devendra-fadnavis-a-a747/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Maharashtra Updates : भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण, जलसंधारण विभागात 8 हजारांहून अधिक पदांची भरती...</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण यांची अखेर भाजपाच्या कार्यकारी प्रदेशाध्यक्षपदी वर्णी; राष्ट्रीय अध्यक्ष जेपी नड्डांची घोषणा</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-01-june-2025-live-updates-assembly-session-live-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-raj-thackeray-uddhav-thackeray-devendra-fadnavis-shivsena-rm82</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mla-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-kvg-85-4820046/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Maharashtra BJP State President: उत्सुकता संपली; भाजपला मिळणार नवा प्रदेशाध्यक्ष! चंद्रशेखर बावनकुळेंच्या जागी रविंद्र चव्हाणांची नियुक्ती होणार</t>
+          <t>“भाजपा हीच माझी ओळख” ; महाराष्ट्र भाजपा प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांची बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
+          <t>https://www.localnewsnetwork.in/bjp-is-my-identity-ravindra-chavan-elected-unopposed-as-maharashtra-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण यांची अखेर भाजपाच्या कार्यकारी प्रदेशाध्यक्षपदी वर्णी; राष्ट्रीय अध्यक्ष जेपी नड्डांची घोषणा</t>
+          <t>Ravindra Chavan : "सामान्य नगरसेवक ते भाजपचे प्रदेशाध्यक्ष..."</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mla-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-kvg-85-4820046/</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/ravindra-chavan-appointed-bjp-president-kiren-rijiju-announcement-and-political-career-as11</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>“भाजपा हीच माझी ओळख” ; महाराष्ट्र भाजपा प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांची बिनविरोध निवड</t>
+          <t>Ravindra Chavan : भाजपचं ठरलं, रवींद्र चव्हाण प्रदेशाध्यक्ष होणार, ठाकरेंच्या बालेकिल्ल्यात पहिलं शक्तिप्रद...</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-is-my-identity-ravindra-chavan-elected-unopposed-as-maharashtra-bjp-state-president/</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : "सामान्य नगरसेवक ते भाजपचे प्रदेशाध्यक्ष..."</t>
+          <t>BJP Ravindra Chavan News: भाजपच्या गोटातून मोठी बातमी समोर Maharashtra Politics</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/ravindra-chavan-appointed-bjp-president-kiren-rijiju-announcement-and-political-career-as11</t>
+          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपचं ठरलं, रवींद्र चव्हाण प्रदेशाध्यक्ष होणार, ठाकरेंच्या बालेकिल्ल्यात पहिलं शक्तिप्रद...</t>
+          <t>रत्नागिरी भाजपमध्ये नारायण राणे, रविंद्र चव्हाण यांच्यातील वाद चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
+          <t>https://www.loksatta.com/politics/dispute-between-narayan-rane-and-ravindra-chavan-in-ratnagiri-bjp-is-on-rise-print-political-news-ocd-94-5140598/</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>BJP Ravindra Chavan News: भाजपच्या गोटातून मोठी बातमी समोर Maharashtra Politics</t>
+          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू अन् RSS च्या मर्जीतले रवींद्र चव्हाण भाजपचे</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>रत्नागिरी भाजपमध्ये नारायण राणे, रविंद्र चव्हाण यांच्यातील वाद चव्हाट्यावर</t>
+          <t>Ravindra Chavan: उद्धव ठाकरेंच्या भाजपसोबतच्या वाढत्या जवळीकतेवर रवींद्र चव्हाण यांचं महत्त्वाचं विधान; म्हणाले, शत्रूही...</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/dispute-between-narayan-rane-and-ravindra-chavan-in-ratnagiri-bjp-is-on-rise-print-political-news-ocd-94-5140598/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-important-statement-on-uddhav-thackeray-closeness-with-bjp-aau85</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू अन् RSS च्या मर्जीतले रवींद्र चव्हाण भाजपचे</t>
+          <t>भाजपा साताऱ्यात निवडणार नवा जिल्हाध्यक्ष, प्रभारी प्रदेशाध्यक्ष रवींद्र चव्हाण यांची आढावा बैठक</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-to-elect-new-district-president-in-satara-review-meeting-by-ravindra-chavan-asj-82-5027101/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: उद्धव ठाकरेंच्या भाजपसोबतच्या वाढत्या जवळीकतेवर रवींद्र चव्हाण यांचं महत्त्वाचं विधान; म्हणाले, शत्रूही...</t>
+          <t>रवींद्र चव्हाण भाजपचे नवे कार्यकारी अध्यक्ष: लवकरच चंद्रशेखर बावनकुळेंकडून स्वीकारणार जबाबदारी, मंत्रिमंडळा...</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-important-statement-on-uddhav-thackeray-closeness-with-bjp-aau85</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>भाजपा साताऱ्यात निवडणार नवा जिल्हाध्यक्ष, प्रभारी प्रदेशाध्यक्ष रवींद्र चव्हाण यांची आढावा बैठक</t>
+          <t>Ravindra Chavan : राजकारणातील सर्वात चर्चेतील नाव! RSS कार्यकर्ते ते भाजप प्रदेशाध्यक्ष झालेले कोण आहेत रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-to-elect-new-district-president-in-satara-review-meeting-by-ravindra-chavan-asj-82-5027101/</t>
+          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजपचे नवे कार्यकारी अध्यक्ष: लवकरच चंद्रशेखर बावनकुळेंकडून स्वीकारणार जबाबदारी, मंत्रिमंडळा...</t>
+          <t>रविंद्र चव्हाण यांच्यावतीने डोंबिवलीत रक्षाबंधनाचा कौटुंबिक सोहळा; हजारो भगिनींनी बांधली राखी</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
+          <t>https://www.localnewsnetwork.in/raksha-bandhan-family-ceremony-in-dombivli-on-behalf-of-ravindra-chavan-thousands-of-sisters-tied-rakhi/</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : राजकारणातील सर्वात चर्चेतील नाव! RSS कार्यकर्ते ते भाजप प्रदेशाध्यक्ष झालेले कोण आहेत रवींद्र चव्हाण?</t>
+          <t>Ravindra Chavan : महापालिका निवडणूक महायुतीत की स्वबळावर? ; रवींद्र चव्हाणांनी सांगितली भाजपची सद्य भूमिका, म्हणाले..</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
+          <t>https://sarkarnama.esakal.com/pune/ravindra-chavan-bjp-current-stand-mahayuti-or-independent-contest-municipal-corporation-elections-maharashtra-politics-msr87</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>रविंद्र चव्हाण यांच्यावतीने डोंबिवलीत रक्षाबंधनाचा कौटुंबिक सोहळा; हजारो भगिनींनी बांधली राखी</t>
+          <t>Photos : रविंद्र चव्हाणांनी स्वीकारला भाजपा प्रदेशाध्यक्ष पदाचा पदभार; मावळत्या अध्यक्षांच्या शुभेच्छा…</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/raksha-bandhan-family-ceremony-in-dombivli-on-behalf-of-ravindra-chavan-thousands-of-sisters-tied-rakhi/</t>
+          <t>https://www.loksatta.com/photos/news/5198695/ravindra-chavan-takes-charge-as-bjp-state-president-best-wishes-from-party-s-outgoing-president-state-headquarter-mumbai-photos-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Photos : रविंद्र चव्हाणांनी स्वीकारला भाजपा प्रदेशाध्यक्ष पदाचा पदभार; मावळत्या अध्यक्षांच्या शुभेच्छा…</t>
+          <t>कल्याण-डोंबिवली परिसर भाजपमय करा, पालिकेवर भाजपचा महापौर बसवा, रवींद्र चव्हाण यांचे कार्यकर्त्यांना आवाहन</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5198695/ravindra-chavan-takes-charge-as-bjp-state-president-best-wishes-from-party-s-outgoing-president-state-headquarter-mumbai-photos-spl-93/</t>
+          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-s-appeal-to-party-workers-to-work-for-bjp-mayor-in-kdmc-zws-70-5277354/</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महापालिका निवडणूक महायुतीत की स्वबळावर? ; रवींद्र चव्हाणांनी सांगितली भाजपची सद्य भूमिका, म्हणाले..</t>
+          <t>डोंबिवलीकर फ्रेंडशिप रनच्या थीमचे अनावरण संपन्न भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले थीमचे अनावरण ही स्पर्धा होणार 9 नोव्हेंबर ला</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/ravindra-chavan-bjp-current-stand-mahayuti-or-independent-contest-municipal-corporation-elections-maharashtra-politics-msr87</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>डोंबिवलीकर फ्रेंडशिप रनच्या थीमचे अनावरण संपन्न भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले थीमचे अनावरण ही स्पर्धा होणार 9 नोव्हेंबर ला</t>
+          <t>फेमस यूट्यूबर ने 33 साल की उम्र में दुनिया को कहा अलविदा, किस बीमारी से थे पीड़ित?</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
+          <t>https://www.patrika.com/mumbai-news/youtuber-shirish-gavas-passed-away-red-soil-stories-channel-33-year-old-founder-died-19834284</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवली परिसर भाजपमय करा, पालिकेवर भाजपचा महापौर बसवा, रवींद्र चव्हाण यांचे कार्यकर्त्यांना आवाहन</t>
+          <t>पक्षकार्यकर्ता ते प्रदेशाध्यक्ष : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-s-appeal-to-party-workers-to-work-for-bjp-mayor-in-kdmc-zws-70-5277354/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>पक्षकार्यकर्ता ते प्रदेशाध्यक्ष : रवींद्र चव्हाण</t>
+          <t>Mahayuti News: शिवरायांच्या पुतळ्यावरून राजकारण तापलं, डोंबिवलीत शिंदे सेनेनं भाजपला डिवचलं</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
+          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Mahayuti News: शिवरायांच्या पुतळ्यावरून राजकारण तापलं, डोंबिवलीत शिंदे सेनेनं भाजपला डिवचलं</t>
+          <t>महाराष्ट्र में किसे मिली BJP की कमान? मुंबई मेट्रो में देखें</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में किसे मिली BJP की कमान? मुंबई मेट्रो में देखें</t>
+          <t>Maharashtra Politics: उद्धव ठाकरे पुन्हा भाजपसोबत? रवींद्र चव्हाण म्हणाले,राजकारणात कोणी कायमचा शत्रू नसतो | VIDEO</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
+          <t>https://saamtv.esakal.com/video/uddhav-thackeray-bjp-alliance-ravindra-chavan-interview-political-future-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: उद्धव ठाकरे पुन्हा भाजपसोबत? रवींद्र चव्हाण म्हणाले,राजकारणात कोणी कायमचा शत्रू नसतो | VIDEO</t>
+          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू, पक्षाच्या मर्जीतले रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/uddhav-thackeray-bjp-alliance-ravindra-chavan-interview-political-future-maharashtra-om0906</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-bjp-ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू, पक्षाच्या मर्जीतले रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष</t>
+          <t>Ravindra Chavan News : भाजपचे प्रदेशाध्यक्ष म्हणतात, आमची संघटनात्मक बांधणी मजबूत, यश पदरात पडेल!</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-bjp-ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-latest-marathi-news-pp0731</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-state-president-ravindra-chavan-confident-of-election-success-says-our-organisation-is-strong-jp75</t>
         </is>
       </c>
     </row>
@@ -2711,2328 +2711,2328 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Ravindra Chavan News : भाजपचे प्रदेशाध्यक्ष म्हणतात, आमची संघटनात्मक बांधणी मजबूत, यश पदरात पडेल!</t>
+          <t>राणे पिता-पुत्रांनी भाजपऐवजी स्ट्राँग केलं स्वतःचं नेटवर्क; नव्या प्रदेशाध्यक्षांचा होमग्राऊंडवरच निघणार घाम!</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-state-president-ravindra-chavan-confident-of-election-success-says-our-organisation-is-strong-jp75</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-maharashtra-state-president-ravindra-chavan-faces-challenge-of-strengthening-party-in-sindhudurg-beyond-rane-family-influence-as11-hn97</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>राणे पिता-पुत्रांनी भाजपऐवजी स्ट्राँग केलं स्वतःचं नेटवर्क; नव्या प्रदेशाध्यक्षांचा होमग्राऊंडवरच निघणार घाम!</t>
+          <t>Ravindra Chavan : महाराष्ट्र भाजपच्या प्रदेशाध्यपदी रविंद्र चव्हाणांची नियुक्ती</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-maharashtra-state-president-ravindra-chavan-faces-challenge-of-strengthening-party-in-sindhudurg-beyond-rane-family-influence-as11-hn97</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महाराष्ट्र भाजपच्या प्रदेशाध्यपदी रविंद्र चव्हाणांची नियुक्ती</t>
+          <t>रवींद्र चव्हाण महाराष्ट्र भाजपच्या कार्याध्यक्षपदी, दोन महिन्यांनी प्रदेशाध्यक्ष हाेणार</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-will-become-state-president-in-two-months-a-a309/</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण महाराष्ट्र भाजपच्या कार्याध्यक्षपदी, दोन महिन्यांनी प्रदेशाध्यक्ष हाेणार</t>
+          <t>Maharashtra BJP News : भाजप प्रदेशाध्यक्षपदासाठी रवींद्र चव्हाण यांनी भरला अर्ज</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-will-become-state-president-in-two-months-a-a309/</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Maharashtra BJP News : भाजप प्रदेशाध्यक्षपदासाठी रवींद्र चव्हाण यांनी भरला अर्ज</t>
+          <t>कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाश्याला बेघर होऊ देणार नाही, रविंद्र चव्हाण यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
+          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाश्याला बेघर होऊ देणार नाही, रविंद्र चव्हाण यांचे आश्वासन</t>
+          <t>रवींद्र चव्हाण भाजपचे नवे कॅप्टन; केंद्रीय मंत्री किरेन रिजिजू यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
+          <t>https://marathi.freepressjournal.in/mumbai/ravindra-chavan-appointed-bjp-maharashtra-president-2025</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजपचे नवे कॅप्टन; केंद्रीय मंत्री किरेन रिजिजू यांनी केली घोषणा</t>
+          <t>Latur Politics: प्रदेशाध्यक्ष रविंद्र चव्हाणांचा लातूरमध्ये मोठा धमाका; दोन बड्या नेत्यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/ravindra-chavan-appointed-bjp-maharashtra-president-2025</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-politics-kapil-makne-nilkanth-mirkale-of-latur-joining-bjp-dk88</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Latur Politics: प्रदेशाध्यक्ष रविंद्र चव्हाणांचा लातूरमध्ये मोठा धमाका; दोन बड्या नेत्यांचा भाजपात प्रवेश</t>
+          <t>मोठा गेम होणार, भाजप प्रदेशाध्यक्षाच्या विधानाने खळबळ; शिंदे गटाला सर्वात मोठं टेन्शन</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-politics-kapil-makne-nilkanth-mirkale-of-latur-joining-bjp-dk88</t>
+          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>मोठा गेम होणार, भाजप प्रदेशाध्यक्षाच्या विधानाने खळबळ; शिंदे गटाला सर्वात मोठं टेन्शन</t>
+          <t>Ravindra Chavan: 'संविधान बचाव'ची 'शो'बाजी करणारे...; PM मोदींवर टीका करणाऱ्या राहुल गांधींना रविंद्र चव्हाणांचं उत्तर</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/those-who-showoff-of-saving-constitution-criticized-pm-modi-reply-by-ravindra-chavan-on-rahul-gandhi-statement-against-prime-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 'संविधान बचाव'ची 'शो'बाजी करणारे...; PM मोदींवर टीका करणाऱ्या राहुल गांधींना रविंद्र चव्हाणांचं उत्तर</t>
+          <t>Maharashtra Politics : देवेंद्र फडणवीस यांचे विश्वासू ते भाजपाचे कार्यकारी अध्यक्ष; कोण आहेत रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/those-who-showoff-of-saving-constitution-criticized-pm-modi-reply-by-ravindra-chavan-on-rahul-gandhi-statement-against-prime-minister-aau85</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-cm-devendra-fadnavis-confidant-to-bjp-working-president-who-is-mla-ravindra-chavan-sdp-92-4822225/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : देवेंद्र फडणवीस यांचे विश्वासू ते भाजपाचे कार्यकारी अध्यक्ष; कोण आहेत रवींद्र चव्हाण?</t>
+          <t>Maharashtra Politics : धुळ्यात काँग्रेसला खिंडार? मातब्बर नेता मुंबईत रायगड निवासस्थानी</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-cm-devendra-fadnavis-confidant-to-bjp-working-president-who-is-mla-ravindra-chavan-sdp-92-4822225/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांच्या नावावर शिक्कामोर्तब? उद्या होणार घोषणा</t>
+          <t>कल्याण डोंबिवलीच्या विकासाचे ग्रहण दूर करण्यासाठी भाजपचा महापौर हवा – भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ravindra-chavan-name-confirmed-as-bjp-maharashtra-president-announcement-to-be-made-soon-aau85</t>
+          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : धुळ्यात काँग्रेसला खिंडार? मातब्बर नेता मुंबईत रायगड निवासस्थानी</t>
+          <t>Ravindra Chavan: भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांच्या नावावर शिक्कामोर्तब? उद्या होणार घोषणा</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
+          <t>https://www.esakal.com/maharashtra/ravindra-chavan-name-confirmed-as-bjp-maharashtra-president-announcement-to-be-made-soon-aau85</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>कल्याण डोंबिवलीच्या विकासाचे ग्रहण दूर करण्यासाठी भाजपचा महापौर हवा – भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण</t>
+          <t>भाजपने माझ्यावर उपकार केलेत, प्रदेशाध्यक्ष बनल्यानंतर रवींद्र चव्हाणांची पहिली प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
+          <t>https://www.tv9marathi.com/politics/bjp-has-done-me-favor-new-state-president-rvindra-chavhan-1st-statement-1436200.html</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>भाजपने माझ्यावर उपकार केलेत, प्रदेशाध्यक्ष बनल्यानंतर रवींद्र चव्हाणांची पहिली प्रतिक्रिया</t>
+          <t>Ravindra Chavan : एकनाथ शिंदेंना शह देण्यासाठी भाजपने दिले कार्याध्यक्षपद? रवींद्र चव्हाणांनी सांगितलं खरं काय?</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-has-done-me-favor-new-state-president-rvindra-chavhan-1st-statement-1436200.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-opens-up-about-bjp-move-in-thane-rm89</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : एकनाथ शिंदेंना शह देण्यासाठी भाजपने दिले कार्याध्यक्षपद? रवींद्र चव्हाणांनी सांगितलं खरं काय?</t>
+          <t>Kalyan News: 'या' इमारतींच्या रखडलेल्या पुनर्विकास लागणार मार्गी, रवींद्र चव्हाण यांची माहिती</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-opens-up-about-bjp-move-in-thane-rm89</t>
+          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Kalyan News: 'या' इमारतींच्या रखडलेल्या पुनर्विकास लागणार मार्गी, रवींद्र चव्हाण यांची माहिती</t>
+          <t>Ravindra Chavhan Interview:महाराष्ट्र भाजप प्रदेशाध्यक्ष पद स्वीकारल्यानंतर रविंद्र चव्हाण EXCLUSIVE</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
+          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ravindra Chavhan Interview:महाराष्ट्र भाजप प्रदेशाध्यक्ष पद स्वीकारल्यानंतर रविंद्र चव्हाण EXCLUSIVE</t>
+          <t>Ravindra Chavan: भाजपच्या कार्यकारी अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
+          <t>https://saamtv.esakal.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-bbj88</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजपच्या कार्यकारी अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>चव्हाणांकडे प्रदेश, सेनेला थेट संदेश; शिंदेंना होमपीचवर शह देण्यासाठी भाजपची जोरदार फिल्डींग</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-bbj88</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>चंद्रशेखर बावनकुळेंचे भावनिक पत्र; प्रदेशाध्यक्ष पदातून मुक्त झाल्यावर लोकसभा निवडणुकीतील अपयशाचे…</t>
+          <t>Ravindra Chavan | रवींद्र चव्‍हाणांनी घेतली भाजप अध्‍यक्ष जे. पी. नड्डांची भेट</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/nagpur/ravindra-chavan-replaces-bawankule-as-bjp-state-president-bawankule-write-emotional-letter-sud-02-5198303/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-bjp-state-president-ravindra-chavan-met-party-president-j-p-nadda-nl76</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>चव्हाणांकडे प्रदेश, सेनेला थेट संदेश; शिंदेंना होमपीचवर शह देण्यासाठी भाजपची जोरदार फिल्डींग</t>
+          <t>प्रदेशाध्यक्षपद देऊन भाजपने माझ्यावर उपकार केले, रवींद्र चव्हाण भाषणात नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>Ravindra Chavan | रवींद्र चव्‍हाणांनी घेतली भाजप अध्‍यक्ष जे. पी. नड्डांची भेट</t>
+          <t>डोंबिवलीतील काँग्रेसचे 4 नगरसेवक भाजपमध्ये; पक्षाकडून त्यांचा नेहमीच सन्मान केला जाणार – प्रदेशाध्यक्ष रविंद्र चव्हाण यांची ग्वाही</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-bjp-state-president-ravindra-chavan-met-party-president-j-p-nadda-nl76</t>
+          <t>https://www.localnewsnetwork.in/4-congress-corporators-from-dombivli-join-bjp-they-will-always-be-respected-by-the-party-state-president-ravindra-chavan-assures/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>प्रदेशाध्यक्षपद देऊन भाजपने माझ्यावर उपकार केले, रवींद्र चव्हाण भाषणात नेमकं काय म्हणाले?</t>
+          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>डोंबिवलीतील काँग्रेसचे 4 नगरसेवक भाजपमध्ये; पक्षाकडून त्यांचा नेहमीच सन्मान केला जाणार – प्रदेशाध्यक्ष रविंद्र चव्हाण यांची ग्वाही</t>
+          <t>Indrayani River Bridge Collapse | संजय राऊत विश्वप्रवक्ते! इंद्रायणी पूल दुरुस्तीसाठी ८० हजार की ८ कोटी... रविंद्र चव्हाण यांनी खरं काय ते सांगितले?</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/4-congress-corporators-from-dombivli-join-bjp-they-will-always-be-respected-by-the-party-state-president-ravindra-chavan-assures/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/bjp-ravindra-chavan-responded-to-sanjay-raut-allegations-over-indrayani-river-bridge-collapse-incident-db79</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
+          <t>BJP Politics : बंडखोरी केलेल्या नेत्याचा भाजप प्रवेश, वेलकम स्वत: रवींद्र चव्हाणांनी केलं; युतीमध्ये वितुष्ट येण्याची शक्यता?</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ravindra-chavan-cancelled-vishal-parabs-bjp-suspension-revoked-creating-alliance-tension-in-sindhudurg-politics-as11</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Indrayani River Bridge Collapse | संजय राऊत विश्वप्रवक्ते! इंद्रायणी पूल दुरुस्तीसाठी ८० हजार की ८ कोटी... रविंद्र चव्हाण यांनी खरं काय ते सांगितले?</t>
+          <t>Ravindra Chavan: आता पालिका विकासाचे ग्रहण दूर होणार; भाजप प्रदेशाध्यक्षांनी निवडणुकीचा प्लॅनच सांगितला</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/bjp-ravindra-chavan-responded-to-sanjay-raut-allegations-over-indrayani-river-bridge-collapse-incident-db79</t>
+          <t>https://www.esakal.com/mumbai/ravindra-chavan-says-bjp-mayor-is-necessary-to-resolve-development-problems-faced-by-kalyan-dombivli-municipal-corporation-on-bmc-election-mvk02</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>BJP Politics : बंडखोरी केलेल्या नेत्याचा भाजप प्रवेश, वेलकम स्वत: रवींद्र चव्हाणांनी केलं; युतीमध्ये वितुष्ट येण्याची शक्यता?</t>
+          <t>Maharashtra BJP State President | भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांचे नाव जवळपास निश्चित, १ जुलैला अधिकृत घोषणा</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ravindra-chavan-cancelled-vishal-parabs-bjp-suspension-revoked-creating-alliance-tension-in-sindhudurg-politics-as11</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-will-be-appointed-maharashtra-bjp-state-president-db79</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Maharashtra BJP State President | भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांचे नाव जवळपास निश्चित, १ जुलैला अधिकृत घोषणा</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-will-be-appointed-maharashtra-bjp-state-president-db79</t>
+          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
+          <t>BJP Dombivli setback - भाजपला डोंबिवलीत धक्का! ; प्रदेश कार्याध्यक्षांवर 'हा' आरोप करत, दोन नगरसेवकांनी सोडला पक्ष</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-dombivli-crisis-vikas-kavita-mhatre-resignation-ravindra-chavan-allegations-msr87</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>BJP Dombivli setback - भाजपला डोंबिवलीत धक्का! ; प्रदेश कार्याध्यक्षांवर 'हा' आरोप करत, दोन नगरसेवकांनी सोडला पक्ष</t>
+          <t>एक-एक मंडल दत्तक घेऊन संघटनात्मक बांधणीचा संकल्प करा; प्रदेशाध्यक्ष रविंद्र चव्हाण यांचे माजी आमदार, खासदारांना आवाहन</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-dombivli-crisis-vikas-kavita-mhatre-resignation-ravindra-chavan-allegations-msr87</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>एक-एक मंडल दत्तक घेऊन संघटनात्मक बांधणीचा संकल्प करा; प्रदेशाध्यक्ष रविंद्र चव्हाण यांचे माजी आमदार, खासदारांना आवाहन</t>
+          <t>Ravindra Chavan Exclusive Interview : राज-उद्धव ठाकरे एकत्र आल्यास भाजपला आव्हान असणार का? प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Exclusive Interview : राज-उद्धव ठाकरे एकत्र आल्यास भाजपला आव्हान असणार का? प्रदेशाध्यक्ष</t>
+          <t>Thane News : भाजपमध्ये मेगाभरती, शरद पवार गटाचा आणखी किल्ला ढासळणार! कुठं होणार राजकीय उलथापालथ?</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-political-masterstroke-ulhasnagar-sharad-pawar-group-breakdown-1445668.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>Thane News : भाजपमध्ये मेगाभरती, शरद पवार गटाचा आणखी किल्ला ढासळणार! कुठं होणार राजकीय उलथापालथ?</t>
+          <t>BJP President: "रवी दादा आगे बढो नाही तर..."; प्रदेशाध्यक्ष होताच रवींद्र चव्हाणांनी व्यक्त केल्या भावना</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-political-masterstroke-ulhasnagar-sharad-pawar-group-breakdown-1445668.html</t>
+          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>BJP President: "रवी दादा आगे बढो नाही तर..."; प्रदेशाध्यक्ष होताच रवींद्र चव्हाणांनी व्यक्त केल्या भावना</t>
+          <t>Maharashtra Politics : भाजपचे नवीन प्रदेशाध्यक्ष कोण? बड्या नेत्याचं नाव पक्कं; उद्या अधिकृत घोषणा होणार</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/ravindra-chavan-fills-the-form-for-the-post-of-new-state-president-of-mumbai-bjp-name-will-be-announced-tomorrow-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : भाजपचे नवीन प्रदेशाध्यक्ष कोण? बड्या नेत्याचं नाव पक्कं; उद्या अधिकृत घोषणा होणार</t>
+          <t>काँग्रेस नेते कैलास गोरंट्यालसह सुरेश वरपूडकर यांचा भाजप प्रवेशाचा मुहूर्त</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/ravindra-chavan-fills-the-form-for-the-post-of-new-state-president-of-mumbai-bjp-name-will-be-announced-tomorrow-latest-marathi-news-pp0731</t>
+          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>काँग्रेस नेते कैलास गोरंट्यालसह सुरेश वरपूडकर यांचा भाजप प्रवेशाचा मुहूर्त</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण भाजपचे कारभारी</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-ravindra-chavan-is-the-bjp-s-steward-1061660.html</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण भाजपचे कारभारी</t>
+          <t>BJP new state president : पक्षनेतृत्वानं दाखवला मोठा भरवसा; मित्रपक्षाला भिडणाऱ्या भाजपच्या नव्या प्रदेशाध्यक्षांना आता गियर बदलावा लागणार</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-ravindra-chavan-is-the-bjp-s-steward-1061660.html</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-state-chief-ravindra-chavan-faces-ally-challenge-amid-trust-sw79</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>BJP new state president : पक्षनेतृत्वानं दाखवला मोठा भरवसा; मित्रपक्षाला भिडणाऱ्या भाजपच्या नव्या प्रदेशाध्यक्षांना आता गियर बदलावा लागणार</t>
+          <t>राज ठाकरे भाजपसोबत जाणार का?: रवींद्र चव्हाण म्हणतात - राज व फडणवीसांचे चांगले संबंध, ते दोघेही मुंबईच्या ह...</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-state-chief-ravindra-chavan-faces-ally-challenge-amid-trust-sw79</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-raj-thackeray-bjp-alliance-speculation-uddhav-thackeray-politics-update-135429372.html</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>राज ठाकरे भाजपसोबत जाणार का?: रवींद्र चव्हाण म्हणतात - राज व फडणवीसांचे चांगले संबंध, ते दोघेही मुंबईच्या ह...</t>
+          <t>Exclusive: 2017 मध्ये शिवसेनेला आम्ही महापौर पद दिलं पण आता... रविंद्र चव्हाणांनी स्पष्टच सांगितलं</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-raj-thackeray-bjp-alliance-speculation-uddhav-thackeray-politics-update-135429372.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/bjp-state-president-ravindra-chavan-on-bmc-mayor-decesion-politics-marathi-news/925443</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>Exclusive: 2017 मध्ये शिवसेनेला आम्ही महापौर पद दिलं पण आता... रविंद्र चव्हाणांनी स्पष्टच सांगितलं</t>
+          <t>"एकनाथ शिंदे मुख्यमंत्री झाल्याने वाईट वाटलं आणि घरी निघून गेलो,पण पुन्हा..."; रवींद्र चव्हाणांचा गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/bjp-state-president-ravindra-chavan-on-bmc-mayor-decesion-politics-marathi-news/925443</t>
+          <t>https://www.lokmat.com/mumbai/bjp-state-president-ravindra-chavan-said-that-he-felt-bad-after-eknath-shinde-became-the-chief-minister-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>"एकनाथ शिंदे मुख्यमंत्री झाल्याने वाईट वाटलं आणि घरी निघून गेलो,पण पुन्हा..."; रवींद्र चव्हाणांचा गौप्यस्फोट</t>
+          <t>Raju Patil: विकासाला ग्रहण लावणाऱ्या 'चांदभाई'चे नाव घ्या! मनसे नेत्याचा भाजप प्रदेशाध्यक्षांना टोला</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-state-president-ravindra-chavan-said-that-he-felt-bad-after-eknath-shinde-became-the-chief-minister-a-a1001/</t>
+          <t>https://www.esakal.com/mumbai/mns-leader-raju-patil-criticism-on-ravindra-chavan-over-kalyan-dombivli-development-maharashtra-politics-mvk02</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>Raju Patil: विकासाला ग्रहण लावणाऱ्या 'चांदभाई'चे नाव घ्या! मनसे नेत्याचा भाजप प्रदेशाध्यक्षांना टोला</t>
+          <t>नितेश राणे आणि गोपीचंद पडळकर दोघांना भाजपने डायरेक्ट वॉर्निंग दिली</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/mns-leader-raju-patil-criticism-on-ravindra-chavan-over-kalyan-dombivli-development-maharashtra-politics-mvk02</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>नितेश राणे आणि गोपीचंद पडळकर दोघांना भाजपने डायरेक्ट वॉर्निंग दिली</t>
+          <t>Ravindra Chavan emotional story: फडणवीस मुख्यमंत्री होणार नसल्याने धक्का बसला, डोळ्यात पाणी आले अन् ...; रवींद्र चव्हाणांनी सांगितला 2022 सालचा किस्सा.....</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-reveals-2022-twist-emotional-reaction-as-devendra-fadnavis-wasnt-named-cm-sw79</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>Ravindra Chavan emotional story: फडणवीस मुख्यमंत्री होणार नसल्याने धक्का बसला, डोळ्यात पाणी आले अन् ...; रवींद्र चव्हाणांनी सांगितला 2022 सालचा किस्सा.....</t>
+          <t>BJP Maharashtra President : भाजपचे महाराष्ट्रातील नवे उत्तराधिकारी कोण? प्रदेशाध्यक्षपदासाठी सर्वात आघाडीवर कोणाचं नाव?</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-reveals-2022-twist-emotional-reaction-as-devendra-fadnavis-wasnt-named-cm-sw79</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President : भाजपचे महाराष्ट्रातील नवे उत्तराधिकारी कोण? प्रदेशाध्यक्षपदासाठी सर्वात आघाडीवर कोणाचं नाव?</t>
+          <t>फडणवीस व चव्हाण यांच्या नेतृत्वात भाजपला मोठे यश मिळेल- ना. विखे पाटील</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
+          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>फडणवीस व चव्हाण यांच्या नेतृत्वात भाजपला मोठे यश मिळेल- ना. विखे पाटील</t>
+          <t>भाजपाचा सामान्य कार्यकर्ता ते प्रदेशाध्यक्ष पर्यंतचा रवींद्र चव्हाण यांचा प्रवास</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
+          <t>https://puneprimenews.com/mumbai/ravindra-chavans-journey-from-ordinary-bjp-worker-to-state-president-update/</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>भाजपाचा सामान्य कार्यकर्ता ते प्रदेशाध्यक्ष पर्यंतचा रवींद्र चव्हाण यांचा प्रवास</t>
+          <t>BMC Elections 2025: भाजपचे मुंबई अध्यक्ष ठरले! 'या' आक्रमक नेत्याची लागली वर्णी; निवडणुकांपूर्वी मोठी खेळी</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/ravindra-chavans-journey-from-ordinary-bjp-worker-to-state-president-update/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: भाजपचे मुंबई अध्यक्ष ठरले! 'या' आक्रमक नेत्याची लागली वर्णी; निवडणुकांपूर्वी मोठी खेळी</t>
+          <t>Ravindra Chavhan BJP : रविंद्र चव्हाण यांनी बोलावली बैठक, निवडणुकीसंदर्भात चर्चा</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>Ravindra Chavhan BJP : रविंद्र चव्हाण यांनी बोलावली बैठक, निवडणुकीसंदर्भात चर्चा</t>
+          <t>महाराष्ट्राच्या राजकारणातील सर्वात मोठी घडामोड! उद्धव ठाकरे पक्षातील 1500 सदस्यांनी एकावेळी पक्ष सोडला आणि...</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात राजकीय भूकंप घडवण्यात रवींद्र चव्हाणांचा मोठा वाटा, भाजपच्या नव्या प्रदेशाध्यक्षांची A टू Z कारकीर्द</t>
+          <t>“ठाकरे बंधूंनी एकत्र येऊ नये असा GR काढलेला नाही”; CM देवेंद्र फडणवीसांचा खोचक टोला</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
+          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-taunt-about-raj-thackeray-and-uddhav-thackeray-likely-to-come-together-for-marathi-language-issue-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Narayan Rane : राणेंचा भाजपच्या प्रदेश प्रभारींनाच कडक इशारा; म्हणाले, 'इथं ढवळाढवळ चालणार नाही, हवं तर...'</t>
+          <t>Dahi Handi 2025 : डोंबिवलीमध्ये पारंपरिक पद्धतीने दहीहंडीचा उत्सव; गोविंदांचा उत्सह शिगेला</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/narayan-rane-slams-ravindra-chavan-over-post-distribution-in-ratnagiri-bjp-as11</t>
+          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>कल्याणमध्ये काँग्रेसला खिंडार! बडे नेते भाजपवासी; प्रदेशाध्यक्षांनी दिले मोठे संकेत</t>
+          <t>मी निष्पाप, निष्ठेने काम करेन, तुमचा आदेश तंतोतंत पाळेन, सुधाकर बडगुजरांचा बावनकुळेंना</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/bjp-grows-stronger-in-kalyan-congress-leaders-join-ravindra-chavan-hints-at-contesting-solo-bdk97</t>
+          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>अमित साटम मुंबई भाजपचे कॅप्टन; भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण यांची घोषणा</t>
+          <t>Nanded Ashok Chavan: अशोक चव्हाणांची डोकेदुखी वाढली; काँग्रेसकडून खिंडीत पकडण्यासाठी प्लॅन तयार, नांदेडमध्ये काय घडतंय?</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/amit-satam-on-becoming-mumbai-bjp-president/935016</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Maharashtra Bar Closure: सरकारच्या निर्णयाला व्यावसायिकांचा विरोध, राज्यभरात बार, परमिट रूम बंद; मदतीसाठी भाजपकडे धाव</t>
+          <t>स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती की स्वबळावर? भाजप प्रदेशाध्यक्षांचं सूचक विधान; म्हणाले, 'आचारसंहिता लागली की...'</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/bar-owners-will-give-letter-to-ravindra-chavan-on-protesting-government-increase-in-value-added-tax-excise-duty-and-license-fee-on-liquor-mvk02</t>
+          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-statement-on-date-of-local-body-elections-mahayuti-alliance-vru98</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>महाराष्ट्राच्या राजकारणातील सर्वात मोठी घडामोड! उद्धव ठाकरे पक्षातील 1500 सदस्यांनी एकावेळी पक्ष सोडला आणि...</t>
+          <t>Devendra Fadnavis : “फेक नरेटिव्ह तयार करणाऱ्यांची फॅक्टरी…” फडणवीस यांचं उद्धव ठाकरेंना त्याच भाषेत उत्तर</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-bjp-president-fadnavis-slams-uddhav-thackeray-over-fake-narrative-as11</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>“ठाकरे बंधूंनी एकत्र येऊ नये असा GR काढलेला नाही”; CM देवेंद्र फडणवीसांचा खोचक टोला</t>
+          <t>Nanded News: नांदेडमध्ये स्थानिक निवडणुकासाठी काँगेस अन् वंचितकडून युतीचे संकेत प्रस्ताव</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-taunt-about-raj-thackeray-and-uddhav-thackeray-likely-to-come-together-for-marathi-language-issue-a-a719/</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Dahi Handi 2025 : डोंबिवलीमध्ये पारंपरिक पद्धतीने दहीहंडीचा उत्सव; गोविंदांचा उत्सह शिगेला</t>
+          <t>छत्रपती शिवाजी महाराजांच्या मेघडंबरीसह पूर्णाकृती पुतळ्याचे डोंबिवलीत अनावरण ; खा. डॉ. श्रीकांत शिंदे, भाजप कार्याध्यक्ष रविंद्र चव्हाण यांची प्रमूख उपस्थिती – LNN</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
+          <t>https://www.localnewsnetwork.in/unveiling-of-the-full-length-statue-of-chhatrapati-shivaji-maharaj-with-a-canopy-in-dombivali/</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>मी निष्पाप, निष्ठेने काम करेन, तुमचा आदेश तंतोतंत पाळेन, सुधाकर बडगुजरांचा बावनकुळेंना</t>
+          <t>Vikas Mhatre - प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला धक्का देणारे विकास म्हात्रे आहेत तरी कोण?</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/vikas-mhatre-resignation-bjp-allegations-on-ravindra-chavan-dombivili-msr87</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Nanded Ashok Chavan: अशोक चव्हाणांची डोकेदुखी वाढली; काँग्रेसकडून खिंडीत पकडण्यासाठी प्लॅन तयार, नांदेडमध्ये काय घडतंय?</t>
+          <t>Dombivli KDMCC School Building |डोंबिवलीत केडीएमसी शाळेची नवी इमारत</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
+          <t>https://pudhari.news/maharashtra/thane/dombivli-kdmcc-school-new-building-bhoomipujan-by-mla-ravindra-chavan-sp96</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती की स्वबळावर? भाजप प्रदेशाध्यक्षांचं सूचक विधान; म्हणाले, 'आचारसंहिता लागली की...'</t>
+          <t>Nitin Gadkari Auto Rickshaw Comment: गडकरींनी सांगितलं ‘ऑटो रिक्षा’ अन् महाराष्ट्र भाजपचं कनेक्शन ; क्षणात एकच हशा पिकला!</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-statement-on-date-of-local-body-elections-mahayuti-alliance-vru98</t>
+          <t>https://www.esakal.com/mumbai/nitin-gadkari-comment-about-auto-rickshaw-maharashtra-bjp-political-reaction-ravindra-chavan-maharashtra-bjp-president-msr87</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : “फेक नरेटिव्ह तयार करणाऱ्यांची फॅक्टरी…” फडणवीस यांचं उद्धव ठाकरेंना त्याच भाषेत उत्तर</t>
+          <t>उत्तर महाराष्ट्रात काँग्रेसला मोठा धक्का ? कुणाल पाटील भाजपात जाणार? राजकीय वर्तुळात चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-bjp-president-fadnavis-slams-uddhav-thackeray-over-fake-narrative-as11</t>
+          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>रायगड : पालकमंत्री पदावरून राजकीय संघर्ष शिगेला, राष्ट्रवादी काँग्रेसची (शरदचंद्र पवार) सुनील तटकरे यांच्यावर टीका</t>
+          <t>Nashik BJP News : भाजप खासदार, आमदारांना मंडल दत्तक देणार</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/escalating-political-tensions-in-raigad-over-guardian-minister-post-ncp-sharad-pawar-leader-targets-sunil-tatkare-maharashtra-news-mhs25081204223</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/nashik-bjp-news-bjp-will-adopt-mandals-for-mps-mlas-ar84</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>Nashik BJP News : भाजप खासदार, आमदारांना मंडल दत्तक देणार</t>
+          <t>उद्धव ठाकरेंपाठोपाठ शरद पवारांनाही धक्का! भाजपामध्ये 'इनकमिंग' सुरूच; अनेकांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/nashik-bjp-news-bjp-will-adopt-mandals-for-mps-mlas-ar84</t>
+          <t>https://www.lokmat.com/maharashtra/after-uddhav-thackeray-sharad-pawar-also-gets-a-shock-many-join-bjp-party-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Nanded News: नांदेडमध्ये स्थानिक निवडणुकासाठी काँगेस अन् वंचितकडून युतीचे संकेत प्रस्ताव</t>
+          <t>युवा उद्योजक विशाल परब यांची भाजप वापसी</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
+          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>इंद्रायणी नदी पुलाला 8 कोटी मंजूर झाल्याचा दावा, संजय राऊतांनी फक्त 80 हजारांचे पत्रच दाखवलं! म्हणाले, एकतर मंत्र्याने झोपेत सही केली किंवा जनतेला मूर्ख बनवलं जात आहे</t>
+          <t>Thane | कल्याण-डोंबिवलीत झोपडपट्टी पुनर्वसन योजना लवकरच कार्यान्वीत</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/claiming-that-rs-8-crore-was-approved-for-the-indrayani-river-bridge-sanjay-raut-showed-only-a-letter-for-rs-80-thousand-devendra-fadnavis-1364502</t>
+          <t>https://pudhari.news/maharashtra/thane/thane-slum-rehabilitation-scheme-to-be-implemented-soon-in-kalyan-dombivli</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>Vikas Mhatre - प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला धक्का देणारे विकास म्हात्रे आहेत तरी कोण?</t>
+          <t>कॉर्पोरेटमधील नोकरी ते मुंबई भाजपाच्या अध्यक्षपदी नियुक्ती, कोण आहेत अमित साटम?</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/vikas-mhatre-resignation-bjp-allegations-on-ravindra-chavan-dombivili-msr87</t>
+          <t>https://www.etvbharat.com/mr/!politics/bmc-election-2025-major-reshuffle-in-bjp-amit-satam-appointed-as-president-of-mumbai-bjp-know-political-reactions-his-profile-coroporate-job-to-politician-mhs25082501410</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Dombivli KDMCC School Building |डोंबिवलीत केडीएमसी शाळेची नवी इमारत</t>
+          <t>Ravindra Chavan : अधिकाऱ्यांनी जर दिरंगाई केली असेल तर…; रविंद्र चव्हाणांचा कारवाईचा इशारा</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/dombivli-kdmcc-school-new-building-bhoomipujan-by-mla-ravindra-chavan-sp96</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5163828/ravindra-chavans-warning-of-action-over-indrayani-river-bridge-collapsed-accident-cas/</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>Nitin Gadkari Auto Rickshaw Comment: गडकरींनी सांगितलं ‘ऑटो रिक्षा’ अन् महाराष्ट्र भाजपचं कनेक्शन ; क्षणात एकच हशा पिकला!</t>
+          <t>नांदेडमध्ये अशोक चव्हाणांना घेरण्यासाठी काँग्रेसची नवी खेळी; 'या' पक्षाशी करणार हातमिळवणी?</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/nitin-gadkari-comment-about-auto-rickshaw-maharashtra-bjp-political-reaction-ravindra-chavan-maharashtra-bjp-president-msr87</t>
+          <t>https://www.navarashtra.com/politics/congress-may-alliance-with-vba-party-in-nanded-for-upcoming-municipal-election-942211.html</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>उत्तर महाराष्ट्रात काँग्रेसला मोठा धक्का ? कुणाल पाटील भाजपात जाणार? राजकीय वर्तुळात चर्चांना उधाण</t>
+          <t>Marathwada Politics : काँग्रेसला जोरदार धक्का, २ दिग्गज नेत्यांनी 'हात' सोडला, २४ तासांत कमळ हातात घेणार</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
+          <t>https://saamtv.esakal.com/maharashtra/big-blow-to-congress-senior-leaders-kailas-gorantyal-and-suresh-warpudkar-set-to-join-bjp-ahead-of-local-polls-latest-news-nck90</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis |महाराष्‍ट्र विकसित करुन दाखवू : मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>शेकाप नेते जयंत पाटील यांच्या घरात राजकीय फूट; बंधू पंडित पाटील यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/lets-develop-maharashtra-chief-minister-devendra-fadnavis-ng81</t>
+          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरेंपाठोपाठ शरद पवारांनाही धक्का! भाजपामध्ये 'इनकमिंग' सुरूच; अनेकांचा पक्षप्रवेश</t>
+          <t>Maharashtra Breaking News : काँग्रेसचे माजी आमदार कुणाल पाटलांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/after-uddhav-thackeray-sharad-pawar-also-gets-a-shock-many-join-bjp-party-a-a747/</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-1st-july-maharashtra-assembly-monsoon-session-2025-of-devendra-fadanvis-eknath-shinde-uddhav-and-raj-thackeray-asc-95-5194810/</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>युवा उद्योजक विशाल परब यांची भाजप वापसी</t>
+          <t>Sanjay Jagtap : पुण्यात काँग्रेसला जोरदार झटका, संजय जगताप यांचा भाजपमध्ये प्रवेश | VIDEO</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
+          <t>https://saamtv.esakal.com/video/sanjay-jagtap-former-congress-mla-joins-bjp-in-grand-saswad-event-political-shift-in-pune-district-mrs01</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>Thane | कल्याण-डोंबिवलीत झोपडपट्टी पुनर्वसन योजना लवकरच कार्यान्वीत</t>
+          <t>मिशन मुंबई, भाजप भाकरी फिरवणार अध्यक्षपदासाठी बैठक, दोन आमदारांनी नावे समोर</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/thane-slum-rehabilitation-scheme-to-be-implemented-soon-in-kalyan-dombivli</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>कॉर्पोरेटमधील नोकरी ते मुंबई भाजपाच्या अध्यक्षपदी नियुक्ती, कोण आहेत अमित साटम?</t>
+          <t>BJP vs MNS : कोकणात भाजपचा मनसेला मोठा धक्का; 'हा' नेता भाजपच्या वाटेवर</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/bmc-election-2025-major-reshuffle-in-bjp-amit-satam-appointed-as-president-of-mumbai-bjp-know-political-reactions-his-profile-coroporate-job-to-politician-mhs25082501410</t>
+          <t>https://www.lokshahi.com/news/vaibhav-khedekar-a-member-of-mnss-konkan-unit-is-on-his-way-to-the-bjp</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : अधिकाऱ्यांनी जर दिरंगाई केली असेल तर…; रविंद्र चव्हाणांचा कारवाईचा इशारा</t>
+          <t>राज्यात आणखी एक घराणं फुटलं; काँग्रेस खासदाराच्या दिराचा भाजपमध्ये प्रवेश, १० माजी नगरसेवकांनीही कमळ हाती घेतलं</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5163828/ravindra-chavans-warning-of-action-over-indrayani-river-bridge-collapsed-accident-cas/</t>
+          <t>https://saamtv.esakal.com/maharashtra/anil-dhanorkar-joins-bjp-in-presence-of-ravindra-chavan-and-hansraj-ahir-along-with-10-corporators-in-chandrapur-bdk97</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>शेकाप नेते जयंत पाटील यांच्या घरात राजकीय फूट; बंधू पंडित पाटील यांचा भाजपात प्रवेश</t>
+          <t>भाजपचा मविआला जोरदार धक्का, वसई-विरार अन् धाराशिवमध्ये राजकीय भूकंप, कोण कोणत्या नेत्यांनी साथ सोडली?</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
+          <t>https://saamtv.esakal.com/maharashtra/major-jolt-to-mva-as-key-leaders-join-bjp-in-vasai-virar-and-dharashiv-nck90</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News : काँग्रेसचे माजी आमदार कुणाल पाटलांचा भाजपात प्रवेश</t>
+          <t>'त्यांच्या प्रवेशामुळे पक्षाची ताकद वाढणार', हजारो समर्थकांसह संजय जगताप यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-1st-july-maharashtra-assembly-monsoon-session-2025-of-devendra-fadanvis-eknath-shinde-uddhav-and-raj-thackeray-asc-95-5194810/</t>
+          <t>https://www.lokmat.com/pune/his-entry-will-increase-the-partys-strength-sanjay-jagtap-joins-bjp-with-thousands-of-supporters-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Sanjay Jagtap : पुण्यात काँग्रेसला जोरदार झटका, संजय जगताप यांचा भाजपमध्ये प्रवेश | VIDEO</t>
+          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/sanjay-jagtap-former-congress-mla-joins-bjp-in-grand-saswad-event-political-shift-in-pune-district-mrs01</t>
+          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>मिशन मुंबई, भाजप भाकरी फिरवणार अध्यक्षपदासाठी बैठक, दोन आमदारांनी नावे समोर</t>
+          <t>Ameet Satam : भाजपमध्ये मोठे फेरबदल ! मुंबई भाजपचे नवे अध्यक्ष अमित साटम, मुख्यमंत्र्यानी केली घोषणा</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
+          <t>https://www.jaimaharashtranews.com/politics/maharashtra-politics-ameet-satam-appointed-as-mumbai-president-of-bjp-cm-devendra-fadanvis-annonced-it-/40320</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>BJP vs MNS : कोकणात भाजपचा मनसेला मोठा धक्का; 'हा' नेता भाजपच्या वाटेवर</t>
+          <t>Thane Politics: शहापुरात मोठी राजकीय उलथापालथ! मविआच्या २७ मोठ्या नेत्यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/vaibhav-khedekar-a-member-of-mnss-konkan-unit-is-on-his-way-to-the-bjp</t>
+          <t>https://saamtv.esakal.com/maharashtra/thane-politics-news-27-key-leaders-join-bjp-in-shahapur-major-blow-to-maha-vikas-aghadi-bdk97</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>राज्यात आणखी एक घराणं फुटलं; काँग्रेस खासदाराच्या दिराचा भाजपमध्ये प्रवेश, १० माजी नगरसेवकांनीही कमळ हाती घेतलं</t>
+          <t>पालघरमध्ये मोठी राजकीय घडामोड! एकनाथ शिंदेंना मोठा धक्का, बड्या नेत्यासह अनेक पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/anil-dhanorkar-joins-bjp-in-presence-of-ravindra-chavan-and-hansraj-ahir-along-with-10-corporators-in-chandrapur-bdk97</t>
+          <t>https://saamtv.esakal.com/maharashtra/big-political-shift-in-palghar-major-leaders-join-bjp-setback-for-eknath-shinde-uddhav-thackeray-and-sharad-pawar-pvm91</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>भाजपचा मविआला जोरदार धक्का, वसई-विरार अन् धाराशिवमध्ये राजकीय भूकंप, कोण कोणत्या नेत्यांनी साथ सोडली?</t>
+          <t>Maharashtra Politics: शरद पवारांना मोठा झटका; नांदेडमधील ९ शिलेदारांनी धरली भाजपची वाट</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/major-jolt-to-mva-as-key-leaders-join-bjp-in-vasai-virar-and-dharashiv-nck90</t>
+          <t>https://saamtv.esakal.com/maharashtra/political-earthquake-in-nanded-major-setback-for-sharad-pawar-in-nanded-as-9-key-supporters-join-bjp-latest-news-pvm91</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Ameet Satam : भाजपमध्ये मोठे फेरबदल ! मुंबई भाजपचे नवे अध्यक्ष अमित साटम, मुख्यमंत्र्यानी केली घोषणा</t>
+          <t>Raigad News : महायुतीत वादाची ठिणगी पडणार? एकनाथ शिंदेंच्या शिवसेनेला भाजपचा धक्का</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/maharashtra-politics-ameet-satam-appointed-as-mumbai-president-of-bjp-cm-devendra-fadanvis-annonced-it-/40320</t>
+          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
+          <t>पुण्यात शरद पवारांसह अजित पवारांना धक्का; भाजपने पाडले खिंडार, शेकडो कार्यकर्त्यांचा राष्ट्रवादीला रामराम</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/big-blow-to-sharad-pawar-in-pune-bhor-and-mulshi-hundreds-of-workers-join-bjp-nck90</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>'त्यांच्या प्रवेशामुळे पक्षाची ताकद वाढणार', हजारो समर्थकांसह संजय जगताप यांचा भाजपात प्रवेश</t>
+          <t>तीन टर्म आमदार राहिलेल्या नेत्याच्या हाती कमळ; भाजपनं वाढवलं बळ, शिंदेसेनेत खळबळ</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/his-entry-will-increase-the-partys-strength-sanjay-jagtap-joins-bjp-with-thousands-of-supporters-a-a727/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Thane Politics: शहापुरात मोठी राजकीय उलथापालथ! मविआच्या २७ मोठ्या नेत्यांचा भाजपात प्रवेश</t>
+          <t>Politics: कोल्हापुरात राजकीय भूकंप! काँग्रेस अन् राष्ट्रवादीला मोठा धक्का; बड्या नेत्यांसह कार्यकर्त्यांनी कमळ हाती घेतलं</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/thane-politics-news-27-key-leaders-join-bjp-in-shahapur-major-blow-to-maha-vikas-aghadi-bdk97</t>
+          <t>https://saamtv.esakal.com/maharashtra/major-political-shakeup-in-kolhapur-ex-congress-and-ncp-leaders-join-bjp-bdk97</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>पालघरमध्ये मोठी राजकीय घडामोड! एकनाथ शिंदेंना मोठा धक्का, बड्या नेत्यासह अनेक पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
+          <t>डोंबिवलीचे आमदार झाले भाजपाचे नवे प्रदेशाध्यक्ष! कल्याण डोंबिवलीत यंदा महापौर कोणाचा?</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/big-political-shift-in-palghar-major-leaders-join-bjp-setback-for-eknath-shinde-uddhav-thackeray-and-sharad-pawar-pvm91</t>
+          <t>https://www.lokmat.com/kalyan-dombivli/dombivli-mla-becomes-bjps-new-state-president-who-will-be-the-mayor-of-kalyan-dombivli-this-year-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: शरद पवारांना मोठा झटका; नांदेडमधील ९ शिलेदारांनी धरली भाजपची वाट</t>
+          <t>Maharashtra Politics: महाविकास आघाडीला मोठं खिंडार, अनेक बडे नेते, संरपंचांसह पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/political-earthquake-in-nanded-major-setback-for-sharad-pawar-in-nanded-as-9-key-supporters-join-bjp-latest-news-pvm91</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-major-blow-to-mva-as-key-leaders-sarpanch-join-bjp-in-shahapur-pvm91</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>Raigad News : महायुतीत वादाची ठिणगी पडणार? एकनाथ शिंदेंच्या शिवसेनेला भाजपचा धक्का</t>
+          <t>खान्देशची बुलंद तोफ भाजपात जाणार? पडद्यामागच्या घडामोडींनी काँग्रेसची चिंता वाढली</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>पुण्यात शरद पवारांसह अजित पवारांना धक्का; भाजपने पाडले खिंडार, शेकडो कार्यकर्त्यांचा राष्ट्रवादीला रामराम</t>
+          <t>Dombivali Politics : भाजप प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला खिंडार; दोन नगरसेवकांचा राजीनामा</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/big-blow-to-sharad-pawar-in-pune-bhor-and-mulshi-hundreds-of-workers-join-bjp-nck90</t>
+          <t>https://www.esakal.com/mumbai/setback-for-bjp-in-state-vice-presidents-constituency-ravindra-chavan-as-two-corporators-vikas-mhatre-and-kavita-mhatre-resign-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>तीन टर्म आमदार राहिलेल्या नेत्याच्या हाती कमळ; भाजपनं वाढवलं बळ, शिंदेसेनेत खळबळ</t>
+          <t>ऑनलाइन हाजिरी लगा रहे भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण, अघाड़ी सम्मेलन में की जीत दिलाने की मांग</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
+          <t>https://navbharatlive.com/maharashtra/akola/aim-provide-health-services-vaidya-aghadi-conference-bjp-mahayuti-ravindra-chavan-1329683.html</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>Politics: कोल्हापुरात राजकीय भूकंप! काँग्रेस अन् राष्ट्रवादीला मोठा धक्का; बड्या नेत्यांसह कार्यकर्त्यांनी कमळ हाती घेतलं</t>
+          <t>भाजपा के कोर कमेटी बैठक में रवींद्र चव्हाण ने दिए निर्देश, चुनावी रणनीति और संगठन मजबूती पर की चर्चा</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/major-political-shakeup-in-kolhapur-ex-congress-and-ncp-leaders-join-bjp-bdk97</t>
+          <t>https://navbharatlive.com/maharashtra/garchiroli/election-strategy-strengthening-organization-ravindra-chavan-instructions-bjp-1326133.html</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>डोंबिवलीचे आमदार झाले भाजपाचे नवे प्रदेशाध्यक्ष! कल्याण डोंबिवलीत यंदा महापौर कोणाचा?</t>
+          <t>Chandrashekhar Bawankule, Ravindra Chavan BJP State President</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kalyan-dombivli/dombivli-mla-becomes-bjps-new-state-president-who-will-be-the-mayor-of-kalyan-dombivli-this-year-a-a653/</t>
+          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात मराठीचीच सक्ती, पण हिंदीचाही अभिमान, दबावाला बळी न पडता विद्यार्थ्यांच्या</t>
+          <t>डोंबिवली में पहलगाम हमले में मारे गए नागरिकों की स्मृति में बनेगा शहीद स्मारक, विधायक रविंद्र चव्हाण ने लिखा पत्र</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/chief-minister-devendra-fadnavis-reaction-regarding-marathi-language-criticism-on-uddhav-thackeray-in-mumbai-1367354</t>
+          <t>https://www.newsnationtv.com/--20250502182005/</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: महाविकास आघाडीला मोठं खिंडार, अनेक बडे नेते, संरपंचांसह पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
+          <t>भाजपला लवकरच मिळणार नवा प्रदेशाध्यक्ष; रविंद्र चव्हाण यांच्यावर सोपवणार जबाबदारी</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-major-blow-to-mva-as-key-leaders-sarpanch-join-bjp-in-shahapur-pvm91</t>
+          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>खान्देशची बुलंद तोफ भाजपात जाणार? पडद्यामागच्या घडामोडींनी काँग्रेसची चिंता वाढली</t>
+          <t>Ravindra Chavan Appointed New BJP Maharashtra President : रविंद्र चव्हाण ठरले भाजपचे नवे कप्तान, महाराष्ट्राच्या संघटनाला नवे नेतृत्व</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Dombivali Politics : भाजप प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला खिंडार; दोन नगरसेवकांचा राजीनामा</t>
+          <t>भाजपला आज मिळणार नवे प्रदेशाध्यक्ष; रवींद्र चव्हाण स्विकारणार सूत्र</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/setback-for-bjp-in-state-vice-presidents-constituency-ravindra-chavan-as-two-corporators-vikas-mhatre-and-kavita-mhatre-resign-politics-pjp78</t>
+          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>Mumbai BJP President : अमित साटम मुंबई भाजपचे नवे अध्यक्ष! प्रदेशाध्यक्ष रविंद्र चव्हाण यांची मोठी घोषणा...</t>
+          <t>मालवण मधील 'उबाठा' च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/amit-satam-appointed-new-mumbai-bjp-president-devendra-fadnavis-announcement-spb94</t>
+          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>संगठन चुनाव से पहले ही छिनी बावनकुले की कुर्सी, रवींद्र चव्हाण बनाए गए महाराष्ट्र भाजपा के कार्यकारी अध्यक्ष</t>
+          <t>Ravindra Chavan होणार महाराष्ट्र भाजपचे नवे प्रदेशाध्यक्ष, ठाकरेंच्या गडात होणार पहिलं शक्तिप्रदर्शन!</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-1098263.html</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule, Ravindra Chavan BJP State President</t>
+          <t>शहापूर तालुक्यातील उबाठा, शरद पवार गट व काँग्रेसच्या अनेक कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
+          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>डोंबिवली में पहलगाम हमले में मारे गए नागरिकों की स्मृति में बनेगा शहीद स्मारक, विधायक रविंद्र चव्हाण ने लिखा पत्र</t>
+          <t>कल्याण – डोंबिवली , चंद्रपूर जिल्ह्यातील अनेक माजी नगरसेवकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/--20250502182005/</t>
+          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed New BJP Maharashtra President : रविंद्र चव्हाण ठरले भाजपचे नवे कप्तान, महाराष्ट्राच्या संघटनाला नवे नेतृत्व</t>
+          <t>मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
+          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>भाजपला आज मिळणार नवे प्रदेशाध्यक्ष; रवींद्र चव्हाण स्विकारणार सूत्र</t>
+          <t>BJP President Banner: भाजप प्रदेशाध्यक्षांच्या निवडीचे बॅनर फाडले... - देशोन्नती</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
+          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>वसई-विरारच्या ‘बविआ’ च्या माजी नगसेवक आणि कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>रविंद्र शिंदेंचा भाजपमध्ये धडाकेबाज प्रवेश; चंद्रपूरच्या राजकारणाला कलाटणी!</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
+          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>मालवण मधील 'उबाठा' च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण; अधिकृत घोषणा आज होणार</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/ravindra-chavan-to-be-bjp-maharashtra-president-announcement-soon</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ravindra Chavan होणार महाराष्ट्र भाजपचे नवे प्रदेशाध्यक्ष, ठाकरेंच्या गडात होणार पहिलं शक्तिप्रदर्शन!</t>
+          <t>Ravindra Chavan MaTa Katta : ठाकरे बंधूंची युती निश्चित, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण म्हणाले, भावनात्मक मुद्द्यांवर कुणाला...</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>भोर, मुळशी तालुक्यातील विविध पक्षातील कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>डोंबिवलीत बुधवारी भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचा जनता दरबार</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
+          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-janta-darbar-in-dombivli-on-wednesday-ssb-93-5314946/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>शहापूर तालुक्यातील उबाठा, शरद पवार गट व काँग्रेसच्या अनेक कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण, १ जुलैला घोषणा; किरण रिजिजू निरीक्षक</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
+          <t>https://www.lokmat.com/mumbai/ravindra-chavan-to-be-bjp-maharashtra-state-president-announcement-on-july-1-kiren-rijiju-observer-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>कल्याण – डोंबिवली , चंद्रपूर जिल्ह्यातील अनेक माजी नगरसेवकांचा भाजपात प्रवेश</t>
+          <t>BJP State President : भाजपा प्रदेशाध्यक्षांची 1 जुलै रोजी निवड; रवींद्र चव्हाणांची वर्णी लागणार?</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
+          <t>https://www.mymahanagar.com/maharashtra/the-election-of-bjp-state-president-will-be-held-on-july-1-and-ravindra-chavan-is-likely-to-be-the-candidate/897175/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>Ravindra Chavan: भाजपमध्ये आता चव्हाणपर्व, रवींद्र चव्हाण बनले नवे भाजपचे प्रदेशाध्यक्ष!</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
+          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>BJP President Banner: भाजप प्रदेशाध्यक्षांच्या निवडीचे बॅनर फाडले... - देशोन्नती</t>
+          <t>डोंंबिवलीच्या विकासाला ग्रहण लावणाऱ्या ‘चाँदभाई’चे नाव घ्या; राजू पाटील यांचे भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांना आवाहन</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
+          <t>https://www.loksatta.com/thane/mns-leader-raju-patil-slams-bjp-state-chief-ravindra-chavan-for-his-bjp-mayor-in-kdmc-remark-zws-70-5279498/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>रविंद्र शिंदेंचा भाजपमध्ये धडाकेबाज प्रवेश; चंद्रपूरच्या राजकारणाला कलाटणी!</t>
+          <t>BJP Politics : भाजप प्रदेशाध्यक्षांच्या ठाकरेंना दे धक्का! बालेकिल्ल्यात 'डॅमेज कंट्रोल', विकास म्हात्रेंचे मन वळवले</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-ravindra-chavan-successfully-resolves-vikas-mhatre-disconten-shivsen-ubt-rm89</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण; अधिकृत घोषणा आज होणार</t>
+          <t>Photo : प्रदेशाध्यक्ष पदाची सूत्रे स्वीकारताच रवींद्र चव्हाण अ‍ॅक्टिव्ह; म्हणाले…</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/ravindra-chavan-to-be-bjp-maharashtra-president-announcement-soon</t>
+          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>Ravindra Chavan MaTa Katta : ठाकरे बंधूंची युती निश्चित, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण म्हणाले, भावनात्मक मुद्द्यांवर कुणाला...</t>
+          <t>अधिवेशन, कायदा-सुव्यवस्था राखण्यासाठी हिंदीची सक्ती रद्द, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
+          <t>https://www.loksatta.com/mumbai/bjp-ravindra-chavan-says-hindi-compulsion-decision-withdrawn-due-to-assembly-session-and-law-and-order-mumbai-print-news-css-98-5217714/</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>डोंबिवलीत बुधवारी भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचा जनता दरबार</t>
+          <t>BJP State President Election | भाजपकडून प्रदेशाध्यक्ष पदासाठी निवडणूक कार्यक्रम जाहीर</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-janta-darbar-in-dombivli-on-wednesday-ssb-93-5314946/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण, १ जुलैला घोषणा; किरण रिजिजू निरीक्षक</t>
+          <t>मालवणमधील 'उबाठा'च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश, भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले स्वागत</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ravindra-chavan-to-be-bjp-maharashtra-state-president-announcement-on-july-1-kiren-rijiju-observer-a-a571/</t>
+          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>BJP State President : भाजपा प्रदेशाध्यक्षांची 1 जुलै रोजी निवड; रवींद्र चव्हाणांची वर्णी लागणार?</t>
+          <t>Sindhudurg Politics | सिंधुदुर्ग जिल्हा व भाजपसाठी आज आनंदाचा दिवस!</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/the-election-of-bjp-state-president-will-be-held-on-july-1-and-ravindra-chavan-is-likely-to-be-the-candidate/897175/</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-bjp-state-president-sindhudurg-politics-sp96</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजपमध्ये आता चव्हाणपर्व, रवींद्र चव्हाण बनले नवे भाजपचे प्रदेशाध्यक्ष!</t>
+          <t>Devendra Fadnavis |महाराष्‍ट्र विकसित करुन दाखवू : मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/lets-develop-maharashtra-chief-minister-devendra-fadnavis-ng81</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>डोंंबिवलीच्या विकासाला ग्रहण लावणाऱ्या ‘चाँदभाई’चे नाव घ्या; राजू पाटील यांचे भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांना आवाहन</t>
+          <t>वसई-विरारच्या ‘बविआ’ च्या माजी नगसेवक आणि कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/mns-leader-raju-patil-slams-bjp-state-chief-ravindra-chavan-for-his-bjp-mayor-in-kdmc-remark-zws-70-5279498/</t>
+          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>BJP Politics : भाजप प्रदेशाध्यक्षांच्या ठाकरेंना दे धक्का! बालेकिल्ल्यात 'डॅमेज कंट्रोल', विकास म्हात्रेंचे मन वळवले</t>
+          <t>भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांच्या हस्ते ‘ध्येयवादी देवेंद्रजी’ कॉफी टेबल बुकचे प्रकाशन</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-ravindra-chavan-successfully-resolves-vikas-mhatre-disconten-shivsen-ubt-rm89</t>
+          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>Photo : प्रदेशाध्यक्ष पदाची सूत्रे स्वीकारताच रवींद्र चव्हाण अ‍ॅक्टिव्ह; म्हणाले…</t>
+          <t>भोर, मुळशी तालुक्यातील विविध पक्षातील कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
+          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>अधिवेशन, कायदा-सुव्यवस्था राखण्यासाठी हिंदीची सक्ती रद्द, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
+          <t>Kedar Jadhav makes bold prediction about India playing Pakistan in Asia Cup</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-ravindra-chavan-says-hindi-compulsion-decision-withdrawn-due-to-assembly-session-and-law-and-order-mumbai-print-news-css-98-5217714/</t>
+          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>BJP State President Election | भाजपकडून प्रदेशाध्यक्ष पदासाठी निवडणूक कार्यक्रम जाहीर</t>
+          <t>4 ex-Congress corporators join BJP in Kalyan-Dombivli</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>मालवणमधील 'उबाठा'च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश, भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले स्वागत</t>
+          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>Sindhudurg Politics | सिंधुदुर्ग जिल्हा व भाजपसाठी आज आनंदाचा दिवस!</t>
+          <t>BJP inducts key PWP leaders before local body elections</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-bjp-state-president-sindhudurg-politics-sp96</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांच्या हस्ते ‘ध्येयवादी देवेंद्रजी’ कॉफी टेबल बुकचे प्रकाशन</t>
+          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
+          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>BJP picks new state chiefs, moves closer to electing JP Nadda's successor</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
+          <t>https://www.indiatoday.in/india/story/with-new-state-presidents-bjp-gears-up-to-choose-jp-nadda-successor-2748768-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Kedar Jadhav makes bold prediction about India playing Pakistan in Asia Cup</t>
+          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
+          <t>After poll drubbing, Prithviraj Chavan may replace Patole in Maharashtra Congress rejig</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/india/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-flags-arrogance-in-leadership-congress-reacts/ar-AA1IuYys</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jan/14/after-poll-drubbing-prithviraj-chavan-may-replace-patole-in-maharashtra-congress-rejig</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>4 ex-Congress corporators join BJP in Kalyan-Dombivli</t>
+          <t>Maharashtra Cabinet Reshuffle: Fadnavis Meets Amit Shah, Nadda Amid Speculation</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>BJP inducts key PWP leaders before local body elections</t>
+          <t>NCP, Shiv Sena (UBT) members join BJP in Nashik</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
+          <t>Congress’s 5 time Ex-MLA Suresh Warpudkar kin set to join BJP</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>Ahead of local body polls, BJP finalises names of 22 district presidents</t>
+          <t>India Politics Highlights| Criminals, gangsters got right to rape, loot under TMC banner: CPI(M)'s Md Salim</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
+          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
+          <t>Maharashtra BJP appoints 58 new district presidents ahead of local body polls</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/May/13/maharashtra-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>BJP picks new state chiefs, moves closer to electing JP Nadda's successor</t>
+          <t>Emotional farewell: Outgoing BJP State President Bawankule pens heartfelt letter to party workers</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/with-new-state-presidents-bjp-gears-up-to-choose-jp-nadda-successor-2748768-2025-07-01</t>
+          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
+          <t>Dombivli MLA Ravindra Chavan Takes Charge as New Maharashtra BJP President, Replacing Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://www.lokmattimes.com/maharashtra/dombivli-mla-ravindra-chavan-takes-charge-as-new-maharashtra-bjp-president-replacing-chandrashekhar-bawankule-a475/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
+          <t>https://www.lokmattimes.com/national/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>After poll drubbing, Prithviraj Chavan may replace Patole in Maharashtra Congress rejig</t>
+          <t>Maharashtra Politics: BJP State Chief Ravindra Chavan Meets PM Modi, Outlines Party’s Expansion Plan</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jan/14/after-poll-drubbing-prithviraj-chavan-may-replace-patole-in-maharashtra-congress-rejig</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-state-chief-ravindra-chavan-meets-pm-modi-outlines-partys-expansion-plan</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Maharashtra Cabinet Reshuffle: Fadnavis Meets Amit Shah, Nadda Amid Speculation</t>
+          <t>Ravindra Chavan: A Visionary Leader Strengthening Maharashtra BJP's Political Landscape</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
+          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>BJP names 22 more district chiefs ahead of civic polls</t>
+          <t>Ameet Satam Appointed As Mumbai BJP President Ahead of BMC Polls</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-names-22-more-district-chiefs-ahead-of-civic-polls/articleshow/121541000.cms</t>
+          <t>https://www.lokmattimes.com/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls-a517/</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>NCP, Shiv Sena (UBT) members join BJP in Nashik</t>
+          <t>Maharashtra Politics: Ex-Congress MLA Sanjay Jagtap Joins BJP With Supporters In Pune; Congress Hits Out,</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ex-congress-mla-sanjay-jagtap-joins-bjp-with-supporters-in-pune-congress-hits-out-calls-bjp-witch-party-video</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Congress’s 5 time Ex-MLA Suresh Warpudkar kin set to join BJP</t>
+          <t>Maharashtra News: Former Congress MLA Sangram Thopte From Punes Bhor Joins BJP After Setback In 2024 Assembly</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-former-congress-mla-sangram-thopte-from-punes-bhor-joins-bjp-after-setback-in-2024-assembly-elections</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>India Politics Highlights| Criminals, gangsters got right to rape, loot under TMC banner: CPI(M)'s Md Salim</t>
+          <t>Maharashtra Politics: State Congress Secretary Dilip Bhalerao, Along With Hundreds Of Supporters, Joins BJP</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-state-congress-secretary-dilip-bhalerao-along-with-hundreds-of-supporters-joins-bjp</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Maharashtra BJP appoints 58 new district presidents ahead of local body polls</t>
+          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/May/13/maharashtra-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
+          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Emotional farewell: Outgoing BJP State President Bawankule pens heartfelt letter to party workers</t>
+          <t>Maharashtra Politics: Former Congress Minister Suresh Warpudkar Joins BJP With Key Supporters</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-minister-suresh-warpudkar-joins-bjp-with-key-supporters</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Ameet Satam Appointed As Mumbai BJP President Ahead of BMC Polls</t>
+          <t>Congress Receives A Jolt After Former Dhule MLA Kunal Patil Joins BJP</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls-a517/</t>
+          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Ex-Congress MLA Sanjay Jagtap Joins BJP With Supporters In Pune; Congress Hits Out,</t>
+          <t>Maharashtra Politics: BJP Appoints 58 New District Presidents Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ex-congress-mla-sanjay-jagtap-joins-bjp-with-supporters-in-pune-congress-hits-out-calls-bjp-witch-party-video</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Maharashtra News: Former Congress MLA Sangram Thopte From Punes Bhor Joins BJP After Setback In 2024 Assembly</t>
+          <t>Ramchander Rao appointed as T'gana BJP President despite opposition: MP gets new chief as Hemant Khandelwal...</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-former-congress-mla-sangram-thopte-from-punes-bhor-joins-bjp-after-setback-in-2024-assembly-elections</t>
+          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
+          <t>BJP announces new state chiefs in 7 states, 2 UTs; moves closer to elect national president</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
+          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: State Congress Secretary Dilip Bhalerao, Along With Hundreds Of Supporters, Joins BJP</t>
+          <t>BJP Steps Closer To Electing National President, List Of State Chiefs Out</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-state-congress-secretary-dilip-bhalerao-along-with-hundreds-of-supporters-joins-bjp</t>
+          <t>https://www.newsx.com/india/who-is-the-new-bjp-party-president-list-of-state-party-president-out-11032/</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Mumbai BJP Leadership Shake-Up: Pravin Darekar And Amit Satam In Contention For City President Post Ahead Of</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-leadership-shake-up-pravin-darekar-and-amit-satam-in-contention-for-city-president-post-ahead-of-bmc-elections</t>
+          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
+          <t>Ex Minister Ravindra Chavan Files Nomination For Maharashtra BJP Chief Post</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
+          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Former Congress Minister Suresh Warpudkar Joins BJP With Key Supporters</t>
+          <t>BJP leader Ravindra Chavan appointed as new state president of Maharashtra</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-minister-suresh-warpudkar-joins-bjp-with-key-supporters</t>
+          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Congress Receives A Jolt After Former Dhule MLA Kunal Patil Joins BJP</t>
+          <t>Once UAPA accused over Dawood ‘links’, Sena (UBT) leader finds place in BJP ahead of Nashik civic polls</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
+          <t>https://indianexpress.com/article/political-pulse/uapa-accused-dawood-links-sena-ubt-leader-in-bjp-nashik-civic-polls-10074232/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP Appoints 58 New District Presidents Ahead Of Local Body Polls</t>
+          <t>"Double-engine govt working in people's best interests": New Maharashtra BJP chief Ravindra Chavan</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253/</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ramchander Rao appointed as T'gana BJP President despite opposition: MP gets new chief as Hemant Khandelwal...</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
+          <t>https://www.socialnews.xyz/2025/06/30/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>BJP announces new state chiefs in 7 states, 2 UTs; moves closer to elect national president</t>
+          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
+          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Pune MP Murlidhar Mohol Launches City’s First 24×7 Digital Citizen Service Office</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-mp-murlidhar-mohol-launches-citys-first-24x7-digital-citizen-service-office/</t>
+          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>BJP Appoints New State Presidents in 9 States Including Maharashtra and Madhya Pradesh</t>
+          <t>सीएम फडणवीस के विश्वासपात्र...रवींद्र चव्हाण महाराष्ट्र भाजपा के नए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
+          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ex Minister Ravindra Chavan Files Nomination For Maharashtra BJP Chief Post</t>
+          <t>Maharashtra: बीजेपी ने महाराष्ट्र में बता दिया कौन बनेगा प्रदेश अध्यक्ष? BMC चुनावों से पहले मराठी दांव</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>BJP leader Ravindra Chavan appointed as new state president of Maharashtra</t>
+          <t>Former Minister Ravindra Chavan Appointed Maharashtra BJP Working President</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
+          <t>https://www.news18.com/politics/former-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-9185878.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>कौन बनेगा महाराष्ट्र भाजपा का अध्यक्ष? इस नाम का चुना जाना लगभग तय</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/06/30/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
+          <t>महाराष्ट्र बीजेपी की कमान अब नए हाथों में, जानिए कौन हैं पार्टी के नवनियुक्त प्रदेश अध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
+          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
+          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
+          <t>https://www.asianage.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888548</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>पूर्व मंत्री रवींद्र चव्हाण बने महाराष्ट्र BJP के कार्यकारी प्रदेश अध्यक्ष, बावनकुले की कुर्सी छिनी</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp-3054565.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>सीएम फडणवीस के विश्वासपात्र...रवींद्र चव्हाण महाराष्ट्र भाजपा के नए प्रदेश अध्यक्ष</t>
+          <t>Ravindra Chavan : भाजपचे प्रदेश कार्यकारी अध्यक्ष होताच रवींद्र चव्हाण अनवाणी पायाने</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>Maharashtra: बीजेपी ने महाराष्ट्र में बता दिया कौन बनेगा प्रदेश अध्यक्ष? BMC चुनावों से पहले मराठी दांव</t>
+          <t>महाराष्ट्र BJP को मिलेगा नया चेहरा; चंद्रशेखर बावनकुले के बाद रवींद्र चव्हाण का नाम सबसे आगे, रिजिजू की निगरानी में होगा ऐलान</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
+          <t>https://sudarshannews.in/news-detail.aspx?id=129159</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Former Minister Ravindra Chavan Appointed Maharashtra BJP Working President</t>
+          <t>भारतीय जनता पार्टीचे नवे प्रदेशाध्यक्ष म्हणून रवींद्र चव्हाण यांची बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/former-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-9185878.html</t>
+          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>कौन बनेगा महाराष्ट्र भाजपा का अध्यक्ष? इस नाम का चुना जाना लगभग तय</t>
+          <t>कौन हैं महाराष्ट्र भाजपा के नए अध्यक्ष रवींद्र चव्हाण, क्या होंगी उनके लिए चुनौतियां</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
+          <t>https://hindi.webdunia.com/maharashtra/who-is-maharashtra-bjp-new-president-ravindra-chavan-know-125070100083_1.html</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: महाराष्ट्र भाजपा को मिला नया अध्यक्ष, रवींद्र चव्हाण सर्वसम्मति से चुने गए</t>
+          <t>हेमंत खंडेलवाल होंगे मध्य प्रदेश बीजेपी के नए अध्यक्ष, रवींद्र चव्हाण को महाराष्ट्र की कमान</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/maharashtra-bjp-gets-new-president-ravindra-chavan-elected-unanimously-b628/</t>
+          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी की कमान अब नए हाथों में, जानिए कौन हैं पार्टी के नवनियुक्त प्रदेश अध्यक्ष रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan News : मंत्रिमंडळात मोठे फेरबदल, 8 जणांना डच्चू मिळणार का? अखेर रवींद्र चव्हाण यांनीच केलं क्लिअर</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/maharashtra-cabinet-reshuffle-2025-ministers-remove-ravindra-chavan-clarification-rm82</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
+          <t>महाराष्ट्र लोकल बॉडी चुनावों को लेकर बड़ा अपडेट, बीजेपी, शिंदे और अजित पवार में रहेगा गठबंधन या फिर टूटेगा, जानें</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888548</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>पूर्व मंत्री रवींद्र चव्हाण बने महाराष्ट्र BJP के कार्यकारी प्रदेश अध्यक्ष, बावनकुले की कुर्सी छिनी</t>
+          <t>Ravindra Chavan : भाजपने प्रदेशाध्यक्षपद देऊन माझ्यावर उपकार केले, माझी ओळख...; रवींद्र चव्हाणांची पक्षावर स्तुतीसुमने</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp-3054565.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-bjp-ravindra-chavan-new-president-ravindra-chavan-speech-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपचे प्रदेश कार्यकारी अध्यक्ष होताच रवींद्र चव्हाण अनवाणी पायाने</t>
+          <t>Kunal Patil News: शिवसेना उद्धव ठाकरे, काँग्रेसला धुळ्यात भाजप एकाच वेळी धक्का देण्याच्या तयारीत?</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/kunal-patil-politics-congress-leader-kunal-patil-shiv-senas-shubhangi-patil-are-on-the-path-to-bjp-sd67</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP को मिलेगा नया चेहरा; चंद्रशेखर बावनकुले के बाद रवींद्र चव्हाण का नाम सबसे आगे, रिजिजू की निगरानी में होगा ऐलान</t>
+          <t>Kedar Jadhav : केदार जाधव क्रिकेटच्या मैदानातून राजकीय आखाड्यात, भाजपमध्ये प्रवेश करणार,</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://sudarshannews.in/news-detail.aspx?id=129159</t>
+          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>हेमंत खंडेलवाल होंगे मध्य प्रदेश बीजेपी के नए अध्यक्ष, रवींद्र चव्हाण को महाराष्ट्र की कमान</t>
+          <t>कुंडमळा पुलासाठी आठ कोटी मंजूर, सही ८० हजाराच्या पत्रावर…, संजय राऊत यांचा रवींद्र चव्हाण...</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/shiv-sena-ubt-leader-sanjay-raut-criticizes-minister-ravindra-chavan-1424686.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>कौन हैं महाराष्ट्र भाजपा के नए अध्यक्ष रवींद्र चव्हाण, क्या होंगी उनके लिए चुनौतियां</t>
+          <t>इंतजार खत्म... बीजेपी ने चार राज्यों में अपने प्रदेश अध्यक्षों के नाम फाइनल किए, जानें कौन है लिस्ट में</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/who-is-maharashtra-bjp-new-president-ravindra-chavan-know-125070100083_1.html</t>
+          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>भारतीय जनता पार्टीचे नवे प्रदेशाध्यक्ष म्हणून रवींद्र चव्हाण यांची बिनविरोध निवड</t>
+          <t>स्थानिक नेत्यांशी चर्चा करुन अन्य पक्षातील नेत्यांना प्रवेश देणार; सरकारला पक्षसंघटनेचे पाठबळ देणार,भाजप नवे प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
+          <t>https://www.loksatta.com/politics/newly-appointed-state-president-ravindra-chavan-stated-while-talking-to-loksatta-print-politics-news-phm-00-5196663/</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>Ravindra Chavan News : मंत्रिमंडळात मोठे फेरबदल, 8 जणांना डच्चू मिळणार का? अखेर रवींद्र चव्हाण यांनीच केलं क्लिअर</t>
+          <t>पुण्यासह पश्चिम महाराष्ट्रावर भाजपचे लक्ष; प्रदेशाध्यक्षांनी पदाधिकाऱ्यांना काय दिल्या सूचना?…</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/maharashtra-cabinet-reshuffle-2025-ministers-remove-ravindra-chavan-clarification-rm82</t>
+          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>महाराष्ट्र लोकल बॉडी चुनावों को लेकर बड़ा अपडेट, बीजेपी, शिंदे और अजित पवार में रहेगा गठबंधन या फिर टूटेगा, जानें</t>
+          <t>BJP Maharashtra President Announcement : भाजपचं ठरलं! प्रदेशाध्यक्षाची लवकरच घोषणा; मुंबई अध्यक्षपदासाठी 'ही' तीन नावे चर्चेत</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/bjp-to-announce-maharashtra-president-soon-3-names-in-contention-for-mumbai-post-sw79</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपने प्रदेशाध्यक्षपद देऊन माझ्यावर उपकार केले, माझी ओळख...; रवींद्र चव्हाणांची पक्षावर स्तुतीसुमने</t>
+          <t>मोदी सरकारच्या अकरा वर्षाच्या काळात २५ कोटी कुटुंबं दारिद्र्य रेषेबाहेर; रवींद्र चव्हाण यांची माहिती</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-bjp-ravindra-chavan-new-president-ravindra-chavan-speech-latest-marathi-news-pp0731</t>
+          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>अशोक चव्हाण यांचा आत्मविश्वास ढासळला, नांदेडमधील काँग्रेस नेत्यांची भाजपावर टीका</t>
+          <t>भाजपच्या संघटन बांधणीला नवे बळ 963 मंडळ अध्यक्षांच्या नियुक्त्या पूर्ण रवींद्र</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mp-ashok-chavan-meeting-leaders-shows-shaken-confidence-said-congress-mp-ravindra-chavan-sud-02-5112129/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>Kunal Patil News: शिवसेना उद्धव ठाकरे, काँग्रेसला धुळ्यात भाजप एकाच वेळी धक्का देण्याच्या तयारीत?</t>
+          <t>महापालिका निवडणूक स्वबळावर लढणार? रवींद्र चव्हाणांनी स्पष्टच सांगितलं; म्हणाले- देवेंद्र फडणवीसांच्या आदेशानुसारच...</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/kunal-patil-politics-congress-leader-kunal-patil-shiv-senas-shubhangi-patil-are-on-the-path-to-bjp-sd67</t>
+          <t>https://www.esakal.com/maharashtra/ravindra-chavan-statement-on-maharashtra-municipal-elections-vru98</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Kedar Jadhav : केदार जाधव क्रिकेटच्या मैदानातून राजकीय आखाड्यात, भाजपमध्ये प्रवेश करणार,</t>
+          <t>Sanjay Jagtap: संजय जगताप यांचा भाजपमध्ये पक्षप्रवेश आगामी निवडणुकीआधी काँग्रेसला</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>कुंडमळा पुलासाठी आठ कोटी मंजूर, सही ८० हजाराच्या पत्रावर…, संजय राऊत यांचा रवींद्र चव्हाण...</t>
+          <t>Maharashtra BJP: बीजेपी ने 58 जिला अध्यक्षों के नाम किए घोषित, अब मुंबई अध्यक्ष की बारी, देखें पूरी लिस्ट</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/shiv-sena-ubt-leader-sanjay-raut-criticizes-minister-ravindra-chavan-1424686.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>स्थानिक नेत्यांशी चर्चा करुन अन्य पक्षातील नेत्यांना प्रवेश देणार; सरकारला पक्षसंघटनेचे पाठबळ देणार,भाजप नवे प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
+          <t>चंद्रशेखर बावनकुळेंकडून स्वीकारली सूत्रे; महापालिका, जिल्हा परिषद निवडणुकीचे आव्हान: फडणवीसांचे निकटवर्तीय ...</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/newly-appointed-state-president-ravindra-chavan-stated-while-talking-to-loksatta-print-politics-news-phm-00-5196663/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/fadnavis-close-aide-ravindra-chavan-becomes-bjp-state-president-accepts-responsibility-from-chandrashekhar-bawankule-challenge-for-municipal-zilla-parishad-elections-135355331.html</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>पुण्यासह पश्चिम महाराष्ट्रावर भाजपचे लक्ष; प्रदेशाध्यक्षांनी पदाधिकाऱ्यांना काय दिल्या सूचना?…</t>
+          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
+          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President Announcement : भाजपचं ठरलं! प्रदेशाध्यक्षाची लवकरच घोषणा; मुंबई अध्यक्षपदासाठी 'ही' तीन नावे चर्चेत</t>
+          <t>महाराष्ट्रात राजकीय भूकंप घडवण्यात रवींद्र चव्हाणांचा मोठा वाटा, भाजपच्या नव्या प्रदेशाध्यक्षांची A टू Z कारकीर्द</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/bjp-to-announce-maharashtra-president-soon-3-names-in-contention-for-mumbai-post-sw79</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>मोदी सरकारच्या अकरा वर्षाच्या काळात २५ कोटी कुटुंबं दारिद्र्य रेषेबाहेर; रवींद्र चव्हाण यांची माहिती</t>
+          <t>Ravindra Chavan : प्रदेशाध्यक्ष बावनकुळेंच्या जागी रवींद्र चव्हाणांची वर्णी ?</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
+          <t>https://www.lokshahi.com/news/leadership-change-in-maharashtra-bjp-ravindra-chavan-appointed-state-president</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>भाजपच्या संघटन बांधणीला नवे बळ 963 मंडळ अध्यक्षांच्या नियुक्त्या पूर्ण रवींद्र</t>
+          <t>मुंबई भाजप अध्यक्षपदी अमित साटम: रवींद्र चव्हाण, फडणवीसांनी केली घोषणा; मुंबई महापालिका निवडणुकीच्या तोंडाव...</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-president-amit-satam-appointed-ahead-bmc-election-135756496.html</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>महापालिका निवडणूक स्वबळावर लढणार? रवींद्र चव्हाणांनी स्पष्टच सांगितलं; म्हणाले- देवेंद्र फडणवीसांच्या आदेशानुसारच...</t>
+          <t>भाजपला घमेंडी म्हणणाऱ्यांना शिंदेसेनेचे नेते समज देतील: रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ravindra-chavan-statement-on-maharashtra-municipal-elections-vru98</t>
+          <t>https://www.lokmat.com/chhatrapati-sambhajinagar/shinde-sena-leaders-will-explain-to-those-who-call-bjp-arrogant-ravindra-chavan-a-a320/</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>Sanjay Jagtap: संजय जगताप यांचा भाजपमध्ये पक्षप्रवेश आगामी निवडणुकीआधी काँग्रेसला</t>
+          <t>महाराष्ट्र में कांग्रेस को बड़ा झटका, यह पूर्व मंत्री अब बीजेपी में हुए शामिल,</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
+          <t>https://www.abplive.com/states/maharashtra/parbhani-congress-leader-suresh-warpudkar-joins-bjp-with-supporters-ahead-of-nagar-nikay-chunav-2987557</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
+          <t>BJP State President | रवींद्र चव्हाण यांची उद्या महाराष्ट्र भाजप प्रदेशाध्यक्षपदी निवड होणार</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
+          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: बीजेपी ने 58 जिला अध्यक्षों के नाम किए घोषित, अब मुंबई अध्यक्ष की बारी, देखें पूरी लिस्ट</t>
+          <t>मुंबई भाजप अध्यक्षपदाच्या निवडीत मराठी चेहऱ्याला प्राधान्य</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
+          <t>https://www.loksatta.com/politics/amit-satam-mumbai-bjp-president-devendra-fadnavis-ravindra-chavan-mumbai-municipal-corporation-print-politics-news-ssb-93-5329396/</t>
         </is>
       </c>
     </row>
@@ -5051,984 +5051,984 @@
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : प्रदेशाध्यक्ष बावनकुळेंच्या जागी रवींद्र चव्हाणांची वर्णी ?</t>
+          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/leadership-change-in-maharashtra-bjp-ravindra-chavan-appointed-state-president</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>चंद्रशेखर बावनकुळेंकडून स्वीकारली सूत्रे; महापालिका, जिल्हा परिषद निवडणुकीचे आव्हान: फडणवीसांचे निकटवर्तीय ...</t>
+          <t>BJP President : भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण निश्चित; मुंबई अध्यक्षपदी दरेकर शक्य</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/fadnavis-close-aide-ravindra-chavan-becomes-bjp-state-president-accepts-responsibility-from-chandrashekhar-bawankule-challenge-for-municipal-zilla-parishad-elections-135355331.html</t>
+          <t>https://www.esakal.com/maharashtra/bjp-president-ravindra-chavan-and-pravin-darekar-mumbai-president-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>भाजपला घमेंडी म्हणणाऱ्यांना शिंदेसेनेचे नेते समज देतील: रवींद्र चव्हाण</t>
+          <t>डोंबिवलीतील विकास म्हात्रे यांचा भाजपमध्येच मुक्काम; मुख्यमंत्री देवेंद्र फडणवीस, प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घेतली भेट</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/chhatrapati-sambhajinagar/shinde-sena-leaders-will-explain-to-those-who-call-bjp-arrogant-ravindra-chavan-a-a320/</t>
+          <t>https://www.loksatta.com/thane/vikas-mhatre-from-dombivli-met-chief-minister-devendra-fadnavis-and-state-president-ravindra-chavan-amy-95-5214180/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>BJP State President | रवींद्र चव्हाण यांची उद्या महाराष्ट्र भाजप प्रदेशाध्यक्षपदी निवड होणार</t>
+          <t>‘एमएमआर’ क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा, प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
+          <t>https://www.loksatta.com/thane/bjps-ravindra-chavan-instructed-mumbai-officials-to-implement-slum-rehabilitation-scheme-effectively-sud-02-4933709/</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>BJP President : भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण निश्चित; मुंबई अध्यक्षपदी दरेकर शक्य</t>
+          <t>Municipal Election: पालिका निवडणुकीसाठी भाजपची जय्यत तयारी सुरू, माजी खासदार आणि आमदारांवर सोपवली मोठी जबाबदारी</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-president-ravindra-chavan-and-pravin-darekar-mumbai-president-politics-pjp78</t>
+          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-has-entrusted-responsibility-of-municipal-elections-in-maharashtra-to-former-mps-and-mlas-vru98</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>मुंबई भाजप अध्यक्षपदाच्या निवडीत मराठी चेहऱ्याला प्राधान्य</t>
+          <t>Ravindra Chavan : साधू महंतांसह भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण श्रीमलंगगडावर</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/amit-satam-mumbai-bjp-president-devendra-fadnavis-ravindra-chavan-mumbai-municipal-corporation-print-politics-news-ssb-93-5329396/</t>
+          <t>https://pudhari.news/maharashtra/raigad/ravindra-chavan-visits-malanggad-with-sadhus-and-bjp-leaders-ab96</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: अखेर प्रतीक्षा संपली! बावनकुळेंनंतर भाजपला नवा धडाकेबाज प्रदेशाध्यक्ष मिळाला</t>
+          <t>Thackeray Shiv Sena Setback | ठाकरे शिवसेनेला मालवण शहरात खिंडार</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-appointed-bjp-maharashtra-new-president-dk88</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/malvan-shiv-sena-defection-bjp-joining-ravindra-chavan-sp96</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : चव्हाण पेलणार का आव्हान!</t>
+          <t>Ravindra Chavan यांचा शिवसेना उबाठाला धक्का, कामगार संघटनेचे दीड हजार सदस्यांचा भाजपमध्ये प्रवेश..</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
+          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-s-shiv-sena-ubatha-is-in-trouble-1500-members-of-the-workers-union-join-bjp-1051360.html</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>प्रसिद्धीपासून दूर, कामगिरीवर भर; भाजप प्रदेशाध्यक्षांचा अनोखा नागपूर दौरा</t>
+          <t>Ravindra Chavan भाजपा हीच माझी ओळख म्हणणारे रवींद्र चव्हाण महाराष्ट्र भाजपच्या प्रदेशाध्यक्षपदी!!</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/ravindra-chavan-nagpur-visit-keeps-media-in-dark-highlights-bjps-new-low-key-strategy-skips-publicity-focuses-on-groundwork-print-political-news-vsd-99-5252822/</t>
+          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>Nitesh Rane : राणेंच्या वक्तव्याचा भाजपच्या कार्यकारी अध्यक्षांना फटका... पत्रकार परिषदच गुंडाळण्याची वेळ!</t>
+          <t>कल्याणमध्ये काँग्रेसला खिंडार! बडे नेते भाजपवासी; प्रदेशाध्यक्षांनी दिले मोठे संकेत</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/nagpur-nitesh-rane-remark-ravindra-chavan-press-conference-disruption-bjp-controversy-hn97-rc70</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-grows-stronger-in-kalyan-congress-leaders-join-ravindra-chavan-hints-at-contesting-solo-bdk97</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महाराष्ट्रात भाजपला मिळाला नवा कॅप्टन; प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची...</t>
+          <t>Ravindra Chavan: ऑपरेशन एकनाथ शिंदेंमध्ये मोठी जबाबदारी ते फडणवीस मुख्यमंत्री होणार नाहीत</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
+          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रवींद्र चव्हाण यांचे नाव आज प्रदेशाध्यक्षपदी जाहीर</t>
+          <t>Who Is Ravindra Chavan: रवींद्र चव्हाण बनले महाराष्ट्र भाजपचे कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा यांची घोषणा Who is Ravindra Chavan Ravindra Chavan becomes the working president of Maharashtra BJP Natio</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/ravindra-chavan-to-be-announced-as-bjp-maharashtra-state-president-vsb99</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण ; सावंतवाडीत कार्यकर्त्यांचा जल्लोष</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
+          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>मुंबई भाजप अध्यक्षपदी अमित साटम: रवींद्र चव्हाण, फडणवीसांनी केली घोषणा; मुंबई महापालिका निवडणुकीच्या तोंडाव...</t>
+          <t>Ravindra Chavan : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड, काय आहे समीकरण?</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-president-amit-satam-appointed-ahead-bmc-election-135756496.html</t>
+          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>डोंबिवलीतील विकास म्हात्रे यांचा भाजपमध्येच मुक्काम; मुख्यमंत्री देवेंद्र फडणवीस, प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घेतली भेट</t>
+          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/vikas-mhatre-from-dombivli-met-chief-minister-devendra-fadnavis-and-state-president-ravindra-chavan-amy-95-5214180/</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>भाजपच्या प्रदेशाध्यक्षपदी रवींद्र चव्हाण; 1 जुलैला मुंबईत होणार घोषणा</t>
+          <t>Local elections | स्थानिक निवडणुका महायुतीत लढू, कार्यकर्त्यांचाही विचार : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/video/ravindra-chavan-bjp-maharashtra-president/918909</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-mahayuti-to-contest-local-elections-ab96</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>‘एमएमआर’ क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा, प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan भाजपमध्ये पक्ष प्रवेशांचा धडाका, लातूर धाराशिव अमरावतीमधील पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjps-ravindra-chavan-instructed-mumbai-officials-to-implement-slum-rehabilitation-scheme-effectively-sud-02-4933709/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : साधू महंतांसह भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण श्रीमलंगगडावर</t>
+          <t>BJP Expansion Strategy: पक्षविस्तार की सत्तेसाठीची तडजोड?</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/raigad/ravindra-chavan-visits-malanggad-with-sadhus-and-bjp-leaders-ab96</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjp-expansion-or-power-compromise-maharashtra-politics-chandrasekhar-bawankule-ravindra-chavan-devendra-fadnavis-mm76</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Thackeray Shiv Sena Setback | ठाकरे शिवसेनेला मालवण शहरात खिंडार</t>
+          <t>Nitesh Rane Statement | नितेश राणे यांच्या विधानामुळे भाजपची कोंडी, रवींद्र चव्हाण यांनी गुंडाळली पत्रकार परिषद</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/malvan-shiv-sena-defection-bjp-joining-ravindra-chavan-sp96</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nitesh-rane-statement-puts-bjp-in-spotlight-ravindra-chavan-cancels-press-meet-sk95</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Ravindra Chavan यांचा शिवसेना उबाठाला धक्का, कामगार संघटनेचे दीड हजार सदस्यांचा भाजपमध्ये प्रवेश..</t>
+          <t>Nanded News : जिल्ह्यातील शेतकऱ्यांच्या खात्यावर विम्याची रक्कम लवकरच जमा होणार</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-s-shiv-sena-ubatha-is-in-trouble-1500-members-of-the-workers-union-join-bjp-1051360.html</t>
+          <t>https://pudhari.news/maharashtra/marathwada/nanded/insurance-amount-will-be-deposited-in-the-accounts-of-farmers-in-the-district-soon-np88</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ravindra Chavan भाजपा हीच माझी ओळख म्हणणारे रवींद्र चव्हाण महाराष्ट्र भाजपच्या प्रदेशाध्यक्षपदी!!</t>
+          <t>भाजपचे कार्याध्यक्ष रवींद्र चव्हाण शनिवारी बीड दौऱ्यावर</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
+          <t>https://www.loksatta.com/aurangabad/bjp-leader-ravindra-chavan-beed-tour-condolence-visit-vsd-99-5123945/</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: ऑपरेशन एकनाथ शिंदेंमध्ये मोठी जबाबदारी ते फडणवीस मुख्यमंत्री होणार नाहीत</t>
+          <t>Maharashtra Politics : काँग्रेसला राज्यात मोठा हादरा, बड्या नेत्याने केला भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-congress-leader-kailas-gorantyal-quits-party-and-joins-bjp-in-presence-of-ravindra-chavan-jalna-strongman-switches-sides-yps99</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan: रवींद्र चव्हाण बनले महाराष्ट्र भाजपचे कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा यांची घोषणा Who is Ravindra Chavan Ravindra Chavan becomes the working president of Maharashtra BJP Natio</t>
+          <t>कल्याण डोंबिवली क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा – भाजप प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
+          <t>https://www.localnewsnetwork.in/implement-slum-rehabilitation-scheme-effectively-in-kalyan-dombivali-area-bjp-state-working-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण ; सावंतवाडीत कार्यकर्त्यांचा जल्लोष</t>
+          <t>प्रत्येकाच्या मनात ‘कमळ’ रुजले पाहिजे</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.loksatta.com/pune/bjp-leader-ravindra-chavan-urges-lotus-must-bloom-in-every-heart-pune-print-news-ocd-94-5167946/</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड, काय आहे समीकरण?</t>
+          <t>BJP Maharashtra President | रवींद्र चव्हाण भाजपचे बारावे महाराष्ट्र प्रदेशाध्यक्ष होणार</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
+          <t>भाजप लोकल बॉडीची निवडणूक स्वबळावर लढणार: पण मुंबईसाठी घेणार शिंदे, दादांची मदत; रवींद्र चव्हाण यांनी घेतली ...</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-bjp-local-body-election-strategy-mumbai-alliance-shinde-ajit-pawar-135526240.html</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Local elections | स्थानिक निवडणुका महायुतीत लढू, कार्यकर्त्यांचाही विचार : रवींद्र चव्हाण</t>
+          <t>BJP Maharashtra President | १ जुलैला रवींद्र चव्हाणांच्या नावाची घोषणा, भाजपचं जोरदार शक्तिप्रदर्शन</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-mahayuti-to-contest-local-elections-ab96</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Ravindra Chavan भाजपमध्ये पक्ष प्रवेशांचा धडाका, लातूर धाराशिव अमरावतीमधील पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>Sanjay Raut : सही करताना झोपेत असतात का? राऊतांचा रवींद्र चव्हाणांवर घणाघात</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
+          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>BJP Expansion Strategy: पक्षविस्तार की सत्तेसाठीची तडजोड?</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाणांचे शुभेच्छा देणार बॅनर फाडले</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjp-expansion-or-power-compromise-maharashtra-politics-chandrasekhar-bawankule-ravindra-chavan-devendra-fadnavis-mm76</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-banners-wishing-ravindra-chavan-were-torn-1062422.html</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Municipal Election: पालिका निवडणुकीसाठी भाजपची जय्यत तयारी सुरू, माजी खासदार आणि आमदारांवर सोपवली मोठी जबाबदारी</t>
+          <t>Jan Suraksha Bill : ‘जनसुरक्षे’मुळे विकासमार्ग खुला; प्रकल्पांना विरोध डाव्यांकडून : भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-has-entrusted-responsibility-of-municipal-elections-in-maharashtra-to-former-mps-and-mlas-vru98</t>
+          <t>https://www.esakal.com/maharashtra/jan-suraksha-bill-will-pave-way-for-development-ravindra-chavan-amp17</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>जिल्ह्यात कमळ अधिक भक्कम करा</t>
+          <t>Maharashtra BJP President: रवींद्र चव्हाण यांच्यासमोर स्थानिक स्वराज्य संस्थांच्या निवडणुकांचे आव्हान</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-appeals-to-strengthen-bjp-maharashtra</t>
+          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Nitesh Rane Statement | नितेश राणे यांच्या विधानामुळे भाजपची कोंडी, रवींद्र चव्हाण यांनी गुंडाळली पत्रकार परिषद</t>
+          <t>Ratnagiri BJP election : रवींद्र चव्हाणांच्या शब्दाला मान; रत्नागिरीत निकटवर्तीयांना संधी, सावंतांची फेर निवड</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nitesh-rane-statement-puts-bjp-in-spotlight-ravindra-chavan-cancels-press-meet-sk95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-appoints-rajesh-sawant-and-satish-more-close-aides-of-party-vice-president-ravindra-chavan-as-district-presidents-for-south-and-north-ratnagiri-as11</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Nanded News : जिल्ह्यातील शेतकऱ्यांच्या खात्यावर विम्याची रक्कम लवकरच जमा होणार</t>
+          <t>Ravindra Chavan Exclusive : ठाकरे बंधूंची युती ते BMC मध्ये भाजपचा महापौर? भाजपच्या नव्या...</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/insurance-amount-will-be-deposited-in-the-accounts-of-farmers-in-the-district-soon-np88</t>
+          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : काँग्रेसला राज्यात मोठा हादरा, बड्या नेत्याने केला भाजपमध्ये प्रवेश</t>
+          <t>‘कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाशाला बेघर होऊ देणार नाही’ - आमदार रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-congress-leader-kailas-gorantyal-quits-party-and-joins-bjp-in-presence-of-ravindra-chavan-jalna-strongman-switches-sides-yps99</t>
+          <t>https://www.lokmat.com/kalyan-dombivli/not-a-single-resident-of-the-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-says-mla-ravindra-chavan-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Maharashtra BJP : भाजपचा आता दर महिन्याला जनता दरबार; दरबारातून जनतेला काय मिळणार?</t>
+          <t>महापालिका निवडणुका महायुती एकत्र लढणार? नवे प्रदेशाध्यक्ष काय म्हणाले?; महापौरपदाबाबतही मोठं विधान</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/mumbai-news-bjp-to-hold-monthly-janata-darbar-rds84</t>
+          <t>https://www.tv9marathi.com/politics/mahayuatis-election-strategy-bjps-chavan-announces-joint-municipal-polls-contests-1444009.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>प्रत्येकाच्या मनात ‘कमळ’ रुजले पाहिजे</t>
+          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/bjp-leader-ravindra-chavan-urges-lotus-must-bloom-in-every-heart-pune-print-news-ocd-94-5167946/</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President | रवींद्र चव्हाण भाजपचे बारावे महाराष्ट्र प्रदेशाध्यक्ष होणार</t>
+          <t>कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
+          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>भाजप लोकल बॉडीची निवडणूक स्वबळावर लढणार: पण मुंबईसाठी घेणार शिंदे, दादांची मदत; रवींद्र चव्हाण यांनी घेतली ...</t>
+          <t>कल्याण-डोंबिवलीची कहाणी: शिंदे-चव्हाण पुढारी असलेल्या KDMC ची एवढी दैना झाली तरी कशी?</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-bjp-local-body-election-strategy-mumbai-alliance-shinde-ajit-pawar-135526240.html</t>
+          <t>https://www.mumbaitak.in/political-news/story/story-of-kalyan-dombivli-why-are-conditions-of-kalyan-and-dombivali-cities-so-bad-despite-powerful-leaders-shrikant-shinde-ravindra-chavan-3197444-2025-08-21</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President | १ जुलैला रवींद्र चव्हाणांच्या नावाची घोषणा, भाजपचं जोरदार शक्तिप्रदर्शन</t>
+          <t>मोठी बातमी: BMC निवडणुकीआधी फडणवीसांनी डाव टाकला; भाजपकडून मुंबईत नव्या अध्यक्षाची घोषणा</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Sanjay Raut : सही करताना झोपेत असतात का? राऊतांचा रवींद्र चव्हाणांवर घणाघात</t>
+          <t>घराण्याची 75 वर्षाची निष्ठा संपली… अखेर काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश, खान्देशात...</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
+          <t>https://www.tv9marathi.com/politics/big-blow-for-congress-in-khandesh-ex-mla-kunal-patil-join-bjp-1436092.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाणांचे शुभेच्छा देणार बॅनर फाडले</t>
+          <t>BJP में शामिल हुए प्रदेश कांग्रेस सचिव दिलीप भालेराव, रवींद्र चव्हाण ने किया स्वागत</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-banners-wishing-ravindra-chavan-were-torn-1062422.html</t>
+          <t>https://navbharatlive.com/maharashtra/state-congress-secretary-dilip-bhalerao-joined-bjp-maharashtra-nikay-chunav-1308763.html</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>Jan Suraksha Bill : ‘जनसुरक्षे’मुळे विकासमार्ग खुला; प्रकल्पांना विरोध डाव्यांकडून : भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
+          <t>भाजपा संगठन चुनाव: महाराष्ट्र में रवींद्र चव्हाण , उत्तराखंड में महेंद्र भट्ट; जानें MP में कौन होगा BJP...</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/jan-suraksha-bill-will-pave-way-for-development-ravindra-chavan-amp17</t>
+          <t>https://www.haribhoomi.com/national/bjp-state-president-elections-ravindra-chavan-mahendra-bhatt-634968</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: रवींद्र चव्हाण यांच्यासमोर स्थानिक स्वराज्य संस्थांच्या निवडणुकांचे आव्हान</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, जानें कौन हैं | Hari Bhoomi</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
+          <t>https://www.haribhoomi.com/state-local/maharastra/ravindra-chavan-appointed-maharashtra-bjp-president-635140</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Ratnagiri BJP election : रवींद्र चव्हाणांच्या शब्दाला मान; रत्नागिरीत निकटवर्तीयांना संधी, सावंतांची फेर निवड</t>
+          <t>Who Is Ravindra Chavan: देवेंद्र फडणवीसांचे विश्वासू रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष! एकमताने निवड</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-appoints-rajesh-sawant-and-satish-more-close-aides-of-party-vice-president-ravindra-chavan-as-district-presidents-for-south-and-north-ratnagiri-as11</t>
+          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Exclusive : ठाकरे बंधूंची युती ते BMC मध्ये भाजपचा महापौर? भाजपच्या नव्या...</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>महापालिका निवडणुका महायुती एकत्र लढणार? नवे प्रदेशाध्यक्ष काय म्हणाले?; महापौरपदाबाबतही मोठं विधान</t>
+          <t>Maharashtra News Highlights : भाजपाला मिळणार नवा प्रदेशाध्यक्ष, रविंद्र चव्हाणांनी भरला अर्ज, मंगळवारी होणार अधिकृत घोषणा</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/mahayuatis-election-strategy-bjps-chavan-announces-joint-municipal-polls-contests-1444009.html</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan : महाराष्ट्रात भाजपला मिळाला नवा कॅप्टन; प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची...</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
+          <t>प्रसिद्धीपासून दूर, कामगिरीवर भर; भाजप प्रदेशाध्यक्षांचा अनोखा नागपूर दौरा</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
+          <t>https://www.loksatta.com/politics/ravindra-chavan-nagpur-visit-keeps-media-in-dark-highlights-bjps-new-low-key-strategy-skips-publicity-focuses-on-groundwork-print-political-news-vsd-99-5252822/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवलीची कहाणी: शिंदे-चव्हाण पुढारी असलेल्या KDMC ची एवढी दैना झाली तरी कशी?</t>
+          <t>Pune News : पुणे जिल्हा 'शत प्रतिशत' भाजप..? अजित पवारांची आणि पवार कुटुंबाची सद्दी संपणार?</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/story-of-kalyan-dombivli-why-are-conditions-of-kalyan-and-dombivali-cities-so-bad-despite-powerful-leaders-shrikant-shinde-ravindra-chavan-3197444-2025-08-21</t>
+          <t>https://marathi.indiatimes.com/maharashtra/pune-news/sanjay-jagtap-joins-bjp-in-the-presence-of-bjp-state-president-ravindra-chavan/articleshow/122572770.cms</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>मोठी बातमी: BMC निवडणुकीआधी फडणवीसांनी डाव टाकला; भाजपकडून मुंबईत नव्या अध्यक्षाची घोषणा</t>
+          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>घराण्याची 75 वर्षाची निष्ठा संपली… अखेर काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश, खान्देशात...</t>
+          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/big-blow-for-congress-in-khandesh-ex-mla-kunal-patil-join-bjp-1436092.html</t>
+          <t>https://english.metrovaartha.com/news/states/ex-minister-ravindra-chavan-is-bjps-new-maharashtra-unit-chief</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>महापालिका निवडणुकीआधी उद्धव ठाकरे गटाला भाजपाचा मोठा धक्का, कोकणातील नगरसेवकांसह शेकडो कार्यकर्त्यांचा...</t>
+          <t>Proud Of Hindi, No Red Carpet For English, Says Maharashtra CM Devendra Fadnavis (VIDEO)</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/uddhav-thackeray-shiv-sena-suffers-major-blow-key-malvan-councilors-join-bjp-political-landscape-1445255.html</t>
+          <t>https://www.freepressjournal.in/mumbai/proud-of-hindi-no-red-carpet-for-english-says-maharashtra-cm-devendra-fadnavis-video</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>ऑनलाइन हाजिरी लगा रहे भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण, अघाड़ी सम्मेलन में की जीत दिलाने की मांग</t>
+          <t>Ahmedabad Plane Crash: Air India Crew Member And Travel Influencer Roshni Songhare Among Victims</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/akola/aim-provide-health-services-vaidya-aghadi-conference-bjp-mahayuti-ravindra-chavan-1329683.html</t>
+          <t>https://www.thedailyjagran.com/entertainment/news/ahmedabad-plane-crash-air-india-crew-member-and-travel-influencer-roshni-songhare-among-victims-photos-videos-10244818</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>BJP में शामिल हुए प्रदेश कांग्रेस सचिव दिलीप भालेराव, रवींद्र चव्हाण ने किया स्वागत</t>
+          <t>Bodies of Pahalgam terror attack victims reach Maharashtra: CM Fadnavis offers final respect to 6 victims b...</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/state-congress-secretary-dilip-bhalerao-joined-bjp-maharashtra-nikay-chunav-1308763.html</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>भाजपा संगठन चुनाव: महाराष्ट्र में रवींद्र चव्हाण , उत्तराखंड में महेंद्र भट्ट; जानें MP में कौन होगा BJP...</t>
+          <t>महाराष्ट्र के शिरडी में BJP का दो दिवसीय अधिवेशन शुरू, अगले प्रदेश अध्यक्ष की हो सकती है घोषणा,जानें कौन आगे</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/national/bjp-state-president-elections-ravindra-chavan-mahendra-bhatt-634968</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, जानें कौन हैं | Hari Bhoomi</t>
+          <t>नए राष्ट्रीय अध्यक्ष को लेकर BJP आलाकमान और संघ के बीच फंसा पेच, इन राज्यों में बदलेगा प्रदेश नेतृत्व</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/maharastra/ravindra-chavan-appointed-maharashtra-bjp-president-635140</t>
+          <t>https://www.aajtak.in/india/news/story/deadlock-between-bjp-high-command-and-rss-over-news-national-president-continues-ntc-rptc-2275062-2025-06-29</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan: देवेंद्र फडणवीसांचे विश्वासू रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष! एकमताने निवड</t>
+          <t>रविंद्र जडेजा का बिहार से क्या रिश्ता? 'क्रिकेट गुरु' महेंद्र सिंह चौहान से महेंद्र सिंह धोनी तक का सफर</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>महाराष्ट्र भाजपा के नए बॉस बने रवींद्र चौहान, जानिए कौन हैं निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
+          <t>https://hindi.news24online.com/state/mumbai/politician-becomes-new-boss-of-maharashtra-bjp-know-who-is-the-president-ravindra-chauhan/1240488/</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights : भाजपाला मिळणार नवा प्रदेशाध्यक्ष, रविंद्र चव्हाणांनी भरला अर्ज, मंगळवारी होणार अधिकृत घोषणा</t>
+          <t>Air India Plane Crash: प्लेन की क्रू मेंबर का निधन, रोशनी सोंघरे की विमान हादसे में गई जान</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
+          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : नाट्यमय घडामोडी, शेवटपर्यंत सस्पेन्स, अखेर नाशिकच्या राजकारणात भूकंप, बडगुजर, घोलप आता 'भाजप'वासी</t>
+          <t>कौन हैं IAS अरविंद चौहान? इंसानियत की मिसाल पेश की, यूपी के इस डीएम की हर तरफ हो रही तारीफ</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nashik/nashik-politics-shiv-sena-ubt-leader-sudhakar-badgujar-and-babanrao-gholap-join-bjp-party/articleshow/121908291.cms</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/photo-gallery-who-is-ias-arvind-chauhan-shamli-dm-sat-on-ground-to-listen-70-year-old-woman-complaint/2813524</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>Pune News : पुणे जिल्हा 'शत प्रतिशत' भाजप..? अजित पवारांची आणि पवार कुटुंबाची सद्दी संपणार?</t>
+          <t>तीन प्रदेशों के भाजपा अध्यक्ष तय - Naya India-Hindi News, Latest Hindi News, Breaking News, Hindi Samachar</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/sanjay-jagtap-joins-bjp-in-the-presence-of-bjp-state-president-ravindra-chavan/articleshow/122572770.cms</t>
+          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
+          <t>महाराष्ट्र BJP को मिला नया अध्यक्ष, रवींद्र चव्हाण बने प्रदेश प्रमुख</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
+          <t>Pune bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/states/ex-minister-ravindra-chavan-is-bjps-new-maharashtra-unit-chief</t>
+          <t>https://m.economictimes.com/news/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/articleshow/121904713.cms</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Proud Of Hindi, No Red Carpet For English, Says Maharashtra CM Devendra Fadnavis (VIDEO)</t>
+          <t>Ahead of civic polls, Maharashtra BJP chief stakes claim for KDMC mayor's post</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/proud-of-hindi-no-red-carpet-for-english-says-maharashtra-cm-devendra-fadnavis-video</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Bodies of Pahalgam terror attack victims reach Maharashtra: CM Fadnavis offers final respect to 6 victims b...</t>
+          <t>Former Cricketer Kedar Jadhav Joins BJP</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
+          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के शिरडी में BJP का दो दिवसीय अधिवेशन शुरू, अगले प्रदेश अध्यक्ष की हो सकती है घोषणा,जानें कौन आगे</t>
+          <t>Ahead of local body polls, BJP finalises names of 22 district presidents</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>नए राष्ट्रीय अध्यक्ष को लेकर BJP आलाकमान और संघ के बीच फंसा पेच, इन राज्यों में बदलेगा प्रदेश नेतृत्व</t>
+          <t>Ex-Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/deadlock-between-bjp-high-command-and-rss-over-news-national-president-continues-ntc-rptc-2275062-2025-06-29</t>
+          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>रविंद्र जडेजा का बिहार से क्या रिश्ता? 'क्रिकेट गुरु' महेंद्र सिंह चौहान से महेंद्र सिंह धोनी तक का सफर</t>
+          <t>BJP holds meeting of former MPs and MLAs ahead of local body polls in Maharashtra</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा के नए बॉस बने रवींद्र चौहान, जानिए कौन हैं निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
+          <t>Ahead of BMC polls 3-term MLA Ameet Satam named new Mumbai BJP chief</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/politician-becomes-new-boss-of-maharashtra-bjp-know-who-is-the-president-ravindra-chauhan/1240488/</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/25/bom2-mh-mumbai-bjp-satam.html</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Air India Plane Crash: प्लेन की क्रू मेंबर का निधन, रोशनी सोंघरे की विमान हादसे में गई जान</t>
+          <t>Ex-Maharashtra minister Cong leader Suresh Warpudkar joins BJP</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/07/29/bes35-mh-ex-minister-bjp.html</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>कौन हैं IAS अरविंद चौहान? इंसानियत की मिसाल पेश की, यूपी के इस डीएम की हर तरफ हो रही तारीफ</t>
+          <t>BJP MLA Amit Satam announced as president of Mumbai unit ahead of BMC polls</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/photo-gallery-who-is-ias-arvind-chauhan-shamli-dm-sat-on-ground-to-listen-70-year-old-woman-complaint/2813524</t>
+          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>तीन प्रदेशों के भाजपा अध्यक्ष तय - Naya India-Hindi News, Latest Hindi News, Breaking News, Hindi Samachar</t>
+          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP को मिला नया अध्यक्ष, रवींद्र चव्हाण बने प्रदेश प्रमुख</t>
+          <t>BJP Strengthens Roots in Vidarbha: 313 Mandals Formed, 275 Presidents Appointed</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-strengthens-roots-in-vidarbha-313-mandals-formed-275-presidents-appointed/articleshow/120463852.cms</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Former Cricketer Kedar Jadhav Joins BJP</t>
+          <t>BJP To Get New Nagpur City Chief Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-to-get-new-nagpur-city-chief-ahead-of-local-body-polls/articleshow/120741284.cms</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Ahead of civic polls, Maharashtra BJP chief stakes claim for KDMC mayor's post</t>
+          <t>Pune: CM Fadnavis Inaugurates Mohol's 24/7 Public Office, Hails Him as a Crisis-Time Leader</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
+          <t>https://www.punekarnews.in/pune-cm-fadnavis-inaugurates-mohols-24-7-public-office-hails-him-as-a-crisis-time-leader/</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>3 term MLA Ameet Satam named BJP Mumbai president ahead of BMC polls</t>
+          <t>केडीएमसी- डॉ. नानासाहेब धर्माधिकारी प्रतिष्ठान कडून स्वच्छता अभियान</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/3-term-mla-ameet-satam-named-bjp-mumbai-president-ahead-of-bmc-polls/ar-AA1L97Xi</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Ahead of BMC polls 3-term MLA Ameet Satam named new Mumbai BJP chief</t>
+          <t>Pandharpur Wari 2025 | डोंबिवलीहून पंढरपूरला निघाली सायकलने दिंडी</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/25/bom2-mh-mumbai-bjp-satam.html</t>
+          <t>https://pudhari.news/maharashtra/thane/pandharpur-wari-2025-dindi-left-for-pandharpur-by-bicycle-from-dombivli-ar84</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>Ex-Maharashtra minister Cong leader Suresh Warpudkar joins BJP</t>
+          <t>BJP Confusion Over Sudhakar Badgujar's Induction: Bawankule Unaware of Former Sena (UBT) Leader's Entry</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/29/bes35-mh-ex-minister-bjp.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>BJP MLA Amit Satam announced as president of Mumbai unit ahead of BMC polls</t>
+          <t>Pune bridge collapse: New bridge sanctioned a year ago but work order came on June 10 | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
+          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>BJP Confusion Over Sudhakar Badgujar's Induction: Bawankule Unaware of Former Sena (UBT) Leader's Entry</t>
+          <t>Ahead of Thackeray reunion, BJP’s Rane claims Uddhav harassed Raj, blames him for Shiv Sena’s downfall</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jul/01/ahead-of-thackeray-reunion-bjps-rane-claims-uddhav-harassed-raj-blames-him-for-shiv-senas-downfall</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Fadnavis Backs Induction Of Shiv Sena (UBT) Leader Earlier Called ‘Anti-National’ By BJP</t>
+          <t>Centre removes Turkish firm Celebi from ground handling work at Mumbai and Delhi airports</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/fadnavis-backs-induction-of-shiv-sena-ubt-leader-earlier-called-anti-national-by-bjp-1886129</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>Pune bridge collapse: New bridge sanctioned a year ago but work order came on June 10 | Latest News India - Hindustan Times</t>
+          <t>HC upholds BJP MLA’s victory, says ‘honest’ disclosure of second marriage permissible in his community won’t flout rules</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
+          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
         </is>
       </c>
     </row>
@@ -6059,60 +6059,60 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Amit Satam BJP Mumbai | अमित साटम यांची मुंबई भाजपच्या अध्यक्षपदी नियुक्ती; प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घोषणा</t>
+          <t>कोकणात शरद पवारांच्या राष्ट्रवादीत भूकंप! उदय सामंतांना होमग्राऊंडवर नितेश राणेंचा दे धक्का, बडा नेता पळवला</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://policenama.com/amit-satam-bjp-mumbai-amit-satam-appointed-as-mumbai-bjp-president-announcement-by-state-president-ravindra-chavan/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-nitesh-rane-reveals-major-political-defection-in-ratnagiri-as11</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>कोकणात शरद पवारांच्या राष्ट्रवादीत भूकंप! उदय सामंतांना होमग्राऊंडवर नितेश राणेंचा दे धक्का, बडा नेता पळवला</t>
+          <t>Sharad Pawar NCP : तळ कोकणात राजकीय भूकंप? शरद पवारांना मोठा धक्का! एकमेव नेत्यानेही साथ सोडत केला भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-nitesh-rane-reveals-major-political-defection-in-ratnagiri-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-with-hundreds-of-supporters-major-blow-to-sharad-pawars-ncp-in-konkan-as11</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>Sharad Pawar NCP : तळ कोकणात राजकीय भूकंप? शरद पवारांना मोठा धक्का! एकमेव नेत्यानेही साथ सोडत केला भाजप प्रवेश</t>
+          <t>उद्धव ठाकरे गटाला मालवणमध्ये भाजपचा मोठा धक्का; तीन नगरसेवकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-with-hundreds-of-supporters-major-blow-to-sharad-pawars-ncp-in-konkan-as11</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/thackeray-sena-setback-three-malvan-councilors-join-bjp-mk94</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे गटाला मालवणमध्ये भाजपचा मोठा धक्का; तीन नगरसेवकांचा भाजपात प्रवेश</t>
+          <t>BJP Politics : रत्नागिरी भाजप जिल्हाध्यक्षपदाच्या रेसमध्ये सावंतासह चौघे; कोणाला मिळणार संधी? नावे झाली पाकिट बंद,धाकधूकही वाढवली</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/thackeray-sena-setback-three-malvan-councilors-join-bjp-mk94</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-south-ratnagiri-district-president-selection-by-state-office-as11</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BJP Politics : रत्नागिरी भाजप जिल्हाध्यक्षपदाच्या रेसमध्ये सावंतासह चौघे; कोणाला मिळणार संधी? नावे झाली पाकिट बंद,धाकधूकही वाढवली</t>
+          <t>BJP Politics : रायगड उत्तरमध्ये जुनाच चेहरा, दक्षिणमध्ये नव्याला संधी; अविनाश कोळी आणि धैर्यशील पाटलांच्या निवडीने भाजपला बळ</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-south-ratnagiri-district-president-selection-by-state-office-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/avinash-koli-and-dhairyashil-patil-appointed-bjp-raigad-district-presidents-north-south</t>
         </is>
       </c>
     </row>
@@ -6179,96 +6179,108 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : 'फक्त निवडणूक डोळ्यासमोर ठेवून योजना आणल्या की..' ; रोहित पवारांचा टोला!</t>
+          <t>Maharashtra BJP: अखेर प्रतीक्षा संपली! बावनकुळेंनंतर भाजपला नवा धडाकेबाज प्रदेशाध्यक्ष मिळाला</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-may-2025-vaishnavi-hagawane-case-pune-court-update-police-custody-character-assassination-allegations-sharad-pawar-devendra-fadnavis-bjp-maharashtra-strategy-gram-panchayat-to-assembly-obc-movement-manoj-jarange-patil-laxman-hake</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-appointed-bjp-maharashtra-new-president-dk88</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>आगामी निवडणुकीत भाजपची नजर ५१ टक्के मतांवर!</t>
+          <t>Ravindra Chavan : चव्हाण पेलणार का आव्हान!</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/new-bjp-state-president-ravindra-chavan-comments-on-upcoming-local-body-elections-in-loksatta-lok-samvad-program-ssb-93-5224541/</t>
+          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>अवजड वाहतूक करणाऱ्या वाहन चालकांचा संप मागे</t>
+          <t>आगामी निवडणुकीत भाजपची नजर ५१ टक्के मतांवर!</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/new-bjp-state-president-ravindra-chavan-comments-on-upcoming-local-body-elections-in-loksatta-lok-samvad-program-ssb-93-5224541/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
+          <t>विधानसभा निवडणुकीत बंडखोरी करणाऱ्या नेत्याचे निलंबन भाजपकडून रद्द, राणेंची डोकेदुखी वाढणार?</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-revokes-vishal-parabs-suspension-for-rebelling-in-assembly-elections-will-ranes-headache-increase-a-a301/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>अवजड वाहतूक करणाऱ्या वाहन चालकांचा संप मागे</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/2692193</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>BJP Gears Up for Maharashtra Civic Polls, Holds Meet with Former MPs, MLAs</t>
+          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP, Shinde-Led Sena Hold Separate Meetings As Calls To Contest Local Elections Solo</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-shinde-led-sena-hold-separate-meetings-as-calls-to-contest-local-elections-solo-grow-louder</t>
+          <t>https://www.ptinews.com/press-release/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/2692193</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
+          <t>BJP Gears Up for Maharashtra Civic Polls, Holds Meet with Former MPs, MLAs</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>Maharashtra Politics: BJP, Shinde-Led Sena Hold Separate Meetings As Calls To Contest Local Elections Solo</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-shinde-led-sena-hold-separate-meetings-as-calls-to-contest-local-elections-solo-grow-louder</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B488"/>
+  <dimension ref="A1:B491"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,72 +455,72 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Former Minister Ravindra Chavan appointed working president of Maharashtra BJP</t>
+          <t>BJP names Ravindra Chavan as state unit chief, with an eye on MMR | Mumbai news</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp/article69089769.ece</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
+          <t>Former Minister Ravindra Chavan appointed working president of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp/article69089769.ece</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
+          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888547</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to head Maha BJP, says Bawankule</t>
+          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://www.deccanchronicle.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888547</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>BJP names Ravindra Chavan as state unit chief, with an eye on MMR | Mumbai news</t>
+          <t>Ravindra Chavan set to head Maha BJP, says Bawankule</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>The man who could be next Maharashtra BJP chief: Why Ravindra Chavan was appointed party’s working president</t>
+          <t>Maharashtra: Ravindra Chavan to be declared state BJP chief Tuesday, files nomination</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-9775047/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ravindra-chavan-to-be-declared-state-bjp-chief-tuesday-files-nomination-10098263/</t>
         </is>
       </c>
     </row>
@@ -563,24 +563,24 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BJP mayor needed to remove the stagnation in Kalyan-Dombivli’s development, says BJP Maharashtra presiden</t>
+          <t>BJP appoints Maratha face as its next Maharashtra president: Who is Ravindra Chavan?</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
+          <t>https://indianexpress.com/article/political-pulse/bjp-appoints-maratha-maharashtra-president-ravindra-chavan-10099887/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Maharashtra: Ravindra Chavan to be declared state BJP chief Tuesday, files nomination</t>
+          <t>BJP mayor needed to remove the stagnation in Kalyan-Dombivli’s development, says BJP Maharashtra presiden</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ravindra-chavan-to-be-declared-state-bjp-chief-tuesday-files-nomination-10098263/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
         </is>
       </c>
     </row>
@@ -599,12 +599,12 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BJP appoints Maratha face as its next Maharashtra president: Who is Ravindra Chavan?</t>
+          <t>The man who could be next Maharashtra BJP chief: Why Ravindra Chavan was appointed party’s working president</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/bjp-appoints-maratha-maharashtra-president-ravindra-chavan-10099887/</t>
+          <t>https://indianexpress.com/article/political-pulse/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-9775047/</t>
         </is>
       </c>
     </row>
@@ -707,12 +707,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed state BJP president: At party meeting, Fadnavis, Rijiju take aim at Oppn</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/ravindra-chavan-appointed-state-bjp-president-at-party-meeting-fadnavis-rijiju-take-aim-at-oppn-10100719/</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-bjp-working-president-ravindra-chavan-devendra-fadnavis-chandrasekhar-bawankule-2663456-2025-01-11</t>
         </is>
       </c>
     </row>
@@ -731,12 +731,12 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP working president</t>
+          <t>Ravindra Chavan appointed state BJP president: At party meeting, Fadnavis, Rijiju take aim at Oppn</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-bjp-working-president-ravindra-chavan-devendra-fadnavis-chandrasekhar-bawankule-2663456-2025-01-11</t>
+          <t>https://indianexpress.com/article/cities/mumbai/ravindra-chavan-appointed-state-bjp-president-at-party-meeting-fadnavis-rijiju-take-aim-at-oppn-10100719/</t>
         </is>
       </c>
     </row>
@@ -803,60 +803,60 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Who are the BJP's 9 new state chiefs? Ravindra Chavan to PVN Madhav</t>
+          <t>Who Is Ravindra Chavan? Strong Maratha Face From Thane Appointed As New Maharashtra BJP Chief</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/who-are-the-bjps-9-new-state-chiefs-ravindra-chavan-to-pvn-madhav-11751449724866.html</t>
+          <t>https://www.news18.com/politics/who-is-ravindra-chavan-strong-maratha-face-from-thane-appointed-as-new-maharashtra-bjp-chief-9415063.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan? Strong Maratha Face From Thane Appointed As New Maharashtra BJP Chief</t>
+          <t>Who are the BJP's 9 new state chiefs? Ravindra Chavan to PVN Madhav</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/who-is-ravindra-chavan-strong-maratha-face-from-thane-appointed-as-new-maharashtra-bjp-chief-9415063.html</t>
+          <t>https://www.livemint.com/politics/news/who-are-the-bjps-9-new-state-chiefs-ravindra-chavan-to-pvn-madhav-11751449724866.html</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan unanimously elected as new Maharashtra BJP president</t>
+          <t>Four-time MLA Ravindra Chavan appointed Maharashtra BJP president</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-unanimously-elected-as-new-maharashtra-bjp-president-23582746</t>
+          <t>https://www.indiatoday.in/india/story/four-time-mla-ravindra-chavan-appointed-maharashtra-bjp-president-2749208-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>How new Maharashtra BJP chief Ravindra Chavan, Fadnavis loyalist with RSS roots, could rattle Shinde Sena</t>
+          <t>Ex-minister Ravindra Chavan unanimously elected as new Maharashtra BJP president</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://theprint.in/politics/how-new-maharashtra-bjp-chief-ravindra-chavan-fadnavis-loyalist-with-rss-roots-could-rattle-shinde-sena/2676017/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-unanimously-elected-as-new-maharashtra-bjp-president-23582746</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Four-time MLA Ravindra Chavan appointed Maharashtra BJP president</t>
+          <t>How new Maharashtra BJP chief Ravindra Chavan, Fadnavis loyalist with RSS roots, could rattle Shinde Sena</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/four-time-mla-ravindra-chavan-appointed-maharashtra-bjp-president-2749208-2025-07-02</t>
+          <t>https://theprint.in/politics/how-new-maharashtra-bjp-chief-ravindra-chavan-fadnavis-loyalist-with-rss-roots-could-rattle-shinde-sena/2676017/</t>
         </is>
       </c>
     </row>
@@ -887,24 +887,24 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Gadkari on Hindutva: Hindutva Not Anti-Religion, True Secularism Treats All Faiths Equally</t>
+          <t>Who Is Ravindra Chavan, New Maharashtra BJP Chief, Close Confidant Of CM Devendra Fadnavis?</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
+          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan, New Maharashtra BJP Chief, Close Confidant Of CM Devendra Fadnavis?</t>
+          <t>Gadkari on Hindutva: Hindutva Not Anti-Religion, True Secularism Treats All Faiths Equally</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
+          <t>https://www.deccanherald.com/india/maharashtra/hindutva-not-against-any-religion-treating-all-religions-equally-is-true-secularism-nitin-gadkari-3611385</t>
         </is>
       </c>
     </row>
@@ -935,204 +935,204 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Ex-Minister Ravindra Chavan Appointed As Working President of BJP in Maharashtra</t>
+          <t>Viral list of dist chiefs fake: BJP; warns of police action</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/ex-minister-ravindra-chavan-appointed-as-working-state-president-of-bjp-in-maharashtra</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/viral-list-of-dist-chiefs-fake-bjp-warns-of-police-action/articleshow/121252533.cms</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Justice Chavan Calls For National Judicial Service, Reforms To Address Vacancies In Judiciary</t>
+          <t>Ex-Minister Ravindra Chavan Appointed As Working President of BJP in Maharashtra</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
+          <t>https://www.republicworld.com/india/ex-minister-ravindra-chavan-appointed-as-working-state-president-of-bjp-in-maharashtra</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan files nomination for post of Maharashtra BJP president</t>
+          <t>Justice Chavan Calls For National Judicial Service, Reforms To Address Vacancies In Judiciary</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Elected Maharashtra BJP President Unanimously</t>
+          <t>Ex-minister Ravindra Chavan files nomination for post of Maharashtra BJP president</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/ravindra-chavan-elected-maharashtra-bjp-president-unanimously</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
+          <t>Ravindra Chavan Elected Maharashtra BJP President Unanimously</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
+          <t>https://www.republicworld.com/india/ravindra-chavan-elected-maharashtra-bjp-president-unanimously</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>How Ravindra Chavan brought Congress's Kunal Patil into BJP fold the day he became Maharashtra party chief</t>
+          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
+          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
+          <t>Money lender booked for suicide abetment of debtor</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://www.inkl.com/news/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/money-lender-booked-for-suicide-abetment-of-debtor/articleshow/121603123.cms</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Indian Political Highlights | Former minister Ravindra Chavan appointed as Maharashtra BJP working president</t>
+          <t>How Ravindra Chavan brought Congress's Kunal Patil into BJP fold the day he became Maharashtra party chief</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
+          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Amit Shah’s Maharashtra Visit: BJP Gears Up for Local Body Polls with Key Outreach</t>
+          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
+          <t>https://www.inkl.com/news/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP President</t>
+          <t>Indian Political Highlights | Former minister Ravindra Chavan appointed as Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
+          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
+          <t>Ahead of Thackeray reunion, BJP’s Rane claims Uddhav harassed Raj, blames him for Shiv Sena’s downfall</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jul/01/ahead-of-thackeray-reunion-bjps-rane-claims-uddhav-harassed-raj-blames-him-for-shiv-senas-downfall</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>58 BJP chiefs of districts named | Mumbai News</t>
+          <t>Once UAPA accused over Dawood ‘links’, Sena (UBT) leader finds place in BJP ahead of Nashik civic polls</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
+          <t>https://indianexpress.com/article/political-pulse/uapa-accused-dawood-links-sena-ubt-leader-in-bjp-nashik-civic-polls-10074232/</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
+          <t>Amit Shah’s Maharashtra Visit: BJP Gears Up for Local Body Polls with Key Outreach</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.dynamitenews.com/story/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
+          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Former Congress MLA Kunal Patil joins BJP</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP President</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/former-congress-mla-kunal-patil-joins-bjp-10100556/</t>
+          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Becomes Maharashtra BJP Chief Unopposed</t>
+          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://english.dainikjagranmpcg.com/politics/ravindra-chavan-becomes-maharashtra-bjp-chief-unopposed/article-2343</t>
+          <t>https://www.dynamitenews.com/story/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BJP chief in Maharashtra brings MNS union workers into party</t>
+          <t>58 BJP chiefs of districts named | Mumbai News</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
+          <t>Ravindra Chavan Becomes Maharashtra BJP Chief Unopposed</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ameet-satam-becomes-bjp-s-new-mumbai-chief-ahead-of-bmc-polls-who-is-he/ar-AA1L9t6x</t>
+          <t>https://english.dainikjagranmpcg.com/politics/ravindra-chavan-becomes-maharashtra-bjp-chief-unopposed/article-2343</t>
         </is>
       </c>
     </row>
@@ -1151,120 +1151,120 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Mumbai Confidential: Wait for the new chief</t>
+          <t>"Double-engine govt working in people's best interests": New Maharashtra BJP chief Ravindra Chavan</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-bjp-maharashtra-new-chief-10055191/</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Indrayani river bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
+          <t>After poll drubbing, Prithviraj Chavan may replace Patole in Maharashtra Congress rejig</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jan/14/after-poll-drubbing-prithviraj-chavan-may-replace-patole-in-maharashtra-congress-rejig</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Dombivli residents demand clarity as railways issue eviction notices</t>
+          <t>Mumbai Confidential: Wait for the new chief</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
+          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-bjp-maharashtra-new-chief-10055191/</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mumbai Confidential: Brother trouble</t>
+          <t>Indrayani river bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
+          <t>https://www.mid-day.com/news/india-news/article/indrayani-river-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure-23571125</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>BJP’s Sankalp to Siddhi campaign to begin this week</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bjps-sankalp-to-siddhi-campaign-to-begin-this-week/articleshow/121606429.cms</t>
+          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>IndiGo’s AGILE Employees Secure Record Salary Hike in Historic Agreement with Union</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Pune Congress leader Sanjay Jagtap joins BJP</t>
+          <t>Bodies Of Pahalgam Terror Attack Victims From Maharashtra Brought To Mumbai</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
+          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>IndiGo’s AGILE Employees Secure Record Salary Hike in Historic Agreement with Union</t>
+          <t>Dombivli MLA Ravindra Chavan Takes Charge as New Maharashtra BJP President, Replacing Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
+          <t>https://www.lokmattimes.com/maharashtra/dombivli-mla-ravindra-chavan-takes-charge-as-new-maharashtra-bjp-president-replacing-chandrashekhar-bawankule-a475/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
+          <t>Maharashtra Politics: BJP State Chief Ravindra Chavan Meets PM Modi, Outlines Party’s Expansion Plan</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-diary-sunday-dossier-23591113</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-state-chief-ravindra-chavan-meets-pm-modi-outlines-partys-expansion-plan</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Bodies Of Pahalgam Terror Attack Victims From Maharashtra Brought To Mumbai</t>
+          <t>Ravindra Chavan: A Visionary Leader Strengthening Maharashtra BJP's Political Landscape</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
+          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Double-Engine Govt Working In Peoples Best Interests: New Maharashtra BJP Chief Ravindra Chavan</t>
+          <t>Ravindra Chavan, Ex-Minister, Files Nomination For Maharashtra BJP Chief Election, Likely To Win Unopposed</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan</t>
+          <t>https://www.thedailyjagran.com/maharashtra/ravindra-chavan-exminister-files-nomination-for-maharashtra-bjp-chief-election-likely-to-win-unopposed-10249053</t>
         </is>
       </c>
     </row>
@@ -1439,72 +1439,72 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Ravindra Chavan, Ex-Minister, Files Nomination For Maharashtra BJP Chief Election, Likely To Win Unopposed</t>
+          <t>Mumbai: Over 2,000 IndiGo Airline Employees Join BJP Ahead Of BMC Election</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/ravindra-chavan-exminister-files-nomination-for-maharashtra-bjp-chief-election-likely-to-win-unopposed-10249053</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-over-2000-indigo-airline-employees-join-bjp-ahead-of-bmc-election</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Mumbai: Over 2,000 IndiGo Airline Employees Join BJP Ahead Of BMC Election</t>
+          <t>BJP Appoints Former Minister Ravindra Chavan As Maharashtra Units Working President</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-over-2000-indigo-airline-employees-join-bjp-ahead-of-bmc-election</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-appoints-former-minister-ravindra-chavan-as-maharashtra-units-working-president</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>BJP Appoints Former Minister Ravindra Chavan As Maharashtra Units Working President</t>
+          <t>Maharashtra: BJP Poaches Key Leaders From Rival Parties In Palghar, Strengthens Hold Ahead Of Upcoming</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-appoints-former-minister-ravindra-chavan-as-maharashtra-units-working-president</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-poaches-key-leaders-from-rival-parties-in-palghar-strengthens-hold-ahead-of-upcoming-elections</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP Poaches Key Leaders From Rival Parties In Palghar, Strengthens Hold Ahead Of Upcoming</t>
+          <t>Ravindra Chavan appointed as BJP state president of Maharashtra</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-poaches-key-leaders-from-rival-parties-in-palghar-strengthens-hold-ahead-of-upcoming-elections</t>
+          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed as BJP state president of Maharashtra</t>
+          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
+          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
+          <t>Maharashtra Politics: Security Downgrade For Shinde Faction Leaders Sparks Tensions Between Fadnavis And</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-security-downgrade-for-shinde-faction-leaders-sparks-tensions-between-fadnavis-and-shinde</t>
         </is>
       </c>
     </row>
@@ -1523,1092 +1523,1092 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Who Is Ameet Satam? Three-Term MLA From Andheri West Appointed As President Of Mumbai BJP Unit</t>
+          <t>Dombivali Bandh Today In Mourning After Pahalgam Terror Attack Claims 3 Local Lives</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/who-is-ameet-satam-three-term-mla-from-andheri-west-appointed-as-president-of-mumbai-bjp-unit</t>
+          <t>https://www.freepressjournal.in/mumbai/dombivali-bandh-today-in-mourning-after-pahalgam-terror-attack-claims-3-local-lives</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
+          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
+          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Maharashtra News: BJP Sets Up 1,221 Mandals Across State, Appoints 963 Presidents Ahead Of Local Body Polls</t>
+          <t>Maharashtra News: BJP Warns Of Legal Action Over Fake List Of 81 District Presidents Circulating On Social</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-sets-up-1221-mandals-across-state-appoints-963-presidents-ahead-of-local-body-polls</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-warns-of-legal-action-over-fake-list-of-81-district-presidents-circulating-on-social-media</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
+          <t>महाराष्ट्र में निकाय चुनाव से पहले BJP का बड़ा प्लान, पूर्व सांसदों और विधायकों</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
+          <t>Ravindra Chavan: बीजेपी ने पूर्व मंत्री रवींद्र चव्हाण को बनाया महाराष्ट्र का कार्यकारी अध्यक्ष, जानें पूरा सफर</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Pune: Kundmala Bridge Collapses 5 Days After Rs 8 Crore Renovation Approval; Sanjay Raut Alleges Corruption, Claims Only Rs 80,000 Was Actually Sanctioned</t>
+          <t>महाराष्ट्र: BJP ने मराठा फेस रवींद्र चव्हाण पर क्यों जताया भरोसा? जानें पूरा सफर</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-kundmala-bridge-collapses-5-days-after-rs-8-crore-renovation-approval-sanjay-raut-alleges-corruption-claims-only-rs-80000-was-actually-sanctioned/</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-why-did-bjp-express-confidence-in-maratha-face-ravindra-chavan-know-journey-3054753.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Maharashtra News: BJP Warns Of Legal Action Over Fake List Of 81 District Presidents Circulating On Social</t>
+          <t>Ravindra Chavan Latest News, Updates in Hindi | रवींद्र चव्हाण के समाचार और अपडेट</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-warns-of-legal-action-over-fake-list-of-81-district-presidents-circulating-on-social-media</t>
+          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Maha: Sudhakar Badgujar, who faced charges of 'links' with underworld, joins BJP</t>
+          <t>कौन होगा महाराष्ट्र भाजपा का नया चीफ? रविंद्र चव्हाण का नाम लगभग तय, जानिए इसके पीछे क्या वजह</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maha-sudhakar-badgujar-who-faced-charges-of-links-with-underworld-joins-bjp</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Over 2,000 IndiGo employees join BJP ahead of BMC elections in Mumbai</t>
+          <t>मराठा चेहरा, कोंकण में पलटी बाजी; बीजेपी ने क्यों जताया रवींद्र चव्हाण पर भरोसा</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/over-2000-indigo-employees-join-bjp-ahead-of-bmc-elections-in-mumbai</t>
+          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में निकाय चुनाव से पहले BJP का बड़ा प्लान, पूर्व सांसदों और विधायकों</t>
+          <t>महाराष्ट्र बीजेपी अध्यक्ष के लिए ये नाम लगभग तय, जानें क्यों माने जाते हैं प्रबल</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: बीजेपी ने पूर्व मंत्री रवींद्र चव्हाण को बनाया महाराष्ट्र का कार्यकारी अध्यक्ष, जानें पूरा सफर</t>
+          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए बॉस, CM फडणवीस के साथ भरा नामांकन, जानें कौन हैं?</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-bjp-will-get-new-president-filed-nomination-know-who-is-ravindra-chavan-19711885</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: BJP ने मराठा फेस रवींद्र चव्हाण पर क्यों जताया भरोसा? जानें पूरा सफर</t>
+          <t>महाराष्ट्र से रविंद्र चव्हाण तो एमपी से खंडेलवाल बने बीजेपी के नए प्रदेश अध्यक्ष, यहां जानें सारी डिटेल्स</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-why-did-bjp-express-confidence-in-maratha-face-ravindra-chavan-know-journey-3054753.html</t>
+          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Latest News, Updates in Hindi | रवींद्र चव्हाण के समाचार और अपडेट</t>
+          <t>Maharashtra BJP Politics: महाराष्ट्र में बड़ी जीत के बाद इस नेता को प्रदेश अध्यक्ष बना सकती है BJP, फडणवीस के हैं करीबी</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
+          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए बॉस, CM फडणवीस के साथ भरा नामांकन, जानें कौन हैं?</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र भाजपा के कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा ने किया एलान</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-bjp-will-get-new-president-filed-nomination-know-who-is-ravindra-chavan-19711885</t>
+          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-23865140.html</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>मराठा चेहरा, कोंकण में पलटी बाजी; बीजेपी ने क्यों जताया रवींद्र चव्हाण पर भरोसा</t>
+          <t>रवींद्र चव्हाण की जीवनी | Ravindra Chavan Biography in Hindi</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
+          <t>https://politalks.news/ravindra-chavan-biography-in-hindi</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>कौन होगा महाराष्ट्र भाजपा का नया चीफ? रविंद्र चव्हाण का नाम लगभग तय, जानिए इसके पीछे क्या वजह</t>
+          <t>Maharashtra: पूर्व मंत्री रवीन्द्र चव्हाण बने महाराष्ट्र भाजपा के नए अध्यक्ष, सीएम देवेंद्र फडणवीस के हैं करीब</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
+          <t>https://www.amarujala.com/india-news/ex-minister-ravindra-chavan-is-bjp-s-new-maharashtra-chief-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी अध्यक्ष के लिए ये नाम लगभग तय, जानें क्यों माने जाते हैं प्रबल</t>
+          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के नए प्रदेश अध्यक्ष, जानें उनका राजनीतिक सफर</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>महाराष्ट्र से रविंद्र चव्हाण तो एमपी से खंडेलवाल बने बीजेपी के नए प्रदेश अध्यक्ष, यहां जानें सारी डिटेल्स</t>
+          <t>Ravindra Chavan: 4 बार के विधायक, मराठा नेता, नतीजे देने की क्षमता, महाराष्ट्र BJP के नए कार्यकारी अध्यक्ष रवींद्र चव्हाण कौन?</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Maharashtra BJP Politics: महाराष्ट्र में बड़ी जीत के बाद इस नेता को प्रदेश अध्यक्ष बना सकती है BJP, फडणवीस के हैं करीबी</t>
+          <t>महाराष्ट्र भाजपा को मिला नया ‘कप्तान’, जानें कौन हैं प्रदेश अध्यक्ष रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
+          <t>https://www.patrika.com/mumbai-news/ravindra-chavan-became-maharashtra-bjp-president-know-who-is-he-19715228</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र भाजपा के कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा ने किया एलान</t>
+          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए अध्यक्ष, किरेन रिजिजू की मौजूदगी में भरा नामांकन - Ravindra Chavan will be the new president of Maharashtra BJP nomination filed in the presence of Kiren Rijiju</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-23865140.html</t>
+          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Maharashtra: पूर्व मंत्री रवीन्द्र चव्हाण बने महाराष्ट्र भाजपा के नए अध्यक्ष, सीएम देवेंद्र फडणवीस के हैं करीब</t>
+          <t>सीएम देवेंद्र फडणवीस के करीबी रवींद्र चव्हाण बने महाराष्ट्र BJP के अध्यक्ष, जानें</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/ex-minister-ravindra-chavan-is-bjp-s-new-maharashtra-chief-2025-07-01</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-elected-maharashtra-bjp-president-ann-2972075</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: रवींद्र चव्हाण बने महाराष्‍ट्र भाजपा के नए अध्‍यक्ष, पद संभालते के बाद क्‍या बोले?</t>
+          <t>महाराष्ट्र BJP प्रदेश अध्यक्ष का नाम हो गया तय, कल शाम 5 बजे होगी घोषणा</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के नए प्रदेश अध्यक्ष, जानें उनका राजनीतिक सफर</t>
+          <t>महाराष्ट्र: रवींद्र चव्हाण बने BJP कार्यकारी प्रदेश अध्यक्ष, क्या छिन गई चंद्रशेखर</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 4 बार के विधायक, मराठा नेता, नतीजे देने की क्षमता, महाराष्ट्र BJP के नए कार्यकारी अध्यक्ष रवींद्र चव्हाण कौन?</t>
+          <t>Maharashtra BJP President: रवींद्र चव्हाण बने महाराष्‍ट्र भाजपा के नए अध्‍यक्ष, पद संभालते के बाद क्‍या बोले?</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा को मिला नया ‘कप्तान’, जानें कौन हैं प्रदेश अध्यक्ष रवींद्र चव्हाण?</t>
+          <t>कौन हैं रविंद्र चव्हाण जिन्हें बीजेपी ने पूरा महाराष्ट्र 'सौंप' दिया है? | The Lallantop</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/ravindra-chavan-became-maharashtra-bjp-president-know-who-is-he-19715228</t>
+          <t>https://www.thelallantop.com/india/post/bjp-appoints-maratha-face-as-its-next-maharashtra-president-who-is-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए अध्यक्ष, किरेन रिजिजू की मौजूदगी में भरा नामांकन - Ravindra Chavan will be the new president of Maharashtra BJP nomination filed in the presence of Kiren Rijiju</t>
+          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, मुंबई महानगर क्षेत्र चुनाव में बदल सकते हैं समीकरण</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
+          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>सीएम देवेंद्र फडणवीस के करीबी रवींद्र चव्हाण बने महाराष्ट्र BJP के अध्यक्ष, जानें</t>
+          <t>भाजपच्या 81 जिल्हाध्यक्षांची ती यादी फेक, व्हायरल करू नका रविंद्र चव्हाणांकडून इशारा</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-elected-maharashtra-bjp-president-ann-2972075</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP प्रदेश अध्यक्ष का नाम हो गया तय, कल शाम 5 बजे होगी घोषणा</t>
+          <t>पार्षद से भाजपा प्रदेश अध्यक्ष तक… कैसा है महाराष्ट्र बीजेपी के नए अध्यक्ष रवींद्र चव्हाण का...</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
+          <t>https://www.tv9hindi.com/india/ravindra-chavan-new-bjp-maharashtra-president-profile-and-political-career-3369773.html</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: रवींद्र चव्हाण बने BJP कार्यकारी प्रदेश अध्यक्ष, क्या छिन गई चंद्रशेखर</t>
+          <t>Maharashtra BJP President: कौन हैं रविंद्र चव्‍हाण? जिनका महाराष्ट्र BJP प्रदेश अध्यक्ष बनना तय है</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-bjp-president-who-is-ravindra-chavan-going-to-take-over-bjp-state-president-post-1328621.html</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>कौन हैं रविंद्र चव्हाण जिन्हें बीजेपी ने पूरा महाराष्ट्र 'सौंप' दिया है? | The Lallantop</t>
+          <t>WHO IS Ravindra Chavan: कौन हैं रवींद्र चव्हाण?, भाजपा ने क्यों खेला दांव, चंद्रशेखर बावनकुले की जगह ले सकते हैं</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.thelallantop.com/india/post/bjp-appoints-maratha-face-as-its-next-maharashtra-president-who-is-ravindra-chavan</t>
+          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, मुंबई महानगर क्षेत्र चुनाव में बदल सकते हैं समीकरण</t>
+          <t>बीजेपी प्रदेश अध्यक्ष बनते ही कांग्रेस में सेंध... पहले ही दिन रवींद्र चव्हाण ने कराई कुणाल पाटिल की जॉइनिंग</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>भाजपच्या 81 जिल्हाध्यक्षांची ती यादी फेक, व्हायरल करू नका रविंद्र चव्हाणांकडून इशारा</t>
+          <t>Kalyan : 'माझी कपिल पाटील आणि रविंद्र चव्हाण यांच्याशी लढाई' कल्याणच्या माजी भाजपा आमदाराची क्लीप Viral</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
+          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>पार्षद से भाजपा प्रदेश अध्यक्ष तक… कैसा है महाराष्ट्र बीजेपी के नए अध्यक्ष रवींद्र चव्हाण का...</t>
+          <t>महाराष्ट्र बीजेपी की कमान अब रवींद्र चव्हाण के हाथ में, निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/ravindra-chavan-new-bjp-maharashtra-president-profile-and-political-career-3369773.html</t>
+          <t>https://www.tv9hindi.com/india/ravindra-chavan-elected-unopposed-as-maharashtra-bjp-president-3369508.html</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: कौन हैं रविंद्र चव्‍हाण? जिनका महाराष्ट्र BJP प्रदेश अध्यक्ष बनना तय है</t>
+          <t>भाजपा महाराष्ट्र प्रदेश अध्यक्ष पद पर रविंद्र चौहान</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-bjp-president-who-is-ravindra-chavan-going-to-take-over-bjp-state-president-post-1328621.html</t>
+          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>WHO IS Ravindra Chavan: कौन हैं रवींद्र चव्हाण?, भाजपा ने क्यों खेला दांव, चंद्रशेखर बावनकुले की जगह ले सकते हैं</t>
+          <t>BJP News : रवींद्र चव्हाण यांची भाजपच्या महाराष्ट्र कार्यकारी अध्यक्षपदी नियुक्ती</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
+          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>बीजेपी प्रदेश अध्यक्ष बनते ही कांग्रेस में सेंध... पहले ही दिन रवींद्र चव्हाण ने कराई कुणाल पाटिल की जॉइनिंग</t>
+          <t>मोठी बातमी! भाजपाच्या प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavan-appointed-as-bjp-maharashtra-chief-1436143.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Kalyan : 'माझी कपिल पाटील आणि रविंद्र चव्हाण यांच्याशी लढाई' कल्याणच्या माजी भाजपा आमदाराची क्लीप Viral</t>
+          <t>Ravindra Chavan : '.....तर उद्धव ठाकरेंनाही सोबत घेऊ' भाजपा प्रदेशाध्यक्षांचं मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी की कमान अब रवींद्र चव्हाण के हाथ में, निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
+          <t>Ravindra Chavan: 'शिंदे मुख्यमंत्री झाल्यावर वाईट वाटलं', चव्हाण यांनी पहिल्यांदाच सांगितलं नाराजीचं कारण</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/ravindra-chavan-elected-unopposed-as-maharashtra-bjp-president-3369508.html</t>
+          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>भाजपा महाराष्ट्र प्रदेश अध्यक्ष पद पर रविंद्र चौहान</t>
+          <t>Who is Ravindra Chavan | डोंबिवलीचे नगरसेवक ते भाजप प्रदेशाध्यक्ष, जाणून घ्या रविंद्र चव्हाण यांचा राजकीय प्रवास</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/who-is-ravindra-chavan-dombivli-corporator-to-bjp-state-president-political-journey-biography-db79</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>BJP News : रवींद्र चव्हाण यांची भाजपच्या महाराष्ट्र कार्यकारी अध्यक्षपदी नियुक्ती</t>
+          <t>Ravindra Chavan : रविंद्र चव्हाण भाजपाचे नवे प्रदेशाध्यक्ष, किरेन रिजिजू यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
+          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-the-new-maharashtra-state-president-of-bjp-announced-by-minister-kiren-rijiju-gkt-96-5196414/</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>मोठी बातमी! भाजपाच्या प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>Ravindra Chavan : रवींद्र चव्हाण भाजपाच्या महाराष्ट्र प्रदेशाध्यक्षपदी विराजमान, जाणून घ्या कशी आहे त्यांची कारकीर्द?</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavan-appointed-as-bjp-maharashtra-chief-1436143.html</t>
+          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-now-president-of-bjp-maharashtra-state-know-about-his-political-career-scj-81-5196879/</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : '.....तर उद्धव ठाकरेंनाही सोबत घेऊ' भाजपा प्रदेशाध्यक्षांचं मोठं वक्तव्य</t>
+          <t>Ravindra Chavan on Cabinet Reshuffle: महाराष्ट्रात मंत्रिमंडळ फेरबदल होणार? ; भाजप प्रदेशाध्यक्ष रविंद्र चव्हाणांनी स्पष्टच दिलं उत्तर, म्हणाले...</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-cabinet-reshuffle-bjp-ravindra-chavan-statement-political-developments-2025-mahayuti-msr87</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 'शिंदे मुख्यमंत्री झाल्यावर वाईट वाटलं', चव्हाण यांनी पहिल्यांदाच सांगितलं नाराजीचं कारण</t>
+          <t>Ravindra Chavan : 'हरकाम्या' कार्यकर्ता ते भाजप प्रदेश कार्याध्यक्ष; रवींद्र चव्हाण कसे बनले नेत्यांच्या गळ्यातील ताईत?</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/ravindra-chavan-political-journey-from-common-worker-to-bjp-executive-president-rm82-pp82</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Who is Ravindra Chavan | डोंबिवलीचे नगरसेवक ते भाजप प्रदेशाध्यक्ष, जाणून घ्या रविंद्र चव्हाण यांचा राजकीय प्रवास</t>
+          <t>भाजपचा नवा प्रदेशाध्यक्ष कोण? ‘या’ बड्या नेत्याचं नाव निश्चित, उद्या नावाची घोषणा होणार!</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/who-is-ravindra-chavan-dombivli-corporator-to-bjp-state-president-political-journey-biography-db79</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-will-be-maharashtra-state-president-of-bjp-name-will-announce-1st-july-1435245.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रविंद्र चव्हाण भाजपाचे नवे प्रदेशाध्यक्ष, किरेन रिजिजू यांनी केली घोषणा</t>
+          <t>रविंद्र चव्हाण लवकरच भाजपचे नवे प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-the-new-maharashtra-state-president-of-bjp-announced-by-minister-kiren-rijiju-gkt-96-5196414/</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-politics-ravindra-chavan-set-to-be-new-bjp-maharashtra-president-mumbai-print-news-vsd-99-5188808/</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रवींद्र चव्हाण भाजपाच्या महाराष्ट्र प्रदेशाध्यक्षपदी विराजमान, जाणून घ्या कशी आहे त्यांची कारकीर्द?</t>
+          <t>Ravindra Chavan | रविंद्र चव्हाण यांची भाजप महाराष्‍ट्र प्रदेशाध्यक्षपदी निवड!</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-now-president-of-bjp-maharashtra-state-know-about-his-political-career-scj-81-5196879/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-appointed-jp-maharashtra-president</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>डेढ़ लाख मराठी भाषियों के लिए महाराष्ट्र परिषद की स्थापना</t>
+          <t>ब्राह्मण, OBC और मराठा... देवेंद्र फडणवीस का अकाट्य फॉर्मूला, कांग्रेस ही नहीं सहयोगी भी चित!</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/maharashtra-council-established-for-1-5-lakh-marathi-speakers/</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ravindra Chavan on Cabinet Reshuffle: महाराष्ट्रात मंत्रिमंडळ फेरबदल होणार? ; भाजप प्रदेशाध्यक्ष रविंद्र चव्हाणांनी स्पष्टच दिलं उत्तर, म्हणाले...</t>
+          <t>Ravindra Chavan : मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-cabinet-reshuffle-bjp-ravindra-chavan-statement-political-developments-2025-mahayuti-msr87</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : 'हरकाम्या' कार्यकर्ता ते भाजप प्रदेश कार्याध्यक्ष; रवींद्र चव्हाण कसे बनले नेत्यांच्या गळ्यातील ताईत?</t>
+          <t>सांगलीचा आगामी महापौर महायुतीचाच – रविंद्र चव्हाण</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/ravindra-chavan-political-journey-from-common-worker-to-bjp-executive-president-rm82-pp82</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-bjp-ravindra-chavan-confident-next-mayor-in-upcoming-civic-poll-will-be-from-mahayuti-rds-00-5299211/</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>इंदापूर तालुक्यातील प्रवीण माने यांचा रविंद्र चव्हाण यांच्या उपस्थितीत भाजपात प्रवेश</t>
+          <t>Ravindra Chavan : फडणवीसांची औरंगजेबाशी तुलना करताच रविंद्र चव्हाण संतापले, काँग्रेस प्रदेशाध्यक्षांना दिलं उत्तर</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/praveen-mane-from-indapur-tehsil-joined-bjp-in-the-presence-of-ravindra-chavan-svk-88-phm-00-5199118/</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>रविंद्र चव्हाण लवकरच भाजपचे नवे प्रदेशाध्यक्ष</t>
+          <t>BJP News : शहराध्यक्ष कसा असावा ? भाजपा कार्याध्यक्ष रविंद्र चव्हाण यांनी पदाधिकारी-कार्यकर्त्यांचे कान टोचले!</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-politics-ravindra-chavan-set-to-be-new-bjp-maharashtra-president-mumbai-print-news-vsd-99-5188808/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-expresses-expectations-from-bjp-city-district-presidents-jp75</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>भाजपचा नवा प्रदेशाध्यक्ष कोण? ‘या’ बड्या नेत्याचं नाव निश्चित, उद्या नावाची घोषणा होणार!</t>
+          <t>Ravindra Chavan : रविंद्र चव्हाण यांनी प्रदेशाध्यक्ष पदाचा पदभार स्विकारला</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-will-be-maharashtra-state-president-of-bjp-name-will-announce-1st-july-1435245.html</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ravindra Chavan | रविंद्र चव्हाण यांची भाजप महाराष्‍ट्र प्रदेशाध्यक्षपदी निवड!</t>
+          <t>नगरसेवक ते थेट भाजपचे प्रदेशाध्यक्ष… रवींद्र चव्हाण यांच्या कारकिर्दीतील हे टप्पे माहीत आहेत...</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-appointed-jp-maharashtra-president</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-new-maharashtra-bjp-presdent-know-his-journey-1436161.html</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>ब्राह्मण, OBC और मराठा... देवेंद्र फडणवीस का अकाट्य फॉर्मूला, कांग्रेस ही नहीं सहयोगी भी चित!</t>
+          <t>इंदापूर तालुक्यातील प्रवीण माने यांचा रविंद्र चव्हाण यांच्या उपस्थितीत भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
+          <t>https://www.loksatta.com/maharashtra/praveen-mane-from-indapur-tehsil-joined-bjp-in-the-presence-of-ravindra-chavan-svk-88-phm-00-5199118/</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>महाराष्ट्र भाजपची धुरा रवींद्र चव्हाण सांभाळणार, कार्यकारी प्रदेशाध्यक्ष म्हणून नियुक्ती</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
+          <t>https://pudhari.news/national/raviindra-chavhan-appointed-maharashtra-bjp-executive-state-president</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : फडणवीसांची औरंगजेबाशी तुलना करताच रविंद्र चव्हाण संतापले, काँग्रेस प्रदेशाध्यक्षांना दिलं उत्तर</t>
+          <t>अण्णासाहेब डांगे दो बेटों के साथ BJP में शामिल, CM देवेंद्र फडणवीस की मौजूदगी में</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
+          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>सांगलीचा आगामी महापौर महायुतीचाच – रविंद्र चव्हाण</t>
+          <t>Maharashtra Politics: कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण, एकमताने निवड, वाचा सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-bjp-ravindra-chavan-confident-next-mayor-in-upcoming-civic-poll-will-be-from-mahayuti-rds-00-5299211/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>BJP News : शहराध्यक्ष कसा असावा ? भाजपा कार्याध्यक्ष रविंद्र चव्हाण यांनी पदाधिकारी-कार्यकर्त्यांचे कान टोचले!</t>
+          <t>RSS स्वयंसेवक ते BJP प्रदेशाध्यक्ष; ‘अशी’ आहे रवींद्र चव्हाण यांची राजकीय कारकीर्द</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-expresses-expectations-from-bjp-city-district-presidents-jp75</t>
+          <t>https://www.lokmat.com/maharashtra/from-rss-volunteer-to-bjp-state-president-know-about-ravindra-chavan-political-career-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रविंद्र चव्हाण यांनी प्रदेशाध्यक्ष पदाचा पदभार स्विकारला</t>
+          <t>भाजपच्या महाराष्ट्र प्रदेश कार्यकारी अध्यक्षपदी रविंद्र चव्हाण यांची नियुक्ती</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
+          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>नगरसेवक ते थेट भाजपचे प्रदेशाध्यक्ष… रवींद्र चव्हाण यांच्या कारकिर्दीतील हे टप्पे माहीत आहेत...</t>
+          <t>Ravindra Chavan : महापालिका आयुक्तांनी प्रोटोकॉल पाळावा, हक्कभंगाची नोटीस देणार, नांदेडचे</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-new-maharashtra-bjp-presdent-know-his-journey-1436161.html</t>
+          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपची धुरा रवींद्र चव्हाण सांभाळणार, कार्यकारी प्रदेशाध्यक्ष म्हणून नियुक्ती</t>
+          <t>Ravindra Chavan : ‘उपरा’ डोंबिवलीकर ते भाजप प्रदेश कार्याध्यक्ष</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/raviindra-chavhan-appointed-maharashtra-bjp-executive-state-president</t>
+          <t>https://www.loksatta.com/thane/bjp-leader-ravindra-chavan-political-journey-started-as-a-worker-to-maharashtra-bjp-chief-zws-70-4821598/</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>अण्णासाहेब डांगे दो बेटों के साथ BJP में शामिल, CM देवेंद्र फडणवीस की मौजूदगी में</t>
+          <t>BJP Politics : कल्याण-डोंबिवलीत भाजप ठाकरेंना धक्का देणार! शिंदेंचीही अडचण वाढवणार; इन्कमिंग सुरू, महापौरपदासाठी स्वबळाचे संकेत</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
+          <t>https://sarkarnama.esakal.com/mumbai/jatin-prajapati-joins-kalyan-dombivli-bjp-welcomed-by-ravindra-chavan-rm89</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण, एकमताने निवड, वाचा सविस्तर माहिती</t>
+          <t>संयमी भूमिका फळली! भाजपच्या कार्यकारी प्रदेशाध्यक्षपदी रविंद्र चव्हाणांची नियुक्ती</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>RSS स्वयंसेवक ते BJP प्रदेशाध्यक्ष; ‘अशी’ आहे रवींद्र चव्हाण यांची राजकीय कारकीर्द</t>
+          <t>Congress News : काँग्रेस खासदार रविंद्र चव्हाण संतापले, महापालिका आयुक्तांना हक्कभंग कारवाईचा इशारा!</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/from-rss-volunteer-to-bjp-state-president-know-about-ravindra-chavan-political-career-a-a719/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/congress-mp-ravindra-chavan-warns-action-against-commissioner-over-amit-shah-event-jp75</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>भाजपच्या महाराष्ट्र प्रदेश कार्यकारी अध्यक्षपदी रविंद्र चव्हाण यांची नियुक्ती</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी, आज अधिवेशनात सूत्रे स्वीकारणार</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-bjp-state-president-will-take-charge-in-the-convention-today-a-a941/</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महापालिका आयुक्तांनी प्रोटोकॉल पाळावा, हक्कभंगाची नोटीस देणार, नांदेडचे</t>
+          <t>Ravindra Chavan: भाजप नेते रविंद्र चव्हाण यांच्यावर पक्षाची महत्वाची जबाबदारी; कार्यकारी अध्यक्षपदी नियुक्ती</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
+          <t>https://www.esakal.com/desh/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-aau85</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : ‘उपरा’ डोंबिवलीकर ते भाजप प्रदेश कार्याध्यक्ष</t>
+          <t>महाराष्ट्र में भाजपा के संगठन निर्माण को मिली नई ताकत, राज्य में 1221 मंडलों का गठन</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-leader-ravindra-chavan-political-journey-started-as-a-worker-to-maharashtra-bjp-chief-zws-70-4821598/</t>
+          <t>https://hindi.news24online.com/state/mumbai/bjp-building-organization-in-maharashtra-gets-new-strength-1221-mandals-formed/1157953/</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>BJP Politics : कल्याण-डोंबिवलीत भाजप ठाकरेंना धक्का देणार! शिंदेंचीही अडचण वाढवणार; इन्कमिंग सुरू, महापौरपदासाठी स्वबळाचे संकेत</t>
+          <t>Ravindra Chavan BJP: रवींद्र चव्हाण भाजपाचे नवे 'कॅप्टन'! महाराष्ट्र प्रदेशाध्यक्षपदी बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/jatin-prajapati-joins-kalyan-dombivli-bjp-welcomed-by-ravindra-chavan-rm89</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-elected-unopposed-as-bjp-maharashtra-state-president-in-mumbai-event-devendra-fadnavis-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Congress News : काँग्रेस खासदार रविंद्र चव्हाण संतापले, महापालिका आयुक्तांना हक्कभंग कारवाईचा इशारा!</t>
+          <t>Maharashtra Updates : भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण, जलसंधारण विभागात 8 हजारांहून अधिक पदांची भरती...</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/congress-mp-ravindra-chavan-warns-action-against-commissioner-over-amit-shah-event-jp75</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-01-june-2025-live-updates-assembly-session-live-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-raj-thackeray-uddhav-thackeray-devendra-fadnavis-shivsena-rm82</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी, आज अधिवेशनात सूत्रे स्वीकारणार</t>
+          <t>BJP News : आमचा पक्ष 24/7 काम करणारा; मोठा - छोटा भाऊ असा सर्व्हे भाजप करत नाही!</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-bjp-state-president-will-take-charge-in-the-convention-today-a-a941/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-ravindra-chavan-statement-on-party-work-and-alliance-jp75</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>संयमी भूमिका फळली! भाजपच्या कार्यकारी प्रदेशाध्यक्षपदी रविंद्र चव्हाणांची नियुक्ती</t>
+          <t>“भाजपा हीच माझी ओळख” ; महाराष्ट्र भाजपा प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांची बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
+          <t>https://www.localnewsnetwork.in/bjp-is-my-identity-ravindra-chavan-elected-unopposed-as-maharashtra-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजप नेते रविंद्र चव्हाण यांच्यावर पक्षाची महत्वाची जबाबदारी; कार्यकारी अध्यक्षपदी नियुक्ती</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण यांची अखेर भाजपाच्या कार्यकारी प्रदेशाध्यक्षपदी वर्णी; राष्ट्रीय अध्यक्ष जेपी नड्डांची घोषणा</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/desh/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-aau85</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mla-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-kvg-85-4820046/</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Ravindra Chavan BJP: रवींद्र चव्हाण भाजपाचे नवे 'कॅप्टन'! महाराष्ट्र प्रदेशाध्यक्षपदी बिनविरोध निवड</t>
+          <t>Maharashtra BJP State President: उत्सुकता संपली; भाजपला मिळणार नवा प्रदेशाध्यक्ष! चंद्रशेखर बावनकुळेंच्या जागी रविंद्र चव्हाणांची नियुक्ती होणार</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-elected-unopposed-as-bjp-maharashtra-state-president-in-mumbai-event-devendra-fadnavis-a-a747/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Maharashtra Updates : भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण, जलसंधारण विभागात 8 हजारांहून अधिक पदांची भरती...</t>
+          <t>Ravindra Chavan : "सामान्य नगरसेवक ते भाजपचे प्रदेशाध्यक्ष..."</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-01-june-2025-live-updates-assembly-session-live-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-raj-thackeray-uddhav-thackeray-devendra-fadnavis-shivsena-rm82</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/ravindra-chavan-appointed-bjp-president-kiren-rijiju-announcement-and-political-career-as11</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Maharashtra BJP State President: उत्सुकता संपली; भाजपला मिळणार नवा प्रदेशाध्यक्ष! चंद्रशेखर बावनकुळेंच्या जागी रविंद्र चव्हाणांची नियुक्ती होणार</t>
+          <t>Ravindra Chavan : भाजपचं ठरलं, रवींद्र चव्हाण प्रदेशाध्यक्ष होणार, ठाकरेंच्या बालेकिल्ल्यात पहिलं शक्तिप्रद...</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण यांची अखेर भाजपाच्या कार्यकारी प्रदेशाध्यक्षपदी वर्णी; राष्ट्रीय अध्यक्ष जेपी नड्डांची घोषणा</t>
+          <t>BJP Ravindra Chavan News: भाजपच्या गोटातून मोठी बातमी समोर Maharashtra Politics</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mla-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-kvg-85-4820046/</t>
+          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>“भाजपा हीच माझी ओळख” ; महाराष्ट्र भाजपा प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांची बिनविरोध निवड</t>
+          <t>रत्नागिरी भाजपमध्ये नारायण राणे, रविंद्र चव्हाण यांच्यातील वाद चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-is-my-identity-ravindra-chavan-elected-unopposed-as-maharashtra-bjp-state-president/</t>
+          <t>https://www.loksatta.com/politics/dispute-between-narayan-rane-and-ravindra-chavan-in-ratnagiri-bjp-is-on-rise-print-political-news-ocd-94-5140598/</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : "सामान्य नगरसेवक ते भाजपचे प्रदेशाध्यक्ष..."</t>
+          <t>Ravindra Chavan: उद्धव ठाकरेंच्या भाजपसोबतच्या वाढत्या जवळीकतेवर रवींद्र चव्हाण यांचं महत्त्वाचं विधान; म्हणाले, शत्रूही...</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/ravindra-chavan-appointed-bjp-president-kiren-rijiju-announcement-and-political-career-as11</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-important-statement-on-uddhav-thackeray-closeness-with-bjp-aau85</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपचं ठरलं, रवींद्र चव्हाण प्रदेशाध्यक्ष होणार, ठाकरेंच्या बालेकिल्ल्यात पहिलं शक्तिप्रद...</t>
+          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू अन् RSS च्या मर्जीतले रवींद्र चव्हाण भाजपचे</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>BJP Ravindra Chavan News: भाजपच्या गोटातून मोठी बातमी समोर Maharashtra Politics</t>
+          <t>रविंद्र चव्हाण यांच्यावतीने डोंबिवलीत रक्षाबंधनाचा कौटुंबिक सोहळा; हजारो भगिनींनी बांधली राखी</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
+          <t>https://www.localnewsnetwork.in/raksha-bandhan-family-ceremony-in-dombivli-on-behalf-of-ravindra-chavan-thousands-of-sisters-tied-rakhi/</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>रत्नागिरी भाजपमध्ये नारायण राणे, रविंद्र चव्हाण यांच्यातील वाद चव्हाट्यावर</t>
+          <t>रवींद्र चव्हाण भाजपचे नवे कार्यकारी अध्यक्ष: लवकरच चंद्रशेखर बावनकुळेंकडून स्वीकारणार जबाबदारी, मंत्रिमंडळा...</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/dispute-between-narayan-rane-and-ravindra-chavan-in-ratnagiri-bjp-is-on-rise-print-political-news-ocd-94-5140598/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू अन् RSS च्या मर्जीतले रवींद्र चव्हाण भाजपचे</t>
+          <t>Ravindra Chavan : राजकारणातील सर्वात चर्चेतील नाव! RSS कार्यकर्ते ते भाजप प्रदेशाध्यक्ष झालेले कोण आहेत रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
+          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: उद्धव ठाकरेंच्या भाजपसोबतच्या वाढत्या जवळीकतेवर रवींद्र चव्हाण यांचं महत्त्वाचं विधान; म्हणाले, शत्रूही...</t>
+          <t>Ravindra Chavan : महापालिका निवडणूक महायुतीत की स्वबळावर? ; रवींद्र चव्हाणांनी सांगितली भाजपची सद्य भूमिका, म्हणाले..</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-important-statement-on-uddhav-thackeray-closeness-with-bjp-aau85</t>
+          <t>https://sarkarnama.esakal.com/pune/ravindra-chavan-bjp-current-stand-mahayuti-or-independent-contest-municipal-corporation-elections-maharashtra-politics-msr87</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>भाजपा साताऱ्यात निवडणार नवा जिल्हाध्यक्ष, प्रभारी प्रदेशाध्यक्ष रवींद्र चव्हाण यांची आढावा बैठक</t>
+          <t>Photos : रविंद्र चव्हाणांनी स्वीकारला भाजपा प्रदेशाध्यक्ष पदाचा पदभार; मावळत्या अध्यक्षांच्या शुभेच्छा…</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-to-elect-new-district-president-in-satara-review-meeting-by-ravindra-chavan-asj-82-5027101/</t>
+          <t>https://www.loksatta.com/photos/news/5198695/ravindra-chavan-takes-charge-as-bjp-state-president-best-wishes-from-party-s-outgoing-president-state-headquarter-mumbai-photos-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजपचे नवे कार्यकारी अध्यक्ष: लवकरच चंद्रशेखर बावनकुळेंकडून स्वीकारणार जबाबदारी, मंत्रिमंडळा...</t>
+          <t>पक्षकार्यकर्ता ते प्रदेशाध्यक्ष : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : राजकारणातील सर्वात चर्चेतील नाव! RSS कार्यकर्ते ते भाजप प्रदेशाध्यक्ष झालेले कोण आहेत रवींद्र चव्हाण?</t>
+          <t>Mahayuti News: शिवरायांच्या पुतळ्यावरून राजकारण तापलं, डोंबिवलीत शिंदे सेनेनं भाजपला डिवचलं</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
+          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>रविंद्र चव्हाण यांच्यावतीने डोंबिवलीत रक्षाबंधनाचा कौटुंबिक सोहळा; हजारो भगिनींनी बांधली राखी</t>
+          <t>महाराष्ट्र में किसे मिली BJP की कमान? मुंबई मेट्रो में देखें</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/raksha-bandhan-family-ceremony-in-dombivli-on-behalf-of-ravindra-chavan-thousands-of-sisters-tied-rakhi/</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महापालिका निवडणूक महायुतीत की स्वबळावर? ; रवींद्र चव्हाणांनी सांगितली भाजपची सद्य भूमिका, म्हणाले..</t>
+          <t>डोंबिवलीकर फ्रेंडशिप रनच्या थीमचे अनावरण संपन्न भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले थीमचे अनावरण ही स्पर्धा होणार 9 नोव्हेंबर ला</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/ravindra-chavan-bjp-current-stand-mahayuti-or-independent-contest-municipal-corporation-elections-maharashtra-politics-msr87</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Photos : रविंद्र चव्हाणांनी स्वीकारला भाजपा प्रदेशाध्यक्ष पदाचा पदभार; मावळत्या अध्यक्षांच्या शुभेच्छा…</t>
+          <t>Maharashtra Politics: उद्धव ठाकरे पुन्हा भाजपसोबत? रवींद्र चव्हाण म्हणाले,राजकारणात कोणी कायमचा शत्रू नसतो | VIDEO</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5198695/ravindra-chavan-takes-charge-as-bjp-state-president-best-wishes-from-party-s-outgoing-president-state-headquarter-mumbai-photos-spl-93/</t>
+          <t>https://saamtv.esakal.com/video/uddhav-thackeray-bjp-alliance-ravindra-chavan-interview-political-future-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवली परिसर भाजपमय करा, पालिकेवर भाजपचा महापौर बसवा, रवींद्र चव्हाण यांचे कार्यकर्त्यांना आवाहन</t>
+          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू, पक्षाच्या मर्जीतले रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-s-appeal-to-party-workers-to-work-for-bjp-mayor-in-kdmc-zws-70-5277354/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-bjp-ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>डोंबिवलीकर फ्रेंडशिप रनच्या थीमचे अनावरण संपन्न भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले थीमचे अनावरण ही स्पर्धा होणार 9 नोव्हेंबर ला</t>
+          <t>Ravindra Chavan News : भाजपचे प्रदेशाध्यक्ष म्हणतात, आमची संघटनात्मक बांधणी मजबूत, यश पदरात पडेल!</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-state-president-ravindra-chavan-confident-of-election-success-says-our-organisation-is-strong-jp75</t>
         </is>
       </c>
     </row>
@@ -2627,1644 +2627,1644 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>पक्षकार्यकर्ता ते प्रदेशाध्यक्ष : रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan : भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण दिल्लीत, जेपी नड्डा यांची घेणार भेट ABP MAJHA</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Mahayuti News: शिवरायांच्या पुतळ्यावरून राजकारण तापलं, डोंबिवलीत शिंदे सेनेनं भाजपला डिवचलं</t>
+          <t>राणे पिता-पुत्रांनी भाजपऐवजी स्ट्राँग केलं स्वतःचं नेटवर्क; नव्या प्रदेशाध्यक्षांचा होमग्राऊंडवरच निघणार घाम!</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-maharashtra-state-president-ravindra-chavan-faces-challenge-of-strengthening-party-in-sindhudurg-beyond-rane-family-influence-as11-hn97</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में किसे मिली BJP की कमान? मुंबई मेट्रो में देखें</t>
+          <t>Ravindra Chavan : महाराष्ट्र भाजपच्या प्रदेशाध्यपदी रविंद्र चव्हाणांची नियुक्ती</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: उद्धव ठाकरे पुन्हा भाजपसोबत? रवींद्र चव्हाण म्हणाले,राजकारणात कोणी कायमचा शत्रू नसतो | VIDEO</t>
+          <t>Maharashtra BJP News : भाजप प्रदेशाध्यक्षपदासाठी रवींद्र चव्हाण यांनी भरला अर्ज</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/uddhav-thackeray-bjp-alliance-ravindra-chavan-interview-political-future-maharashtra-om0906</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू, पक्षाच्या मर्जीतले रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष</t>
+          <t>कल्याण-डोंबिवली परिसर भाजपमय करा, पालिकेवर भाजपचा महापौर बसवा, रवींद्र चव्हाण यांचे कार्यकर्त्यांना आवाहन</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-bjp-ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-latest-marathi-news-pp0731</t>
+          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-s-appeal-to-party-workers-to-work-for-bjp-mayor-in-kdmc-zws-70-5277354/</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Ravindra Chavan News : भाजपचे प्रदेशाध्यक्ष म्हणतात, आमची संघटनात्मक बांधणी मजबूत, यश पदरात पडेल!</t>
+          <t>रवींद्र चव्हाण महाराष्ट्र भाजपच्या कार्याध्यक्षपदी, दोन महिन्यांनी प्रदेशाध्यक्ष हाेणार</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-state-president-ravindra-chavan-confident-of-election-success-says-our-organisation-is-strong-jp75</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-will-become-state-president-in-two-months-a-a309/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण दिल्लीत, जेपी नड्डा यांची घेणार भेट ABP MAJHA</t>
+          <t>कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाश्याला बेघर होऊ देणार नाही, रविंद्र चव्हाण यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
+          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>राणे पिता-पुत्रांनी भाजपऐवजी स्ट्राँग केलं स्वतःचं नेटवर्क; नव्या प्रदेशाध्यक्षांचा होमग्राऊंडवरच निघणार घाम!</t>
+          <t>रवींद्र चव्हाण भाजपचे नवे कॅप्टन; केंद्रीय मंत्री किरेन रिजिजू यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-maharashtra-state-president-ravindra-chavan-faces-challenge-of-strengthening-party-in-sindhudurg-beyond-rane-family-influence-as11-hn97</t>
+          <t>https://marathi.freepressjournal.in/mumbai/ravindra-chavan-appointed-bjp-maharashtra-president-2025</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महाराष्ट्र भाजपच्या प्रदेशाध्यपदी रविंद्र चव्हाणांची नियुक्ती</t>
+          <t>Kalyan News: 'या' इमारतींच्या रखडलेल्या पुनर्विकास लागणार मार्गी, रवींद्र चव्हाण यांची माहिती</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण महाराष्ट्र भाजपच्या कार्याध्यक्षपदी, दोन महिन्यांनी प्रदेशाध्यक्ष हाेणार</t>
+          <t>Latur Politics: प्रदेशाध्यक्ष रविंद्र चव्हाणांचा लातूरमध्ये मोठा धमाका; दोन बड्या नेत्यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-will-become-state-president-in-two-months-a-a309/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-politics-kapil-makne-nilkanth-mirkale-of-latur-joining-bjp-dk88</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Maharashtra BJP News : भाजप प्रदेशाध्यक्षपदासाठी रवींद्र चव्हाण यांनी भरला अर्ज</t>
+          <t>Ravindra Chavan: 'संविधान बचाव'ची 'शो'बाजी करणारे...; PM मोदींवर टीका करणाऱ्या राहुल गांधींना रविंद्र चव्हाणांचं उत्तर</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/those-who-showoff-of-saving-constitution-criticized-pm-modi-reply-by-ravindra-chavan-on-rahul-gandhi-statement-against-prime-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाश्याला बेघर होऊ देणार नाही, रविंद्र चव्हाण यांचे आश्वासन</t>
+          <t>Maharashtra Politics : देवेंद्र फडणवीस यांचे विश्वासू ते भाजपाचे कार्यकारी अध्यक्ष; कोण आहेत रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-cm-devendra-fadnavis-confidant-to-bjp-working-president-who-is-mla-ravindra-chavan-sdp-92-4822225/</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजपचे नवे कॅप्टन; केंद्रीय मंत्री किरेन रिजिजू यांनी केली घोषणा</t>
+          <t>भाजप कार्यकर्ता काम करताना रस्त्यावर दिसायला हवा; रवींद्र चव्हाण यांनी घेतली कार्यकर्त्यांची शाळा</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/ravindra-chavan-appointed-bjp-maharashtra-president-2025</t>
+          <t>https://www.lokmat.com/pune/bjp-workers-should-be-visible-on-the-streets-while-working-ravindra-chavan-took-the-school-of-workers-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Latur Politics: प्रदेशाध्यक्ष रविंद्र चव्हाणांचा लातूरमध्ये मोठा धमाका; दोन बड्या नेत्यांचा भाजपात प्रवेश</t>
+          <t>Ravindra Chavan: भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांच्या नावावर शिक्कामोर्तब? उद्या होणार घोषणा</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-politics-kapil-makne-nilkanth-mirkale-of-latur-joining-bjp-dk88</t>
+          <t>https://www.esakal.com/maharashtra/ravindra-chavan-name-confirmed-as-bjp-maharashtra-president-announcement-to-be-made-soon-aau85</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>मोठा गेम होणार, भाजप प्रदेशाध्यक्षाच्या विधानाने खळबळ; शिंदे गटाला सर्वात मोठं टेन्शन</t>
+          <t>Maharashtra Politics : धुळ्यात काँग्रेसला खिंडार? मातब्बर नेता मुंबईत रायगड निवासस्थानी</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 'संविधान बचाव'ची 'शो'बाजी करणारे...; PM मोदींवर टीका करणाऱ्या राहुल गांधींना रविंद्र चव्हाणांचं उत्तर</t>
+          <t>भाजपने माझ्यावर उपकार केलेत, प्रदेशाध्यक्ष बनल्यानंतर रवींद्र चव्हाणांची पहिली प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/those-who-showoff-of-saving-constitution-criticized-pm-modi-reply-by-ravindra-chavan-on-rahul-gandhi-statement-against-prime-minister-aau85</t>
+          <t>https://www.tv9marathi.com/politics/bjp-has-done-me-favor-new-state-president-rvindra-chavhan-1st-statement-1436200.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : देवेंद्र फडणवीस यांचे विश्वासू ते भाजपाचे कार्यकारी अध्यक्ष; कोण आहेत रवींद्र चव्हाण?</t>
+          <t>कल्याण डोंबिवलीच्या विकासाचे ग्रहण दूर करण्यासाठी भाजपचा महापौर हवा – भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-cm-devendra-fadnavis-confidant-to-bjp-working-president-who-is-mla-ravindra-chavan-sdp-92-4822225/</t>
+          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : धुळ्यात काँग्रेसला खिंडार? मातब्बर नेता मुंबईत रायगड निवासस्थानी</t>
+          <t>Ravindra Chavhan Interview:महाराष्ट्र भाजप प्रदेशाध्यक्ष पद स्वीकारल्यानंतर रविंद्र चव्हाण EXCLUSIVE</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
+          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>कल्याण डोंबिवलीच्या विकासाचे ग्रहण दूर करण्यासाठी भाजपचा महापौर हवा – भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण</t>
+          <t>Ravindra Chavan: भाजपच्या कार्यकारी अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
+          <t>https://saamtv.esakal.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-bbj88</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांच्या नावावर शिक्कामोर्तब? उद्या होणार घोषणा</t>
+          <t>चव्हाणांकडे प्रदेश, सेनेला थेट संदेश; शिंदेंना होमपीचवर शह देण्यासाठी भाजपची जोरदार फिल्डींग</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ravindra-chavan-name-confirmed-as-bjp-maharashtra-president-announcement-to-be-made-soon-aau85</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>भाजपने माझ्यावर उपकार केलेत, प्रदेशाध्यक्ष बनल्यानंतर रवींद्र चव्हाणांची पहिली प्रतिक्रिया</t>
+          <t>Ravindra Chavan | रवींद्र चव्‍हाणांनी घेतली भाजप अध्‍यक्ष जे. पी. नड्डांची भेट</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-has-done-me-favor-new-state-president-rvindra-chavhan-1st-statement-1436200.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-bjp-state-president-ravindra-chavan-met-party-president-j-p-nadda-nl76</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : एकनाथ शिंदेंना शह देण्यासाठी भाजपने दिले कार्याध्यक्षपद? रवींद्र चव्हाणांनी सांगितलं खरं काय?</t>
+          <t>मोठा गेम होणार, भाजप प्रदेशाध्यक्षाच्या विधानाने खळबळ; शिंदे गटाला सर्वात मोठं टेन्शन</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-opens-up-about-bjp-move-in-thane-rm89</t>
+          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Kalyan News: 'या' इमारतींच्या रखडलेल्या पुनर्विकास लागणार मार्गी, रवींद्र चव्हाण यांची माहिती</t>
+          <t>प्रदेशाध्यक्षपद देऊन भाजपने माझ्यावर उपकार केले, रवींद्र चव्हाण भाषणात नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Ravindra Chavhan Interview:महाराष्ट्र भाजप प्रदेशाध्यक्ष पद स्वीकारल्यानंतर रविंद्र चव्हाण EXCLUSIVE</t>
+          <t>डोंबिवलीतील काँग्रेसचे 4 नगरसेवक भाजपमध्ये; पक्षाकडून त्यांचा नेहमीच सन्मान केला जाणार – प्रदेशाध्यक्ष रविंद्र चव्हाण यांची ग्वाही</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
+          <t>https://www.localnewsnetwork.in/4-congress-corporators-from-dombivli-join-bjp-they-will-always-be-respected-by-the-party-state-president-ravindra-chavan-assures/</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजपच्या कार्यकारी अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>Indrayani River Bridge Collapse | संजय राऊत विश्वप्रवक्ते! इंद्रायणी पूल दुरुस्तीसाठी ८० हजार की ८ कोटी... रविंद्र चव्हाण यांनी खरं काय ते सांगितले?</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-bbj88</t>
+          <t>https://pudhari.news/maharashtra/mumbai/bjp-ravindra-chavan-responded-to-sanjay-raut-allegations-over-indrayani-river-bridge-collapse-incident-db79</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>चव्हाणांकडे प्रदेश, सेनेला थेट संदेश; शिंदेंना होमपीचवर शह देण्यासाठी भाजपची जोरदार फिल्डींग</t>
+          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Ravindra Chavan | रवींद्र चव्‍हाणांनी घेतली भाजप अध्‍यक्ष जे. पी. नड्डांची भेट</t>
+          <t>BJP Politics : बंडखोरी केलेल्या नेत्याचा भाजप प्रवेश, वेलकम स्वत: रवींद्र चव्हाणांनी केलं; युतीमध्ये वितुष्ट येण्याची शक्यता?</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-bjp-state-president-ravindra-chavan-met-party-president-j-p-nadda-nl76</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ravindra-chavan-cancelled-vishal-parabs-bjp-suspension-revoked-creating-alliance-tension-in-sindhudurg-politics-as11</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>प्रदेशाध्यक्षपद देऊन भाजपने माझ्यावर उपकार केले, रवींद्र चव्हाण भाषणात नेमकं काय म्हणाले?</t>
+          <t>Maharashtra BJP State President | भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांचे नाव जवळपास निश्चित, १ जुलैला अधिकृत घोषणा</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-will-be-appointed-maharashtra-bjp-state-president-db79</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>डोंबिवलीतील काँग्रेसचे 4 नगरसेवक भाजपमध्ये; पक्षाकडून त्यांचा नेहमीच सन्मान केला जाणार – प्रदेशाध्यक्ष रविंद्र चव्हाण यांची ग्वाही</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/4-congress-corporators-from-dombivli-join-bjp-they-will-always-be-respected-by-the-party-state-president-ravindra-chavan-assures/</t>
+          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
+          <t>BJP Dombivli setback - भाजपला डोंबिवलीत धक्का! ; प्रदेश कार्याध्यक्षांवर 'हा' आरोप करत, दोन नगरसेवकांनी सोडला पक्ष</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-dombivli-crisis-vikas-kavita-mhatre-resignation-ravindra-chavan-allegations-msr87</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Indrayani River Bridge Collapse | संजय राऊत विश्वप्रवक्ते! इंद्रायणी पूल दुरुस्तीसाठी ८० हजार की ८ कोटी... रविंद्र चव्हाण यांनी खरं काय ते सांगितले?</t>
+          <t>Ravindra Chavan: आता पालिका विकासाचे ग्रहण दूर होणार; भाजप प्रदेशाध्यक्षांनी निवडणुकीचा प्लॅनच सांगितला</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/bjp-ravindra-chavan-responded-to-sanjay-raut-allegations-over-indrayani-river-bridge-collapse-incident-db79</t>
+          <t>https://www.esakal.com/mumbai/ravindra-chavan-says-bjp-mayor-is-necessary-to-resolve-development-problems-faced-by-kalyan-dombivli-municipal-corporation-on-bmc-election-mvk02</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BJP Politics : बंडखोरी केलेल्या नेत्याचा भाजप प्रवेश, वेलकम स्वत: रवींद्र चव्हाणांनी केलं; युतीमध्ये वितुष्ट येण्याची शक्यता?</t>
+          <t>BJP President: "रवी दादा आगे बढो नाही तर..."; प्रदेशाध्यक्ष होताच रवींद्र चव्हाणांनी व्यक्त केल्या भावना</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ravindra-chavan-cancelled-vishal-parabs-bjp-suspension-revoked-creating-alliance-tension-in-sindhudurg-politics-as11</t>
+          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: आता पालिका विकासाचे ग्रहण दूर होणार; भाजप प्रदेशाध्यक्षांनी निवडणुकीचा प्लॅनच सांगितला</t>
+          <t>एक-एक मंडल दत्तक घेऊन संघटनात्मक बांधणीचा संकल्प करा; प्रदेशाध्यक्ष रविंद्र चव्हाण यांचे माजी आमदार, खासदारांना आवाहन</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/ravindra-chavan-says-bjp-mayor-is-necessary-to-resolve-development-problems-faced-by-kalyan-dombivli-municipal-corporation-on-bmc-election-mvk02</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Maharashtra BJP State President | भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांचे नाव जवळपास निश्चित, १ जुलैला अधिकृत घोषणा</t>
+          <t>Ravindra Chavan Exclusive Interview : राज-उद्धव ठाकरे एकत्र आल्यास भाजपला आव्हान असणार का? प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-will-be-appointed-maharashtra-bjp-state-president-db79</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
+          <t>Maharashtra Politics : भाजपचे नवीन प्रदेशाध्यक्ष कोण? बड्या नेत्याचं नाव पक्कं; उद्या अधिकृत घोषणा होणार</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/ravindra-chavan-fills-the-form-for-the-post-of-new-state-president-of-mumbai-bjp-name-will-be-announced-tomorrow-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>BJP Dombivli setback - भाजपला डोंबिवलीत धक्का! ; प्रदेश कार्याध्यक्षांवर 'हा' आरोप करत, दोन नगरसेवकांनी सोडला पक्ष</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण भाजपचे कारभारी</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-dombivli-crisis-vikas-kavita-mhatre-resignation-ravindra-chavan-allegations-msr87</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-ravindra-chavan-is-the-bjp-s-steward-1061660.html</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>एक-एक मंडल दत्तक घेऊन संघटनात्मक बांधणीचा संकल्प करा; प्रदेशाध्यक्ष रविंद्र चव्हाण यांचे माजी आमदार, खासदारांना आवाहन</t>
+          <t>काँग्रेस नेते कैलास गोरंट्यालसह सुरेश वरपूडकर यांचा भाजप प्रवेशाचा मुहूर्त</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
+          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Exclusive Interview : राज-उद्धव ठाकरे एकत्र आल्यास भाजपला आव्हान असणार का? प्रदेशाध्यक्ष</t>
+          <t>BJP new state president : पक्षनेतृत्वानं दाखवला मोठा भरवसा; मित्रपक्षाला भिडणाऱ्या भाजपच्या नव्या प्रदेशाध्यक्षांना आता गियर बदलावा लागणार</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-state-chief-ravindra-chavan-faces-ally-challenge-amid-trust-sw79</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>Thane News : भाजपमध्ये मेगाभरती, शरद पवार गटाचा आणखी किल्ला ढासळणार! कुठं होणार राजकीय उलथापालथ?</t>
+          <t>राज ठाकरे भाजपसोबत जाणार का?: रवींद्र चव्हाण म्हणतात - राज व फडणवीसांचे चांगले संबंध, ते दोघेही मुंबईच्या ह...</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-political-masterstroke-ulhasnagar-sharad-pawar-group-breakdown-1445668.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-raj-thackeray-bjp-alliance-speculation-uddhav-thackeray-politics-update-135429372.html</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>BJP President: "रवी दादा आगे बढो नाही तर..."; प्रदेशाध्यक्ष होताच रवींद्र चव्हाणांनी व्यक्त केल्या भावना</t>
+          <t>"एकनाथ शिंदे मुख्यमंत्री झाल्याने वाईट वाटलं आणि घरी निघून गेलो,पण पुन्हा..."; रवींद्र चव्हाणांचा गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
+          <t>https://www.lokmat.com/mumbai/bjp-state-president-ravindra-chavan-said-that-he-felt-bad-after-eknath-shinde-became-the-chief-minister-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : भाजपचे नवीन प्रदेशाध्यक्ष कोण? बड्या नेत्याचं नाव पक्कं; उद्या अधिकृत घोषणा होणार</t>
+          <t>Raju Patil: विकासाला ग्रहण लावणाऱ्या 'चांदभाई'चे नाव घ्या! मनसे नेत्याचा भाजप प्रदेशाध्यक्षांना टोला</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/ravindra-chavan-fills-the-form-for-the-post-of-new-state-president-of-mumbai-bjp-name-will-be-announced-tomorrow-latest-marathi-news-pp0731</t>
+          <t>https://www.esakal.com/mumbai/mns-leader-raju-patil-criticism-on-ravindra-chavan-over-kalyan-dombivli-development-maharashtra-politics-mvk02</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>काँग्रेस नेते कैलास गोरंट्यालसह सुरेश वरपूडकर यांचा भाजप प्रवेशाचा मुहूर्त</t>
+          <t>Ravindra Chavan emotional story: फडणवीस मुख्यमंत्री होणार नसल्याने धक्का बसला, डोळ्यात पाणी आले अन् ...; रवींद्र चव्हाणांनी सांगितला 2022 सालचा किस्सा.....</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-reveals-2022-twist-emotional-reaction-as-devendra-fadnavis-wasnt-named-cm-sw79</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण भाजपचे कारभारी</t>
+          <t>BJP Maharashtra President : भाजपचे महाराष्ट्रातील नवे उत्तराधिकारी कोण? प्रदेशाध्यक्षपदासाठी सर्वात आघाडीवर कोणाचं नाव?</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-ravindra-chavan-is-the-bjp-s-steward-1061660.html</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>BJP new state president : पक्षनेतृत्वानं दाखवला मोठा भरवसा; मित्रपक्षाला भिडणाऱ्या भाजपच्या नव्या प्रदेशाध्यक्षांना आता गियर बदलावा लागणार</t>
+          <t>नितेश राणे आणि गोपीचंद पडळकर दोघांना भाजपने डायरेक्ट वॉर्निंग दिली</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-state-chief-ravindra-chavan-faces-ally-challenge-amid-trust-sw79</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>राज ठाकरे भाजपसोबत जाणार का?: रवींद्र चव्हाण म्हणतात - राज व फडणवीसांचे चांगले संबंध, ते दोघेही मुंबईच्या ह...</t>
+          <t>फडणवीस व चव्हाण यांच्या नेतृत्वात भाजपला मोठे यश मिळेल- ना. विखे पाटील</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-raj-thackeray-bjp-alliance-speculation-uddhav-thackeray-politics-update-135429372.html</t>
+          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>Exclusive: 2017 मध्ये शिवसेनेला आम्ही महापौर पद दिलं पण आता... रविंद्र चव्हाणांनी स्पष्टच सांगितलं</t>
+          <t>भाजपाचा सामान्य कार्यकर्ता ते प्रदेशाध्यक्ष पर्यंतचा रवींद्र चव्हाण यांचा प्रवास</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/bjp-state-president-ravindra-chavan-on-bmc-mayor-decesion-politics-marathi-news/925443</t>
+          <t>https://puneprimenews.com/mumbai/ravindra-chavans-journey-from-ordinary-bjp-worker-to-state-president-update/</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>"एकनाथ शिंदे मुख्यमंत्री झाल्याने वाईट वाटलं आणि घरी निघून गेलो,पण पुन्हा..."; रवींद्र चव्हाणांचा गौप्यस्फोट</t>
+          <t>BMC Elections 2025: भाजपचे मुंबई अध्यक्ष ठरले! 'या' आक्रमक नेत्याची लागली वर्णी; निवडणुकांपूर्वी मोठी खेळी</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-state-president-ravindra-chavan-said-that-he-felt-bad-after-eknath-shinde-became-the-chief-minister-a-a1001/</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Raju Patil: विकासाला ग्रहण लावणाऱ्या 'चांदभाई'चे नाव घ्या! मनसे नेत्याचा भाजप प्रदेशाध्यक्षांना टोला</t>
+          <t>Ravindra Chavhan BJP : रविंद्र चव्हाण यांनी बोलावली बैठक, निवडणुकीसंदर्भात चर्चा</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/mns-leader-raju-patil-criticism-on-ravindra-chavan-over-kalyan-dombivli-development-maharashtra-politics-mvk02</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>नितेश राणे आणि गोपीचंद पडळकर दोघांना भाजपने डायरेक्ट वॉर्निंग दिली</t>
+          <t>महाराष्ट्रात राजकीय भूकंप घडवण्यात रवींद्र चव्हाणांचा मोठा वाटा, भाजपच्या नव्या प्रदेशाध्यक्षांची A टू Z कारकीर्द</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Ravindra Chavan emotional story: फडणवीस मुख्यमंत्री होणार नसल्याने धक्का बसला, डोळ्यात पाणी आले अन् ...; रवींद्र चव्हाणांनी सांगितला 2022 सालचा किस्सा.....</t>
+          <t>Narayan Rane : राणेंचा भाजपच्या प्रदेश प्रभारींनाच कडक इशारा; म्हणाले, 'इथं ढवळाढवळ चालणार नाही, हवं तर...'</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-reveals-2022-twist-emotional-reaction-as-devendra-fadnavis-wasnt-named-cm-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/narayan-rane-slams-ravindra-chavan-over-post-distribution-in-ratnagiri-bjp-as11</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President : भाजपचे महाराष्ट्रातील नवे उत्तराधिकारी कोण? प्रदेशाध्यक्षपदासाठी सर्वात आघाडीवर कोणाचं नाव?</t>
+          <t>BJP : अण्णासाहेब डांगे यांचा दोन्ही मुलांसह भाजप प्रवेश; फडणवीस म्हणाले, पक्षावाढीत त्यांचा मोलाचा वाटा</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
+          <t>https://www.mymahanagar.com/mahamumbai/bjp-live-devendra-fadnavis-annasaheb-dange-join-bjp-30th-july-ravindra-chavan-chardrakant-patil/907022/</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>फडणवीस व चव्हाण यांच्या नेतृत्वात भाजपला मोठे यश मिळेल- ना. विखे पाटील</t>
+          <t>जिल्हाध्यक्षपदाची माळ रवींद्र चव्हाणांच्या निकटवर्तीयाच्या गळ्यात; KDMC निवडणुकीआधी भाजपात मोठे बदल</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/big-changes-underway-in-bjp-kdmc-ahead-of-municipal-elections/articleshow/121160143.cms</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>भाजपाचा सामान्य कार्यकर्ता ते प्रदेशाध्यक्ष पर्यंतचा रवींद्र चव्हाण यांचा प्रवास</t>
+          <t>महाराष्ट्राच्या राजकारणातील सर्वात मोठी घडामोड! उद्धव ठाकरे पक्षातील 1500 सदस्यांनी एकावेळी पक्ष सोडला आणि...</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/ravindra-chavans-journey-from-ordinary-bjp-worker-to-state-president-update/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: भाजपचे मुंबई अध्यक्ष ठरले! 'या' आक्रमक नेत्याची लागली वर्णी; निवडणुकांपूर्वी मोठी खेळी</t>
+          <t>“ठाकरे बंधूंनी एकत्र येऊ नये असा GR काढलेला नाही”; CM देवेंद्र फडणवीसांचा खोचक टोला</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
+          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-taunt-about-raj-thackeray-and-uddhav-thackeray-likely-to-come-together-for-marathi-language-issue-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Ravindra Chavhan BJP : रविंद्र चव्हाण यांनी बोलावली बैठक, निवडणुकीसंदर्भात चर्चा</t>
+          <t>Dahi Handi 2025 : डोंबिवलीमध्ये पारंपरिक पद्धतीने दहीहंडीचा उत्सव; गोविंदांचा उत्सह शिगेला</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
+          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>महाराष्ट्राच्या राजकारणातील सर्वात मोठी घडामोड! उद्धव ठाकरे पक्षातील 1500 सदस्यांनी एकावेळी पक्ष सोडला आणि...</t>
+          <t>मी निष्पाप, निष्ठेने काम करेन, तुमचा आदेश तंतोतंत पाळेन, सुधाकर बडगुजरांचा बावनकुळेंना</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
+          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>“ठाकरे बंधूंनी एकत्र येऊ नये असा GR काढलेला नाही”; CM देवेंद्र फडणवीसांचा खोचक टोला</t>
+          <t>Nanded Ashok Chavan: अशोक चव्हाणांची डोकेदुखी वाढली; काँग्रेसकडून खिंडीत पकडण्यासाठी प्लॅन तयार, नांदेडमध्ये काय घडतंय?</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-taunt-about-raj-thackeray-and-uddhav-thackeray-likely-to-come-together-for-marathi-language-issue-a-a719/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>Dahi Handi 2025 : डोंबिवलीमध्ये पारंपरिक पद्धतीने दहीहंडीचा उत्सव; गोविंदांचा उत्सह शिगेला</t>
+          <t>कल्याणमध्ये काँग्रेसला खिंडार! बडे नेते भाजपवासी; प्रदेशाध्यक्षांनी दिले मोठे संकेत</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-grows-stronger-in-kalyan-congress-leaders-join-ravindra-chavan-hints-at-contesting-solo-bdk97</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>मी निष्पाप, निष्ठेने काम करेन, तुमचा आदेश तंतोतंत पाळेन, सुधाकर बडगुजरांचा बावनकुळेंना</t>
+          <t>स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती की स्वबळावर? भाजप प्रदेशाध्यक्षांचं सूचक विधान; म्हणाले, 'आचारसंहिता लागली की...'</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
+          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-statement-on-date-of-local-body-elections-mahayuti-alliance-vru98</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Nanded Ashok Chavan: अशोक चव्हाणांची डोकेदुखी वाढली; काँग्रेसकडून खिंडीत पकडण्यासाठी प्लॅन तयार, नांदेडमध्ये काय घडतंय?</t>
+          <t>Devendra Fadnavis : “फेक नरेटिव्ह तयार करणाऱ्यांची फॅक्टरी…” फडणवीस यांचं उद्धव ठाकरेंना त्याच भाषेत उत्तर</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-bjp-president-fadnavis-slams-uddhav-thackeray-over-fake-narrative-as11</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती की स्वबळावर? भाजप प्रदेशाध्यक्षांचं सूचक विधान; म्हणाले, 'आचारसंहिता लागली की...'</t>
+          <t>Nanded News: नांदेडमध्ये स्थानिक निवडणुकासाठी काँगेस अन् वंचितकडून युतीचे संकेत प्रस्ताव</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-statement-on-date-of-local-body-elections-mahayuti-alliance-vru98</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : “फेक नरेटिव्ह तयार करणाऱ्यांची फॅक्टरी…” फडणवीस यांचं उद्धव ठाकरेंना त्याच भाषेत उत्तर</t>
+          <t>Dombivli: संघाच्या बालेकिल्ल्यात हादरा, भाजप नेत्याचा राजीनामा, नेतृत्वावर आरोप, मशाल हाती घेण्याचे संकेत</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-bjp-president-fadnavis-slams-uddhav-thackeray-over-fake-narrative-as11</t>
+          <t>https://news18marathi.com/maharashtra/bjp-leader-vikas-mhatre-resigns-from-bjp-ahead-dombivli-mahapalika-election-allegation-on-ravindra-chavan-1423215.html</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>Nanded News: नांदेडमध्ये स्थानिक निवडणुकासाठी काँगेस अन् वंचितकडून युतीचे संकेत प्रस्ताव</t>
+          <t>छत्रपती शिवाजी महाराजांच्या मेघडंबरीसह पूर्णाकृती पुतळ्याचे डोंबिवलीत अनावरण ; खा. डॉ. श्रीकांत शिंदे, भाजप कार्याध्यक्ष रविंद्र चव्हाण यांची प्रमूख उपस्थिती – LNN</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
+          <t>https://www.localnewsnetwork.in/unveiling-of-the-full-length-statue-of-chhatrapati-shivaji-maharaj-with-a-canopy-in-dombivali/</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>छत्रपती शिवाजी महाराजांच्या मेघडंबरीसह पूर्णाकृती पुतळ्याचे डोंबिवलीत अनावरण ; खा. डॉ. श्रीकांत शिंदे, भाजप कार्याध्यक्ष रविंद्र चव्हाण यांची प्रमूख उपस्थिती – LNN</t>
+          <t>Vikas Mhatre - प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला धक्का देणारे विकास म्हात्रे आहेत तरी कोण?</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/unveiling-of-the-full-length-statue-of-chhatrapati-shivaji-maharaj-with-a-canopy-in-dombivali/</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/vikas-mhatre-resignation-bjp-allegations-on-ravindra-chavan-dombivili-msr87</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Vikas Mhatre - प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला धक्का देणारे विकास म्हात्रे आहेत तरी कोण?</t>
+          <t>Dombivli KDMCC School Building |डोंबिवलीत केडीएमसी शाळेची नवी इमारत</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/vikas-mhatre-resignation-bjp-allegations-on-ravindra-chavan-dombivili-msr87</t>
+          <t>https://pudhari.news/maharashtra/thane/dombivli-kdmcc-school-new-building-bhoomipujan-by-mla-ravindra-chavan-sp96</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Dombivli KDMCC School Building |डोंबिवलीत केडीएमसी शाळेची नवी इमारत</t>
+          <t>Nitin Gadkari Auto Rickshaw Comment: गडकरींनी सांगितलं ‘ऑटो रिक्षा’ अन् महाराष्ट्र भाजपचं कनेक्शन ; क्षणात एकच हशा पिकला!</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/dombivli-kdmcc-school-new-building-bhoomipujan-by-mla-ravindra-chavan-sp96</t>
+          <t>https://www.esakal.com/mumbai/nitin-gadkari-comment-about-auto-rickshaw-maharashtra-bjp-political-reaction-ravindra-chavan-maharashtra-bjp-president-msr87</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>Nitin Gadkari Auto Rickshaw Comment: गडकरींनी सांगितलं ‘ऑटो रिक्षा’ अन् महाराष्ट्र भाजपचं कनेक्शन ; क्षणात एकच हशा पिकला!</t>
+          <t>उत्तर महाराष्ट्रात काँग्रेसला मोठा धक्का ? कुणाल पाटील भाजपात जाणार? राजकीय वर्तुळात चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/nitin-gadkari-comment-about-auto-rickshaw-maharashtra-bjp-political-reaction-ravindra-chavan-maharashtra-bjp-president-msr87</t>
+          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>उत्तर महाराष्ट्रात काँग्रेसला मोठा धक्का ? कुणाल पाटील भाजपात जाणार? राजकीय वर्तुळात चर्चांना उधाण</t>
+          <t>Nashik BJP News : भाजप खासदार, आमदारांना मंडल दत्तक देणार</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/nashik-bjp-news-bjp-will-adopt-mandals-for-mps-mlas-ar84</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>Nashik BJP News : भाजप खासदार, आमदारांना मंडल दत्तक देणार</t>
+          <t>उद्धव ठाकरेंपाठोपाठ शरद पवारांनाही धक्का! भाजपामध्ये 'इनकमिंग' सुरूच; अनेकांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/nashik-bjp-news-bjp-will-adopt-mandals-for-mps-mlas-ar84</t>
+          <t>https://www.lokmat.com/maharashtra/after-uddhav-thackeray-sharad-pawar-also-gets-a-shock-many-join-bjp-party-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरेंपाठोपाठ शरद पवारांनाही धक्का! भाजपामध्ये 'इनकमिंग' सुरूच; अनेकांचा पक्षप्रवेश</t>
+          <t>युवा उद्योजक विशाल परब यांची भाजप वापसी</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/after-uddhav-thackeray-sharad-pawar-also-gets-a-shock-many-join-bjp-party-a-a747/</t>
+          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>युवा उद्योजक विशाल परब यांची भाजप वापसी</t>
+          <t>Thane | कल्याण-डोंबिवलीत झोपडपट्टी पुनर्वसन योजना लवकरच कार्यान्वीत</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
+          <t>https://pudhari.news/maharashtra/thane/thane-slum-rehabilitation-scheme-to-be-implemented-soon-in-kalyan-dombivli</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Thane | कल्याण-डोंबिवलीत झोपडपट्टी पुनर्वसन योजना लवकरच कार्यान्वीत</t>
+          <t>Ravindra Chavan : अधिकाऱ्यांनी जर दिरंगाई केली असेल तर…; रविंद्र चव्हाणांचा कारवाईचा इशारा</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/thane-slum-rehabilitation-scheme-to-be-implemented-soon-in-kalyan-dombivli</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5163828/ravindra-chavans-warning-of-action-over-indrayani-river-bridge-collapsed-accident-cas/</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>कॉर्पोरेटमधील नोकरी ते मुंबई भाजपाच्या अध्यक्षपदी नियुक्ती, कोण आहेत अमित साटम?</t>
+          <t>नांदेडमध्ये अशोक चव्हाणांना घेरण्यासाठी काँग्रेसची नवी खेळी; 'या' पक्षाशी करणार हातमिळवणी?</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!politics/bmc-election-2025-major-reshuffle-in-bjp-amit-satam-appointed-as-president-of-mumbai-bjp-know-political-reactions-his-profile-coroporate-job-to-politician-mhs25082501410</t>
+          <t>https://www.navarashtra.com/politics/congress-may-alliance-with-vba-party-in-nanded-for-upcoming-municipal-election-942211.html</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : अधिकाऱ्यांनी जर दिरंगाई केली असेल तर…; रविंद्र चव्हाणांचा कारवाईचा इशारा</t>
+          <t>Marathwada Politics : काँग्रेसला जोरदार धक्का, २ दिग्गज नेत्यांनी 'हात' सोडला, २४ तासांत कमळ हातात घेणार</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5163828/ravindra-chavans-warning-of-action-over-indrayani-river-bridge-collapsed-accident-cas/</t>
+          <t>https://saamtv.esakal.com/maharashtra/big-blow-to-congress-senior-leaders-kailas-gorantyal-and-suresh-warpudkar-set-to-join-bjp-ahead-of-local-polls-latest-news-nck90</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>नांदेडमध्ये अशोक चव्हाणांना घेरण्यासाठी काँग्रेसची नवी खेळी; 'या' पक्षाशी करणार हातमिळवणी?</t>
+          <t>शेकाप नेते जयंत पाटील यांच्या घरात राजकीय फूट; बंधू पंडित पाटील यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/congress-may-alliance-with-vba-party-in-nanded-for-upcoming-municipal-election-942211.html</t>
+          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Marathwada Politics : काँग्रेसला जोरदार धक्का, २ दिग्गज नेत्यांनी 'हात' सोडला, २४ तासांत कमळ हातात घेणार</t>
+          <t>Maharashtra Breaking News : काँग्रेसचे माजी आमदार कुणाल पाटलांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/big-blow-to-congress-senior-leaders-kailas-gorantyal-and-suresh-warpudkar-set-to-join-bjp-ahead-of-local-polls-latest-news-nck90</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-1st-july-maharashtra-assembly-monsoon-session-2025-of-devendra-fadanvis-eknath-shinde-uddhav-and-raj-thackeray-asc-95-5194810/</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>शेकाप नेते जयंत पाटील यांच्या घरात राजकीय फूट; बंधू पंडित पाटील यांचा भाजपात प्रवेश</t>
+          <t>Sanjay Jagtap : पुण्यात काँग्रेसला जोरदार झटका, संजय जगताप यांचा भाजपमध्ये प्रवेश | VIDEO</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
+          <t>https://saamtv.esakal.com/video/sanjay-jagtap-former-congress-mla-joins-bjp-in-grand-saswad-event-political-shift-in-pune-district-mrs01</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News : काँग्रेसचे माजी आमदार कुणाल पाटलांचा भाजपात प्रवेश</t>
+          <t>मिशन मुंबई, भाजप भाकरी फिरवणार अध्यक्षपदासाठी बैठक, दोन आमदारांनी नावे समोर</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-1st-july-maharashtra-assembly-monsoon-session-2025-of-devendra-fadanvis-eknath-shinde-uddhav-and-raj-thackeray-asc-95-5194810/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>Sanjay Jagtap : पुण्यात काँग्रेसला जोरदार झटका, संजय जगताप यांचा भाजपमध्ये प्रवेश | VIDEO</t>
+          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/sanjay-jagtap-former-congress-mla-joins-bjp-in-grand-saswad-event-political-shift-in-pune-district-mrs01</t>
+          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>मिशन मुंबई, भाजप भाकरी फिरवणार अध्यक्षपदासाठी बैठक, दोन आमदारांनी नावे समोर</t>
+          <t>राज्यात आणखी एक घराणं फुटलं; काँग्रेस खासदाराच्या दिराचा भाजपमध्ये प्रवेश, १० माजी नगरसेवकांनीही कमळ हाती घेतलं</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
+          <t>https://saamtv.esakal.com/maharashtra/anil-dhanorkar-joins-bjp-in-presence-of-ravindra-chavan-and-hansraj-ahir-along-with-10-corporators-in-chandrapur-bdk97</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>BJP vs MNS : कोकणात भाजपचा मनसेला मोठा धक्का; 'हा' नेता भाजपच्या वाटेवर</t>
+          <t>भाजपचा मविआला जोरदार धक्का, वसई-विरार अन् धाराशिवमध्ये राजकीय भूकंप, कोण कोणत्या नेत्यांनी साथ सोडली?</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/vaibhav-khedekar-a-member-of-mnss-konkan-unit-is-on-his-way-to-the-bjp</t>
+          <t>https://saamtv.esakal.com/maharashtra/major-jolt-to-mva-as-key-leaders-join-bjp-in-vasai-virar-and-dharashiv-nck90</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>राज्यात आणखी एक घराणं फुटलं; काँग्रेस खासदाराच्या दिराचा भाजपमध्ये प्रवेश, १० माजी नगरसेवकांनीही कमळ हाती घेतलं</t>
+          <t>'त्यांच्या प्रवेशामुळे पक्षाची ताकद वाढणार', हजारो समर्थकांसह संजय जगताप यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/anil-dhanorkar-joins-bjp-in-presence-of-ravindra-chavan-and-hansraj-ahir-along-with-10-corporators-in-chandrapur-bdk97</t>
+          <t>https://www.lokmat.com/pune/his-entry-will-increase-the-partys-strength-sanjay-jagtap-joins-bjp-with-thousands-of-supporters-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>भाजपचा मविआला जोरदार धक्का, वसई-विरार अन् धाराशिवमध्ये राजकीय भूकंप, कोण कोणत्या नेत्यांनी साथ सोडली?</t>
+          <t>Thane Politics: शहापुरात मोठी राजकीय उलथापालथ! मविआच्या २७ मोठ्या नेत्यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/major-jolt-to-mva-as-key-leaders-join-bjp-in-vasai-virar-and-dharashiv-nck90</t>
+          <t>https://saamtv.esakal.com/maharashtra/thane-politics-news-27-key-leaders-join-bjp-in-shahapur-major-blow-to-maha-vikas-aghadi-bdk97</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>'त्यांच्या प्रवेशामुळे पक्षाची ताकद वाढणार', हजारो समर्थकांसह संजय जगताप यांचा भाजपात प्रवेश</t>
+          <t>Ameet Satam : भाजपमध्ये मोठे फेरबदल ! मुंबई भाजपचे नवे अध्यक्ष अमित साटम, मुख्यमंत्र्यानी केली घोषणा</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/his-entry-will-increase-the-partys-strength-sanjay-jagtap-joins-bjp-with-thousands-of-supporters-a-a727/</t>
+          <t>https://www.jaimaharashtranews.com/politics/maharashtra-politics-ameet-satam-appointed-as-mumbai-president-of-bjp-cm-devendra-fadanvis-annonced-it-/40320</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
+          <t>Maharashtra Politics: शरद पवारांना मोठा झटका; नांदेडमधील ९ शिलेदारांनी धरली भाजपची वाट</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
+          <t>https://saamtv.esakal.com/maharashtra/political-earthquake-in-nanded-major-setback-for-sharad-pawar-in-nanded-as-9-key-supporters-join-bjp-latest-news-pvm91</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>Ameet Satam : भाजपमध्ये मोठे फेरबदल ! मुंबई भाजपचे नवे अध्यक्ष अमित साटम, मुख्यमंत्र्यानी केली घोषणा</t>
+          <t>पालघरमध्ये मोठी राजकीय घडामोड! एकनाथ शिंदेंना मोठा धक्का, बड्या नेत्यासह अनेक पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/maharashtra-politics-ameet-satam-appointed-as-mumbai-president-of-bjp-cm-devendra-fadanvis-annonced-it-/40320</t>
+          <t>https://saamtv.esakal.com/maharashtra/big-political-shift-in-palghar-major-leaders-join-bjp-setback-for-eknath-shinde-uddhav-thackeray-and-sharad-pawar-pvm91</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Thane Politics: शहापुरात मोठी राजकीय उलथापालथ! मविआच्या २७ मोठ्या नेत्यांचा भाजपात प्रवेश</t>
+          <t>Raigad News : महायुतीत वादाची ठिणगी पडणार? एकनाथ शिंदेंच्या शिवसेनेला भाजपचा धक्का</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/thane-politics-news-27-key-leaders-join-bjp-in-shahapur-major-blow-to-maha-vikas-aghadi-bdk97</t>
+          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>पालघरमध्ये मोठी राजकीय घडामोड! एकनाथ शिंदेंना मोठा धक्का, बड्या नेत्यासह अनेक पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
+          <t>पुण्यात शरद पवारांसह अजित पवारांना धक्का; भाजपने पाडले खिंडार, शेकडो कार्यकर्त्यांचा राष्ट्रवादीला रामराम</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/big-political-shift-in-palghar-major-leaders-join-bjp-setback-for-eknath-shinde-uddhav-thackeray-and-sharad-pawar-pvm91</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/big-blow-to-sharad-pawar-in-pune-bhor-and-mulshi-hundreds-of-workers-join-bjp-nck90</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: शरद पवारांना मोठा झटका; नांदेडमधील ९ शिलेदारांनी धरली भाजपची वाट</t>
+          <t>तीन टर्म आमदार राहिलेल्या नेत्याच्या हाती कमळ; भाजपनं वाढवलं बळ, शिंदेसेनेत खळबळ</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/political-earthquake-in-nanded-major-setback-for-sharad-pawar-in-nanded-as-9-key-supporters-join-bjp-latest-news-pvm91</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Raigad News : महायुतीत वादाची ठिणगी पडणार? एकनाथ शिंदेंच्या शिवसेनेला भाजपचा धक्का</t>
+          <t>Politics: कोल्हापुरात राजकीय भूकंप! काँग्रेस अन् राष्ट्रवादीला मोठा धक्का; बड्या नेत्यांसह कार्यकर्त्यांनी कमळ हाती घेतलं</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/major-political-shakeup-in-kolhapur-ex-congress-and-ncp-leaders-join-bjp-bdk97</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>पुण्यात शरद पवारांसह अजित पवारांना धक्का; भाजपने पाडले खिंडार, शेकडो कार्यकर्त्यांचा राष्ट्रवादीला रामराम</t>
+          <t>डोंबिवलीचे आमदार झाले भाजपाचे नवे प्रदेशाध्यक्ष! कल्याण डोंबिवलीत यंदा महापौर कोणाचा?</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/big-blow-to-sharad-pawar-in-pune-bhor-and-mulshi-hundreds-of-workers-join-bjp-nck90</t>
+          <t>https://www.lokmat.com/kalyan-dombivli/dombivli-mla-becomes-bjps-new-state-president-who-will-be-the-mayor-of-kalyan-dombivli-this-year-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>तीन टर्म आमदार राहिलेल्या नेत्याच्या हाती कमळ; भाजपनं वाढवलं बळ, शिंदेसेनेत खळबळ</t>
+          <t>Maharashtra Politics: महाविकास आघाडीला मोठं खिंडार, अनेक बडे नेते, संरपंचांसह पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-major-blow-to-mva-as-key-leaders-sarpanch-join-bjp-in-shahapur-pvm91</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>Politics: कोल्हापुरात राजकीय भूकंप! काँग्रेस अन् राष्ट्रवादीला मोठा धक्का; बड्या नेत्यांसह कार्यकर्त्यांनी कमळ हाती घेतलं</t>
+          <t>खान्देशची बुलंद तोफ भाजपात जाणार? पडद्यामागच्या घडामोडींनी काँग्रेसची चिंता वाढली</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/major-political-shakeup-in-kolhapur-ex-congress-and-ncp-leaders-join-bjp-bdk97</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>डोंबिवलीचे आमदार झाले भाजपाचे नवे प्रदेशाध्यक्ष! कल्याण डोंबिवलीत यंदा महापौर कोणाचा?</t>
+          <t>Dombivali Politics : भाजप प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला खिंडार; दोन नगरसेवकांचा राजीनामा</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kalyan-dombivli/dombivli-mla-becomes-bjps-new-state-president-who-will-be-the-mayor-of-kalyan-dombivli-this-year-a-a653/</t>
+          <t>https://www.esakal.com/mumbai/setback-for-bjp-in-state-vice-presidents-constituency-ravindra-chavan-as-two-corporators-vikas-mhatre-and-kavita-mhatre-resign-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: महाविकास आघाडीला मोठं खिंडार, अनेक बडे नेते, संरपंचांसह पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
+          <t>Mumbai BJP President : अमित साटम मुंबई भाजपचे नवे अध्यक्ष! प्रदेशाध्यक्ष रविंद्र चव्हाण यांची मोठी घोषणा...</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-major-blow-to-mva-as-key-leaders-sarpanch-join-bjp-in-shahapur-pvm91</t>
+          <t>https://www.esakal.com/mumbai/amit-satam-appointed-new-mumbai-bjp-president-devendra-fadnavis-announcement-spb94</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>खान्देशची बुलंद तोफ भाजपात जाणार? पडद्यामागच्या घडामोडींनी काँग्रेसची चिंता वाढली</t>
+          <t>ऑनलाइन हाजिरी लगा रहे भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण, अघाड़ी सम्मेलन में की जीत दिलाने की मांग</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
+          <t>https://navbharatlive.com/maharashtra/akola/aim-provide-health-services-vaidya-aghadi-conference-bjp-mahayuti-ravindra-chavan-1329683.html</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>Dombivali Politics : भाजप प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला खिंडार; दोन नगरसेवकांचा राजीनामा</t>
+          <t>भाजपा के कोर कमेटी बैठक में रवींद्र चव्हाण ने दिए निर्देश, चुनावी रणनीति और संगठन मजबूती पर की चर्चा</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/setback-for-bjp-in-state-vice-presidents-constituency-ravindra-chavan-as-two-corporators-vikas-mhatre-and-kavita-mhatre-resign-politics-pjp78</t>
+          <t>https://navbharatlive.com/maharashtra/garchiroli/election-strategy-strengthening-organization-ravindra-chavan-instructions-bjp-1326133.html</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>ऑनलाइन हाजिरी लगा रहे भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण, अघाड़ी सम्मेलन में की जीत दिलाने की मांग</t>
+          <t>Chandrashekhar Bawankule, Ravindra Chavan BJP State President</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/akola/aim-provide-health-services-vaidya-aghadi-conference-bjp-mahayuti-ravindra-chavan-1329683.html</t>
+          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>भाजपा के कोर कमेटी बैठक में रवींद्र चव्हाण ने दिए निर्देश, चुनावी रणनीति और संगठन मजबूती पर की चर्चा</t>
+          <t>डोंबिवली में पहलगाम हमले में मारे गए नागरिकों की स्मृति में बनेगा शहीद स्मारक, विधायक रविंद्र चव्हाण ने लिखा पत्र</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/garchiroli/election-strategy-strengthening-organization-ravindra-chavan-instructions-bjp-1326133.html</t>
+          <t>https://www.newsnationtv.com/--20250502182005/</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule, Ravindra Chavan BJP State President</t>
+          <t>भाजपला लवकरच मिळणार नवा प्रदेशाध्यक्ष; रविंद्र चव्हाण यांच्यावर सोपवणार जबाबदारी</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
+          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>डोंबिवली में पहलगाम हमले में मारे गए नागरिकों की स्मृति में बनेगा शहीद स्मारक, विधायक रविंद्र चव्हाण ने लिखा पत्र</t>
+          <t>Ravindra Chavan Appointed New BJP Maharashtra President : रविंद्र चव्हाण ठरले भाजपचे नवे कप्तान, महाराष्ट्राच्या संघटनाला नवे नेतृत्व</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/--20250502182005/</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>भाजपला लवकरच मिळणार नवा प्रदेशाध्यक्ष; रविंद्र चव्हाण यांच्यावर सोपवणार जबाबदारी</t>
+          <t>भाजपला आज मिळणार नवे प्रदेशाध्यक्ष; रवींद्र चव्हाण स्विकारणार सूत्र</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
+          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed New BJP Maharashtra President : रविंद्र चव्हाण ठरले भाजपचे नवे कप्तान, महाराष्ट्राच्या संघटनाला नवे नेतृत्व</t>
+          <t>मालवण मधील 'उबाठा' च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
+          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>भाजपला आज मिळणार नवे प्रदेशाध्यक्ष; रवींद्र चव्हाण स्विकारणार सूत्र</t>
+          <t>Ravindra Chavan होणार महाराष्ट्र भाजपचे नवे प्रदेशाध्यक्ष, ठाकरेंच्या गडात होणार पहिलं शक्तिप्रदर्शन!</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>मालवण मधील 'उबाठा' च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश</t>
+          <t>भोर, मुळशी तालुक्यातील विविध पक्षातील कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
+          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>Ravindra Chavan होणार महाराष्ट्र भाजपचे नवे प्रदेशाध्यक्ष, ठाकरेंच्या गडात होणार पहिलं शक्तिप्रदर्शन!</t>
+          <t>शहापूर तालुक्यातील उबाठा, शरद पवार गट व काँग्रेसच्या अनेक कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
+          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>शहापूर तालुक्यातील उबाठा, शरद पवार गट व काँग्रेसच्या अनेक कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>कल्याण – डोंबिवली , चंद्रपूर जिल्ह्यातील अनेक माजी नगरसेवकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
+          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>कल्याण – डोंबिवली , चंद्रपूर जिल्ह्यातील अनेक माजी नगरसेवकांचा भाजपात प्रवेश</t>
+          <t>मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
+          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>BJP President Banner: भाजप प्रदेशाध्यक्षांच्या निवडीचे बॅनर फाडले... - देशोन्नती</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
+          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>BJP President Banner: भाजप प्रदेशाध्यक्षांच्या निवडीचे बॅनर फाडले... - देशोन्नती</t>
+          <t>रविंद्र शिंदेंचा भाजपमध्ये धडाकेबाज प्रवेश; चंद्रपूरच्या राजकारणाला कलाटणी!</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
+          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>रविंद्र शिंदेंचा भाजपमध्ये धडाकेबाज प्रवेश; चंद्रपूरच्या राजकारणाला कलाटणी!</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण; अधिकृत घोषणा आज होणार</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/ravindra-chavan-to-be-bjp-maharashtra-president-announcement-soon</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण; अधिकृत घोषणा आज होणार</t>
+          <t>Ravindra Chavan MaTa Katta : ठाकरे बंधूंची युती निश्चित, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण म्हणाले, भावनात्मक मुद्द्यांवर कुणाला...</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/ravindra-chavan-to-be-bjp-maharashtra-president-announcement-soon</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>Ravindra Chavan MaTa Katta : ठाकरे बंधूंची युती निश्चित, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण म्हणाले, भावनात्मक मुद्द्यांवर कुणाला...</t>
+          <t>डोंबिवलीत बुधवारी भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचा जनता दरबार</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
+          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-janta-darbar-in-dombivli-on-wednesday-ssb-93-5314946/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>डोंबिवलीत बुधवारी भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचा जनता दरबार</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण, १ जुलैला घोषणा; किरण रिजिजू निरीक्षक</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-janta-darbar-in-dombivli-on-wednesday-ssb-93-5314946/</t>
+          <t>https://www.lokmat.com/mumbai/ravindra-chavan-to-be-bjp-maharashtra-state-president-announcement-on-july-1-kiren-rijiju-observer-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण, १ जुलैला घोषणा; किरण रिजिजू निरीक्षक</t>
+          <t>Ravindra Chavan: भाजपमध्ये आता चव्हाणपर्व, रवींद्र चव्हाण बनले नवे भाजपचे प्रदेशाध्यक्ष!</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ravindra-chavan-to-be-bjp-maharashtra-state-president-announcement-on-july-1-kiren-rijiju-observer-a-a571/</t>
+          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>BJP State President : भाजपा प्रदेशाध्यक्षांची 1 जुलै रोजी निवड; रवींद्र चव्हाणांची वर्णी लागणार?</t>
+          <t>डोंंबिवलीच्या विकासाला ग्रहण लावणाऱ्या ‘चाँदभाई’चे नाव घ्या; राजू पाटील यांचे भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांना आवाहन</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/the-election-of-bjp-state-president-will-be-held-on-july-1-and-ravindra-chavan-is-likely-to-be-the-candidate/897175/</t>
+          <t>https://www.loksatta.com/thane/mns-leader-raju-patil-slams-bjp-state-chief-ravindra-chavan-for-his-bjp-mayor-in-kdmc-remark-zws-70-5279498/</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजपमध्ये आता चव्हाणपर्व, रवींद्र चव्हाण बनले नवे भाजपचे प्रदेशाध्यक्ष!</t>
+          <t>BJP Politics : भाजप प्रदेशाध्यक्षांच्या ठाकरेंना दे धक्का! बालेकिल्ल्यात 'डॅमेज कंट्रोल', विकास म्हात्रेंचे मन वळवले</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-ravindra-chavan-successfully-resolves-vikas-mhatre-disconten-shivsen-ubt-rm89</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>डोंंबिवलीच्या विकासाला ग्रहण लावणाऱ्या ‘चाँदभाई’चे नाव घ्या; राजू पाटील यांचे भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांना आवाहन</t>
+          <t>Photo : प्रदेशाध्यक्ष पदाची सूत्रे स्वीकारताच रवींद्र चव्हाण अ‍ॅक्टिव्ह; म्हणाले…</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/mns-leader-raju-patil-slams-bjp-state-chief-ravindra-chavan-for-his-bjp-mayor-in-kdmc-remark-zws-70-5279498/</t>
+          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>BJP Politics : भाजप प्रदेशाध्यक्षांच्या ठाकरेंना दे धक्का! बालेकिल्ल्यात 'डॅमेज कंट्रोल', विकास म्हात्रेंचे मन वळवले</t>
+          <t>अधिवेशन, कायदा-सुव्यवस्था राखण्यासाठी हिंदीची सक्ती रद्द, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-ravindra-chavan-successfully-resolves-vikas-mhatre-disconten-shivsen-ubt-rm89</t>
+          <t>https://www.loksatta.com/mumbai/bjp-ravindra-chavan-says-hindi-compulsion-decision-withdrawn-due-to-assembly-session-and-law-and-order-mumbai-print-news-css-98-5217714/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>Photo : प्रदेशाध्यक्ष पदाची सूत्रे स्वीकारताच रवींद्र चव्हाण अ‍ॅक्टिव्ह; म्हणाले…</t>
+          <t>BJP State President Election | भाजपकडून प्रदेशाध्यक्ष पदासाठी निवडणूक कार्यक्रम जाहीर</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>अधिवेशन, कायदा-सुव्यवस्था राखण्यासाठी हिंदीची सक्ती रद्द, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
+          <t>मालवणमधील 'उबाठा'च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश, भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले स्वागत</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-ravindra-chavan-says-hindi-compulsion-decision-withdrawn-due-to-assembly-session-and-law-and-order-mumbai-print-news-css-98-5217714/</t>
+          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>BJP State President Election | भाजपकडून प्रदेशाध्यक्ष पदासाठी निवडणूक कार्यक्रम जाहीर</t>
+          <t>Sindhudurg Politics | सिंधुदुर्ग जिल्हा व भाजपसाठी आज आनंदाचा दिवस!</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-bjp-state-president-sindhudurg-politics-sp96</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>मालवणमधील 'उबाठा'च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश, भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले स्वागत</t>
+          <t>Devendra Fadnavis |महाराष्‍ट्र विकसित करुन दाखवू : मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
+          <t>https://pudhari.news/maharashtra/mumbai/lets-develop-maharashtra-chief-minister-devendra-fadnavis-ng81</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>Sindhudurg Politics | सिंधुदुर्ग जिल्हा व भाजपसाठी आज आनंदाचा दिवस!</t>
+          <t>वसई-विरारच्या ‘बविआ’ च्या माजी नगसेवक आणि कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-bjp-state-president-sindhudurg-politics-sp96</t>
+          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis |महाराष्‍ट्र विकसित करुन दाखवू : मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांच्या हस्ते ‘ध्येयवादी देवेंद्रजी’ कॉफी टेबल बुकचे प्रकाशन</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/lets-develop-maharashtra-chief-minister-devendra-fadnavis-ng81</t>
+          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>वसई-विरारच्या ‘बविआ’ च्या माजी नगसेवक आणि कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>Kedar Jadhav makes bold prediction about India playing Pakistan in Asia Cup</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
+          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांच्या हस्ते ‘ध्येयवादी देवेंद्रजी’ कॉफी टेबल बुकचे प्रकाशन</t>
+          <t>4 ex-Congress corporators join BJP in Kalyan-Dombivli</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>भोर, मुळशी तालुक्यातील विविध पक्षातील कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>Kedar Jadhav makes bold prediction about India playing Pakistan in Asia Cup</t>
+          <t>BJP inducts key PWP leaders before local body elections</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>4 ex-Congress corporators join BJP in Kalyan-Dombivli</t>
+          <t>Former Congress MLA Kunal Patil joins BJP</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/former-congress-mla-kunal-patil-joins-bjp-10100556/</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
+          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BJP inducts key PWP leaders before local body elections</t>
+          <t>BJP picks new state chiefs, moves closer to electing JP Nadda's successor</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
+          <t>https://www.indiatoday.in/india/story/with-new-state-presidents-bjp-gears-up-to-choose-jp-nadda-successor-2748768-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
+          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>BJP picks new state chiefs, moves closer to electing JP Nadda's successor</t>
+          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/with-new-state-presidents-bjp-gears-up-to-choose-jp-nadda-successor-2748768-2025-07-01</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
+          <t>Maharashtra Cabinet Reshuffle: Fadnavis Meets Amit Shah, Nadda Amid Speculation</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>After poll drubbing, Prithviraj Chavan may replace Patole in Maharashtra Congress rejig</t>
+          <t>Mumbai Confidential: Brother trouble</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jan/14/after-poll-drubbing-prithviraj-chavan-may-replace-patole-in-maharashtra-congress-rejig</t>
+          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Maharashtra Cabinet Reshuffle: Fadnavis Meets Amit Shah, Nadda Amid Speculation</t>
+          <t>Pune Congress leader Sanjay Jagtap joins BJP</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
+          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
         </is>
       </c>
     </row>
@@ -4331,408 +4331,408 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Dombivli MLA Ravindra Chavan Takes Charge as New Maharashtra BJP President, Replacing Chandrashekhar Bawankule</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/dombivli-mla-ravindra-chavan-takes-charge-as-new-maharashtra-bjp-president-replacing-chandrashekhar-bawankule-a475/</t>
+          <t>https://www.lokmattimes.com/national/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>Ameet Satam Appointed As Mumbai BJP President Ahead of BMC Polls</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://www.lokmattimes.com/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls-a517/</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP State Chief Ravindra Chavan Meets PM Modi, Outlines Party’s Expansion Plan</t>
+          <t>Maharashtra Politics: Ex-Congress MLA Sanjay Jagtap Joins BJP With Supporters In Pune; Congress Hits Out,</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-state-chief-ravindra-chavan-meets-pm-modi-outlines-partys-expansion-plan</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ex-congress-mla-sanjay-jagtap-joins-bjp-with-supporters-in-pune-congress-hits-out-calls-bjp-witch-party-video</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: A Visionary Leader Strengthening Maharashtra BJP's Political Landscape</t>
+          <t>Maharashtra News: Former Congress MLA Sangram Thopte From Punes Bhor Joins BJP After Setback In 2024 Assembly</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-former-congress-mla-sangram-thopte-from-punes-bhor-joins-bjp-after-setback-in-2024-assembly-elections</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Ameet Satam Appointed As Mumbai BJP President Ahead of BMC Polls</t>
+          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls-a517/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Ex-Congress MLA Sanjay Jagtap Joins BJP With Supporters In Pune; Congress Hits Out,</t>
+          <t>Maharashtra Politics: State Congress Secretary Dilip Bhalerao, Along With Hundreds Of Supporters, Joins BJP</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ex-congress-mla-sanjay-jagtap-joins-bjp-with-supporters-in-pune-congress-hits-out-calls-bjp-witch-party-video</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-state-congress-secretary-dilip-bhalerao-along-with-hundreds-of-supporters-joins-bjp</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Maharashtra News: Former Congress MLA Sangram Thopte From Punes Bhor Joins BJP After Setback In 2024 Assembly</t>
+          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-former-congress-mla-sangram-thopte-from-punes-bhor-joins-bjp-after-setback-in-2024-assembly-elections</t>
+          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: State Congress Secretary Dilip Bhalerao, Along With Hundreds Of Supporters, Joins BJP</t>
+          <t>Maharashtra Politics: Former Congress Minister Suresh Warpudkar Joins BJP With Key Supporters</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-state-congress-secretary-dilip-bhalerao-along-with-hundreds-of-supporters-joins-bjp</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-minister-suresh-warpudkar-joins-bjp-with-key-supporters</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
+          <t>Congress Receives A Jolt After Former Dhule MLA Kunal Patil Joins BJP</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
+          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Former Congress Minister Suresh Warpudkar Joins BJP With Key Supporters</t>
+          <t>Maharashtra Politics: BJP Appoints 58 New District Presidents Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-minister-suresh-warpudkar-joins-bjp-with-key-supporters</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Congress Receives A Jolt After Former Dhule MLA Kunal Patil Joins BJP</t>
+          <t>Ramchander Rao appointed as T'gana BJP President despite opposition: MP gets new chief as Hemant Khandelwal...</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
+          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP Appoints 58 New District Presidents Ahead Of Local Body Polls</t>
+          <t>BJP announces new state chiefs in 7 states, 2 UTs; moves closer to elect national president</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
+          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Ramchander Rao appointed as T'gana BJP President despite opposition: MP gets new chief as Hemant Khandelwal...</t>
+          <t>Pune MP Murlidhar Mohol Launches City’s First 24×7 Digital Citizen Service Office</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
+          <t>https://www.mypunepulse.com/pune-mp-murlidhar-mohol-launches-citys-first-24x7-digital-citizen-service-office/</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BJP announces new state chiefs in 7 states, 2 UTs; moves closer to elect national president</t>
+          <t>BJP Appoints New State Presidents in 9 States Including Maharashtra and Madhya Pradesh</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
+          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>BJP Steps Closer To Electing National President, List Of State Chiefs Out</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://www.newsx.com/india/who-is-the-new-bjp-party-president-list-of-state-party-president-out-11032/</t>
+          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>Ex Minister Ravindra Chavan Files Nomination For Maharashtra BJP Chief Post</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
+          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>Ex Minister Ravindra Chavan Files Nomination For Maharashtra BJP Chief Post</t>
+          <t>BJP leader Ravindra Chavan appointed as new state president of Maharashtra</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
+          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>BJP leader Ravindra Chavan appointed as new state president of Maharashtra</t>
+          <t>Pune bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
+          <t>https://m.economictimes.com/news/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/articleshow/121904713.cms</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Once UAPA accused over Dawood ‘links’, Sena (UBT) leader finds place in BJP ahead of Nashik civic polls</t>
+          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/uapa-accused-dawood-links-sena-ubt-leader-in-bjp-nashik-civic-polls-10074232/</t>
+          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>"Double-engine govt working in people's best interests": New Maharashtra BJP chief Ravindra Chavan</t>
+          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>Kailas Gorantyal Set to Join BJP Today</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/06/30/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/?utm_source=rss&amp;utm_medium=rss&amp;utm_campaign=ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow</t>
+          <t>https://english.lokshahi.com/politics/kailash-gorantyal-to-join-bjp-today</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
+          <t>https://www.socialnews.xyz/2025/06/30/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>Maharashtra News: BJP Sets Up 1,221 Mandals Across State, Appoints 963 Presidents Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-sets-up-1221-mandals-across-state-appoints-963-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>सीएम फडणवीस के विश्वासपात्र...रवींद्र चव्हाण महाराष्ट्र भाजपा के नए प्रदेश अध्यक्ष</t>
+          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
+          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Maharashtra: बीजेपी ने महाराष्ट्र में बता दिया कौन बनेगा प्रदेश अध्यक्ष? BMC चुनावों से पहले मराठी दांव</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
+          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>Former Minister Ravindra Chavan Appointed Maharashtra BJP Working President</t>
+          <t>सीएम फडणवीस के विश्वासपात्र...रवींद्र चव्हाण महाराष्ट्र भाजपा के नए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/former-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-9185878.html</t>
+          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>कौन बनेगा महाराष्ट्र भाजपा का अध्यक्ष? इस नाम का चुना जाना लगभग तय</t>
+          <t>Maharashtra: बीजेपी ने महाराष्ट्र में बता दिया कौन बनेगा प्रदेश अध्यक्ष? BMC चुनावों से पहले मराठी दांव</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी की कमान अब नए हाथों में, जानिए कौन हैं पार्टी के नवनियुक्त प्रदेश अध्यक्ष रवींद्र चव्हाण</t>
+          <t>Former Minister Ravindra Chavan Appointed Maharashtra BJP Working President</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
+          <t>https://www.news18.com/politics/former-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-9185878.html</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
+          <t>कौन बनेगा महाराष्ट्र भाजपा का अध्यक्ष? इस नाम का चुना जाना लगभग तय</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888548</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>पूर्व मंत्री रवींद्र चव्हाण बने महाराष्ट्र BJP के कार्यकारी प्रदेश अध्यक्ष, बावनकुले की कुर्सी छिनी</t>
+          <t>महाराष्ट्र बीजेपी की कमान अब नए हाथों में, जानिए कौन हैं पार्टी के नवनियुक्त प्रदेश अध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp-3054565.html</t>
+          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपचे प्रदेश कार्यकारी अध्यक्ष होताच रवींद्र चव्हाण अनवाणी पायाने</t>
+          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
+          <t>https://www.asianage.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888548</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP को मिलेगा नया चेहरा; चंद्रशेखर बावनकुले के बाद रवींद्र चव्हाण का नाम सबसे आगे, रिजिजू की निगरानी में होगा ऐलान</t>
+          <t>पूर्व मंत्री रवींद्र चव्हाण बने महाराष्ट्र BJP के कार्यकारी प्रदेश अध्यक्ष, बावनकुले की कुर्सी छिनी</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://sudarshannews.in/news-detail.aspx?id=129159</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp-3054565.html</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>भारतीय जनता पार्टीचे नवे प्रदेशाध्यक्ष म्हणून रवींद्र चव्हाण यांची बिनविरोध निवड</t>
+          <t>Ravindra Chavan : भाजपचे प्रदेश कार्यकारी अध्यक्ष होताच रवींद्र चव्हाण अनवाणी पायाने</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>कौन हैं महाराष्ट्र भाजपा के नए अध्यक्ष रवींद्र चव्हाण, क्या होंगी उनके लिए चुनौतियां</t>
+          <t>महाराष्ट्र BJP को मिलेगा नया चेहरा; चंद्रशेखर बावनकुले के बाद रवींद्र चव्हाण का नाम सबसे आगे, रिजिजू की निगरानी में होगा ऐलान</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://hindi.webdunia.com/maharashtra/who-is-maharashtra-bjp-new-president-ravindra-chavan-know-125070100083_1.html</t>
+          <t>https://sudarshannews.in/news-detail.aspx?id=129159</t>
         </is>
       </c>
     </row>
@@ -4751,144 +4751,144 @@
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>Ravindra Chavan News : मंत्रिमंडळात मोठे फेरबदल, 8 जणांना डच्चू मिळणार का? अखेर रवींद्र चव्हाण यांनीच केलं क्लिअर</t>
+          <t>भारतीय जनता पार्टीचे नवे प्रदेशाध्यक्ष म्हणून रवींद्र चव्हाण यांची बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/maharashtra-cabinet-reshuffle-2025-ministers-remove-ravindra-chavan-clarification-rm82</t>
+          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>महाराष्ट्र लोकल बॉडी चुनावों को लेकर बड़ा अपडेट, बीजेपी, शिंदे और अजित पवार में रहेगा गठबंधन या फिर टूटेगा, जानें</t>
+          <t>Ravindra Chavan News : मंत्रिमंडळात मोठे फेरबदल, 8 जणांना डच्चू मिळणार का? अखेर रवींद्र चव्हाण यांनीच केलं क्लिअर</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://sarkarnama.esakal.com/mumbai/maharashtra-cabinet-reshuffle-2025-ministers-remove-ravindra-chavan-clarification-rm82</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपने प्रदेशाध्यक्षपद देऊन माझ्यावर उपकार केले, माझी ओळख...; रवींद्र चव्हाणांची पक्षावर स्तुतीसुमने</t>
+          <t>महाराष्ट्र लोकल बॉडी चुनावों को लेकर बड़ा अपडेट, बीजेपी, शिंदे और अजित पवार में रहेगा गठबंधन या फिर टूटेगा, जानें</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-bjp-ravindra-chavan-new-president-ravindra-chavan-speech-latest-marathi-news-pp0731</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Kunal Patil News: शिवसेना उद्धव ठाकरे, काँग्रेसला धुळ्यात भाजप एकाच वेळी धक्का देण्याच्या तयारीत?</t>
+          <t>Ravindra Chavan : भाजपने प्रदेशाध्यक्षपद देऊन माझ्यावर उपकार केले, माझी ओळख...; रवींद्र चव्हाणांची पक्षावर स्तुतीसुमने</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/kunal-patil-politics-congress-leader-kunal-patil-shiv-senas-shubhangi-patil-are-on-the-path-to-bjp-sd67</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-bjp-ravindra-chavan-new-president-ravindra-chavan-speech-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>Kedar Jadhav : केदार जाधव क्रिकेटच्या मैदानातून राजकीय आखाड्यात, भाजपमध्ये प्रवेश करणार,</t>
+          <t>अशोक चव्हाण यांचा आत्मविश्वास ढासळला, नांदेडमधील काँग्रेस नेत्यांची भाजपावर टीका</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mp-ashok-chavan-meeting-leaders-shows-shaken-confidence-said-congress-mp-ravindra-chavan-sud-02-5112129/</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>कुंडमळा पुलासाठी आठ कोटी मंजूर, सही ८० हजाराच्या पत्रावर…, संजय राऊत यांचा रवींद्र चव्हाण...</t>
+          <t>Kunal Patil News: शिवसेना उद्धव ठाकरे, काँग्रेसला धुळ्यात भाजप एकाच वेळी धक्का देण्याच्या तयारीत?</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/shiv-sena-ubt-leader-sanjay-raut-criticizes-minister-ravindra-chavan-1424686.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/kunal-patil-politics-congress-leader-kunal-patil-shiv-senas-shubhangi-patil-are-on-the-path-to-bjp-sd67</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>इंतजार खत्म... बीजेपी ने चार राज्यों में अपने प्रदेश अध्यक्षों के नाम फाइनल किए, जानें कौन है लिस्ट में</t>
+          <t>Kedar Jadhav : केदार जाधव क्रिकेटच्या मैदानातून राजकीय आखाड्यात, भाजपमध्ये प्रवेश करणार,</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
+          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>स्थानिक नेत्यांशी चर्चा करुन अन्य पक्षातील नेत्यांना प्रवेश देणार; सरकारला पक्षसंघटनेचे पाठबळ देणार,भाजप नवे प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
+          <t>कुंडमळा पुलासाठी आठ कोटी मंजूर, सही ८० हजाराच्या पत्रावर…, संजय राऊत यांचा रवींद्र चव्हाण...</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/newly-appointed-state-president-ravindra-chavan-stated-while-talking-to-loksatta-print-politics-news-phm-00-5196663/</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/shiv-sena-ubt-leader-sanjay-raut-criticizes-minister-ravindra-chavan-1424686.html</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>पुण्यासह पश्चिम महाराष्ट्रावर भाजपचे लक्ष; प्रदेशाध्यक्षांनी पदाधिकाऱ्यांना काय दिल्या सूचना?…</t>
+          <t>स्थानिक नेत्यांशी चर्चा करुन अन्य पक्षातील नेत्यांना प्रवेश देणार; सरकारला पक्षसंघटनेचे पाठबळ देणार,भाजप नवे प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
+          <t>https://www.loksatta.com/politics/newly-appointed-state-president-ravindra-chavan-stated-while-talking-to-loksatta-print-politics-news-phm-00-5196663/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President Announcement : भाजपचं ठरलं! प्रदेशाध्यक्षाची लवकरच घोषणा; मुंबई अध्यक्षपदासाठी 'ही' तीन नावे चर्चेत</t>
+          <t>पुण्यासह पश्चिम महाराष्ट्रावर भाजपचे लक्ष; प्रदेशाध्यक्षांनी पदाधिकाऱ्यांना काय दिल्या सूचना?…</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/bjp-to-announce-maharashtra-president-soon-3-names-in-contention-for-mumbai-post-sw79</t>
+          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>मोदी सरकारच्या अकरा वर्षाच्या काळात २५ कोटी कुटुंबं दारिद्र्य रेषेबाहेर; रवींद्र चव्हाण यांची माहिती</t>
+          <t>BJP Maharashtra President Announcement : भाजपचं ठरलं! प्रदेशाध्यक्षाची लवकरच घोषणा; मुंबई अध्यक्षपदासाठी 'ही' तीन नावे चर्चेत</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/bjp-to-announce-maharashtra-president-soon-3-names-in-contention-for-mumbai-post-sw79</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>भाजपच्या संघटन बांधणीला नवे बळ 963 मंडळ अध्यक्षांच्या नियुक्त्या पूर्ण रवींद्र</t>
+          <t>मोदी सरकारच्या अकरा वर्षाच्या काळात २५ कोटी कुटुंबं दारिद्र्य रेषेबाहेर; रवींद्र चव्हाण यांची माहिती</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
+          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
         </is>
       </c>
     </row>
@@ -4907,60 +4907,60 @@
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>Sanjay Jagtap: संजय जगताप यांचा भाजपमध्ये पक्षप्रवेश आगामी निवडणुकीआधी काँग्रेसला</t>
+          <t>भाजपच्या संघटन बांधणीला नवे बळ 963 मंडळ अध्यक्षांच्या नियुक्त्या पूर्ण रवींद्र</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: बीजेपी ने 58 जिला अध्यक्षों के नाम किए घोषित, अब मुंबई अध्यक्ष की बारी, देखें पूरी लिस्ट</t>
+          <t>Sanjay Jagtap: संजय जगताप यांचा भाजपमध्ये पक्षप्रवेश आगामी निवडणुकीआधी काँग्रेसला</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>चंद्रशेखर बावनकुळेंकडून स्वीकारली सूत्रे; महापालिका, जिल्हा परिषद निवडणुकीचे आव्हान: फडणवीसांचे निकटवर्तीय ...</t>
+          <t>Maharashtra BJP: बीजेपी ने 58 जिला अध्यक्षों के नाम किए घोषित, अब मुंबई अध्यक्ष की बारी, देखें पूरी लिस्ट</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/fadnavis-close-aide-ravindra-chavan-becomes-bjp-state-president-accepts-responsibility-from-chandrashekhar-bawankule-challenge-for-municipal-zilla-parishad-elections-135355331.html</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
+          <t>चंद्रशेखर बावनकुळेंकडून स्वीकारली सूत्रे; महापालिका, जिल्हा परिषद निवडणुकीचे आव्हान: फडणवीसांचे निकटवर्तीय ...</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/fadnavis-close-aide-ravindra-chavan-becomes-bjp-state-president-accepts-responsibility-from-chandrashekhar-bawankule-challenge-for-municipal-zilla-parishad-elections-135355331.html</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात राजकीय भूकंप घडवण्यात रवींद्र चव्हाणांचा मोठा वाटा, भाजपच्या नव्या प्रदेशाध्यक्षांची A टू Z कारकीर्द</t>
+          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
+          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
         </is>
       </c>
     </row>
@@ -4979,36 +4979,36 @@
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>मुंबई भाजप अध्यक्षपदी अमित साटम: रवींद्र चव्हाण, फडणवीसांनी केली घोषणा; मुंबई महापालिका निवडणुकीच्या तोंडाव...</t>
+          <t>MCA Election | रवींद्र चव्हाण MCA च्या मैदानात? दिल्ली दौऱ्यानंतर चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-president-amit-satam-appointed-ahead-bmc-election-135756496.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>भाजपला घमेंडी म्हणणाऱ्यांना शिंदेसेनेचे नेते समज देतील: रवींद्र चव्हाण</t>
+          <t>मुंबई भाजप अध्यक्षपदी अमित साटम: रवींद्र चव्हाण, फडणवीसांनी केली घोषणा; मुंबई महापालिका निवडणुकीच्या तोंडाव...</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/chhatrapati-sambhajinagar/shinde-sena-leaders-will-explain-to-those-who-call-bjp-arrogant-ravindra-chavan-a-a320/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-president-amit-satam-appointed-ahead-bmc-election-135756496.html</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में कांग्रेस को बड़ा झटका, यह पूर्व मंत्री अब बीजेपी में हुए शामिल,</t>
+          <t>भाजपला घमेंडी म्हणणाऱ्यांना शिंदेसेनेचे नेते समज देतील: रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/parbhani-congress-leader-suresh-warpudkar-joins-bjp-with-supporters-ahead-of-nagar-nikay-chunav-2987557</t>
+          <t>https://www.lokmat.com/chhatrapati-sambhajinagar/shinde-sena-leaders-will-explain-to-those-who-call-bjp-arrogant-ravindra-chavan-a-a320/</t>
         </is>
       </c>
     </row>
@@ -5039,1248 +5039,1284 @@
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>MCA Election | रवींद्र चव्हाण MCA च्या मैदानात? दिल्ली दौऱ्यानंतर चर्चांना उधाण</t>
+          <t>Sthanik Swarajya Sanstha :स्थानिक स्वराज्य संस्था निवडणुकांनंतर Ravindra Chavan प्रदेशाध्यक्ष?</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-bjp-party-maharashtra-state-president-after-sthanik-swarajya-sanstha-election-chandrashekhar-bawankule-maharashtra-news-12-jan-2025-abp-majha-1338092</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
+          <t>Ravindra Chavan : चव्हाण पेलणार का आव्हान!</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
+          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>BJP President : भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण निश्चित; मुंबई अध्यक्षपदी दरेकर शक्य</t>
+          <t>Maharashtra BJP: अखेर प्रतीक्षा संपली! बावनकुळेंनंतर भाजपला नवा धडाकेबाज प्रदेशाध्यक्ष मिळाला</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-president-ravindra-chavan-and-pravin-darekar-mumbai-president-politics-pjp78</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-appointed-bjp-maharashtra-new-president-dk88</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>डोंबिवलीतील विकास म्हात्रे यांचा भाजपमध्येच मुक्काम; मुख्यमंत्री देवेंद्र फडणवीस, प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घेतली भेट</t>
+          <t>प्रसिद्धीपासून दूर, कामगिरीवर भर; भाजप प्रदेशाध्यक्षांचा अनोखा नागपूर दौरा</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/vikas-mhatre-from-dombivli-met-chief-minister-devendra-fadnavis-and-state-president-ravindra-chavan-amy-95-5214180/</t>
+          <t>https://www.loksatta.com/politics/ravindra-chavan-nagpur-visit-keeps-media-in-dark-highlights-bjps-new-low-key-strategy-skips-publicity-focuses-on-groundwork-print-political-news-vsd-99-5252822/</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>‘एमएमआर’ क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा, प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
+          <t>Nitesh Rane : राणेंच्या वक्तव्याचा भाजपच्या कार्यकारी अध्यक्षांना फटका... पत्रकार परिषदच गुंडाळण्याची वेळ!</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjps-ravindra-chavan-instructed-mumbai-officials-to-implement-slum-rehabilitation-scheme-effectively-sud-02-4933709/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/nagpur-nitesh-rane-remark-ravindra-chavan-press-conference-disruption-bjp-controversy-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Municipal Election: पालिका निवडणुकीसाठी भाजपची जय्यत तयारी सुरू, माजी खासदार आणि आमदारांवर सोपवली मोठी जबाबदारी</t>
+          <t>Ravindra Chavan : महाराष्ट्रात भाजपला मिळाला नवा कॅप्टन; प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची...</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-has-entrusted-responsibility-of-municipal-elections-in-maharashtra-to-former-mps-and-mlas-vru98</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : साधू महंतांसह भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण श्रीमलंगगडावर</t>
+          <t>Ravindra Chavan : रवींद्र चव्हाण यांचे नाव आज प्रदेशाध्यक्षपदी जाहीर</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/raigad/ravindra-chavan-visits-malanggad-with-sadhus-and-bjp-leaders-ab96</t>
+          <t>https://www.esakal.com/mumbai/ravindra-chavan-to-be-announced-as-bjp-maharashtra-state-president-vsb99</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Thackeray Shiv Sena Setback | ठाकरे शिवसेनेला मालवण शहरात खिंडार</t>
+          <t>Maharashtra BJP: भाजपची मोर्चेबांधणी; स्थानिक निवडणुकांसाठी माजी खासदार, आमदारांची महत्त्वपूर्ण बैठक</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/malvan-shiv-sena-defection-bjp-joining-ravindra-chavan-sp96</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-state-president-ravindra-chavan-held-meeting-former-mps-mlas-for-preparation-upcoming-local-body-elections/articleshow/123032835.cms</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>Ravindra Chavan यांचा शिवसेना उबाठाला धक्का, कामगार संघटनेचे दीड हजार सदस्यांचा भाजपमध्ये प्रवेश..</t>
+          <t>BJP President : भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण निश्चित; मुंबई अध्यक्षपदी दरेकर शक्य</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-s-shiv-sena-ubatha-is-in-trouble-1500-members-of-the-workers-union-join-bjp-1051360.html</t>
+          <t>https://www.esakal.com/maharashtra/bjp-president-ravindra-chavan-and-pravin-darekar-mumbai-president-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>Ravindra Chavan भाजपा हीच माझी ओळख म्हणणारे रवींद्र चव्हाण महाराष्ट्र भाजपच्या प्रदेशाध्यक्षपदी!!</t>
+          <t>डोंबिवलीतील विकास म्हात्रे यांचा भाजपमध्येच मुक्काम; मुख्यमंत्री देवेंद्र फडणवीस, प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घेतली भेट</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
+          <t>https://www.loksatta.com/thane/vikas-mhatre-from-dombivli-met-chief-minister-devendra-fadnavis-and-state-president-ravindra-chavan-amy-95-5214180/</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>कल्याणमध्ये काँग्रेसला खिंडार! बडे नेते भाजपवासी; प्रदेशाध्यक्षांनी दिले मोठे संकेत</t>
+          <t>‘एमएमआर’ क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा, प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/bjp-grows-stronger-in-kalyan-congress-leaders-join-ravindra-chavan-hints-at-contesting-solo-bdk97</t>
+          <t>https://www.loksatta.com/thane/bjps-ravindra-chavan-instructed-mumbai-officials-to-implement-slum-rehabilitation-scheme-effectively-sud-02-4933709/</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: ऑपरेशन एकनाथ शिंदेंमध्ये मोठी जबाबदारी ते फडणवीस मुख्यमंत्री होणार नाहीत</t>
+          <t>Municipal Election: पालिका निवडणुकीसाठी भाजपची जय्यत तयारी सुरू, माजी खासदार आणि आमदारांवर सोपवली मोठी जबाबदारी</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
+          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-has-entrusted-responsibility-of-municipal-elections-in-maharashtra-to-former-mps-and-mlas-vru98</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan: रवींद्र चव्हाण बनले महाराष्ट्र भाजपचे कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा यांची घोषणा Who is Ravindra Chavan Ravindra Chavan becomes the working president of Maharashtra BJP Natio</t>
+          <t>Ravindra Chavan : साधू महंतांसह भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण श्रीमलंगगडावर</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
+          <t>https://pudhari.news/maharashtra/raigad/ravindra-chavan-visits-malanggad-with-sadhus-and-bjp-leaders-ab96</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण ; सावंतवाडीत कार्यकर्त्यांचा जल्लोष</t>
+          <t>अतुल भोसले सातारा जिल्हा भाजपमय करतील, रवींद्र चव्हाण यांचा विश्वास</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.loksatta.com/maharashtra/karad-ravindra-chavan-atul-bhosale-satara-bjp-president-vsd-99-5121887/</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड, काय आहे समीकरण?</t>
+          <t>Thackeray Shiv Sena Setback | ठाकरे शिवसेनेला मालवण शहरात खिंडार</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/malvan-shiv-sena-defection-bjp-joining-ravindra-chavan-sp96</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
+          <t>Ravindra Chavan यांचा शिवसेना उबाठाला धक्का, कामगार संघटनेचे दीड हजार सदस्यांचा भाजपमध्ये प्रवेश..</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-s-shiv-sena-ubatha-is-in-trouble-1500-members-of-the-workers-union-join-bjp-1051360.html</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Local elections | स्थानिक निवडणुका महायुतीत लढू, कार्यकर्त्यांचाही विचार : रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan भाजपा हीच माझी ओळख म्हणणारे रवींद्र चव्हाण महाराष्ट्र भाजपच्या प्रदेशाध्यक्षपदी!!</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-mahayuti-to-contest-local-elections-ab96</t>
+          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Ravindra Chavan भाजपमध्ये पक्ष प्रवेशांचा धडाका, लातूर धाराशिव अमरावतीमधील पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>Maharashtra Politics : पुण्यात भाजपची ताकद वाढली, काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
+          <t>https://saamtv.esakal.com/video/maharashtra-politics-congress-leader-sanjay-jagtap-joins-bjp-in-pune-in-presence-of-state-president-ravindra-chavan-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>BJP Expansion Strategy: पक्षविस्तार की सत्तेसाठीची तडजोड?</t>
+          <t>Ravindra Chavan: ऑपरेशन एकनाथ शिंदेंमध्ये मोठी जबाबदारी ते फडणवीस मुख्यमंत्री होणार नाहीत</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjp-expansion-or-power-compromise-maharashtra-politics-chandrasekhar-bawankule-ravindra-chavan-devendra-fadnavis-mm76</t>
+          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Nitesh Rane Statement | नितेश राणे यांच्या विधानामुळे भाजपची कोंडी, रवींद्र चव्हाण यांनी गुंडाळली पत्रकार परिषद</t>
+          <t>Who Is Ravindra Chavan: रवींद्र चव्हाण बनले महाराष्ट्र भाजपचे कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा यांची घोषणा Who is Ravindra Chavan Ravindra Chavan becomes the working president of Maharashtra BJP Natio</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nitesh-rane-statement-puts-bjp-in-spotlight-ravindra-chavan-cancels-press-meet-sk95</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>Nanded News : जिल्ह्यातील शेतकऱ्यांच्या खात्यावर विम्याची रक्कम लवकरच जमा होणार</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण ; सावंतवाडीत कार्यकर्त्यांचा जल्लोष</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/insurance-amount-will-be-deposited-in-the-accounts-of-farmers-in-the-district-soon-np88</t>
+          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>भाजपचे कार्याध्यक्ष रवींद्र चव्हाण शनिवारी बीड दौऱ्यावर</t>
+          <t>Ravindra Chavan : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड, काय आहे समीकरण?</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/aurangabad/bjp-leader-ravindra-chavan-beed-tour-condolence-visit-vsd-99-5123945/</t>
+          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : काँग्रेसला राज्यात मोठा हादरा, बड्या नेत्याने केला भाजपमध्ये प्रवेश</t>
+          <t>Local elections | स्थानिक निवडणुका महायुतीत लढू, कार्यकर्त्यांचाही विचार : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-congress-leader-kailas-gorantyal-quits-party-and-joins-bjp-in-presence-of-ravindra-chavan-jalna-strongman-switches-sides-yps99</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-mahayuti-to-contest-local-elections-ab96</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>कल्याण डोंबिवली क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा – भाजप प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan भाजपमध्ये पक्ष प्रवेशांचा धडाका, लातूर धाराशिव अमरावतीमधील पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/implement-slum-rehabilitation-scheme-effectively-in-kalyan-dombivali-area-bjp-state-working-president-ravindra-chavan/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>प्रत्येकाच्या मनात ‘कमळ’ रुजले पाहिजे</t>
+          <t>BJP Expansion Strategy: पक्षविस्तार की सत्तेसाठीची तडजोड?</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/bjp-leader-ravindra-chavan-urges-lotus-must-bloom-in-every-heart-pune-print-news-ocd-94-5167946/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjp-expansion-or-power-compromise-maharashtra-politics-chandrasekhar-bawankule-ravindra-chavan-devendra-fadnavis-mm76</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President | रवींद्र चव्हाण भाजपचे बारावे महाराष्ट्र प्रदेशाध्यक्ष होणार</t>
+          <t>Nitesh Rane Statement | नितेश राणे यांच्या विधानामुळे भाजपची कोंडी, रवींद्र चव्हाण यांनी गुंडाळली पत्रकार परिषद</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nitesh-rane-statement-puts-bjp-in-spotlight-ravindra-chavan-cancels-press-meet-sk95</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>भाजप लोकल बॉडीची निवडणूक स्वबळावर लढणार: पण मुंबईसाठी घेणार शिंदे, दादांची मदत; रवींद्र चव्हाण यांनी घेतली ...</t>
+          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-bjp-local-body-election-strategy-mumbai-alliance-shinde-ajit-pawar-135526240.html</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President | १ जुलैला रवींद्र चव्हाणांच्या नावाची घोषणा, भाजपचं जोरदार शक्तिप्रदर्शन</t>
+          <t>Nanded News : जिल्ह्यातील शेतकऱ्यांच्या खात्यावर विम्याची रक्कम लवकरच जमा होणार</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
+          <t>https://pudhari.news/maharashtra/marathwada/nanded/insurance-amount-will-be-deposited-in-the-accounts-of-farmers-in-the-district-soon-np88</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>Sanjay Raut : सही करताना झोपेत असतात का? राऊतांचा रवींद्र चव्हाणांवर घणाघात</t>
+          <t>भाजपचे कार्याध्यक्ष रवींद्र चव्हाण शनिवारी बीड दौऱ्यावर</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
+          <t>https://www.loksatta.com/aurangabad/bjp-leader-ravindra-chavan-beed-tour-condolence-visit-vsd-99-5123945/</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाणांचे शुभेच्छा देणार बॅनर फाडले</t>
+          <t>Maharashtra Politics : काँग्रेसला राज्यात मोठा हादरा, बड्या नेत्याने केला भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-banners-wishing-ravindra-chavan-were-torn-1062422.html</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-congress-leader-kailas-gorantyal-quits-party-and-joins-bjp-in-presence-of-ravindra-chavan-jalna-strongman-switches-sides-yps99</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>Jan Suraksha Bill : ‘जनसुरक्षे’मुळे विकासमार्ग खुला; प्रकल्पांना विरोध डाव्यांकडून : भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
+          <t>कल्याण डोंबिवली क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा – भाजप प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/jan-suraksha-bill-will-pave-way-for-development-ravindra-chavan-amp17</t>
+          <t>https://www.localnewsnetwork.in/implement-slum-rehabilitation-scheme-effectively-in-kalyan-dombivali-area-bjp-state-working-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: रवींद्र चव्हाण यांच्यासमोर स्थानिक स्वराज्य संस्थांच्या निवडणुकांचे आव्हान</t>
+          <t>प्रत्येकाच्या मनात ‘कमळ’ रुजले पाहिजे</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
+          <t>https://www.loksatta.com/pune/bjp-leader-ravindra-chavan-urges-lotus-must-bloom-in-every-heart-pune-print-news-ocd-94-5167946/</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>Ratnagiri BJP election : रवींद्र चव्हाणांच्या शब्दाला मान; रत्नागिरीत निकटवर्तीयांना संधी, सावंतांची फेर निवड</t>
+          <t>BJP Maharashtra President | रवींद्र चव्हाण भाजपचे बारावे महाराष्ट्र प्रदेशाध्यक्ष होणार</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-appoints-rajesh-sawant-and-satish-more-close-aides-of-party-vice-president-ravindra-chavan-as-district-presidents-for-south-and-north-ratnagiri-as11</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Exclusive : ठाकरे बंधूंची युती ते BMC मध्ये भाजपचा महापौर? भाजपच्या नव्या...</t>
+          <t>भाजप लोकल बॉडीची निवडणूक स्वबळावर लढणार: पण मुंबईसाठी घेणार शिंदे, दादांची मदत; रवींद्र चव्हाण यांनी घेतली ...</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-bjp-local-body-election-strategy-mumbai-alliance-shinde-ajit-pawar-135526240.html</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>‘कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाशाला बेघर होऊ देणार नाही’ - आमदार रवींद्र चव्हाण</t>
+          <t>BJP Maharashtra President | १ जुलैला रवींद्र चव्हाणांच्या नावाची घोषणा, भाजपचं जोरदार शक्तिप्रदर्शन</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kalyan-dombivli/not-a-single-resident-of-the-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-says-mla-ravindra-chavan-a-a653/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>महापालिका निवडणुका महायुती एकत्र लढणार? नवे प्रदेशाध्यक्ष काय म्हणाले?; महापौरपदाबाबतही मोठं विधान</t>
+          <t>Sanjay Raut : सही करताना झोपेत असतात का? राऊतांचा रवींद्र चव्हाणांवर घणाघात</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/mahayuatis-election-strategy-bjps-chavan-announces-joint-municipal-polls-contests-1444009.html</t>
+          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाणांचे शुभेच्छा देणार बॅनर फाडले</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-banners-wishing-ravindra-chavan-were-torn-1062422.html</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
+          <t>Maharashtra BJP President: रवींद्र चव्हाण यांच्यासमोर स्थानिक स्वराज्य संस्थांच्या निवडणुकांचे आव्हान</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
+          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवलीची कहाणी: शिंदे-चव्हाण पुढारी असलेल्या KDMC ची एवढी दैना झाली तरी कशी?</t>
+          <t>Ratnagiri BJP election : रवींद्र चव्हाणांच्या शब्दाला मान; रत्नागिरीत निकटवर्तीयांना संधी, सावंतांची फेर निवड</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://www.mumbaitak.in/political-news/story/story-of-kalyan-dombivli-why-are-conditions-of-kalyan-and-dombivali-cities-so-bad-despite-powerful-leaders-shrikant-shinde-ravindra-chavan-3197444-2025-08-21</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-appoints-rajesh-sawant-and-satish-more-close-aides-of-party-vice-president-ravindra-chavan-as-district-presidents-for-south-and-north-ratnagiri-as11</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>मोठी बातमी: BMC निवडणुकीआधी फडणवीसांनी डाव टाकला; भाजपकडून मुंबईत नव्या अध्यक्षाची घोषणा</t>
+          <t>Jan Suraksha Bill : ‘जनसुरक्षे’मुळे विकासमार्ग खुला; प्रकल्पांना विरोध डाव्यांकडून : भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
+          <t>https://www.esakal.com/maharashtra/jan-suraksha-bill-will-pave-way-for-development-ravindra-chavan-amp17</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>घराण्याची 75 वर्षाची निष्ठा संपली… अखेर काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश, खान्देशात...</t>
+          <t>Ravindra Chavan Exclusive : ठाकरे बंधूंची युती ते BMC मध्ये भाजपचा महापौर? भाजपच्या नव्या...</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/big-blow-for-congress-in-khandesh-ex-mla-kunal-patil-join-bjp-1436092.html</t>
+          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>BJP में शामिल हुए प्रदेश कांग्रेस सचिव दिलीप भालेराव, रवींद्र चव्हाण ने किया स्वागत</t>
+          <t>‘कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाशाला बेघर होऊ देणार नाही’ - आमदार रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/state-congress-secretary-dilip-bhalerao-joined-bjp-maharashtra-nikay-chunav-1308763.html</t>
+          <t>https://www.lokmat.com/kalyan-dombivli/not-a-single-resident-of-the-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-says-mla-ravindra-chavan-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>भाजपा संगठन चुनाव: महाराष्ट्र में रवींद्र चव्हाण , उत्तराखंड में महेंद्र भट्ट; जानें MP में कौन होगा BJP...</t>
+          <t>महापालिका निवडणुका महायुती एकत्र लढणार? नवे प्रदेशाध्यक्ष काय म्हणाले?; महापौरपदाबाबतही मोठं विधान</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/national/bjp-state-president-elections-ravindra-chavan-mahendra-bhatt-634968</t>
+          <t>https://www.tv9marathi.com/politics/mahayuatis-election-strategy-bjps-chavan-announces-joint-municipal-polls-contests-1444009.html</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, जानें कौन हैं | Hari Bhoomi</t>
+          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/maharastra/ravindra-chavan-appointed-maharashtra-bjp-president-635140</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan: देवेंद्र फडणवीसांचे विश्वासू रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष! एकमताने निवड</t>
+          <t>कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
+          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>मोठी बातमी: BMC निवडणुकीआधी फडणवीसांनी डाव टाकला; भाजपकडून मुंबईत नव्या अध्यक्षाची घोषणा</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights : भाजपाला मिळणार नवा प्रदेशाध्यक्ष, रविंद्र चव्हाणांनी भरला अर्ज, मंगळवारी होणार अधिकृत घोषणा</t>
+          <t>घराण्याची 75 वर्षाची निष्ठा संपली… अखेर काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश, खान्देशात...</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
+          <t>https://www.tv9marathi.com/politics/big-blow-for-congress-in-khandesh-ex-mla-kunal-patil-join-bjp-1436092.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महाराष्ट्रात भाजपला मिळाला नवा कॅप्टन; प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची...</t>
+          <t>BJP में शामिल हुए प्रदेश कांग्रेस सचिव दिलीप भालेराव, रवींद्र चव्हाण ने किया स्वागत</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
+          <t>https://navbharatlive.com/maharashtra/state-congress-secretary-dilip-bhalerao-joined-bjp-maharashtra-nikay-chunav-1308763.html</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>प्रसिद्धीपासून दूर, कामगिरीवर भर; भाजप प्रदेशाध्यक्षांचा अनोखा नागपूर दौरा</t>
+          <t>भाजपा संगठन चुनाव: महाराष्ट्र में रवींद्र चव्हाण , उत्तराखंड में महेंद्र भट्ट; जानें MP में कौन होगा BJP...</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/ravindra-chavan-nagpur-visit-keeps-media-in-dark-highlights-bjps-new-low-key-strategy-skips-publicity-focuses-on-groundwork-print-political-news-vsd-99-5252822/</t>
+          <t>https://www.haribhoomi.com/national/bjp-state-president-elections-ravindra-chavan-mahendra-bhatt-634968</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Pune News : पुणे जिल्हा 'शत प्रतिशत' भाजप..? अजित पवारांची आणि पवार कुटुंबाची सद्दी संपणार?</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, जानें कौन हैं | Hari Bhoomi</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/pune-news/sanjay-jagtap-joins-bjp-in-the-presence-of-bjp-state-president-ravindra-chavan/articleshow/122572770.cms</t>
+          <t>https://www.haribhoomi.com/state-local/maharastra/ravindra-chavan-appointed-maharashtra-bjp-president-635140</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
+          <t>कांग्रेस के पूर्व मंत्री वरपुडकर बने भाजपाई, रवींद्र चव्हाण ने किया स्वागत</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
+          <t>https://navbharatlive.com/maharashtra/parbhani-senior-congress-leader-suresh-varpudkar-joined-bjp-1300751.html</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
+          <t>Who Is Ravindra Chavan: देवेंद्र फडणवीसांचे विश्वासू रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष! एकमताने निवड</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/states/ex-minister-ravindra-chavan-is-bjps-new-maharashtra-unit-chief</t>
+          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Proud Of Hindi, No Red Carpet For English, Says Maharashtra CM Devendra Fadnavis (VIDEO)</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/proud-of-hindi-no-red-carpet-for-english-says-maharashtra-cm-devendra-fadnavis-video</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Ahmedabad Plane Crash: Air India Crew Member And Travel Influencer Roshni Songhare Among Victims</t>
+          <t>Maharashtra News Highlights : भाजपाला मिळणार नवा प्रदेशाध्यक्ष, रविंद्र चव्हाणांनी भरला अर्ज, मंगळवारी होणार अधिकृत घोषणा</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/entertainment/news/ahmedabad-plane-crash-air-india-crew-member-and-travel-influencer-roshni-songhare-among-victims-photos-videos-10244818</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Bodies of Pahalgam terror attack victims reach Maharashtra: CM Fadnavis offers final respect to 6 victims b...</t>
+          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के शिरडी में BJP का दो दिवसीय अधिवेशन शुरू, अगले प्रदेश अध्यक्ष की हो सकती है घोषणा,जानें कौन आगे</t>
+          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>नए राष्ट्रीय अध्यक्ष को लेकर BJP आलाकमान और संघ के बीच फंसा पेच, इन राज्यों में बदलेगा प्रदेश नेतृत्व</t>
+          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/news/story/deadlock-between-bjp-high-command-and-rss-over-news-national-president-continues-ntc-rptc-2275062-2025-06-29</t>
+          <t>https://english.metrovaartha.com/news/states/ex-minister-ravindra-chavan-is-bjps-new-maharashtra-unit-chief</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>रविंद्र जडेजा का बिहार से क्या रिश्ता? 'क्रिकेट गुरु' महेंद्र सिंह चौहान से महेंद्र सिंह धोनी तक का सफर</t>
+          <t>Proud Of Hindi, No Red Carpet For English, Says Maharashtra CM Devendra Fadnavis (VIDEO)</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/proud-of-hindi-no-red-carpet-for-english-says-maharashtra-cm-devendra-fadnavis-video</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा के नए बॉस बने रवींद्र चौहान, जानिए कौन हैं निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
+          <t>Ahmedabad Plane Crash: Air India Crew Member And Travel Influencer Roshni Songhare Among Victims</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/politician-becomes-new-boss-of-maharashtra-bjp-know-who-is-the-president-ravindra-chauhan/1240488/</t>
+          <t>https://www.thedailyjagran.com/entertainment/news/ahmedabad-plane-crash-air-india-crew-member-and-travel-influencer-roshni-songhare-among-victims-photos-videos-10244818</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Air India Plane Crash: प्लेन की क्रू मेंबर का निधन, रोशनी सोंघरे की विमान हादसे में गई जान</t>
+          <t>Bodies of Pahalgam terror attack victims reach Maharashtra: CM Fadnavis offers final respect to 6 victims b...</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>कौन हैं IAS अरविंद चौहान? इंसानियत की मिसाल पेश की, यूपी के इस डीएम की हर तरफ हो रही तारीफ</t>
+          <t>महाराष्ट्र के शिरडी में BJP का दो दिवसीय अधिवेशन शुरू, अगले प्रदेश अध्यक्ष की हो सकती है घोषणा,जानें कौन आगे</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/photo-gallery-who-is-ias-arvind-chauhan-shamli-dm-sat-on-ground-to-listen-70-year-old-woman-complaint/2813524</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>तीन प्रदेशों के भाजपा अध्यक्ष तय - Naya India-Hindi News, Latest Hindi News, Breaking News, Hindi Samachar</t>
+          <t>जनवरी में UP-MP समेत 7 राज्यों में भाजपा अध्यक्ष बदलेंगे: नया राष्ट्रीय अध्यक्ष फरवरी तक, 15 जनवरी तक 50% र...</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
+          <t>https://www.bhaskar.com/national/news/bjp-organizational-election-meeting-2024-update-134203814.html</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP को मिला नया अध्यक्ष, रवींद्र चव्हाण बने प्रदेश प्रमुख</t>
+          <t>रविंद्र जडेजा का बिहार से क्या रिश्ता? 'क्रिकेट गुरु' महेंद्र सिंह चौहान से महेंद्र सिंह धोनी तक का सफर</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>Pune bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
+          <t>महाराष्ट्र भाजपा के नए बॉस बने रवींद्र चौहान, जानिए कौन हैं निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/articleshow/121904713.cms</t>
+          <t>https://hindi.news24online.com/state/mumbai/politician-becomes-new-boss-of-maharashtra-bjp-know-who-is-the-president-ravindra-chauhan/1240488/</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Ahead of civic polls, Maharashtra BJP chief stakes claim for KDMC mayor's post</t>
+          <t>Air India Plane Crash: प्लेन की क्रू मेंबर का निधन, रोशनी सोंघरे की विमान हादसे में गई जान</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
+          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>Former Cricketer Kedar Jadhav Joins BJP</t>
+          <t>कौन हैं IAS अरविंद चौहान? इंसानियत की मिसाल पेश की, यूपी के इस डीएम की हर तरफ हो रही तारीफ</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/photo-gallery-who-is-ias-arvind-chauhan-shamli-dm-sat-on-ground-to-listen-70-year-old-woman-complaint/2813524</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>Ahead of local body polls, BJP finalises names of 22 district presidents</t>
+          <t>महाराष्ट्र भाजपा अध्यक्ष के लिए रवींद्र चव्हाण का नाम तय! कल 5 बजे होगी घोषणा</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ravindra-chavan-maharashtra-bjp-president-announcement-devendra-fadnavis-1-july-1270075.html</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>Ex-Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
+          <t>तीन प्रदेशों के भाजपा अध्यक्ष तय - Naya India-Hindi News, Latest Hindi News, Breaking News, Hindi Samachar</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>BJP holds meeting of former MPs and MLAs ahead of local body polls in Maharashtra</t>
+          <t>महाराष्ट्र BJP को मिला नया अध्यक्ष, रवींद्र चव्हाण बने प्रदेश प्रमुख</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Ahead of BMC polls 3-term MLA Ameet Satam named new Mumbai BJP chief</t>
+          <t>Maharashtra: BJP Leader Ravindra Chavan Appointed As New State President</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/25/bom2-mh-mumbai-bjp-satam.html</t>
+          <t>https://globalgreenews.com/2025/07/02/maharashtra-bjp-leader-ravindra-chavan-appointed-as-new-state-president/</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Ex-Maharashtra minister Cong leader Suresh Warpudkar joins BJP</t>
+          <t>Former Cricketer Kedar Jadhav Joins BJP</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/29/bes35-mh-ex-minister-bjp.html</t>
+          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BJP MLA Amit Satam announced as president of Mumbai unit ahead of BMC polls</t>
+          <t>BJP chief in Maharashtra brings MNS union workers into party</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
+          <t>Ahead of civic polls, Maharashtra BJP chief stakes claim for KDMC mayor's post</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>BJP Strengthens Roots in Vidarbha: 313 Mandals Formed, 275 Presidents Appointed</t>
+          <t>Ahead of local body polls, BJP finalises names of 22 district presidents</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-strengthens-roots-in-vidarbha-313-mandals-formed-275-presidents-appointed/articleshow/120463852.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>BJP To Get New Nagpur City Chief Ahead Of Local Body Polls</t>
+          <t>Former Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/bjp-to-get-new-nagpur-city-chief-ahead-of-local-body-polls/articleshow/120741284.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra-23587437</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Pune: CM Fadnavis Inaugurates Mohol's 24/7 Public Office, Hails Him as a Crisis-Time Leader</t>
+          <t>Ex-Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.punekarnews.in/pune-cm-fadnavis-inaugurates-mohols-24-7-public-office-hails-him-as-a-crisis-time-leader/</t>
+          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>केडीएमसी- डॉ. नानासाहेब धर्माधिकारी प्रतिष्ठान कडून स्वच्छता अभियान</t>
+          <t>BJP holds meeting of former MPs and MLAs ahead of local body polls in Maharashtra</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Pandharpur Wari 2025 | डोंबिवलीहून पंढरपूरला निघाली सायकलने दिंडी</t>
+          <t>Ahead of BMC polls 3-term MLA Ameet Satam named new Mumbai BJP chief</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/pandharpur-wari-2025-dindi-left-for-pandharpur-by-bicycle-from-dombivli-ar84</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/25/bom2-mh-mumbai-bjp-satam.html</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>BJP Confusion Over Sudhakar Badgujar's Induction: Bawankule Unaware of Former Sena (UBT) Leader's Entry</t>
+          <t>BJP MLA Amit Satam announced as president of Mumbai unit ahead of BMC polls</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Pune bridge collapse: New bridge sanctioned a year ago but work order came on June 10 | Latest News India - Hindustan Times</t>
+          <t>Maha: Sudhakar Badgujar, who faced charges of 'links' with underworld, joins BJP</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
+          <t>https://www.thehawk.in/news/india/maha-sudhakar-badgujar-who-faced-charges-of-links-with-underworld-joins-bjp</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>Ahead of Thackeray reunion, BJP’s Rane claims Uddhav harassed Raj, blames him for Shiv Sena’s downfall</t>
+          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jul/01/ahead-of-thackeray-reunion-bjps-rane-claims-uddhav-harassed-raj-blames-him-for-shiv-senas-downfall</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Centre removes Turkish firm Celebi from ground handling work at Mumbai and Delhi airports</t>
+          <t>Over 2,000 IndiGo employees join BJP ahead of BMC elections in Mumbai</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
+          <t>https://english.varthabharati.in/india/over-2000-indigo-employees-join-bjp-ahead-of-bmc-elections-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>HC upholds BJP MLA’s victory, says ‘honest’ disclosure of second marriage permissible in his community won’t flout rules</t>
+          <t>केडीएमसी- डॉ. नानासाहेब धर्माधिकारी प्रतिष्ठान कडून स्वच्छता अभियान</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>मुंबईत ‘आयकॉनिक इमारती’ उभारण्यासाठी नवीन धोरण</t>
+          <t>Pandharpur Wari 2025 | डोंबिवलीहून पंढरपूरला निघाली सायकलने दिंडी</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
+          <t>https://pudhari.news/maharashtra/thane/pandharpur-wari-2025-dindi-left-for-pandharpur-by-bicycle-from-dombivli-ar84</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>Hindi language row : ‘हिंदी’वर नवा जीआर; ठाकरेंच्या दणक्यानंतर सरकार ताकही फुंकून पिणार, जाधव समितीला देश पालथा घालावा लागणार...</t>
+          <t>BJP Confusion Over Sudhakar Badgujar's Induction: Bawankule Unaware of Former Sena (UBT) Leader's Entry</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
+          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>कोकणात शरद पवारांच्या राष्ट्रवादीत भूकंप! उदय सामंतांना होमग्राऊंडवर नितेश राणेंचा दे धक्का, बडा नेता पळवला</t>
+          <t>Pune bridge collapse: New bridge sanctioned a year ago but work order came on June 10 | Latest News India - Hindustan Times</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-nitesh-rane-reveals-major-political-defection-in-ratnagiri-as11</t>
+          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Sharad Pawar NCP : तळ कोकणात राजकीय भूकंप? शरद पवारांना मोठा धक्का! एकमेव नेत्यानेही साथ सोडत केला भाजप प्रवेश</t>
+          <t>Centre removes Turkish firm Celebi from ground handling work at Mumbai and Delhi airports</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-with-hundreds-of-supporters-major-blow-to-sharad-pawars-ncp-in-konkan-as11</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे गटाला मालवणमध्ये भाजपचा मोठा धक्का; तीन नगरसेवकांचा भाजपात प्रवेश</t>
+          <t>HC upholds BJP MLA’s victory, says ‘honest’ disclosure of second marriage permissible in his community won’t flout rules</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/thackeray-sena-setback-three-malvan-councilors-join-bjp-mk94</t>
+          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>BJP Politics : रत्नागिरी भाजप जिल्हाध्यक्षपदाच्या रेसमध्ये सावंतासह चौघे; कोणाला मिळणार संधी? नावे झाली पाकिट बंद,धाकधूकही वाढवली</t>
+          <t>मुंबईत ‘आयकॉनिक इमारती’ उभारण्यासाठी नवीन धोरण</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-south-ratnagiri-district-president-selection-by-state-office-as11</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>BJP Politics : रायगड उत्तरमध्ये जुनाच चेहरा, दक्षिणमध्ये नव्याला संधी; अविनाश कोळी आणि धैर्यशील पाटलांच्या निवडीने भाजपला बळ</t>
+          <t>Hindi language row : ‘हिंदी’वर नवा जीआर; ठाकरेंच्या दणक्यानंतर सरकार ताकही फुंकून पिणार, जाधव समितीला देश पालथा घालावा लागणार...</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/avinash-koli-and-dhairyashil-patil-appointed-bjp-raigad-district-presidents-north-south</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>Eknath Shinde : आजचा दिवस एकनाथ शिंदेंसाठी महत्त्वाचा; ठाण्यात भाजप मोठा धक्का देणार? युतीही तुटणार...</t>
+          <t>कोकणात शरद पवारांच्या राष्ट्रवादीत भूकंप! उदय सामंतांना होमग्राऊंडवर नितेश राणेंचा दे धक्का, बडा नेता पळवला</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/bjp-strategy-meeting-thane-municipal-elections-eknath-shinde-rm89</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-nitesh-rane-reveals-major-political-defection-in-ratnagiri-as11</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>निवडणुकांची तयारी, भाजपने भाकरी फिरवली राज्यात 58 जिल्हाध्यक्षांची नवी यादी</t>
+          <t>Sharad Pawar NCP : तळ कोकणात राजकीय भूकंप? शरद पवारांना मोठा धक्का! एकमेव नेत्यानेही साथ सोडत केला भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-new-list-of-58-district-presidents-announced-in-the-state-with-mumbai-preparations-for-elections-devendra-fadnavis-chandrashekhar-bawankule-marathi-news-1358929</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-with-hundreds-of-supporters-major-blow-to-sharad-pawars-ncp-in-konkan-as11</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>Ravindra Chavan यांची भाजपाच्या प्रदेशाध्यक्षपदी निवड</t>
+          <t>उद्धव ठाकरे गटाला मालवणमध्ये भाजपचा मोठा धक्का; तीन नगरसेवकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/thackeray-sena-setback-three-malvan-councilors-join-bjp-mk94</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>BJP Politics : रत्नागिरी भाजप जिल्हाध्यक्षपदाच्या रेसमध्ये सावंतासह चौघे; कोणाला मिळणार संधी? नावे झाली पाकिट बंद,धाकधूकही वाढवली</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-south-ratnagiri-district-president-selection-by-state-office-as11</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>25.03.2025: Governor Radhakrishnan, CM Devendra Fadnavis perform Bhumipujan of Tribute Wall</t>
+          <t>BJP Politics : रायगड उत्तरमध्ये जुनाच चेहरा, दक्षिणमध्ये नव्याला संधी; अविनाश कोळी आणि धैर्यशील पाटलांच्या निवडीने भाजपला बळ</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/25-03-2025-governor-radhakrishnan-cm-devendra-fadnavis-perform-bhumipujan-of-tribute-wall/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/avinash-koli-and-dhairyashil-patil-appointed-bjp-raigad-district-presidents-north-south</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: अखेर प्रतीक्षा संपली! बावनकुळेंनंतर भाजपला नवा धडाकेबाज प्रदेशाध्यक्ष मिळाला</t>
+          <t>Eknath Shinde : आजचा दिवस एकनाथ शिंदेंसाठी महत्त्वाचा; ठाण्यात भाजप मोठा धक्का देणार? युतीही तुटणार...</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-appointed-bjp-maharashtra-new-president-dk88</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/bjp-strategy-meeting-thane-municipal-elections-eknath-shinde-rm89</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : चव्हाण पेलणार का आव्हान!</t>
+          <t>निवडणुकांची तयारी, भाजपने भाकरी फिरवली राज्यात 58 जिल्हाध्यक्षांची नवी यादी</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-new-list-of-58-district-presidents-announced-in-the-state-with-mumbai-preparations-for-elections-devendra-fadnavis-chandrashekhar-bawankule-marathi-news-1358929</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>आगामी निवडणुकीत भाजपची नजर ५१ टक्के मतांवर!</t>
+          <t>Ravindra Chavan यांची भाजपाच्या प्रदेशाध्यक्षपदी निवड</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/new-bjp-state-president-ravindra-chavan-comments-on-upcoming-local-body-elections-in-loksatta-lok-samvad-program-ssb-93-5224541/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>विधानसभा निवडणुकीत बंडखोरी करणाऱ्या नेत्याचे निलंबन भाजपकडून रद्द, राणेंची डोकेदुखी वाढणार?</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-revokes-vishal-parabs-suspension-for-rebelling-in-assembly-elections-will-ranes-headache-increase-a-a301/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>अवजड वाहतूक करणाऱ्या वाहन चालकांचा संप मागे</t>
+          <t>25.03.2025: Governor Radhakrishnan, CM Devendra Fadnavis perform Bhumipujan of Tribute Wall</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/25-03-2025-governor-radhakrishnan-cm-devendra-fadnavis-perform-bhumipujan-of-tribute-wall/</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
+          <t>Ravindra Chavan BJP : मुंबईहून भाजप कार्याध्यक्षांचा फोन अन् मंडल अध्यक्षाच्या निवडीला स्थगिती; विखे समर्थकाची कोणी केली तक्रार?</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/ahilyanagar-bjp-shevgaon-president-appointment-stalled-ravindra-chavan-order-pp82</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>Maharashtra Live Updates : 'फक्त निवडणूक डोळ्यासमोर ठेवून योजना आणल्या की..' ; रोहित पवारांचा टोला!</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/press-release/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/2692193</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-may-2025-vaishnavi-hagawane-case-pune-court-update-police-custody-character-assassination-allegations-sharad-pawar-devendra-fadnavis-bjp-maharashtra-strategy-gram-panchayat-to-assembly-obc-movement-manoj-jarange-patil-laxman-hake</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>BJP Gears Up for Maharashtra Civic Polls, Holds Meet with Former MPs, MLAs</t>
+          <t>आगामी निवडणुकीत भाजपची नजर ५१ टक्के मतांवर!</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/new-bjp-state-president-ravindra-chavan-comments-on-upcoming-local-body-elections-in-loksatta-lok-samvad-program-ssb-93-5224541/</t>
         </is>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP, Shinde-Led Sena Hold Separate Meetings As Calls To Contest Local Elections Solo</t>
+          <t>विधानसभा निवडणुकीत बंडखोरी करणाऱ्या नेत्याचे निलंबन भाजपकडून रद्द, राणेंची डोकेदुखी वाढणार?</t>
         </is>
       </c>
       <c r="B488" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-shinde-led-sena-hold-separate-meetings-as-calls-to-contest-local-elections-solo-grow-louder</t>
+          <t>https://www.lokmat.com/maharashtra/bjp-revokes-vishal-parabs-suspension-for-rebelling-in-assembly-elections-will-ranes-headache-increase-a-a301/</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>अवजड वाहतूक करणाऱ्या वाहन चालकांचा संप मागे</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>BJP Gears Up for Maharashtra Civic Polls, Holds Meet with Former MPs, MLAs</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B491"/>
+  <dimension ref="A1:B487"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -455,84 +455,84 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BJP names Ravindra Chavan as state unit chief, with an eye on MMR | Mumbai news</t>
+          <t>BJP mayor needed to remove the stagnation in Kalyan-Dombivli’s development, says BJP Maharashtra presiden</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Former Minister Ravindra Chavan appointed working president of Maharashtra BJP</t>
+          <t>BJP names Ravindra Chavan as state unit chief, with an eye on MMR | Mumbai news</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://www.thehindu.com/news/national/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp/article69089769.ece</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-names-ravindra-chavan-as-state-unit-chief-with-an-eye-on-mmr-101748631790329.html</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
+          <t>Hemant Khandelwal To Ravindra Chavan: A Look At 9 New BJP State Chiefs</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
+          <t>https://www.ndtv.com/india-news/hemant-khandelwal-ravindra-chavan-pvn-madhav-n-ramchander-rao-a-look-at-9-new-bjp-state-chiefs-before-jp-naddas-replacement-polls-8812562</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
+          <t>Former Minister Ravindra Chavan appointed working president of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888547</t>
+          <t>https://www.thehindu.com/news/national/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp/article69089769.ece</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to head Maha BJP, says Bawankule</t>
+          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-3351330</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Maharashtra: Ravindra Chavan to be declared state BJP chief Tuesday, files nomination</t>
+          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ravindra-chavan-to-be-declared-state-bjp-chief-tuesday-files-nomination-10098263/</t>
+          <t>https://www.deccanchronicle.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888547</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
+          <t>Three-language policy was withdrawn to avoid law and order problems: Ravindra Chavan</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president/articleshow/117155260.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/three-language-policy-was-withdrawn-to-avoid-law-and-order-problems-ravindra-chavan-10117229/</t>
         </is>
       </c>
     </row>
@@ -551,72 +551,72 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed as Maharashtra unit BJP president</t>
+          <t>Ex-minister Ravindra Chavan appointed Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://english.gujaratsamachar.com/news/mumbai/ravindra-chavan-appointed-as-maharashtra-unit-bjp-president</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ex-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president/articleshow/117155260.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BJP appoints Maratha face as its next Maharashtra president: Who is Ravindra Chavan?</t>
+          <t>Ravindra Chavan appointed as Maharashtra unit BJP president</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/bjp-appoints-maratha-maharashtra-president-ravindra-chavan-10099887/</t>
+          <t>https://english.gujaratsamachar.com/news/mumbai/ravindra-chavan-appointed-as-maharashtra-unit-bjp-president</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BJP mayor needed to remove the stagnation in Kalyan-Dombivli’s development, says BJP Maharashtra presiden</t>
+          <t>Ravindra Chavan set to head Maha BJP, says Bawankule</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/bjp-mayor-needed-to-remove-the-stagnation-in-kalyan-dombivlis-development-says-bjp-maharashtra-president-ravindra-chavan/articleshow/123073337.cms</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ravindra-chavan-set-to-head-maha-bjp-says-bawankule/articleshow/121504377.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Maharashtra BJP to get new chief? Ex-minister Ravindra Chavan joins the race; CM says ‘happy he filed nomination’</t>
+          <t>BJP appoints Maratha face as its next Maharashtra president: Who is Ravindra Chavan?</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/maharashtra-bjp-to-get-new-chief-ex-minister-ravindra-chavan-joins-the-race-cm-says-happy-he-filed-nomination-11751293697889.html</t>
+          <t>https://indianexpress.com/article/political-pulse/bjp-appoints-maratha-maharashtra-president-ravindra-chavan-10099887/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>The man who could be next Maharashtra BJP chief: Why Ravindra Chavan was appointed party’s working president</t>
+          <t>Maharashtra: Ravindra Chavan to be declared state BJP chief Tuesday, files nomination</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-9775047/</t>
+          <t>https://indianexpress.com/article/cities/mumbai/maharashtra-ravindra-chavan-to-be-declared-state-bjp-chief-tuesday-files-nomination-10098263/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Three-language policy was withdrawn to avoid law and order problems: Ravindra Chavan</t>
+          <t>The man who could be next Maharashtra BJP chief: Why Ravindra Chavan was appointed party’s working president</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/three-language-policy-was-withdrawn-to-avoid-law-and-order-problems-ravindra-chavan-10117229/</t>
+          <t>https://indianexpress.com/article/political-pulse/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-9775047/</t>
         </is>
       </c>
     </row>
@@ -635,108 +635,108 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Hemant Khandelwal To Ravindra Chavan: A Look At 9 New BJP State Chiefs</t>
+          <t>Maharashtra BJP to get new chief? Ex-minister Ravindra Chavan joins the race; CM says ‘happy he filed nomination’</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/hemant-khandelwal-ravindra-chavan-pvn-madhav-n-ramchander-rao-a-look-at-9-new-bjp-state-chiefs-before-jp-naddas-replacement-polls-8812562</t>
+          <t>https://www.livemint.com/politics/news/maharashtra-bjp-to-get-new-chief-ex-minister-ravindra-chavan-joins-the-race-cm-says-happy-he-filed-nomination-11751293697889.html</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected Maharashtra BJP president ahead of crucial Mumbai civic body polls</t>
+          <t>Dombivli MLA Ravindra Chavan to be appointed Maharashtra BJP prez</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/politics-and-nation/ravindra-chavan-elected-maharashtra-bjp-president-ahead-of-crucial-mumbai-civic-body-polls/articleshow/122185741.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez-23582620</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Dombivli MLA Ravindra Chavan to be appointed Maharashtra BJP prez</t>
+          <t>Newly Appointed Working President Ravindra Chavan Can Be Next Maharashtra BJP Chief—Here's Why</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez-23582620</t>
+          <t>https://swarajyamag.com/news-brief/newly-appointed-working-president-ravindra-chavan-can-be-next-maharashtra-bjp-chiefheres-why</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Newly Appointed Working President Ravindra Chavan Can Be Next Maharashtra BJP Chief—Here's Why</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP president ahead of crucial MMR polls</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://swarajyamag.com/news-brief/newly-appointed-working-president-ravindra-chavan-can-be-next-maharashtra-bjp-chiefheres-why</t>
+          <t>https://www.indiatvnews.com/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-polls-2025-07-01-996989</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP president ahead of crucial MMR polls</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://www.indiatvnews.com/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-polls-2025-07-01-996989</t>
+          <t>https://www.indiatoday.in/india/story/maharashtra-bjp-working-president-ravindra-chavan-devendra-fadnavis-chandrasekhar-bawankule-2663456-2025-01-11</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Why BJP is keen to go solo in local body polls in most of Maharashtra</t>
+          <t>Ravindra Chavan elected Maharashtra BJP president ahead of crucial Mumbai civic body polls</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/why-bjp-keen-to-go-solo-local-body-polls-maharashtra-10153064/</t>
+          <t>https://m.economictimes.com/news/politics-and-nation/ravindra-chavan-elected-maharashtra-bjp-president-ahead-of-crucial-mumbai-civic-body-polls/articleshow/122185741.cms</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP working president</t>
+          <t>Why BJP is keen to go solo in local body polls in most of Maharashtra</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/maharashtra-bjp-working-president-ravindra-chavan-devendra-fadnavis-chandrasekhar-bawankule-2663456-2025-01-11</t>
+          <t>https://indianexpress.com/article/political-pulse/why-bjp-keen-to-go-solo-local-body-polls-maharashtra-10153064/</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>‘Dombivli Pride 2025’: Grand dahi handi celebrates Janmashtami; BJP leader Ravindra Chavan urges youth to</t>
+          <t>Ravindra Chavan appointed state BJP president: At party meeting, Fadnavis, Rijiju take aim at Oppn</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/ravindra-chavan-appointed-state-bjp-president-at-party-meeting-fadnavis-rijiju-take-aim-at-oppn-10100719/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed state BJP president: At party meeting, Fadnavis, Rijiju take aim at Oppn</t>
+          <t>‘Dombivli Pride 2025’: Grand dahi handi celebrates Janmashtami; BJP leader Ravindra Chavan urges youth to</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/ravindra-chavan-appointed-state-bjp-president-at-party-meeting-fadnavis-rijiju-take-aim-at-oppn-10100719/</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/dombivli-pride-2025-grand-dahi-handi-celebrates-janmashtami-bjp-leader-ravindra-chavan-urges-youth-to-drive-maharashtras-growth/articleshow/123332580.cms</t>
         </is>
       </c>
     </row>
@@ -779,24 +779,24 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Maharashtra BJP Leadership: Ravindra Chavan to Replace Bawankule as State President</t>
+          <t>'Meeting With Ravindra Chavan Personal, Not Political': Maha Congress Leader Kunal Patil Dismisses BJP Switch Rumours</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
+          <t>https://www.etvbharat.com/en/!state/meeting-with-ravindra-chavan-personal-not-political-maharashtra-congress-leader-kunal-patil-dismisses-bjp-switch-rumours-enn25062503849</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>'Meeting With Ravindra Chavan Personal, Not Political': Maha Congress Leader Kunal Patil Dismisses BJP Switch Rumours</t>
+          <t>Maharashtra BJP Leadership: Ravindra Chavan to Replace Bawankule as State President</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/meeting-with-ravindra-chavan-personal-not-political-maharashtra-congress-leader-kunal-patil-dismisses-bjp-switch-rumours-enn25062503849</t>
+          <t>https://www.deccanherald.com/india/maharashtra/ravindra-chavan-to-be-new-bjp-chief-for-maharashtra-3609432</t>
         </is>
       </c>
     </row>
@@ -815,24 +815,24 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Who are the BJP's 9 new state chiefs? Ravindra Chavan to PVN Madhav</t>
+          <t>Four-time MLA Ravindra Chavan appointed Maharashtra BJP president</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/who-are-the-bjps-9-new-state-chiefs-ravindra-chavan-to-pvn-madhav-11751449724866.html</t>
+          <t>https://www.indiatoday.in/india/story/four-time-mla-ravindra-chavan-appointed-maharashtra-bjp-president-2749208-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Four-time MLA Ravindra Chavan appointed Maharashtra BJP president</t>
+          <t>Who are the BJP's 9 new state chiefs? Ravindra Chavan to PVN Madhav</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/four-time-mla-ravindra-chavan-appointed-maharashtra-bjp-president-2749208-2025-07-02</t>
+          <t>https://www.livemint.com/politics/news/who-are-the-bjps-9-new-state-chiefs-ravindra-chavan-to-pvn-madhav-11751449724866.html</t>
         </is>
       </c>
     </row>
@@ -887,12 +887,12 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan, New Maharashtra BJP Chief, Close Confidant Of CM Devendra Fadnavis?</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP president ahead of crucial civic polls</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
+          <t>https://www.moneycontrol.com/news/india/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-civic-polls-13214817.html</t>
         </is>
       </c>
     </row>
@@ -911,12 +911,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP president ahead of crucial civic polls</t>
+          <t>Ex-Minister Ravindra Chavan Appointed As Working President of BJP in Maharashtra</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-civic-polls-13214817.html</t>
+          <t>https://www.republicworld.com/india/ex-minister-ravindra-chavan-appointed-as-working-state-president-of-bjp-in-maharashtra</t>
         </is>
       </c>
     </row>
@@ -947,180 +947,180 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Ex-Minister Ravindra Chavan Appointed As Working President of BJP in Maharashtra</t>
+          <t>Justice Chavan Calls For National Judicial Service, Reforms To Address Vacancies In Judiciary</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/ex-minister-ravindra-chavan-appointed-as-working-state-president-of-bjp-in-maharashtra</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Justice Chavan Calls For National Judicial Service, Reforms To Address Vacancies In Judiciary</t>
+          <t>Ex-minister Ravindra Chavan files nomination for post of Maharashtra BJP president</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/justice-chavan-calls-for-national-judicial-service-reforms-to-address-vacancies-in-judiciary/articleshow/121299899.cms</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan files nomination for post of Maharashtra BJP president</t>
+          <t>Ravindra Chavan Elected Maharashtra BJP President Unanimously</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/ex-minister-ravindra-chavan-files-nomination-for-post-of-maharashtra-bjp-president-23582507</t>
+          <t>https://www.republicworld.com/india/ravindra-chavan-elected-maharashtra-bjp-president-unanimously</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Elected Maharashtra BJP President Unanimously</t>
+          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://www.republicworld.com/india/ravindra-chavan-elected-maharashtra-bjp-president-unanimously</t>
+          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
+          <t>How Ravindra Chavan brought Congress's Kunal Patil into BJP fold the day he became Maharashtra party chief</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/ex-minister-ravindra-chavan-is-bjp's-new-maharashtra-unit-chief/2690729</t>
+          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Money lender booked for suicide abetment of debtor</t>
+          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/money-lender-booked-for-suicide-abetment-of-debtor/articleshow/121603123.cms</t>
+          <t>https://www.inkl.com/news/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>How Ravindra Chavan brought Congress's Kunal Patil into BJP fold the day he became Maharashtra party chief</t>
+          <t>Indian Political Highlights | Former minister Ravindra Chavan appointed as Maharashtra BJP working president</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/news/india/2025/07/01/who-is-ravindra-chavan-maharashtra-bjp-president-brings-congress-s-kunal-patil-into-party-fold.html</t>
+          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
+          <t>Once UAPA accused over Dawood ‘links’, Sena (UBT) leader finds place in BJP ahead of Nashik civic polls</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.inkl.com/news/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
+          <t>https://indianexpress.com/article/political-pulse/uapa-accused-dawood-links-sena-ubt-leader-in-bjp-nashik-civic-polls-10074232/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Indian Political Highlights | Former minister Ravindra Chavan appointed as Maharashtra BJP working president</t>
+          <t>Amit Shah’s Maharashtra Visit: BJP Gears Up for Local Body Polls with Key Outreach</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/india-political-updates-latest-pm-narendra-modi-arvind-kejriwal-atishi-sanjay-singh-aap-bjp-congress-rahul-gandhi-delhi-assembly-elections-polls-live-politics-news-3350792</t>
+          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ahead of Thackeray reunion, BJP’s Rane claims Uddhav harassed Raj, blames him for Shiv Sena’s downfall</t>
+          <t>Ravindra Chavan appointed Maharashtra BJP President</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jul/01/ahead-of-thackeray-reunion-bjps-rane-claims-uddhav-harassed-raj-blames-him-for-shiv-senas-downfall</t>
+          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Once UAPA accused over Dawood ‘links’, Sena (UBT) leader finds place in BJP ahead of Nashik civic polls</t>
+          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/uapa-accused-dawood-links-sena-ubt-leader-in-bjp-nashik-civic-polls-10074232/</t>
+          <t>https://www.dynamitenews.com/story/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Amit Shah’s Maharashtra Visit: BJP Gears Up for Local Body Polls with Key Outreach</t>
+          <t>Pune bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/amit-shah-to-begin-3-day-maharashtra-visit-ahead-of-local-body-polls-3556463</t>
+          <t>https://m.economictimes.com/news/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/articleshow/121904713.cms</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed Maharashtra BJP President</t>
+          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/ravindra-chavan-appointed-maharashtra-bjp-president/07021333</t>
+          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BJP nominates Ravindra Chavan as acting President of Maharashtra State</t>
+          <t>58 BJP chiefs of districts named | Mumbai News</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>https://www.dynamitenews.com/story/bjp-nominates-ravindra-chavan-as-acting-president-of-maharashtra-state</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>58 BJP chiefs of districts named | Mumbai News</t>
+          <t>Former Congress MLA Kunal Patil joins BJP</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/58-bjp-chiefs-of-districts-named/articleshow/121146293.cms</t>
+          <t>https://indianexpress.com/article/cities/mumbai/former-congress-mla-kunal-patil-joins-bjp-10100556/</t>
         </is>
       </c>
     </row>
@@ -1151,24 +1151,24 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>"Double-engine govt working in people's best interests": New Maharashtra BJP chief Ravindra Chavan</t>
+          <t>BJP chief in Maharashtra brings MNS union workers into party</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>After poll drubbing, Prithviraj Chavan may replace Patole in Maharashtra Congress rejig</t>
+          <t>"Double-engine govt working in people's best interests": New Maharashtra BJP chief Ravindra Chavan</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Jan/14/after-poll-drubbing-prithviraj-chavan-may-replace-patole-in-maharashtra-congress-rejig</t>
+          <t>https://www.aninews.in/news/national/politics/double-engine-govt-working-in-peoples-best-interests-new-maharashtra-bjp-chief-ravindra-chavan20250702021253</t>
         </is>
       </c>
     </row>
@@ -1199,5122 +1199,5074 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>Dombivli residents demand clarity as railways issue eviction notices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://www.newsband.in/article_detail/dombivli-residents-demand-clarity-as-railways-issue-eviction-notices</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IndiGo’s AGILE Employees Secure Record Salary Hike in Historic Agreement with Union</t>
+          <t>Mumbai Confidential: Brother trouble</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
+          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Bodies Of Pahalgam Terror Attack Victims From Maharashtra Brought To Mumbai</t>
+          <t>BJP’s Sankalp to Siddhi campaign to begin this week</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/bjps-sankalp-to-siddhi-campaign-to-begin-this-week/articleshow/121606429.cms</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Dombivli MLA Ravindra Chavan Takes Charge as New Maharashtra BJP President, Replacing Chandrashekhar Bawankule</t>
+          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/maharashtra/dombivli-mla-ravindra-chavan-takes-charge-as-new-maharashtra-bjp-president-replacing-chandrashekhar-bawankule-a475/</t>
+          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP State Chief Ravindra Chavan Meets PM Modi, Outlines Party’s Expansion Plan</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-state-chief-ravindra-chavan-meets-pm-modi-outlines-partys-expansion-plan</t>
+          <t>https://tennews.in/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: A Visionary Leader Strengthening Maharashtra BJP's Political Landscape</t>
+          <t>IndiGo’s AGILE Employees Secure Record Salary Hike in Historic Agreement with Union</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
+          <t>https://thecsrjournal.in/indigos-agile-employees-secure-record-salary-hike-in-historic-agreement-with-union/</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Ravindra Chavan, Trusted Lieutenant Of Maharashtra CM Devendra Fadnavis, Appointed BJP State Unit President</t>
+          <t>Pune Congress leader Sanjay Jagtap joins BJP</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-trusted-lieutenant-of-maharashtra-cm-devendra-fadnavis-appointed-bjp-state-unit-president</t>
+          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Meets PM Modi In New Delhi After Taking Charge As Maharashtra State BJP Chief</t>
+          <t>Bodies Of Pahalgam Terror Attack Victims From Maharashtra Brought To Mumbai</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-meets-pm-modi-in-new-delhi-after-taking-charge-as-maharashtra-state-bjp-chief</t>
+          <t>https://www.etvbharat.com/en/!state/bodies-of-pahalgam-terror-attack-victims-from-maharashtra-brought-to-mumbai-enn25042305870</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>BJP’s idea of nationalism will be taken to the common man: Ravindra Chavan</t>
+          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/bjps-idea-of-nationalism-will-be-taken-to-the-common-man-ravindra-chavan/</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>27-Year-Old Flight Attendant from Dombivli Among Victims of Ahmedabad Plane Crash Confirms Maharashtra MLA Ravindra Chavan</t>
+          <t>Ex-Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/thane/27-year-old-flight-attendant-from-dombivli-among-victims-of-ahmedabad-plane-crash-confirms-maharashtra-mla-ravindra-chavan-a475/</t>
+          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ravindra Chavan To Lead Maharashtra BJP Telangana, Andhra, Uttarakhand Unit Chiefs To Be Named Tomorrow</t>
+          <t>Kailas Gorantyal Set to Join BJP Today</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/news/india/ravindra-chavan-to-lead-maharashtra-bjp-telangana-andhra-uttarakhand-unit-chiefs-to-be-named-tomorrow-1784254</t>
+          <t>https://english.lokshahi.com/politics/kailash-gorantyal-to-join-bjp-today</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Files Nomination for Maharashtra BJP President #Gallery</t>
+          <t>BJP holds meeting of former MPs and MLAs ahead of local body polls in Maharashtra</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Former Congress MLA Kailas Gorantyal Joins BJP With Supporters In Mumbai; Ravindra</t>
+          <t>Dombivli MLA Ravindra Chavan Takes Charge as New Maharashtra BJP President, Replacing Chandrashekhar Bawankule</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-mla-kailas-gorantyal-joins-bjp-with-supporters-in-mumbai-ravindra-chavan-welcomes-induction</t>
+          <t>https://www.lokmattimes.com/maharashtra/dombivli-mla-ravindra-chavan-takes-charge-as-new-maharashtra-bjp-president-replacing-chandrashekhar-bawankule-a475/</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>BJP-Mahayuti Govt Committed To Farmers’ Progress &amp; Dairy Sector Growth: Ravindra Chavan</t>
+          <t>Maharashtra Politics: BJP State Chief Ravindra Chavan Meets PM Modi, Outlines Party’s Expansion Plan</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-state-chief-ravindra-chavan-meets-pm-modi-outlines-partys-expansion-plan</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Punes Kundmala Bridge Collapse: Opposition Alleges Corruption, Demands Culpable Homicide Charges</t>
+          <t>Ravindra Chavan, Trusted Lieutenant Of Maharashtra CM Devendra Fadnavis, Appointed BJP State Unit President</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/punes-kundmala-bridge-collapse-opposition-alleges-corruption-demands-culpable-homicide-charges</t>
+          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-trusted-lieutenant-of-maharashtra-cm-devendra-fadnavis-appointed-bjp-state-unit-president</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Read Ravindra Chavan bane BJP ke naye Maharashtra President</t>
+          <t>Ravindra Chavan: A Visionary Leader Strengthening Maharashtra BJP's Political Landscape</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
+          <t>https://www.afternoonvoice.com/ravindra-chavan-a-visionary-leader-strengthening-maharashtra-bjps-political-landscape.html</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Files Nomination For BJP Maharashtra President Post</t>
+          <t>Ravindra Chavan Meets PM Modi In New Delhi After Taking Charge As Maharashtra State BJP Chief</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-files-nomination-for-bjp-maharashtra-president-post</t>
+          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-meets-pm-modi-in-new-delhi-after-taking-charge-as-maharashtra-state-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>BJP Picks Ravindra Chavan As Maharashtra Chief Ahead Of Key Civic Polls</t>
+          <t>BJP’s idea of nationalism will be taken to the common man: Ravindra Chavan</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
+          <t>https://www.lokmattimes.com/national/bjps-idea-of-nationalism-will-be-taken-to-the-common-man-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Ravindra Chavan, Ex-Minister, Files Nomination For Maharashtra BJP Chief Election, Likely To Win Unopposed</t>
+          <t>27-Year-Old Flight Attendant from Dombivli Among Victims of Ahmedabad Plane Crash Confirms Maharashtra MLA Ravindra Chavan</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/maharashtra/ravindra-chavan-exminister-files-nomination-for-maharashtra-bjp-chief-election-likely-to-win-unopposed-10249053</t>
+          <t>https://www.lokmattimes.com/thane/27-year-old-flight-attendant-from-dombivli-among-victims-of-ahmedabad-plane-crash-confirms-maharashtra-mla-ravindra-chavan-a475/</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>Ravindra Chavan To Lead Maharashtra BJP Telangana, Andhra, Uttarakhand Unit Chiefs To Be Named Tomorrow</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>https://www.sakshipost.com/news/ravindra-chavan-set-take-over-maharashtra-unit-bjp-chief-tomorrow-424218</t>
+          <t>https://news.abplive.com/news/india/ravindra-chavan-to-lead-maharashtra-bjp-telangana-andhra-uttarakhand-unit-chiefs-to-be-named-tomorrow-1784254</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Mumbai: Over 2,000 IndiGo Airline Employees Join BJP Ahead Of BMC Election</t>
+          <t>Maharashtra Politics: Former Congress MLA Kailas Gorantyal Joins BJP With Supporters In Mumbai; Ravindra</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/mumbai-over-2000-indigo-airline-employees-join-bjp-ahead-of-bmc-election</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-mla-kailas-gorantyal-joins-bjp-with-supporters-in-mumbai-ravindra-chavan-welcomes-induction</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BJP Appoints Former Minister Ravindra Chavan As Maharashtra Units Working President</t>
+          <t>Ravindra Chavan Files Nomination for Maharashtra BJP President #Gallery</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjp-appoints-former-minister-ravindra-chavan-as-maharashtra-units-working-president</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP Poaches Key Leaders From Rival Parties In Palghar, Strengthens Hold Ahead Of Upcoming</t>
+          <t>BJP-Mahayuti Govt Committed To Farmers’ Progress &amp; Dairy Sector Growth: Ravindra Chavan</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-poaches-key-leaders-from-rival-parties-in-palghar-strengthens-hold-ahead-of-upcoming-elections</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-mahayuti-govt-committed-to-farmers-progress-dairy-sector-growth-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Ravindra Chavan appointed as BJP state president of Maharashtra</t>
+          <t>Punes Kundmala Bridge Collapse: Opposition Alleges Corruption, Demands Culpable Homicide Charges</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
+          <t>https://www.freepressjournal.in/mumbai/punes-kundmala-bridge-collapse-opposition-alleges-corruption-demands-culpable-homicide-charges</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
+          <t>Read Ravindra Chavan bane BJP ke naye Maharashtra President</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
+          <t>https://gallinews.com/ravindra-chavan-bane-bjp-ke-naye-maharashtra-president/</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Security Downgrade For Shinde Faction Leaders Sparks Tensions Between Fadnavis And</t>
+          <t>Ravindra Chavan Files Nomination For BJP Maharashtra President Post</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-security-downgrade-for-shinde-faction-leaders-sparks-tensions-between-fadnavis-and-shinde</t>
+          <t>https://www.freepressjournal.in/mumbai/ravindra-chavan-files-nomination-for-bjp-maharashtra-president-post</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Public Gave Us Landslide Victory: Deputy CM Eknath Shinde Exerts Confidence On Win Of Mahayuti In</t>
+          <t>BJP Picks Ravindra Chavan As Maharashtra Chief Ahead Of Key Civic Polls</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/public-gave-us-landslide-victory-deputy-cm-eknath-shinde-exerts-confidence-on-win-of-mahayuti-in-maharashtra-elections</t>
+          <t>https://www.afternoonvoice.com/bjp-picks-ravindra-chavan-as-maharashtra-chief-ahead-of-key-civic-polls.html</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Dombivali Bandh Today In Mourning After Pahalgam Terror Attack Claims 3 Local Lives</t>
+          <t>Ravindra Chavan, Ex-Minister, Files Nomination For Maharashtra BJP Chief Election, Likely To Win Unopposed</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/dombivali-bandh-today-in-mourning-after-pahalgam-terror-attack-claims-3-local-lives</t>
+          <t>https://www.thedailyjagran.com/maharashtra/ravindra-chavan-exminister-files-nomination-for-maharashtra-bjp-chief-election-likely-to-win-unopposed-10249053</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
+          <t>https://www.sakshipost.com/news/ravindra-chavan-set-take-over-maharashtra-unit-bjp-chief-tomorrow-424218</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Maharashtra News: BJP Warns Of Legal Action Over Fake List Of 81 District Presidents Circulating On Social</t>
+          <t>Mumbai: Over 2,000 IndiGo Airline Employees Join BJP Ahead Of BMC Election</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-warns-of-legal-action-over-fake-list-of-81-district-presidents-circulating-on-social-media</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-over-2000-indigo-airline-employees-join-bjp-ahead-of-bmc-election</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में निकाय चुनाव से पहले BJP का बड़ा प्लान, पूर्व सांसदों और विधायकों</t>
+          <t>BJP Appoints Former Minister Ravindra Chavan As Maharashtra Units Working President</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
+          <t>https://www.freepressjournal.in/mumbai/bjp-appoints-former-minister-ravindra-chavan-as-maharashtra-units-working-president</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: बीजेपी ने पूर्व मंत्री रवींद्र चव्हाण को बनाया महाराष्ट्र का कार्यकारी अध्यक्ष, जानें पूरा सफर</t>
+          <t>Ex-Minister Ravindra Chavan Appointed Maharashtra BJP’s Working President</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
+          <t>https://ommcomnews.com/india-news/ex-minister-ravindra-chavan-appointed-maharashtra-bjps-working-president/</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: BJP ने मराठा फेस रवींद्र चव्हाण पर क्यों जताया भरोसा? जानें पूरा सफर</t>
+          <t>Ravindra Chavan Files Nomination for Maharashtra BJP President</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-why-did-bjp-express-confidence-in-maratha-face-ravindra-chavan-know-journey-3054753.html</t>
+          <t>https://www.prokerala.com/news/photos/ravindra-chavan-files-nomination-for-maharashtra-bjp-president-3732733.html</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Latest News, Updates in Hindi | रवींद्र चव्हाण के समाचार और अपडेट</t>
+          <t>Maharashtra: BJP Poaches Key Leaders From Rival Parties In Palghar, Strengthens Hold Ahead Of Upcoming</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-poaches-key-leaders-from-rival-parties-in-palghar-strengthens-hold-ahead-of-upcoming-elections</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>कौन होगा महाराष्ट्र भाजपा का नया चीफ? रविंद्र चव्हाण का नाम लगभग तय, जानिए इसके पीछे क्या वजह</t>
+          <t>Ravindra Chavan appointed as BJP state president of Maharashtra</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
+          <t>https://theindianawaaz.com/ravindra-chavan-appointed-as-bjp-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>मराठा चेहरा, कोंकण में पलटी बाजी; बीजेपी ने क्यों जताया रवींद्र चव्हाण पर भरोसा</t>
+          <t>2000 Indigo Airlines Employees Officially Join BJP In Mumbai</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
+          <t>https://trak.in/stories/2000-indigo-airlines-employees-officially-join-bjp-in-mumbai/</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी अध्यक्ष के लिए ये नाम लगभग तय, जानें क्यों माने जाते हैं प्रबल</t>
+          <t>BJP’s Mega Blood Donation Drive On Fadnavis’ Birthday Sets Two World Records, Says Asia Book Of Records</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
+          <t>https://www.freepressjournal.in/mumbai/bjps-mega-blood-donation-drive-on-fadnavis-birthday-sets-two-world-records-says-asia-book-of-records</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए बॉस, CM फडणवीस के साथ भरा नामांकन, जानें कौन हैं?</t>
+          <t>Public Gave Us Landslide Victory: Deputy CM Eknath Shinde Exerts Confidence On Win Of Mahayuti In</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/maharashtra-bjp-will-get-new-president-filed-nomination-know-who-is-ravindra-chavan-19711885</t>
+          <t>https://www.freepressjournal.in/mumbai/public-gave-us-landslide-victory-deputy-cm-eknath-shinde-exerts-confidence-on-win-of-mahayuti-in-maharashtra-elections</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>महाराष्ट्र से रविंद्र चव्हाण तो एमपी से खंडेलवाल बने बीजेपी के नए प्रदेश अध्यक्ष, यहां जानें सारी डिटेल्स</t>
+          <t>Who Is Ameet Satam? Three-Term MLA From Andheri West Appointed As President Of Mumbai BJP Unit</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
+          <t>https://www.freepressjournal.in/mumbai/who-is-ameet-satam-three-term-mla-from-andheri-west-appointed-as-president-of-mumbai-bjp-unit</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Maharashtra BJP Politics: महाराष्ट्र में बड़ी जीत के बाद इस नेता को प्रदेश अध्यक्ष बना सकती है BJP, फडणवीस के हैं करीबी</t>
+          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
+          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र भाजपा के कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा ने किया एलान</t>
+          <t>Maharashtra News: BJP Sets Up 1,221 Mandals Across State, Appoints 963 Presidents Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-23865140.html</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-sets-up-1221-mandals-across-state-appoints-963-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण की जीवनी | Ravindra Chavan Biography in Hindi</t>
+          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>https://politalks.news/ravindra-chavan-biography-in-hindi</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Maharashtra: पूर्व मंत्री रवीन्द्र चव्हाण बने महाराष्ट्र भाजपा के नए अध्यक्ष, सीएम देवेंद्र फडणवीस के हैं करीब</t>
+          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>https://www.amarujala.com/india-news/ex-minister-ravindra-chavan-is-bjp-s-new-maharashtra-chief-2025-07-01</t>
+          <t>https://www.cityairnews.com/content/ravindra-chavan-elected-unopposed-as-maha-bjp-chief</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के नए प्रदेश अध्यक्ष, जानें उनका राजनीतिक सफर</t>
+          <t>Nanded-Pune Vande Bharat Express to Start by December 2025</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
+          <t>https://www.lokmattimes.com/maharashtra/nanded-pune-vande-bharat-express-to-start-by-december-2025-a517/</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 4 बार के विधायक, मराठा नेता, नतीजे देने की क्षमता, महाराष्ट्र BJP के नए कार्यकारी अध्यक्ष रवींद्र चव्हाण कौन?</t>
+          <t>Maharashtra News: BJP Warns Of Legal Action Over Fake List Of 81 District Presidents Circulating On Social</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-warns-of-legal-action-over-fake-list-of-81-district-presidents-circulating-on-social-media</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा को मिला नया ‘कप्तान’, जानें कौन हैं प्रदेश अध्यक्ष रवींद्र चव्हाण?</t>
+          <t>Over 2,000 IndiGo employees join BJP ahead of BMC elections in Mumbai</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/ravindra-chavan-became-maharashtra-bjp-president-know-who-is-he-19715228</t>
+          <t>https://english.varthabharati.in/india/over-2000-indigo-employees-join-bjp-ahead-of-bmc-elections-in-mumbai</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए अध्यक्ष, किरेन रिजिजू की मौजूदगी में भरा नामांकन - Ravindra Chavan will be the new president of Maharashtra BJP nomination filed in the presence of Kiren Rijiju</t>
+          <t>महाराष्ट्र में निकाय चुनाव से पहले BJP का बड़ा प्लान, पूर्व सांसदों और विधायकों</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-local-election-bjp-president-ravindra-chavan-asked-former-mps-and-mlas-to-adopt-one-mandal-each-ann-2988472</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>सीएम देवेंद्र फडणवीस के करीबी रवींद्र चव्हाण बने महाराष्ट्र BJP के अध्यक्ष, जानें</t>
+          <t>Ravindra Chavan: बीजेपी ने पूर्व मंत्री रवींद्र चव्हाण को बनाया महाराष्ट्र का कार्यकारी अध्यक्ष, जानें पूरा सफर</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-elected-maharashtra-bjp-president-ann-2972075</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-appointed-ravindra-chavan-as-working-state-president-of-maharashtra-know-his-journey/articleshow/117154523.cms</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP प्रदेश अध्यक्ष का नाम हो गया तय, कल शाम 5 बजे होगी घोषणा</t>
+          <t>महाराष्ट्र: BJP ने मराठा फेस रवींद्र चव्हाण पर क्यों जताया भरोसा? जानें पूरा सफर</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/maharashtra-why-did-bjp-express-confidence-in-maratha-face-ravindra-chavan-know-journey-3054753.html</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>महाराष्ट्र: रवींद्र चव्हाण बने BJP कार्यकारी प्रदेश अध्यक्ष, क्या छिन गई चंद्रशेखर</t>
+          <t>Ravindra Chavan Latest News, Updates in Hindi | रवींद्र चव्हाण के समाचार और अपडेट</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
+          <t>https://www.aajtak.in/topic/ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: रवींद्र चव्हाण बने महाराष्‍ट्र भाजपा के नए अध्‍यक्ष, पद संभालते के बाद क्‍या बोले?</t>
+          <t>कौन होगा महाराष्ट्र भाजपा का नया चीफ? रविंद्र चव्हाण का नाम लगभग तय, जानिए इसके पीछे क्या वजह</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-new-chief-of-maharashtra-bjp-ravindra-chavan-name-is-almost-finalised-9348436.html</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>कौन हैं रविंद्र चव्हाण जिन्हें बीजेपी ने पूरा महाराष्ट्र 'सौंप' दिया है? | The Lallantop</t>
+          <t>महाराष्ट्र बीजेपी अध्यक्ष के लिए ये नाम लगभग तय, जानें क्यों माने जाते हैं प्रबल</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>https://www.thelallantop.com/india/post/bjp-appoints-maratha-face-as-its-next-maharashtra-president-who-is-ravindra-chavan</t>
+          <t>https://www.abplive.com/states/maharashtra/maharashtra-ravindra-chavan-can-become-president-of-maharashtra-bjp-mumbai-ann-2969682</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, मुंबई महानगर क्षेत्र चुनाव में बदल सकते हैं समीकरण</t>
+          <t>मराठा चेहरा, कोंकण में पलटी बाजी; बीजेपी ने क्यों जताया रवींद्र चव्हाण पर भरोसा</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
+          <t>https://www.livehindustan.com/national/why-bjp-gave-responsibility-of-maharashtra-unit-to-ravindra-chavan-maratha-face-201736616683779.html</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>भाजपच्या 81 जिल्हाध्यक्षांची ती यादी फेक, व्हायरल करू नका रविंद्र चव्हाणांकडून इशारा</t>
+          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए बॉस, CM फडणवीस के साथ भरा नामांकन, जानें कौन हैं?</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
+          <t>https://www.patrika.com/mumbai-news/maharashtra-bjp-will-get-new-president-filed-nomination-know-who-is-ravindra-chavan-19711885</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>पार्षद से भाजपा प्रदेश अध्यक्ष तक… कैसा है महाराष्ट्र बीजेपी के नए अध्यक्ष रवींद्र चव्हाण का...</t>
+          <t>महाराष्ट्र से रविंद्र चव्हाण तो एमपी से खंडेलवाल बने बीजेपी के नए प्रदेश अध्यक्ष, यहां जानें सारी डिटेल्स</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/ravindra-chavan-new-bjp-maharashtra-president-profile-and-political-career-3369773.html</t>
+          <t>https://ndtv.in/india/ravindra-chavan-from-maharashtra-khandelwal-from-mp-became-new-state-president-of-bjp-know-all-details-here-8812249</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: कौन हैं रविंद्र चव्‍हाण? जिनका महाराष्ट्र BJP प्रदेश अध्यक्ष बनना तय है</t>
+          <t>Maharashtra BJP Politics: महाराष्ट्र में बड़ी जीत के बाद इस नेता को प्रदेश अध्यक्ष बना सकती है BJP, फडणवीस के हैं करीबी</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-bjp-president-who-is-ravindra-chavan-going-to-take-over-bjp-state-president-post-1328621.html</t>
+          <t>https://www.jansatta.com/national/bjp-may-appoint-ravindra-chavan-maharashtra-state-president-cm-devendra-fadnavis/3775586/</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>WHO IS Ravindra Chavan: कौन हैं रवींद्र चव्हाण?, भाजपा ने क्यों खेला दांव, चंद्रशेखर बावनकुले की जगह ले सकते हैं</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र भाजपा के कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा ने किया एलान</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
+          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-23865140.html</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>बीजेपी प्रदेश अध्यक्ष बनते ही कांग्रेस में सेंध... पहले ही दिन रवींद्र चव्हाण ने कराई कुणाल पाटिल की जॉइनिंग</t>
+          <t>रवींद्र चव्हाण की जीवनी | Ravindra Chavan Biography in Hindi</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
+          <t>https://politalks.news/ravindra-chavan-biography-in-hindi</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Kalyan : 'माझी कपिल पाटील आणि रविंद्र चव्हाण यांच्याशी लढाई' कल्याणच्या माजी भाजपा आमदाराची क्लीप Viral</t>
+          <t>Maharashtra: पूर्व मंत्री रवीन्द्र चव्हाण बने महाराष्ट्र भाजपा के नए अध्यक्ष, सीएम देवेंद्र फडणवीस के हैं करीब</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
+          <t>https://www.amarujala.com/india-news/ex-minister-ravindra-chavan-is-bjp-s-new-maharashtra-chief-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी की कमान अब रवींद्र चव्हाण के हाथ में, निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
+          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के नए प्रदेश अध्यक्ष, जानें उनका राजनीतिक सफर</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/india/ravindra-chavan-elected-unopposed-as-maharashtra-bjp-president-3369508.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/ravindra-chavan-becomes-maharashtra-bjp-new-president-know-political-career-ntc-rpti-2277379-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>भाजपा महाराष्ट्र प्रदेश अध्यक्ष पद पर रविंद्र चौहान</t>
+          <t>Ravindra Chavan: 4 बार के विधायक, मराठा नेता, नतीजे देने की क्षमता, महाराष्ट्र BJP के नए कार्यकारी अध्यक्ष रवींद्र चव्हाण कौन?</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-working-president-dombivali-mla-ravindra-chavan-why-party-appointed-know-all/articleshow/117210600.cms</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>BJP News : रवींद्र चव्हाण यांची भाजपच्या महाराष्ट्र कार्यकारी अध्यक्षपदी नियुक्ती</t>
+          <t>महाराष्ट्र भाजपा को मिला नया ‘कप्तान’, जानें कौन हैं प्रदेश अध्यक्ष रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
+          <t>https://www.patrika.com/mumbai-news/ravindra-chavan-became-maharashtra-bjp-president-know-who-is-he-19715228</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>मोठी बातमी! भाजपाच्या प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>रवींद्र चव्हाण होंगे महाराष्ट्र भाजपा के नए अध्यक्ष, किरेन रिजिजू की मौजूदगी में भरा नामांकन - Ravindra Chavan will be the new president of Maharashtra BJP nomination filed in the presence of Kiren Rijiju</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavan-appointed-as-bjp-maharashtra-chief-1436143.html</t>
+          <t>https://www.jagran.com/maharashtra/mumbai-ravindra-chavan-will-be-the-new-president-of-maharashtra-bjp-nomination-filed-in-the-presence-of-kiren-rijiju-23971616.html</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : '.....तर उद्धव ठाकरेंनाही सोबत घेऊ' भाजपा प्रदेशाध्यक्षांचं मोठं वक्तव्य</t>
+          <t>सीएम देवेंद्र फडणवीस के करीबी रवींद्र चव्हाण बने महाराष्ट्र BJP के अध्यक्ष, जानें</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-elected-maharashtra-bjp-president-ann-2972075</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 'शिंदे मुख्यमंत्री झाल्यावर वाईट वाटलं', चव्हाण यांनी पहिल्यांदाच सांगितलं नाराजीचं कारण</t>
+          <t>महाराष्ट्र BJP प्रदेश अध्यक्ष का नाम हो गया तय, कल शाम 5 बजे होगी घोषणा</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-name-suggested-as-maharashtra-bjp-president-by-chandrashekhar-bawankule-2971280</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Who is Ravindra Chavan | डोंबिवलीचे नगरसेवक ते भाजप प्रदेशाध्यक्ष, जाणून घ्या रविंद्र चव्हाण यांचा राजकीय प्रवास</t>
+          <t>महाराष्ट्र: रवींद्र चव्हाण बने BJP कार्यकारी प्रदेश अध्यक्ष, क्या छिन गई चंद्रशेखर</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/who-is-ravindra-chavan-dombivli-corporator-to-bjp-state-president-political-journey-biography-db79</t>
+          <t>https://www.abplive.com/states/maharashtra/ravindra-chavan-appointed-maharashtra-bjp-working-president-cm-devendra-fadnavis-welcomes-2861067</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रविंद्र चव्हाण भाजपाचे नवे प्रदेशाध्यक्ष, किरेन रिजिजू यांनी केली घोषणा</t>
+          <t>Maharashtra BJP President: रवींद्र चव्हाण बने महाराष्‍ट्र भाजपा के नए अध्‍यक्ष, पद संभालते के बाद क्‍या बोले?</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-the-new-maharashtra-state-president-of-bjp-announced-by-minister-kiren-rijiju-gkt-96-5196414/</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/ravindra-chavan-became-the-new-president-of-maharashtra-bjp-took-this-promise-1329755.html</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रवींद्र चव्हाण भाजपाच्या महाराष्ट्र प्रदेशाध्यक्षपदी विराजमान, जाणून घ्या कशी आहे त्यांची कारकीर्द?</t>
+          <t>कौन हैं रविंद्र चव्हाण जिन्हें बीजेपी ने पूरा महाराष्ट्र 'सौंप' दिया है? | The Lallantop</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-now-president-of-bjp-maharashtra-state-know-about-his-political-career-scj-81-5196879/</t>
+          <t>https://www.thelallantop.com/india/post/bjp-appoints-maratha-face-as-its-next-maharashtra-president-who-is-ravindra-chavan</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Ravindra Chavan on Cabinet Reshuffle: महाराष्ट्रात मंत्रिमंडळ फेरबदल होणार? ; भाजप प्रदेशाध्यक्ष रविंद्र चव्हाणांनी स्पष्टच दिलं उत्तर, म्हणाले...</t>
+          <t>रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, मुंबई महानगर क्षेत्र चुनाव में बदल सकते हैं समीकरण</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/maharashtra-cabinet-reshuffle-bjp-ravindra-chavan-statement-political-developments-2025-mahayuti-msr87</t>
+          <t>https://ndtv.in/maharashtra-news/ravindra-chavan-new-maharashtra-bjp-president-know-his-political-journey-8811120</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : 'हरकाम्या' कार्यकर्ता ते भाजप प्रदेश कार्याध्यक्ष; रवींद्र चव्हाण कसे बनले नेत्यांच्या गळ्यातील ताईत?</t>
+          <t>भाजपच्या 81 जिल्हाध्यक्षांची ती यादी फेक, व्हायरल करू नका रविंद्र चव्हाणांकडून इशारा</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/ravindra-chavan-political-journey-from-common-worker-to-bjp-executive-president-rm82-pp82</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-ravindra-chavan-warns-throw-away-the-list-of-81-district-presidents-of-bjp-don-t-make-it-viral-social-media-1359706</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>भाजपचा नवा प्रदेशाध्यक्ष कोण? ‘या’ बड्या नेत्याचं नाव निश्चित, उद्या नावाची घोषणा होणार!</t>
+          <t>पार्षद से भाजपा प्रदेश अध्यक्ष तक… कैसा है महाराष्ट्र बीजेपी के नए अध्यक्ष रवींद्र चव्हाण का...</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-will-be-maharashtra-state-president-of-bjp-name-will-announce-1st-july-1435245.html</t>
+          <t>https://www.tv9hindi.com/india/ravindra-chavan-new-bjp-maharashtra-president-profile-and-political-career-3369773.html</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>रविंद्र चव्हाण लवकरच भाजपचे नवे प्रदेशाध्यक्ष</t>
+          <t>Maharashtra BJP President: कौन हैं रविंद्र चव्‍हाण? जिनका महाराष्ट्र BJP प्रदेश अध्यक्ष बनना तय है</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/maharashtra-politics-ravindra-chavan-set-to-be-new-bjp-maharashtra-president-mumbai-print-news-vsd-99-5188808/</t>
+          <t>https://hindi.oneindia.com/news/maharashtra/maharashtra-bjp-president-who-is-ravindra-chavan-going-to-take-over-bjp-state-president-post-1328621.html</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ravindra Chavan | रविंद्र चव्हाण यांची भाजप महाराष्‍ट्र प्रदेशाध्यक्षपदी निवड!</t>
+          <t>WHO IS Ravindra Chavan: कौन हैं रवींद्र चव्हाण?, भाजपा ने क्यों खेला दांव, चंद्रशेखर बावनकुले की जगह ले सकते हैं</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-appointed-jp-maharashtra-president</t>
+          <t>https://www.lokmatnews.in/india/who-is-ravindra-chavan-bjp-mla-appointed-working-state-president-maharashtra-replace-chandrashekhar-bawankule-b507/</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>ब्राह्मण, OBC और मराठा... देवेंद्र फडणवीस का अकाट्य फॉर्मूला, कांग्रेस ही नहीं सहयोगी भी चित!</t>
+          <t>बीजेपी प्रदेश अध्यक्ष बनते ही कांग्रेस में सेंध... पहले ही दिन रवींद्र चव्हाण ने कराई कुणाल पाटिल की जॉइनिंग</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
+          <t>https://www.aajtak.in/india/maharashtra/story/bjp-maharashtra-president-ravindra-chavan-kunal-patil-congress-north-maharashtra-dhule-ntcpbt-dskc-2277786-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>महाराष्ट्र बीजेपी की कमान अब रवींद्र चव्हाण के हाथ में, निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
+          <t>https://www.tv9hindi.com/india/ravindra-chavan-elected-unopposed-as-maharashtra-bjp-president-3369508.html</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>सांगलीचा आगामी महापौर महायुतीचाच – रविंद्र चव्हाण</t>
+          <t>Kalyan : 'माझी कपिल पाटील आणि रविंद्र चव्हाण यांच्याशी लढाई' कल्याणच्या माजी भाजपा आमदाराची क्लीप Viral</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/sangli-bjp-ravindra-chavan-confident-next-mayor-in-upcoming-civic-poll-will-be-from-mahayuti-rds-00-5299211/</t>
+          <t>https://marathi.ndtv.com/cities/kalyan-ex-bjp-mla-feud-viral-clip-shows-strong-words-against-kapil-patil-and-ravindra-chavan-in-heated-exchange-9007785</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : फडणवीसांची औरंगजेबाशी तुलना करताच रविंद्र चव्हाण संतापले, काँग्रेस प्रदेशाध्यक्षांना दिलं उत्तर</t>
+          <t>भाजपा महाराष्ट्र प्रदेश अध्यक्ष पद पर रविंद्र चौहान</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
+          <t>https://mandalnews.com/maharashtra/ravindra-chauhan-on-the-post-of-bjp-maharashtra-state-president/</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>BJP News : शहराध्यक्ष कसा असावा ? भाजपा कार्याध्यक्ष रविंद्र चव्हाण यांनी पदाधिकारी-कार्यकर्त्यांचे कान टोचले!</t>
+          <t>BJP News : रवींद्र चव्हाण यांची भाजपच्या महाराष्ट्र कार्यकारी अध्यक्षपदी नियुक्ती</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-expresses-expectations-from-bjp-city-district-presidents-jp75</t>
+          <t>https://marathi.ndtv.com/cities/bjp-news-ravindra-chavan-appointed-bjps-maharashtra-working-president-7451905</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रविंद्र चव्हाण यांनी प्रदेशाध्यक्ष पदाचा पदभार स्विकारला</t>
+          <t>मोठी बातमी! भाजपाच्या प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavan-appointed-as-bjp-maharashtra-chief-1436143.html</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>नगरसेवक ते थेट भाजपचे प्रदेशाध्यक्ष… रवींद्र चव्हाण यांच्या कारकिर्दीतील हे टप्पे माहीत आहेत...</t>
+          <t>Ravindra Chavan : '.....तर उद्धव ठाकरेंनाही सोबत घेऊ' भाजपा प्रदेशाध्यक्षांचं मोठं वक्तव्य</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-new-maharashtra-bjp-presdent-know-his-journey-1436161.html</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-president-ravindra-chavan-makes-big-statement-on-alliance-with-uddhav-thackeray-8864806</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>इंदापूर तालुक्यातील प्रवीण माने यांचा रविंद्र चव्हाण यांच्या उपस्थितीत भाजपात प्रवेश</t>
+          <t>Ravindra Chavan: 'शिंदे मुख्यमंत्री झाल्यावर वाईट वाटलं', चव्हाण यांनी पहिल्यांदाच सांगितलं नाराजीचं कारण</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/praveen-mane-from-indapur-tehsil-joined-bjp-in-the-presence-of-ravindra-chavan-svk-88-phm-00-5199118/</t>
+          <t>https://marathi.ndtv.com/politics/ravindra-chavan-opens-up-about-disappointment-over-eknath-shinde-becoming-chief-minister-reveals-true-feelings-8865262</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपची धुरा रवींद्र चव्हाण सांभाळणार, कार्यकारी प्रदेशाध्यक्ष म्हणून नियुक्ती</t>
+          <t>Who is Ravindra Chavan | डोंबिवलीचे नगरसेवक ते भाजप प्रदेशाध्यक्ष, जाणून घ्या रविंद्र चव्हाण यांचा राजकीय प्रवास</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>https://pudhari.news/national/raviindra-chavhan-appointed-maharashtra-bjp-executive-state-president</t>
+          <t>https://pudhari.news/maharashtra/mumbai/who-is-ravindra-chavan-dombivli-corporator-to-bjp-state-president-political-journey-biography-db79</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>अण्णासाहेब डांगे दो बेटों के साथ BJP में शामिल, CM देवेंद्र फडणवीस की मौजूदगी में</t>
+          <t>Ravindra Chavan : रविंद्र चव्हाण भाजपाचे नवे प्रदेशाध्यक्ष, किरेन रिजिजू यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
+          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-the-new-maharashtra-state-president-of-bjp-announced-by-minister-kiren-rijiju-gkt-96-5196414/</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण, एकमताने निवड, वाचा सविस्तर माहिती</t>
+          <t>Ravindra Chavan on Cabinet Reshuffle: महाराष्ट्रात मंत्रिमंडळ फेरबदल होणार? ; भाजप प्रदेशाध्यक्ष रविंद्र चव्हाणांनी स्पष्टच दिलं उत्तर, म्हणाले...</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
+          <t>https://www.esakal.com/maharashtra/maharashtra-cabinet-reshuffle-bjp-ravindra-chavan-statement-political-developments-2025-mahayuti-msr87</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>RSS स्वयंसेवक ते BJP प्रदेशाध्यक्ष; ‘अशी’ आहे रवींद्र चव्हाण यांची राजकीय कारकीर्द</t>
+          <t>Ravindra Chavan : रवींद्र चव्हाण भाजपाच्या महाराष्ट्र प्रदेशाध्यक्षपदी विराजमान, जाणून घ्या कशी आहे त्यांची कारकीर्द?</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/from-rss-volunteer-to-bjp-state-president-know-about-ravindra-chavan-political-career-a-a719/</t>
+          <t>https://www.loksatta.com/maharashtra/ravindra-chavan-is-now-president-of-bjp-maharashtra-state-know-about-his-political-career-scj-81-5196879/</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>भाजपच्या महाराष्ट्र प्रदेश कार्यकारी अध्यक्षपदी रविंद्र चव्हाण यांची नियुक्ती</t>
+          <t>Ravindra Chavan : 'हरकाम्या' कार्यकर्ता ते भाजप प्रदेश कार्याध्यक्ष; रवींद्र चव्हाण कसे बनले नेत्यांच्या गळ्यातील ताईत?</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/ravindra-chavan-political-journey-from-common-worker-to-bjp-executive-president-rm82-pp82</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महापालिका आयुक्तांनी प्रोटोकॉल पाळावा, हक्कभंगाची नोटीस देणार, नांदेडचे</t>
+          <t>रविंद्र चव्हाण लवकरच भाजपचे नवे प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
+          <t>https://www.loksatta.com/mumbai/maharashtra-politics-ravindra-chavan-set-to-be-new-bjp-maharashtra-president-mumbai-print-news-vsd-99-5188808/</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : ‘उपरा’ डोंबिवलीकर ते भाजप प्रदेश कार्याध्यक्ष</t>
+          <t>भाजपचा नवा प्रदेशाध्यक्ष कोण? ‘या’ बड्या नेत्याचं नाव निश्चित, उद्या नावाची घोषणा होणार!</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-leader-ravindra-chavan-political-journey-started-as-a-worker-to-maharashtra-bjp-chief-zws-70-4821598/</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-will-be-maharashtra-state-president-of-bjp-name-will-announce-1st-july-1435245.html</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>BJP Politics : कल्याण-डोंबिवलीत भाजप ठाकरेंना धक्का देणार! शिंदेंचीही अडचण वाढवणार; इन्कमिंग सुरू, महापौरपदासाठी स्वबळाचे संकेत</t>
+          <t>Ravindra Chavan | रविंद्र चव्हाण यांची भाजप महाराष्‍ट्र प्रदेशाध्यक्षपदी निवड!</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/jatin-prajapati-joins-kalyan-dombivli-bjp-welcomed-by-ravindra-chavan-rm89</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-appointed-jp-maharashtra-president</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>संयमी भूमिका फळली! भाजपच्या कार्यकारी प्रदेशाध्यक्षपदी रविंद्र चव्हाणांची नियुक्ती</t>
+          <t>Ravindra Chavan : मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-elected-as-bjp-working-state-president-maharashtra-politics-marathi-news-1338059</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Congress News : काँग्रेस खासदार रविंद्र चव्हाण संतापले, महापालिका आयुक्तांना हक्कभंग कारवाईचा इशारा!</t>
+          <t>Ravindra Chavan : फडणवीसांची औरंगजेबाशी तुलना करताच रविंद्र चव्हाण संतापले, काँग्रेस प्रदेशाध्यक्षांना दिलं उत्तर</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/congress-mp-ravindra-chavan-warns-action-against-commissioner-over-amit-shah-event-jp75</t>
+          <t>https://marathi.ndtv.com/politics/bjp-state-working-president-ravindra-chavan-responds-congress-state-president-harshvardhan-sapkal-8802075</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी, आज अधिवेशनात सूत्रे स्वीकारणार</t>
+          <t>BJP News : शहराध्यक्ष कसा असावा ? भाजपा कार्याध्यक्ष रविंद्र चव्हाण यांनी पदाधिकारी-कार्यकर्त्यांचे कान टोचले!</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-bjp-state-president-will-take-charge-in-the-convention-today-a-a941/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-expresses-expectations-from-bjp-city-district-presidents-jp75</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजप नेते रविंद्र चव्हाण यांच्यावर पक्षाची महत्वाची जबाबदारी; कार्यकारी अध्यक्षपदी नियुक्ती</t>
+          <t>ब्राह्मण, OBC और मराठा... देवेंद्र फडणवीस का अकाट्य फॉर्मूला, कांग्रेस ही नहीं सहयोगी भी चित!</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/desh/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-aau85</t>
+          <t>https://hindi.news18.com/news/maharashtra/mumbai-maharashtra-politics-devendra-fadnavis-brahmin-obc-maratha-formula-ravindra-chouhan-chandrashekhar-bawankule-8954968.html</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में भाजपा के संगठन निर्माण को मिली नई ताकत, राज्य में 1221 मंडलों का गठन</t>
+          <t>भास्कर अपडेट्स: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी के कार्यकारी प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/bjp-building-organization-in-maharashtra-gets-new-strength-1221-mandals-formed/1157953/</t>
+          <t>https://www.bhaskar.com/national/news/breaking-news-live-updates-headlines-6-january-rajasthan-delhi-mp-uttar-pradesh-maharashtra-mumbai-punjab-134273875.html</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Ravindra Chavan BJP: रवींद्र चव्हाण भाजपाचे नवे 'कॅप्टन'! महाराष्ट्र प्रदेशाध्यक्षपदी बिनविरोध निवड</t>
+          <t>Ravindra Chavan : रविंद्र चव्हाण यांनी प्रदेशाध्यक्ष पदाचा पदभार स्विकारला</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-elected-unopposed-as-bjp-maharashtra-state-president-in-mumbai-event-devendra-fadnavis-a-a747/</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-appointed-maharashtra-bjp-president-1436968.html</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Maharashtra Updates : भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण, जलसंधारण विभागात 8 हजारांहून अधिक पदांची भरती...</t>
+          <t>नगरसेवक ते थेट भाजपचे प्रदेशाध्यक्ष… रवींद्र चव्हाण यांच्या कारकिर्दीतील हे टप्पे माहीत आहेत...</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-01-june-2025-live-updates-assembly-session-live-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-raj-thackeray-uddhav-thackeray-devendra-fadnavis-shivsena-rm82</t>
+          <t>https://www.tv9marathi.com/politics/ravindra-chavhan-new-maharashtra-bjp-presdent-know-his-journey-1436161.html</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>BJP News : आमचा पक्ष 24/7 काम करणारा; मोठा - छोटा भाऊ असा सर्व्हे भाजप करत नाही!</t>
+          <t>इंदापूर तालुक्यातील प्रवीण माने यांचा रविंद्र चव्हाण यांच्या उपस्थितीत भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-ravindra-chavan-statement-on-party-work-and-alliance-jp75</t>
+          <t>https://www.loksatta.com/maharashtra/praveen-mane-from-indapur-tehsil-joined-bjp-in-the-presence-of-ravindra-chavan-svk-88-phm-00-5199118/</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>“भाजपा हीच माझी ओळख” ; महाराष्ट्र भाजपा प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांची बिनविरोध निवड</t>
+          <t>सांगलीचा आगामी महापौर महायुतीचाच – रविंद्र चव्हाण</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-is-my-identity-ravindra-chavan-elected-unopposed-as-maharashtra-bjp-state-president/</t>
+          <t>https://www.loksatta.com/maharashtra/sangli-bjp-ravindra-chavan-confident-next-mayor-in-upcoming-civic-poll-will-be-from-mahayuti-rds-00-5299211/</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण यांची अखेर भाजपाच्या कार्यकारी प्रदेशाध्यक्षपदी वर्णी; राष्ट्रीय अध्यक्ष जेपी नड्डांची घोषणा</t>
+          <t>अण्णासाहेब डांगे दो बेटों के साथ BJP में शामिल, CM देवेंद्र फडणवीस की मौजूदगी में</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mla-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-kvg-85-4820046/</t>
+          <t>https://www.abplive.com/states/maharashtra/annasaheb-dange-joins-bjp-with-his-two-sons-chiman-and-vishwanath-dange-in-the-presence-of-cm-devendra-fadnavis-ann-2987987</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Maharashtra BJP State President: उत्सुकता संपली; भाजपला मिळणार नवा प्रदेशाध्यक्ष! चंद्रशेखर बावनकुळेंच्या जागी रविंद्र चव्हाणांची नियुक्ती होणार</t>
+          <t>महाराष्ट्र भाजपची धुरा रवींद्र चव्हाण सांभाळणार, कार्यकारी प्रदेशाध्यक्ष म्हणून नियुक्ती</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
+          <t>https://pudhari.news/national/raviindra-chavhan-appointed-maharashtra-bjp-executive-state-president</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : "सामान्य नगरसेवक ते भाजपचे प्रदेशाध्यक्ष..."</t>
+          <t>Maharashtra Politics: कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण, एकमताने निवड, वाचा सविस्तर माहिती</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/ravindra-chavan-appointed-bjp-president-kiren-rijiju-announcement-and-political-career-as11</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/maharashtra-politics-bjp-leader-ravindra-chavan-unanimously-elected-maharashtra-bjp-president-80826</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपचं ठरलं, रवींद्र चव्हाण प्रदेशाध्यक्ष होणार, ठाकरेंच्या बालेकिल्ल्यात पहिलं शक्तिप्रद...</t>
+          <t>RSS स्वयंसेवक ते BJP प्रदेशाध्यक्ष; ‘अशी’ आहे रवींद्र चव्हाण यांची राजकीय कारकीर्द</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
+          <t>https://www.lokmat.com/maharashtra/from-rss-volunteer-to-bjp-state-president-know-about-ravindra-chavan-political-career-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>BJP Ravindra Chavan News: भाजपच्या गोटातून मोठी बातमी समोर Maharashtra Politics</t>
+          <t>भाजपच्या महाराष्ट्र प्रदेश कार्यकारी अध्यक्षपदी रविंद्र चव्हाण यांची नियुक्ती</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
+          <t>https://www.localnewsnetwork.in/mla-ravindra-chavan-has-been-appointed-as-the-maharashtra-state-executive-president-of-bjp/</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>रत्नागिरी भाजपमध्ये नारायण राणे, रविंद्र चव्हाण यांच्यातील वाद चव्हाट्यावर</t>
+          <t>Ravindra Chavan : महापालिका आयुक्तांनी प्रोटोकॉल पाळावा, हक्कभंगाची नोटीस देणार, नांदेडचे</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/dispute-between-narayan-rane-and-ravindra-chavan-in-ratnagiri-bjp-is-on-rise-print-political-news-ocd-94-5140598/</t>
+          <t>https://marathi.abplive.com/news/nanded/congress-mp-ravindra-chavan-warning-to-follow-protocol-due-to-nanded-municipal-corporation-commissioner-over-not-inviting-for-programme-1360903</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: उद्धव ठाकरेंच्या भाजपसोबतच्या वाढत्या जवळीकतेवर रवींद्र चव्हाण यांचं महत्त्वाचं विधान; म्हणाले, शत्रूही...</t>
+          <t>Ravindra Chavan : ‘उपरा’ डोंबिवलीकर ते भाजप प्रदेश कार्याध्यक्ष</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-important-statement-on-uddhav-thackeray-closeness-with-bjp-aau85</t>
+          <t>https://www.loksatta.com/thane/bjp-leader-ravindra-chavan-political-journey-started-as-a-worker-to-maharashtra-bjp-chief-zws-70-4821598/</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू अन् RSS च्या मर्जीतले रवींद्र चव्हाण भाजपचे</t>
+          <t>संयमी भूमिका फळली! भाजपच्या कार्यकारी प्रदेशाध्यक्षपदी रविंद्र चव्हाणांची नियुक्ती</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-appointed-as-bjp-state-working-president-by-j-p-nadda/articleshow/117154533.cms</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>रविंद्र चव्हाण यांच्यावतीने डोंबिवलीत रक्षाबंधनाचा कौटुंबिक सोहळा; हजारो भगिनींनी बांधली राखी</t>
+          <t>Congress News : काँग्रेस खासदार रविंद्र चव्हाण संतापले, महापालिका आयुक्तांना हक्कभंग कारवाईचा इशारा!</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/raksha-bandhan-family-ceremony-in-dombivli-on-behalf-of-ravindra-chavan-thousands-of-sisters-tied-rakhi/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/congress-mp-ravindra-chavan-warns-action-against-commissioner-over-amit-shah-event-jp75</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजपचे नवे कार्यकारी अध्यक्ष: लवकरच चंद्रशेखर बावनकुळेंकडून स्वीकारणार जबाबदारी, मंत्रिमंडळा...</t>
+          <t>इंतजार खत्म... बीजेपी ने चार राज्यों में अपने प्रदेश अध्यक्षों के नाम फाइनल किए, जानें कौन है लिस्ट में</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
+          <t>https://navbharattimes.indiatimes.com/india/bjp-announces-new-state-presidents-in-4-states-changes-in-maharashtra-uttarakhand-telangana-and-himachal-pradesh/articleshow/122163940.cms</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : राजकारणातील सर्वात चर्चेतील नाव! RSS कार्यकर्ते ते भाजप प्रदेशाध्यक्ष झालेले कोण आहेत रवींद्र चव्हाण?</t>
+          <t>Ravindra Chavan: भाजप नेते रविंद्र चव्हाण यांच्यावर पक्षाची महत्वाची जबाबदारी; कार्यकारी अध्यक्षपदी नियुक्ती</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
+          <t>https://www.esakal.com/desh/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-aau85</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महापालिका निवडणूक महायुतीत की स्वबळावर? ; रवींद्र चव्हाणांनी सांगितली भाजपची सद्य भूमिका, म्हणाले..</t>
+          <t>BJP Politics : कल्याण-डोंबिवलीत भाजप ठाकरेंना धक्का देणार! शिंदेंचीही अडचण वाढवणार; इन्कमिंग सुरू, महापौरपदासाठी स्वबळाचे संकेत</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/pune/ravindra-chavan-bjp-current-stand-mahayuti-or-independent-contest-municipal-corporation-elections-maharashtra-politics-msr87</t>
+          <t>https://sarkarnama.esakal.com/mumbai/jatin-prajapati-joins-kalyan-dombivli-bjp-welcomed-by-ravindra-chavan-rm89</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Photos : रविंद्र चव्हाणांनी स्वीकारला भाजपा प्रदेशाध्यक्ष पदाचा पदभार; मावळत्या अध्यक्षांच्या शुभेच्छा…</t>
+          <t>महाराष्ट्र में भाजपा के संगठन निर्माण को मिली नई ताकत, राज्य में 1221 मंडलों का गठन</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/photos/news/5198695/ravindra-chavan-takes-charge-as-bjp-state-president-best-wishes-from-party-s-outgoing-president-state-headquarter-mumbai-photos-spl-93/</t>
+          <t>https://hindi.news24online.com/state/mumbai/bjp-building-organization-in-maharashtra-gets-new-strength-1221-mandals-formed/1157953/</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>पक्षकार्यकर्ता ते प्रदेशाध्यक्ष : रवींद्र चव्हाण</t>
+          <t>Ravindra Chavan BJP: रवींद्र चव्हाण भाजपाचे नवे 'कॅप्टन'! महाराष्ट्र प्रदेशाध्यक्षपदी बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-elected-unopposed-as-bjp-maharashtra-state-president-in-mumbai-event-devendra-fadnavis-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Mahayuti News: शिवरायांच्या पुतळ्यावरून राजकारण तापलं, डोंबिवलीत शिंदे सेनेनं भाजपला डिवचलं</t>
+          <t>Maharashtra Updates : भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण, जलसंधारण विभागात 8 हजारांहून अधिक पदांची भरती...</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/politics/mahayuti-news-unveiling-of-chhatrapati-shivaji-maharaj-statue-in-dombivli-shiv-sena-shinde-faction-criticizes-bjp-mla-ravindra-chavan-7945018</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-politics-marathi-latest-news-update-01-june-2025-live-updates-assembly-session-live-mahayuti-bjp-shivsena-ncp-mahavikas-aaghadi-raj-thackeray-uddhav-thackeray-devendra-fadnavis-shivsena-rm82</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>महाराष्ट्र में किसे मिली BJP की कमान? मुंबई मेट्रो में देखें</t>
+          <t>BJP News : आमचा पक्ष 24/7 काम करणारा; मोठा - छोटा भाऊ असा सर्व्हे भाजप करत नाही!</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-ravindra-chavan-statement-on-party-work-and-alliance-jp75</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>डोंबिवलीकर फ्रेंडशिप रनच्या थीमचे अनावरण संपन्न भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले थीमचे अनावरण ही स्पर्धा होणार 9 नोव्हेंबर ला</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण यांची अखेर भाजपाच्या कार्यकारी प्रदेशाध्यक्षपदी वर्णी; राष्ट्रीय अध्यक्ष जेपी नड्डांची घोषणा</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mla-ravindra-chavan-appointed-as-working-state-president-of-maharashtra-kvg-85-4820046/</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: उद्धव ठाकरे पुन्हा भाजपसोबत? रवींद्र चव्हाण म्हणाले,राजकारणात कोणी कायमचा शत्रू नसतो | VIDEO</t>
+          <t>“भाजपा हीच माझी ओळख” ; महाराष्ट्र भाजपा प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांची बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/uddhav-thackeray-bjp-alliance-ravindra-chavan-interview-political-future-maharashtra-om0906</t>
+          <t>https://www.localnewsnetwork.in/bjp-is-my-identity-ravindra-chavan-elected-unopposed-as-maharashtra-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू, पक्षाच्या मर्जीतले रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष</t>
+          <t>Maharashtra BJP State President: उत्सुकता संपली; भाजपला मिळणार नवा प्रदेशाध्यक्ष! चंद्रशेखर बावनकुळेंच्या जागी रविंद्र चव्हाणांची नियुक्ती होणार</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-bjp-ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-latest-marathi-news-pp0731</t>
+          <t>https://marathi.abplive.com/news/maharashtra/bjp-will-get-a-new-maharashtra-president-ravindra-chavan-will-be-appointed-in-place-of-chandrashekhar-bawankule-1366663</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Ravindra Chavan News : भाजपचे प्रदेशाध्यक्ष म्हणतात, आमची संघटनात्मक बांधणी मजबूत, यश पदरात पडेल!</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी, आज अधिवेशनात सूत्रे स्वीकारणार</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-state-president-ravindra-chavan-confident-of-election-success-says-our-organisation-is-strong-jp75</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-bjp-state-president-will-take-charge-in-the-convention-today-a-a941/</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>फेमस यूट्यूबर ने 33 साल की उम्र में दुनिया को कहा अलविदा, किस बीमारी से थे पीड़ित?</t>
+          <t>Ravindra Chavan : "सामान्य नगरसेवक ते भाजपचे प्रदेशाध्यक्ष..."</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/youtuber-shirish-gavas-passed-away-red-soil-stories-channel-33-year-old-founder-died-19834284</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/ravindra-chavan-appointed-bjp-president-kiren-rijiju-announcement-and-political-career-as11</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण दिल्लीत, जेपी नड्डा यांची घेणार भेट ABP MAJHA</t>
+          <t>Ravindra Chavan : भाजपचं ठरलं, रवींद्र चव्हाण प्रदेशाध्यक्ष होणार, ठाकरेंच्या बालेकिल्ल्यात पहिलं शक्तिप्रद...</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-to-be-new-maharashtra-bjp-president-show-of-power-at-aaditya-thackeray-constituency-1425668.html</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>राणे पिता-पुत्रांनी भाजपऐवजी स्ट्राँग केलं स्वतःचं नेटवर्क; नव्या प्रदेशाध्यक्षांचा होमग्राऊंडवरच निघणार घाम!</t>
+          <t>BJP Ravindra Chavan News: भाजपच्या गोटातून मोठी बातमी समोर Maharashtra Politics</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-maharashtra-state-president-ravindra-chavan-faces-challenge-of-strengthening-party-in-sindhudurg-beyond-rane-family-influence-as11-hn97</t>
+          <t>https://www.msn.com/mr-in/news/other/bjp-ravindra-chavan-news-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%97-%E0%A4%9F-%E0%A4%A4%E0%A5%82%E0%A4%A8-%E0%A4%AE-%E0%A4%A0-%E0%A4%AC-%E0%A4%A4%E0%A4%AE-%E0%A4%B8%E0%A4%AE-%E0%A4%B0-maharashtra-politics/vi-AA1K12wX</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महाराष्ट्र भाजपच्या प्रदेशाध्यपदी रविंद्र चव्हाणांची नियुक्ती</t>
+          <t>रत्नागिरी भाजपमध्ये नारायण राणे, रविंद्र चव्हाण यांच्यातील वाद चव्हाट्यावर</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.loksatta.com/politics/dispute-between-narayan-rane-and-ravindra-chavan-in-ratnagiri-bjp-is-on-rise-print-political-news-ocd-94-5140598/</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Maharashtra BJP News : भाजप प्रदेशाध्यक्षपदासाठी रवींद्र चव्हाण यांनी भरला अर्ज</t>
+          <t>Ravindra Chavan: उद्धव ठाकरेंच्या भाजपसोबतच्या वाढत्या जवळीकतेवर रवींद्र चव्हाण यांचं महत्त्वाचं विधान; म्हणाले, शत्रूही...</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-important-statement-on-uddhav-thackeray-closeness-with-bjp-aau85</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवली परिसर भाजपमय करा, पालिकेवर भाजपचा महापौर बसवा, रवींद्र चव्हाण यांचे कार्यकर्त्यांना आवाहन</t>
+          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू अन् RSS च्या मर्जीतले रवींद्र चव्हाण भाजपचे</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-s-appeal-to-party-workers-to-work-for-bjp-mayor-in-kdmc-zws-70-5277354/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-mumbai-politics-marathi-news-1367337</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण महाराष्ट्र भाजपच्या कार्याध्यक्षपदी, दोन महिन्यांनी प्रदेशाध्यक्ष हाेणार</t>
+          <t>रविंद्र चव्हाण यांच्यावतीने डोंबिवलीत रक्षाबंधनाचा कौटुंबिक सोहळा; हजारो भगिनींनी बांधली राखी</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-will-become-state-president-in-two-months-a-a309/</t>
+          <t>https://www.localnewsnetwork.in/raksha-bandhan-family-ceremony-in-dombivli-on-behalf-of-ravindra-chavan-thousands-of-sisters-tied-rakhi/</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाश्याला बेघर होऊ देणार नाही, रविंद्र चव्हाण यांचे आश्वासन</t>
+          <t>रवींद्र चव्हाण भाजपचे नवे कॅप्टन; केंद्रीय मंत्री किरेन रिजिजू यांनी केली घोषणा</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
+          <t>https://marathi.freepressjournal.in/mumbai/ravindra-chavan-appointed-bjp-maharashtra-president-2025</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजपचे नवे कॅप्टन; केंद्रीय मंत्री किरेन रिजिजू यांनी केली घोषणा</t>
+          <t>रवींद्र चव्हाण भाजपचे नवे कार्यकारी अध्यक्ष: लवकरच चंद्रशेखर बावनकुळेंकडून स्वीकारणार जबाबदारी, मंत्रिमंडळा...</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/mumbai/ravindra-chavan-appointed-bjp-maharashtra-president-2025</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/news/ravindra-chavan-appointed-as-working-state-president-of-maharashtra-bjp-134276483.html</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Kalyan News: 'या' इमारतींच्या रखडलेल्या पुनर्विकास लागणार मार्गी, रवींद्र चव्हाण यांची माहिती</t>
+          <t>Ravindra Chavan : राजकारणातील सर्वात चर्चेतील नाव! RSS कार्यकर्ते ते भाजप प्रदेशाध्यक्ष झालेले कोण आहेत रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
+          <t>https://www.navarashtra.com/maharashtra/new-bjp-maharashtra-state-president-ravindra-chavan-political-journey-complete-information-marathi-916730.html</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Latur Politics: प्रदेशाध्यक्ष रविंद्र चव्हाणांचा लातूरमध्ये मोठा धमाका; दोन बड्या नेत्यांचा भाजपात प्रवेश</t>
+          <t>Ravindra Chavan : महापालिका निवडणूक महायुतीत की स्वबळावर? ; रवींद्र चव्हाणांनी सांगितली भाजपची सद्य भूमिका, म्हणाले..</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-politics-kapil-makne-nilkanth-mirkale-of-latur-joining-bjp-dk88</t>
+          <t>https://sarkarnama.esakal.com/pune/ravindra-chavan-bjp-current-stand-mahayuti-or-independent-contest-municipal-corporation-elections-maharashtra-politics-msr87</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: 'संविधान बचाव'ची 'शो'बाजी करणारे...; PM मोदींवर टीका करणाऱ्या राहुल गांधींना रविंद्र चव्हाणांचं उत्तर</t>
+          <t>Photos : रविंद्र चव्हाणांनी स्वीकारला भाजपा प्रदेशाध्यक्ष पदाचा पदभार; मावळत्या अध्यक्षांच्या शुभेच्छा…</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/those-who-showoff-of-saving-constitution-criticized-pm-modi-reply-by-ravindra-chavan-on-rahul-gandhi-statement-against-prime-minister-aau85</t>
+          <t>https://www.loksatta.com/photos/news/5198695/ravindra-chavan-takes-charge-as-bjp-state-president-best-wishes-from-party-s-outgoing-president-state-headquarter-mumbai-photos-spl-93/</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : देवेंद्र फडणवीस यांचे विश्वासू ते भाजपाचे कार्यकारी अध्यक्ष; कोण आहेत रवींद्र चव्हाण?</t>
+          <t>पक्षकार्यकर्ता ते प्रदेशाध्यक्ष : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/maharashtra-politics-cm-devendra-fadnavis-confidant-to-bjp-working-president-who-is-mla-ravindra-chavan-sdp-92-4822225/</t>
+          <t>https://www.mahamtb.com/Encyc/2025/6/30/from-party-worker-to-state-president.html</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>भाजप कार्यकर्ता काम करताना रस्त्यावर दिसायला हवा; रवींद्र चव्हाण यांनी घेतली कार्यकर्त्यांची शाळा</t>
+          <t>महाराष्ट्र में किसे मिली BJP की कमान? मुंबई मेट्रो में देखें</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/bjp-workers-should-be-visible-on-the-streets-while-working-ravindra-chavan-took-the-school-of-workers-a-a727/</t>
+          <t>https://www.aajtak.in/programmes/mumbai-metro/video/bjp-appointed-ravindra-chavan-as-maharashtra-unit-cheif-mumbai-metro-frvd-2277550-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांच्या नावावर शिक्कामोर्तब? उद्या होणार घोषणा</t>
+          <t>डोंबिवलीकर फ्रेंडशिप रनच्या थीमचे अनावरण संपन्न भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले थीमचे अनावरण ही स्पर्धा होणार 9 नोव्हेंबर ला</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ravindra-chavan-name-confirmed-as-bjp-maharashtra-president-announcement-to-be-made-soon-aau85</t>
+          <t>https://www.mahamtb.com/Encyc/2025/8/3/the-theme-of-the-dombivalikar-friendship-run-was-unveiled-by-bjp-state-president-ravindra-chavan.html</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : धुळ्यात काँग्रेसला खिंडार? मातब्बर नेता मुंबईत रायगड निवासस्थानी</t>
+          <t>Ravindra Chavan : देवेंद्र फडणवीसांचे विश्वासू, पक्षाच्या मर्जीतले रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/maharashtra-bjp-ravindra-chavan-bjp-new-president-profile-dombivli-mla-maharashtra-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>भाजपने माझ्यावर उपकार केलेत, प्रदेशाध्यक्ष बनल्यानंतर रवींद्र चव्हाणांची पहिली प्रतिक्रिया</t>
+          <t>श्रीकांत शिंदेंनाही भाजप घेरणार, कल्याण-डोंबिवलीत शड्डू ठोकला, होम ग्राउंडवर रविंद्र चव्हाण आक्रमक</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/bjp-has-done-me-favor-new-state-president-rvindra-chavhan-1st-statement-1436200.html</t>
+          <t>https://news18marathi.com/maharashtra/ravindra-chavan-aggressive-on-home-ground-kdmc-election-eknath-shinde-led-shiv-sena-faced-trouble-1450204.html</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>कल्याण डोंबिवलीच्या विकासाचे ग्रहण दूर करण्यासाठी भाजपचा महापौर हवा – भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण</t>
+          <t>Ravindra Chavan News : भाजपचे प्रदेशाध्यक्ष म्हणतात, आमची संघटनात्मक बांधणी मजबूत, यश पदरात पडेल!</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/bjp-state-president-ravindra-chavan-confident-of-election-success-says-our-organisation-is-strong-jp75</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Ravindra Chavhan Interview:महाराष्ट्र भाजप प्रदेशाध्यक्ष पद स्वीकारल्यानंतर रविंद्र चव्हाण EXCLUSIVE</t>
+          <t>फेमस यूट्यूबर ने 33 साल की उम्र में दुनिया को कहा अलविदा, किस बीमारी से थे पीड़ित?</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
+          <t>https://www.patrika.com/mumbai-news/youtuber-shirish-gavas-passed-away-red-soil-stories-channel-33-year-old-founder-died-19834284</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजपच्या कार्यकारी अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>Ravindra Chavan : भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण दिल्लीत, जेपी नड्डा यांची घेणार भेट ABP MAJHA</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-bbj88</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bjp-leadership-meet-ravindra-chavan-meets-jp-nadda-in-delhi-first-meeting-as-state-president-earlier-met-amit-shah-in-pune-1368594</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>चव्हाणांकडे प्रदेश, सेनेला थेट संदेश; शिंदेंना होमपीचवर शह देण्यासाठी भाजपची जोरदार फिल्डींग</t>
+          <t>राणे पिता-पुत्रांनी भाजपऐवजी स्ट्राँग केलं स्वतःचं नेटवर्क; नव्या प्रदेशाध्यक्षांचा होमग्राऊंडवरच निघणार घाम!</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-maharashtra-state-president-ravindra-chavan-faces-challenge-of-strengthening-party-in-sindhudurg-beyond-rane-family-influence-as11-hn97</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>Ravindra Chavan | रवींद्र चव्‍हाणांनी घेतली भाजप अध्‍यक्ष जे. पी. नड्डांची भेट</t>
+          <t>Maharashtra BJP News : भाजप प्रदेशाध्यक्षपदासाठी रवींद्र चव्हाण यांनी भरला अर्ज</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-bjp-state-president-ravindra-chavan-met-party-president-j-p-nadda-nl76</t>
+          <t>https://deshdoot.com/maharashtra-bjp-news-former-minister-ravindra-chavan-files-application-for-bjp-state-president-post/</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>मोठा गेम होणार, भाजप प्रदेशाध्यक्षाच्या विधानाने खळबळ; शिंदे गटाला सर्वात मोठं टेन्शन</t>
+          <t>कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाश्याला बेघर होऊ देणार नाही, रविंद्र चव्हाण यांचे आश्वासन</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
+          <t>https://www.navarashtra.com/maharashtra/not-a-single-resident-of-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-assures-ravindra-chavan-817558.html</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>प्रदेशाध्यक्षपद देऊन भाजपने माझ्यावर उपकार केले, रवींद्र चव्हाण भाषणात नेमकं काय म्हणाले?</t>
+          <t>Kalyan News: 'या' इमारतींच्या रखडलेल्या पुनर्विकास लागणार मार्गी, रवींद्र चव्हाण यांची माहिती</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
+          <t>https://www.navarashtra.com/maharashtra/regarding-the-stalled-redevelopment-case-of-shantidoot-housing-society-and-lig-1-buildings-in-kalyan-956786.html</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>डोंबिवलीतील काँग्रेसचे 4 नगरसेवक भाजपमध्ये; पक्षाकडून त्यांचा नेहमीच सन्मान केला जाणार – प्रदेशाध्यक्ष रविंद्र चव्हाण यांची ग्वाही</t>
+          <t>Latur Politics: प्रदेशाध्यक्ष रविंद्र चव्हाणांचा लातूरमध्ये मोठा धमाका; दोन बड्या नेत्यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/4-congress-corporators-from-dombivli-join-bjp-they-will-always-be-respected-by-the-party-state-president-ravindra-chavan-assures/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/marathwada/ravindra-chavan-politics-kapil-makne-nilkanth-mirkale-of-latur-joining-bjp-dk88</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Indrayani River Bridge Collapse | संजय राऊत विश्वप्रवक्ते! इंद्रायणी पूल दुरुस्तीसाठी ८० हजार की ८ कोटी... रविंद्र चव्हाण यांनी खरं काय ते सांगितले?</t>
+          <t>रवींद्र चव्हाण महाराष्ट्र भाजपच्या कार्याध्यक्षपदी, दोन महिन्यांनी प्रदेशाध्यक्ष हाेणार</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/bjp-ravindra-chavan-responded-to-sanjay-raut-allegations-over-indrayani-river-bridge-collapse-incident-db79</t>
+          <t>https://www.lokmat.com/maharashtra/ravindra-chavan-appointed-as-maharashtra-bjp-working-president-will-become-state-president-in-two-months-a-a309/</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
+          <t>Ravindra Chavan: 'संविधान बचाव'ची 'शो'बाजी करणारे...; PM मोदींवर टीका करणाऱ्या राहुल गांधींना रविंद्र चव्हाणांचं उत्तर</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
+          <t>https://sarkarnama.esakal.com/mumbai/those-who-showoff-of-saving-constitution-criticized-pm-modi-reply-by-ravindra-chavan-on-rahul-gandhi-statement-against-prime-minister-aau85</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>BJP Politics : बंडखोरी केलेल्या नेत्याचा भाजप प्रवेश, वेलकम स्वत: रवींद्र चव्हाणांनी केलं; युतीमध्ये वितुष्ट येण्याची शक्यता?</t>
+          <t>भाजप कार्यकर्ता काम करताना रस्त्यावर दिसायला हवा; रवींद्र चव्हाण यांनी घेतली कार्यकर्त्यांची शाळा</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ravindra-chavan-cancelled-vishal-parabs-bjp-suspension-revoked-creating-alliance-tension-in-sindhudurg-politics-as11</t>
+          <t>https://www.lokmat.com/pune/bjp-workers-should-be-visible-on-the-streets-while-working-ravindra-chavan-took-the-school-of-workers-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>Maharashtra BJP State President | भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांचे नाव जवळपास निश्चित, १ जुलैला अधिकृत घोषणा</t>
+          <t>Maharashtra Politics : धुळ्यात काँग्रेसला खिंडार? मातब्बर नेता मुंबईत रायगड निवासस्थानी</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-will-be-appointed-maharashtra-bjp-state-president-db79</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-former-congress-mla-kunal-patil-likely-to-join-bjp-meets-ravindra-chavan-in-mumbai-marathi-news-1365750</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
+          <t>Ravindra Chavan: भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांच्या नावावर शिक्कामोर्तब? उद्या होणार घोषणा</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
+          <t>https://www.esakal.com/maharashtra/ravindra-chavan-name-confirmed-as-bjp-maharashtra-president-announcement-to-be-made-soon-aau85</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>BJP Dombivli setback - भाजपला डोंबिवलीत धक्का! ; प्रदेश कार्याध्यक्षांवर 'हा' आरोप करत, दोन नगरसेवकांनी सोडला पक्ष</t>
+          <t>भाजपने माझ्यावर उपकार केलेत, प्रदेशाध्यक्ष बनल्यानंतर रवींद्र चव्हाणांची पहिली प्रतिक्रिया</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-dombivli-crisis-vikas-kavita-mhatre-resignation-ravindra-chavan-allegations-msr87</t>
+          <t>https://www.tv9marathi.com/politics/bjp-has-done-me-favor-new-state-president-rvindra-chavhan-1st-statement-1436200.html</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: आता पालिका विकासाचे ग्रहण दूर होणार; भाजप प्रदेशाध्यक्षांनी निवडणुकीचा प्लॅनच सांगितला</t>
+          <t>कल्याण डोंबिवलीच्या विकासाचे ग्रहण दूर करण्यासाठी भाजपचा महापौर हवा – भाजप प्रदेशाध्यक्ष रविंद्र चव्हाण</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/ravindra-chavan-says-bjp-mayor-is-necessary-to-resolve-development-problems-faced-by-kalyan-dombivli-municipal-corporation-on-bmc-election-mvk02</t>
+          <t>https://www.localnewsnetwork.in/bjp-needs-a-mayor-to-remove-the-development-eclipse-of-kalyan-dombivali-bjp-state-president-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>BJP President: "रवी दादा आगे बढो नाही तर..."; प्रदेशाध्यक्ष होताच रवींद्र चव्हाणांनी व्यक्त केल्या भावना</t>
+          <t>Ravindra Chavhan Interview:महाराष्ट्र भाजप प्रदेशाध्यक्ष पद स्वीकारल्यानंतर रविंद्र चव्हाण EXCLUSIVE</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
+          <t>https://marathi.abplive.com/tv-show/majha-vishesh/maharashtra-bjp-president-ravindra-chavan-s-first-interview-reveals-role-in-operation-shinde-discusses-mahayuti-election-strategy-it-notices-and-marathi-politics-1369435</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>एक-एक मंडल दत्तक घेऊन संघटनात्मक बांधणीचा संकल्प करा; प्रदेशाध्यक्ष रविंद्र चव्हाण यांचे माजी आमदार, खासदारांना आवाहन</t>
+          <t>Maharashtra Politics : देवेंद्र फडणवीस यांचे विश्वासू ते भाजपाचे कार्यकारी अध्यक्ष; कोण आहेत रवींद्र चव्हाण?</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
+          <t>https://www.loksatta.com/politics/maharashtra-politics-cm-devendra-fadnavis-confidant-to-bjp-working-president-who-is-mla-ravindra-chavan-sdp-92-4822225/</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Exclusive Interview : राज-उद्धव ठाकरे एकत्र आल्यास भाजपला आव्हान असणार का? प्रदेशाध्यक्ष</t>
+          <t>Ravindra Chavan: भाजपच्या कार्यकारी अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
+          <t>https://saamtv.esakal.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-bbj88</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : भाजपचे नवीन प्रदेशाध्यक्ष कोण? बड्या नेत्याचं नाव पक्कं; उद्या अधिकृत घोषणा होणार</t>
+          <t>चव्हाणांकडे प्रदेश, सेनेला थेट संदेश; शिंदेंना होमपीचवर शह देण्यासाठी भाजपची जोरदार फिल्डींग</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/ravindra-chavan-fills-the-form-for-the-post-of-new-state-president-of-mumbai-bjp-name-will-be-announced-tomorrow-latest-marathi-news-pp0731</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/ravindra-chavan-appointed-maharashtra-bjp-president-ahead-of-crucial-mmr-and-local-body-polls/articleshow/122185894.cms</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण भाजपचे कारभारी</t>
+          <t>Ravindra Chavan | रवींद्र चव्‍हाणांनी घेतली भाजप अध्‍यक्ष जे. पी. नड्डांची भेट</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-ravindra-chavan-is-the-bjp-s-steward-1061660.html</t>
+          <t>https://pudhari.news/maharashtra/mumbai/maharashtra-bjp-state-president-ravindra-chavan-met-party-president-j-p-nadda-nl76</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>काँग्रेस नेते कैलास गोरंट्यालसह सुरेश वरपूडकर यांचा भाजप प्रवेशाचा मुहूर्त</t>
+          <t>मोठा गेम होणार, भाजप प्रदेशाध्यक्षाच्या विधानाने खळबळ; शिंदे गटाला सर्वात मोठं टेन्शन</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
+          <t>https://www.tv9marathi.com/maharashtra/bjp-state-president-ravindra-chavan-big-statement-regarding-municipal-elections-shiv-sena-tension-will-increase-1460977.html</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>BJP new state president : पक्षनेतृत्वानं दाखवला मोठा भरवसा; मित्रपक्षाला भिडणाऱ्या भाजपच्या नव्या प्रदेशाध्यक्षांना आता गियर बदलावा लागणार</t>
+          <t>प्रदेशाध्यक्षपद देऊन भाजपने माझ्यावर उपकार केले, रवींद्र चव्हाण भाषणात नेमकं काय म्हणाले?</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-state-chief-ravindra-chavan-faces-ally-challenge-amid-trust-sw79</t>
+          <t>https://marathi.indiatimes.com/maharashtra/ahmednagar-news/ravindra-chavan-says-thanks-to-his-party-after-selected-for-bjp-maharashtra-president/articleshow/122185577.cms</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>राज ठाकरे भाजपसोबत जाणार का?: रवींद्र चव्हाण म्हणतात - राज व फडणवीसांचे चांगले संबंध, ते दोघेही मुंबईच्या ह...</t>
+          <t>डोंबिवलीतील काँग्रेसचे 4 नगरसेवक भाजपमध्ये; पक्षाकडून त्यांचा नेहमीच सन्मान केला जाणार – प्रदेशाध्यक्ष रविंद्र चव्हाण यांची ग्वाही</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-raj-thackeray-bjp-alliance-speculation-uddhav-thackeray-politics-update-135429372.html</t>
+          <t>https://www.localnewsnetwork.in/4-congress-corporators-from-dombivli-join-bjp-they-will-always-be-respected-by-the-party-state-president-ravindra-chavan-assures/</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>"एकनाथ शिंदे मुख्यमंत्री झाल्याने वाईट वाटलं आणि घरी निघून गेलो,पण पुन्हा..."; रवींद्र चव्हाणांचा गौप्यस्फोट</t>
+          <t>Indrayani River Bridge Collapse | संजय राऊत विश्वप्रवक्ते! इंद्रायणी पूल दुरुस्तीसाठी ८० हजार की ८ कोटी... रविंद्र चव्हाण यांनी खरं काय ते सांगितले?</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/bjp-state-president-ravindra-chavan-said-that-he-felt-bad-after-eknath-shinde-became-the-chief-minister-a-a1001/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/bjp-ravindra-chavan-responded-to-sanjay-raut-allegations-over-indrayani-river-bridge-collapse-incident-db79</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>Raju Patil: विकासाला ग्रहण लावणाऱ्या 'चांदभाई'चे नाव घ्या! मनसे नेत्याचा भाजप प्रदेशाध्यक्षांना टोला</t>
+          <t>चंद्रकांतदादांनी वेटिंगवर ठेवलेल्या 'संजयकाकांचा' भाजप प्रवेश फिक्स : प्रदेशाध्यक्ष रवींद्र चव्हाणांचे संकेत</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/mns-leader-raju-patil-criticism-on-ravindra-chavan-over-kalyan-dombivli-development-maharashtra-politics-mvk02</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/sanjay-patils-return-to-bjp-gets-support-from-ravindra-chavan-despite-chandrakant-patils-objection-as11</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>Ravindra Chavan emotional story: फडणवीस मुख्यमंत्री होणार नसल्याने धक्का बसला, डोळ्यात पाणी आले अन् ...; रवींद्र चव्हाणांनी सांगितला 2022 सालचा किस्सा.....</t>
+          <t>BJP Politics : बंडखोरी केलेल्या नेत्याचा भाजप प्रवेश, वेलकम स्वत: रवींद्र चव्हाणांनी केलं; युतीमध्ये वितुष्ट येण्याची शक्यता?</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-reveals-2022-twist-emotional-reaction-as-devendra-fadnavis-wasnt-named-cm-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/ravindra-chavan-cancelled-vishal-parabs-bjp-suspension-revoked-creating-alliance-tension-in-sindhudurg-politics-as11</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President : भाजपचे महाराष्ट्रातील नवे उत्तराधिकारी कोण? प्रदेशाध्यक्षपदासाठी सर्वात आघाडीवर कोणाचं नाव?</t>
+          <t>Maharashtra BJP State President | भाजप प्रदेशाध्यक्षपदी रविंद्र चव्हाण यांचे नाव जवळपास निश्चित, १ जुलैला अधिकृत घोषणा</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-will-be-appointed-maharashtra-bjp-state-president-db79</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>नितेश राणे आणि गोपीचंद पडळकर दोघांना भाजपने डायरेक्ट वॉर्निंग दिली</t>
+          <t>रवींद्र चव्हाण भाजप प्रदेशाध्यक्षपदी बिनविरोध, आज औपचारिक घोषणा</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
+          <t>https://www.loksatta.com/mumbai/ravindra-chavan-elected-unopposed-as-bjp-state-president-formal-announcement-today-mumbai-print-news-ssb-93-5194361/</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>फडणवीस व चव्हाण यांच्या नेतृत्वात भाजपला मोठे यश मिळेल- ना. विखे पाटील</t>
+          <t>Maharashtra Politics: उद्धव ठाकरे पुन्हा भाजपसोबत? रवींद्र चव्हाण म्हणाले,राजकारणात कोणी कायमचा शत्रू नसतो | VIDEO</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
+          <t>https://saamtv.esakal.com/video/uddhav-thackeray-bjp-alliance-ravindra-chavan-interview-political-future-maharashtra-om0906</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>भाजपाचा सामान्य कार्यकर्ता ते प्रदेशाध्यक्ष पर्यंतचा रवींद्र चव्हाण यांचा प्रवास</t>
+          <t>BJP Dombivli setback - भाजपला डोंबिवलीत धक्का! ; प्रदेश कार्याध्यक्षांवर 'हा' आरोप करत, दोन नगरसेवकांनी सोडला पक्ष</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/mumbai/ravindra-chavans-journey-from-ordinary-bjp-worker-to-state-president-update/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-dombivli-crisis-vikas-kavita-mhatre-resignation-ravindra-chavan-allegations-msr87</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: भाजपचे मुंबई अध्यक्ष ठरले! 'या' आक्रमक नेत्याची लागली वर्णी; निवडणुकांपूर्वी मोठी खेळी</t>
+          <t>Ravindra Chavan: आता पालिका विकासाचे ग्रहण दूर होणार; भाजप प्रदेशाध्यक्षांनी निवडणुकीचा प्लॅनच सांगितला</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
+          <t>https://www.esakal.com/mumbai/ravindra-chavan-says-bjp-mayor-is-necessary-to-resolve-development-problems-faced-by-kalyan-dombivli-municipal-corporation-on-bmc-election-mvk02</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>Ravindra Chavhan BJP : रविंद्र चव्हाण यांनी बोलावली बैठक, निवडणुकीसंदर्भात चर्चा</t>
+          <t>BJP President: "रवी दादा आगे बढो नाही तर..."; प्रदेशाध्यक्ष होताच रवींद्र चव्हाणांनी व्यक्त केल्या भावना</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
+          <t>https://www.navarashtra.com/maharashtra/bjp-leader-ravindra-chavan-express-feeelings-after-become-a-bjp-maharashtra-president-916809.html</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>महाराष्ट्रात राजकीय भूकंप घडवण्यात रवींद्र चव्हाणांचा मोठा वाटा, भाजपच्या नव्या प्रदेशाध्यक्षांची A टू Z कारकीर्द</t>
+          <t>एक-एक मंडल दत्तक घेऊन संघटनात्मक बांधणीचा संकल्प करा; प्रदेशाध्यक्ष रविंद्र चव्हाण यांचे माजी आमदार, खासदारांना आवाहन</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
+          <t>https://www.mahamtb.com/Encyc/2025/7/31/adopt-one-mandal-each-and-resolve-to-build-an-organization-state-president-ravindra-chavan-appeals-to-former-m.html</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>Narayan Rane : राणेंचा भाजपच्या प्रदेश प्रभारींनाच कडक इशारा; म्हणाले, 'इथं ढवळाढवळ चालणार नाही, हवं तर...'</t>
+          <t>Maharashtra Politics : भाजपचे नवीन प्रदेशाध्यक्ष कोण? बड्या नेत्याचं नाव पक्कं; उद्या अधिकृत घोषणा होणार</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/narayan-rane-slams-ravindra-chavan-over-post-distribution-in-ratnagiri-bjp-as11</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/ravindra-chavan-fills-the-form-for-the-post-of-new-state-president-of-mumbai-bjp-name-will-be-announced-tomorrow-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>BJP : अण्णासाहेब डांगे यांचा दोन्ही मुलांसह भाजप प्रवेश; फडणवीस म्हणाले, पक्षावाढीत त्यांचा मोलाचा वाटा</t>
+          <t>Ravindra Chavan Exclusive Interview : राज-उद्धव ठाकरे एकत्र आल्यास भाजपला आव्हान असणार का? प्रदेशाध्यक्ष</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/bjp-live-devendra-fadnavis-annasaheb-dange-join-bjp-30th-july-ravindra-chavan-chardrakant-patil/907022/</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-exclusive-interview-talk-about-will-there-be-challenge-to-bjp-if-raj-thackeray-uddhav-thackeray-come-together-maharashtra-politics-marathi-news-1369421</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>जिल्हाध्यक्षपदाची माळ रवींद्र चव्हाणांच्या निकटवर्तीयाच्या गळ्यात; KDMC निवडणुकीआधी भाजपात मोठे बदल</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण भाजपचे कारभारी</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/big-changes-underway-in-bjp-kdmc-ahead-of-municipal-elections/articleshow/121160143.cms</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-ravindra-chavan-is-the-bjp-s-steward-1061660.html</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>महाराष्ट्राच्या राजकारणातील सर्वात मोठी घडामोड! उद्धव ठाकरे पक्षातील 1500 सदस्यांनी एकावेळी पक्ष सोडला आणि...</t>
+          <t>BJP new state president : पक्षनेतृत्वानं दाखवला मोठा भरवसा; मित्रपक्षाला भिडणाऱ्या भाजपच्या नव्या प्रदेशाध्यक्षांना आता गियर बदलावा लागणार</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjps-new-state-chief-ravindra-chavan-faces-ally-challenge-amid-trust-sw79</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>“ठाकरे बंधूंनी एकत्र येऊ नये असा GR काढलेला नाही”; CM देवेंद्र फडणवीसांचा खोचक टोला</t>
+          <t>राज ठाकरे भाजपसोबत जाणार का?: रवींद्र चव्हाण म्हणतात - राज व फडणवीसांचे चांगले संबंध, ते दोघेही मुंबईच्या ह...</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-taunt-about-raj-thackeray-and-uddhav-thackeray-likely-to-come-together-for-marathi-language-issue-a-a719/</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-raj-thackeray-bjp-alliance-speculation-uddhav-thackeray-politics-update-135429372.html</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>Dahi Handi 2025 : डोंबिवलीमध्ये पारंपरिक पद्धतीने दहीहंडीचा उत्सव; गोविंदांचा उत्सह शिगेला</t>
+          <t>काँग्रेस नेते कैलास गोरंट्यालसह सुरेश वरपूडकर यांचा भाजप प्रवेशाचा मुहूर्त</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
+          <t>https://marathi.abplive.com/news/politics/congress-leader-kailash-gorantyal-and-suresh-varpudkar-will-join-bjp-under-the-leadership-of-state-president-ravindra-chavan-at-mumbai-jalna-constituency-before-election-1373052</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>मी निष्पाप, निष्ठेने काम करेन, तुमचा आदेश तंतोतंत पाळेन, सुधाकर बडगुजरांचा बावनकुळेंना</t>
+          <t>BJP Maharashtra President : भाजपचे महाराष्ट्रातील नवे उत्तराधिकारी कोण? प्रदेशाध्यक्षपदासाठी सर्वात आघाडीवर कोणाचं नाव?</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
+          <t>https://marathi.indiatimes.com/india-news/ravindra-chavan-may-be-elected-as-bjp-state-president-for-maharashtra-marathi-news/articleshow/122124651.cms</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>Nanded Ashok Chavan: अशोक चव्हाणांची डोकेदुखी वाढली; काँग्रेसकडून खिंडीत पकडण्यासाठी प्लॅन तयार, नांदेडमध्ये काय घडतंय?</t>
+          <t>फडणवीस व चव्हाण यांच्या नेतृत्वात भाजपला मोठे यश मिळेल- ना. विखे पाटील</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
+          <t>https://deshdoot.com/bjp-state-president-ravindra-chavan-good-luck-minister-vikhe-patil-rahata/</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>कल्याणमध्ये काँग्रेसला खिंडार! बडे नेते भाजपवासी; प्रदेशाध्यक्षांनी दिले मोठे संकेत</t>
+          <t>नितेश राणे आणि गोपीचंद पडळकर दोघांना भाजपने डायरेक्ट वॉर्निंग दिली</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/bjp-grows-stronger-in-kalyan-congress-leaders-join-ravindra-chavan-hints-at-contesting-solo-bdk97</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/nitesh-rane-and-gopichand-padalkar-bjp-gave-direct-warning-ravindra-chavan-on-bjp-leaders-maharashtra-politics/925249</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती की स्वबळावर? भाजप प्रदेशाध्यक्षांचं सूचक विधान; म्हणाले, 'आचारसंहिता लागली की...'</t>
+          <t>भाजपाचा सामान्य कार्यकर्ता ते प्रदेशाध्यक्ष पर्यंतचा रवींद्र चव्हाण यांचा प्रवास</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-statement-on-date-of-local-body-elections-mahayuti-alliance-vru98</t>
+          <t>https://puneprimenews.com/mumbai/ravindra-chavans-journey-from-ordinary-bjp-worker-to-state-president-update/</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis : “फेक नरेटिव्ह तयार करणाऱ्यांची फॅक्टरी…” फडणवीस यांचं उद्धव ठाकरेंना त्याच भाषेत उत्तर</t>
+          <t>"एकनाथ शिंदे मुख्यमंत्री झाल्याने वाईट वाटलं आणि घरी निघून गेलो,पण पुन्हा..."; रवींद्र चव्हाणांचा गौप्यस्फोट</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-bjp-president-fadnavis-slams-uddhav-thackeray-over-fake-narrative-as11</t>
+          <t>https://www.lokmat.com/mumbai/bjp-state-president-ravindra-chavan-said-that-he-felt-bad-after-eknath-shinde-became-the-chief-minister-a-a1001/</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>Nanded News: नांदेडमध्ये स्थानिक निवडणुकासाठी काँगेस अन् वंचितकडून युतीचे संकेत प्रस्ताव</t>
+          <t>BMC Elections 2025: भाजपचे मुंबई अध्यक्ष ठरले! 'या' आक्रमक नेत्याची लागली वर्णी; निवडणुकांपूर्वी मोठी खेळी</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-politics-amit-satam-elected-as-mumbai-president-of-bjp-cm-devendra-fadnavis-9153593</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>Dombivli: संघाच्या बालेकिल्ल्यात हादरा, भाजप नेत्याचा राजीनामा, नेतृत्वावर आरोप, मशाल हाती घेण्याचे संकेत</t>
+          <t>Ravindra Chavhan BJP : रविंद्र चव्हाण यांनी बोलावली बैठक, निवडणुकीसंदर्भात चर्चा</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/bjp-leader-vikas-mhatre-resigns-from-bjp-ahead-dombivli-mahapalika-election-allegation-on-ravindra-chavan-1423215.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-bmc-elections-bjp-calls-urgent-meeting-in-mumbai-raj-thackeray-takes-aggressive-stance-on-matak-sodi-allegations-1379525</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>छत्रपती शिवाजी महाराजांच्या मेघडंबरीसह पूर्णाकृती पुतळ्याचे डोंबिवलीत अनावरण ; खा. डॉ. श्रीकांत शिंदे, भाजप कार्याध्यक्ष रविंद्र चव्हाण यांची प्रमूख उपस्थिती – LNN</t>
+          <t>Sanjay Raut : सही करताना झोपेत असतात का? राऊतांचा रवींद्र चव्हाणांवर घणाघात</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/unveiling-of-the-full-length-statue-of-chhatrapati-shivaji-maharaj-with-a-canopy-in-dombivali/</t>
+          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>Vikas Mhatre - प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला धक्का देणारे विकास म्हात्रे आहेत तरी कोण?</t>
+          <t>महाराष्ट्रात राजकीय भूकंप घडवण्यात रवींद्र चव्हाणांचा मोठा वाटा, भाजपच्या नव्या प्रदेशाध्यक्षांची A टू Z कारकीर्द</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/ampstories/web-stories/vikas-mhatre-resignation-bjp-allegations-on-ravindra-chavan-dombivili-msr87</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/ravindra-chavan-important-role-when-eknath-shinde-takeover-shiv-sena/photoshow/122188079.cms</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>Dombivli KDMCC School Building |डोंबिवलीत केडीएमसी शाळेची नवी इमारत</t>
+          <t>Raju Patil: विकासाला ग्रहण लावणाऱ्या 'चांदभाई'चे नाव घ्या! मनसे नेत्याचा भाजप प्रदेशाध्यक्षांना टोला</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/dombivli-kdmcc-school-new-building-bhoomipujan-by-mla-ravindra-chavan-sp96</t>
+          <t>https://www.esakal.com/mumbai/mns-leader-raju-patil-criticism-on-ravindra-chavan-over-kalyan-dombivli-development-maharashtra-politics-mvk02</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>Nitin Gadkari Auto Rickshaw Comment: गडकरींनी सांगितलं ‘ऑटो रिक्षा’ अन् महाराष्ट्र भाजपचं कनेक्शन ; क्षणात एकच हशा पिकला!</t>
+          <t>Narayan Rane : राणेंचा भाजपच्या प्रदेश प्रभारींनाच कडक इशारा; म्हणाले, 'इथं ढवळाढवळ चालणार नाही, हवं तर...'</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/nitin-gadkari-comment-about-auto-rickshaw-maharashtra-bjp-political-reaction-ravindra-chavan-maharashtra-bjp-president-msr87</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/narayan-rane-slams-ravindra-chavan-over-post-distribution-in-ratnagiri-bjp-as11</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>उत्तर महाराष्ट्रात काँग्रेसला मोठा धक्का ? कुणाल पाटील भाजपात जाणार? राजकीय वर्तुळात चर्चांना उधाण</t>
+          <t>BJP : अण्णासाहेब डांगे यांचा दोन्ही मुलांसह भाजप प्रवेश; फडणवीस म्हणाले, पक्षावाढीत त्यांचा मोलाचा वाटा</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
+          <t>https://www.mymahanagar.com/mahamumbai/bjp-live-devendra-fadnavis-annasaheb-dange-join-bjp-30th-july-ravindra-chavan-chardrakant-patil/907022/</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>Nashik BJP News : भाजप खासदार, आमदारांना मंडल दत्तक देणार</t>
+          <t>जिल्हाध्यक्षपदाची माळ रवींद्र चव्हाणांच्या निकटवर्तीयाच्या गळ्यात; KDMC निवडणुकीआधी भाजपात मोठे बदल</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/nashik-bjp-news-bjp-will-adopt-mandals-for-mps-mlas-ar84</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/big-changes-underway-in-bjp-kdmc-ahead-of-municipal-elections/articleshow/121160143.cms</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरेंपाठोपाठ शरद पवारांनाही धक्का! भाजपामध्ये 'इनकमिंग' सुरूच; अनेकांचा पक्षप्रवेश</t>
+          <t>महाराष्ट्राच्या राजकारणातील सर्वात मोठी घडामोड! उद्धव ठाकरे पक्षातील 1500 सदस्यांनी एकावेळी पक्ष सोडला आणि...</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/after-uddhav-thackeray-sharad-pawar-also-gets-a-shock-many-join-bjp-party-a-a747/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/maharashtra-politics-1500-members-of-uddhav-thackerays-party-join-bjp-party-entry-in-mumbai-in-the-presence-of-ravindra-chavan/910127</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>युवा उद्योजक विशाल परब यांची भाजप वापसी</t>
+          <t>“ठाकरे बंधूंनी एकत्र येऊ नये असा GR काढलेला नाही”; CM देवेंद्र फडणवीसांचा खोचक टोला</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
+          <t>https://www.lokmat.com/mumbai/cm-devendra-fadnavis-taunt-about-raj-thackeray-and-uddhav-thackeray-likely-to-come-together-for-marathi-language-issue-a-a719/</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>Thane | कल्याण-डोंबिवलीत झोपडपट्टी पुनर्वसन योजना लवकरच कार्यान्वीत</t>
+          <t>Dahi Handi 2025 : डोंबिवलीमध्ये पारंपरिक पद्धतीने दहीहंडीचा उत्सव; गोविंदांचा उत्सह शिगेला</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/thane-slum-rehabilitation-scheme-to-be-implemented-soon-in-kalyan-dombivli</t>
+          <t>https://www.mymahanagar.com/mahamumbai/dahi-handi-2025-dahi-handi-celebrated-in-a-traditional-manner-in-dombivli-bjp-mla-ravindra-chavan/912575/</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : अधिकाऱ्यांनी जर दिरंगाई केली असेल तर…; रविंद्र चव्हाणांचा कारवाईचा इशारा</t>
+          <t>Nanded Ashok Chavan: अशोक चव्हाणांची डोकेदुखी वाढली; काँग्रेसकडून खिंडीत पकडण्यासाठी प्लॅन तयार, नांदेडमध्ये काय घडतंय?</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/videos/vishesh-vartankan/5163828/ravindra-chavans-warning-of-action-over-indrayani-river-bridge-collapsed-accident-cas/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/set-back-for-bjp-ashok-chavan-discussion-on-alliance-between-congress-and-prakash-ambedkar-vanchit-bahujan-aghadi/articleshow/122873066.cms</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>नांदेडमध्ये अशोक चव्हाणांना घेरण्यासाठी काँग्रेसची नवी खेळी; 'या' पक्षाशी करणार हातमिळवणी?</t>
+          <t>मी निष्पाप, निष्ठेने काम करेन, तुमचा आदेश तंतोतंत पाळेन, सुधाकर बडगुजरांचा बावनकुळेंना</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/politics/congress-may-alliance-with-vba-party-in-nanded-for-upcoming-municipal-election-942211.html</t>
+          <t>https://marathi.abplive.com/news/politics/sudhakar-badgujar-bjp-chandrashekhar-bawankule-he-join-bjp-with-girish-mahajan-and-ravindra-chavan-1364736</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>Marathwada Politics : काँग्रेसला जोरदार धक्का, २ दिग्गज नेत्यांनी 'हात' सोडला, २४ तासांत कमळ हातात घेणार</t>
+          <t>कल्याणमध्ये काँग्रेसला खिंडार! बडे नेते भाजपवासी; प्रदेशाध्यक्षांनी दिले मोठे संकेत</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/big-blow-to-congress-senior-leaders-kailas-gorantyal-and-suresh-warpudkar-set-to-join-bjp-ahead-of-local-polls-latest-news-nck90</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/bjp-grows-stronger-in-kalyan-congress-leaders-join-ravindra-chavan-hints-at-contesting-solo-bdk97</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>शेकाप नेते जयंत पाटील यांच्या घरात राजकीय फूट; बंधू पंडित पाटील यांचा भाजपात प्रवेश</t>
+          <t>स्थानिक स्वराज्य संस्थांच्या निवडणुका महायुती की स्वबळावर? भाजप प्रदेशाध्यक्षांचं सूचक विधान; म्हणाले, 'आचारसंहिता लागली की...'</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
+          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-statement-on-date-of-local-body-elections-mahayuti-alliance-vru98</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News : काँग्रेसचे माजी आमदार कुणाल पाटलांचा भाजपात प्रवेश</t>
+          <t>Devendra Fadnavis : “फेक नरेटिव्ह तयार करणाऱ्यांची फॅक्टरी…” फडणवीस यांचं उद्धव ठाकरेंना त्याच भाषेत उत्तर</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-1st-july-maharashtra-assembly-monsoon-session-2025-of-devendra-fadanvis-eknath-shinde-uddhav-and-raj-thackeray-asc-95-5194810/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-bjp-president-fadnavis-slams-uddhav-thackeray-over-fake-narrative-as11</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>Sanjay Jagtap : पुण्यात काँग्रेसला जोरदार झटका, संजय जगताप यांचा भाजपमध्ये प्रवेश | VIDEO</t>
+          <t>Nanded News: नांदेडमध्ये स्थानिक निवडणुकासाठी काँगेस अन् वंचितकडून युतीचे संकेत प्रस्ताव</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/sanjay-jagtap-former-congress-mla-joins-bjp-in-grand-saswad-event-political-shift-in-pune-district-mrs01</t>
+          <t>https://marathi.abplive.com/news/nanded/nanded-news-congress-and-vanchit-hint-at-alliance-for-local-government-elections-in-nanded-will-consider-proposal-if-received-1371522</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>मिशन मुंबई, भाजप भाकरी फिरवणार अध्यक्षपदासाठी बैठक, दोन आमदारांनी नावे समोर</t>
+          <t>Dombivli: संघाच्या बालेकिल्ल्यात हादरा, भाजप नेत्याचा राजीनामा, नेतृत्वावर आरोप, मशाल हाती घेण्याचे संकेत</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
+          <t>https://news18marathi.com/maharashtra/bjp-leader-vikas-mhatre-resigns-from-bjp-ahead-dombivli-mahapalika-election-allegation-on-ravindra-chavan-1423215.html</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
+          <t>छत्रपती शिवाजी महाराजांच्या मेघडंबरीसह पूर्णाकृती पुतळ्याचे डोंबिवलीत अनावरण ; खा. डॉ. श्रीकांत शिंदे, भाजप कार्याध्यक्ष रविंद्र चव्हाण यांची प्रमूख उपस्थिती – LNN</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
+          <t>https://www.localnewsnetwork.in/unveiling-of-the-full-length-statue-of-chhatrapati-shivaji-maharaj-with-a-canopy-in-dombivali/</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>राज्यात आणखी एक घराणं फुटलं; काँग्रेस खासदाराच्या दिराचा भाजपमध्ये प्रवेश, १० माजी नगरसेवकांनीही कमळ हाती घेतलं</t>
+          <t>Vikas Mhatre - प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला धक्का देणारे विकास म्हात्रे आहेत तरी कोण?</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/anil-dhanorkar-joins-bjp-in-presence-of-ravindra-chavan-and-hansraj-ahir-along-with-10-corporators-in-chandrapur-bdk97</t>
+          <t>https://sarkarnama.esakal.com/ampstories/web-stories/vikas-mhatre-resignation-bjp-allegations-on-ravindra-chavan-dombivili-msr87</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>भाजपचा मविआला जोरदार धक्का, वसई-विरार अन् धाराशिवमध्ये राजकीय भूकंप, कोण कोणत्या नेत्यांनी साथ सोडली?</t>
+          <t>Dombivli KDMCC School Building |डोंबिवलीत केडीएमसी शाळेची नवी इमारत</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/major-jolt-to-mva-as-key-leaders-join-bjp-in-vasai-virar-and-dharashiv-nck90</t>
+          <t>https://pudhari.news/maharashtra/thane/dombivli-kdmcc-school-new-building-bhoomipujan-by-mla-ravindra-chavan-sp96</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>'त्यांच्या प्रवेशामुळे पक्षाची ताकद वाढणार', हजारो समर्थकांसह संजय जगताप यांचा भाजपात प्रवेश</t>
+          <t>उत्तर महाराष्ट्रात काँग्रेसला मोठा धक्का ? कुणाल पाटील भाजपात जाणार? राजकीय वर्तुळात चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/pune/his-entry-will-increase-the-partys-strength-sanjay-jagtap-joins-bjp-with-thousands-of-supporters-a-a727/</t>
+          <t>https://www.etvbharat.com/mr/!state/dhule-congress-leader-kunal-patil-dismisses-rumors-of-joining-bjp-maharashtra-news-mhs25062501797</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>Thane Politics: शहापुरात मोठी राजकीय उलथापालथ! मविआच्या २७ मोठ्या नेत्यांचा भाजपात प्रवेश</t>
+          <t>Nashik BJP News : भाजप खासदार, आमदारांना मंडल दत्तक देणार</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/thane-politics-news-27-key-leaders-join-bjp-in-shahapur-major-blow-to-maha-vikas-aghadi-bdk97</t>
+          <t>https://pudhari.news/maharashtra/north-maharashtra/nashik/nashik-bjp-news-bjp-will-adopt-mandals-for-mps-mlas-ar84</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>Ameet Satam : भाजपमध्ये मोठे फेरबदल ! मुंबई भाजपचे नवे अध्यक्ष अमित साटम, मुख्यमंत्र्यानी केली घोषणा</t>
+          <t>Kalyan : त्या ६५ इमारतीबाबत भाजपचा मोठा निर्णय, प्रकरण फडणवीसांच्या कोर्टात, पुढे काय?</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/politics/maharashtra-politics-ameet-satam-appointed-as-mumbai-president-of-bjp-cm-devendra-fadanvis-annonced-it-/40320</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/no-resident-from-kalyan-dombivli-65-buildings-will-be-left-homeless-says-bjp-leader-ravindra-chavan-latest-marathi-news-nck90</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: शरद पवारांना मोठा झटका; नांदेडमधील ९ शिलेदारांनी धरली भाजपची वाट</t>
+          <t>Nitin Gadkari Auto Rickshaw Comment: गडकरींनी सांगितलं ‘ऑटो रिक्षा’ अन् महाराष्ट्र भाजपचं कनेक्शन ; क्षणात एकच हशा पिकला!</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/political-earthquake-in-nanded-major-setback-for-sharad-pawar-in-nanded-as-9-key-supporters-join-bjp-latest-news-pvm91</t>
+          <t>https://www.esakal.com/mumbai/nitin-gadkari-comment-about-auto-rickshaw-maharashtra-bjp-political-reaction-ravindra-chavan-maharashtra-bjp-president-msr87</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>पालघरमध्ये मोठी राजकीय घडामोड! एकनाथ शिंदेंना मोठा धक्का, बड्या नेत्यासह अनेक पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
+          <t>Devendra Fadnavis |महाराष्‍ट्र विकसित करुन दाखवू : मुख्यमंत्री देवेंद्र फडणवीस</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/big-political-shift-in-palghar-major-leaders-join-bjp-setback-for-eknath-shinde-uddhav-thackeray-and-sharad-pawar-pvm91</t>
+          <t>https://pudhari.news/maharashtra/mumbai/lets-develop-maharashtra-chief-minister-devendra-fadnavis-ng81</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>Raigad News : महायुतीत वादाची ठिणगी पडणार? एकनाथ शिंदेंच्या शिवसेनेला भाजपचा धक्का</t>
+          <t>उद्धव ठाकरेंपाठोपाठ शरद पवारांनाही धक्का! भाजपामध्ये 'इनकमिंग' सुरूच; अनेकांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
+          <t>https://www.lokmat.com/maharashtra/after-uddhav-thackeray-sharad-pawar-also-gets-a-shock-many-join-bjp-party-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>पुण्यात शरद पवारांसह अजित पवारांना धक्का; भाजपने पाडले खिंडार, शेकडो कार्यकर्त्यांचा राष्ट्रवादीला रामराम</t>
+          <t>युवा उद्योजक विशाल परब यांची भाजप वापसी</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/big-blow-to-sharad-pawar-in-pune-bhor-and-mulshi-hundreds-of-workers-join-bjp-nck90</t>
+          <t>https://www.tarunbharat.com/youth-leader-vishal-parab-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>तीन टर्म आमदार राहिलेल्या नेत्याच्या हाती कमळ; भाजपनं वाढवलं बळ, शिंदेसेनेत खळबळ</t>
+          <t>Thane | कल्याण-डोंबिवलीत झोपडपट्टी पुनर्वसन योजना लवकरच कार्यान्वीत</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
+          <t>https://pudhari.news/maharashtra/thane/thane-slum-rehabilitation-scheme-to-be-implemented-soon-in-kalyan-dombivli</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>Politics: कोल्हापुरात राजकीय भूकंप! काँग्रेस अन् राष्ट्रवादीला मोठा धक्का; बड्या नेत्यांसह कार्यकर्त्यांनी कमळ हाती घेतलं</t>
+          <t>Ravindra Chavan : अधिकाऱ्यांनी जर दिरंगाई केली असेल तर…; रविंद्र चव्हाणांचा कारवाईचा इशारा</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/major-political-shakeup-in-kolhapur-ex-congress-and-ncp-leaders-join-bjp-bdk97</t>
+          <t>https://www.loksatta.com/videos/vishesh-vartankan/5163828/ravindra-chavans-warning-of-action-over-indrayani-river-bridge-collapsed-accident-cas/</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>डोंबिवलीचे आमदार झाले भाजपाचे नवे प्रदेशाध्यक्ष! कल्याण डोंबिवलीत यंदा महापौर कोणाचा?</t>
+          <t>'मिशन पालिका' सुसाटsss... शरद पवार गट, 'प्रहार'च्या अनेक कार्यकर्त्यांचा भाजपामध्ये पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kalyan-dombivli/dombivli-mla-becomes-bjps-new-state-president-who-will-be-the-mayor-of-kalyan-dombivli-this-year-a-a653/</t>
+          <t>https://www.lokmat.com/maharashtra/many-political-party-workers-of-sharad-pawar-group-prahar-sanghatana-joins-bjp-for-municipal-elections-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: महाविकास आघाडीला मोठं खिंडार, अनेक बडे नेते, संरपंचांसह पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
+          <t>शेकाप नेते जयंत पाटील यांच्या घरात राजकीय फूट; बंधू पंडित पाटील यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-major-blow-to-mva-as-key-leaders-sarpanch-join-bjp-in-shahapur-pvm91</t>
+          <t>https://www.etvbharat.com/mr/!state/shetkari-kamgar-paksha-skp-jayant-patils-brother-pandit-patil-to-join-bjp-mumbai-maharashtra-maharashtra-news-mhs25041603477</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>खान्देशची बुलंद तोफ भाजपात जाणार? पडद्यामागच्या घडामोडींनी काँग्रेसची चिंता वाढली</t>
+          <t>Marathwada Politics : काँग्रेसला जोरदार धक्का, २ दिग्गज नेत्यांनी 'हात' सोडला, २४ तासांत कमळ हातात घेणार</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/big-blow-to-congress-senior-leaders-kailas-gorantyal-and-suresh-warpudkar-set-to-join-bjp-ahead-of-local-polls-latest-news-nck90</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>Dombivali Politics : भाजप प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला खिंडार; दोन नगरसेवकांचा राजीनामा</t>
+          <t>Sanjay Jagtap : पुण्यात काँग्रेसला जोरदार झटका, संजय जगताप यांचा भाजपमध्ये प्रवेश | VIDEO</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/setback-for-bjp-in-state-vice-presidents-constituency-ravindra-chavan-as-two-corporators-vikas-mhatre-and-kavita-mhatre-resign-politics-pjp78</t>
+          <t>https://saamtv.esakal.com/video/sanjay-jagtap-former-congress-mla-joins-bjp-in-grand-saswad-event-political-shift-in-pune-district-mrs01</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>Mumbai BJP President : अमित साटम मुंबई भाजपचे नवे अध्यक्ष! प्रदेशाध्यक्ष रविंद्र चव्हाण यांची मोठी घोषणा...</t>
+          <t>Maharashtra Breaking News : काँग्रेसचे माजी आमदार कुणाल पाटलांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/amit-satam-appointed-new-mumbai-bjp-president-devendra-fadnavis-announcement-spb94</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-1st-july-maharashtra-assembly-monsoon-session-2025-of-devendra-fadanvis-eknath-shinde-uddhav-and-raj-thackeray-asc-95-5194810/</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>ऑनलाइन हाजिरी लगा रहे भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण, अघाड़ी सम्मेलन में की जीत दिलाने की मांग</t>
+          <t>मिशन मुंबई, भाजप भाकरी फिरवणार अध्यक्षपदासाठी बैठक, दोन आमदारांनी नावे समोर</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/akola/aim-provide-health-services-vaidya-aghadi-conference-bjp-mahayuti-ravindra-chavan-1329683.html</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-misssion-mumbai-bjp-will-turn-the-tables-meeting-for-the-post-of-mumbai-president-on-place-of-ashish-shelar-two-mlas-put-forward-their-names-pravin-darekar-1354321</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>भाजपा के कोर कमेटी बैठक में रवींद्र चव्हाण ने दिए निर्देश, चुनावी रणनीति और संगठन मजबूती पर की चर्चा</t>
+          <t>'त्यांच्या प्रवेशामुळे पक्षाची ताकद वाढणार', हजारो समर्थकांसह संजय जगताप यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/garchiroli/election-strategy-strengthening-organization-ravindra-chavan-instructions-bjp-1326133.html</t>
+          <t>https://www.lokmat.com/pune/his-entry-will-increase-the-partys-strength-sanjay-jagtap-joins-bjp-with-thousands-of-supporters-a-a727/</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>Chandrashekhar Bawankule, Ravindra Chavan BJP State President</t>
+          <t>राज्यात आणखी एक घराणं फुटलं; काँग्रेस खासदाराच्या दिराचा भाजपमध्ये प्रवेश, १० माजी नगरसेवकांनीही कमळ हाती घेतलं</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
         <is>
-          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
+          <t>https://saamtv.esakal.com/maharashtra/anil-dhanorkar-joins-bjp-in-presence-of-ravindra-chavan-and-hansraj-ahir-along-with-10-corporators-in-chandrapur-bdk97</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>डोंबिवली में पहलगाम हमले में मारे गए नागरिकों की स्मृति में बनेगा शहीद स्मारक, विधायक रविंद्र चव्हाण ने लिखा पत्र</t>
+          <t>भाजपचा मविआला जोरदार धक्का, वसई-विरार अन् धाराशिवमध्ये राजकीय भूकंप, कोण कोणत्या नेत्यांनी साथ सोडली?</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>https://www.newsnationtv.com/--20250502182005/</t>
+          <t>https://saamtv.esakal.com/maharashtra/major-jolt-to-mva-as-key-leaders-join-bjp-in-vasai-virar-and-dharashiv-nck90</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>भाजपला लवकरच मिळणार नवा प्रदेशाध्यक्ष; रविंद्र चव्हाण यांच्यावर सोपवणार जबाबदारी</t>
+          <t>Thane Politics: शहापुरात मोठी राजकीय उलथापालथ! मविआच्या २७ मोठ्या नेत्यांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
+          <t>https://saamtv.esakal.com/maharashtra/thane-politics-news-27-key-leaders-join-bjp-in-shahapur-major-blow-to-maha-vikas-aghadi-bdk97</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed New BJP Maharashtra President : रविंद्र चव्हाण ठरले भाजपचे नवे कप्तान, महाराष्ट्राच्या संघटनाला नवे नेतृत्व</t>
+          <t>Ameet Satam : भाजपमध्ये मोठे फेरबदल ! मुंबई भाजपचे नवे अध्यक्ष अमित साटम, मुख्यमंत्र्यानी केली घोषणा</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
+          <t>https://www.jaimaharashtranews.com/politics/maharashtra-politics-ameet-satam-appointed-as-mumbai-president-of-bjp-cm-devendra-fadanvis-annonced-it-/40320</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>भाजपला आज मिळणार नवे प्रदेशाध्यक्ष; रवींद्र चव्हाण स्विकारणार सूत्र</t>
+          <t>मुख्यमंत्र्यांच्या वाढदिवसानिमित्त भाजपातर्फे आयोजित रक्तदान कार्यक्रमाने रचले २ विश्वविक्रम</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/bjp-will-get-a-new-state-president-today-ravindra-chavan-will-accept-the-oath/</t>
+          <t>https://www.lokmat.com/maharashtra/blood-donation-program-organized-by-bjp-on-the-occasion-of-cm-devendra-fadnavis-birthday-sets-2-world-records-a-a747/</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>मालवण मधील 'उबाठा' च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश</t>
+          <t>Maharashtra Politics: शरद पवारांना मोठा झटका; नांदेडमधील ९ शिलेदारांनी धरली भाजपची वाट</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/four-former-corporators-of-ubatha-in-malvan-join-bjp-along-with-their-supporters/cid1752483678.htm</t>
+          <t>https://saamtv.esakal.com/maharashtra/political-earthquake-in-nanded-major-setback-for-sharad-pawar-in-nanded-as-9-key-supporters-join-bjp-latest-news-pvm91</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>Ravindra Chavan होणार महाराष्ट्र भाजपचे नवे प्रदेशाध्यक्ष, ठाकरेंच्या गडात होणार पहिलं शक्तिप्रदर्शन!</t>
+          <t>पालघरमध्ये मोठी राजकीय घडामोड! एकनाथ शिंदेंना मोठा धक्का, बड्या नेत्यासह अनेक पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
         <is>
-          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
+          <t>https://saamtv.esakal.com/maharashtra/big-political-shift-in-palghar-major-leaders-join-bjp-setback-for-eknath-shinde-uddhav-thackeray-and-sharad-pawar-pvm91</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>भोर, मुळशी तालुक्यातील विविध पक्षातील कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>Raigad News : महायुतीत वादाची ठिणगी पडणार? एकनाथ शिंदेंच्या शिवसेनेला भाजपचा धक्का</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/raigad/shivsena-mla-mahendra-thorve-join-bjp-in-raigad-before-local-government-elections-marathi-news/articleshow/121927356.cms</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>शहापूर तालुक्यातील उबाठा, शरद पवार गट व काँग्रेसच्या अनेक कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>पुण्यात शरद पवारांसह अजित पवारांना धक्का; भाजपने पाडले खिंडार, शेकडो कार्यकर्त्यांचा राष्ट्रवादीला रामराम</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/big-blow-to-sharad-pawar-in-pune-bhor-and-mulshi-hundreds-of-workers-join-bjp-nck90</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>कल्याण – डोंबिवली , चंद्रपूर जिल्ह्यातील अनेक माजी नगरसेवकांचा भाजपात प्रवेश</t>
+          <t>तीन टर्म आमदार राहिलेल्या नेत्याच्या हाती कमळ; भाजपनं वाढवलं बळ, शिंदेसेनेत खळबळ</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/former-congress-mla-kailash-gorantyal-joins-bjp-major-challenge-for-shinde-led-shiv-sena-in-jalna/articleshow/123019959.cms</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
+          <t>Politics: कोल्हापुरात राजकीय भूकंप! काँग्रेस अन् राष्ट्रवादीला मोठा धक्का; बड्या नेत्यांसह कार्यकर्त्यांनी कमळ हाती घेतलं</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
+          <t>https://saamtv.esakal.com/maharashtra/major-political-shakeup-in-kolhapur-ex-congress-and-ncp-leaders-join-bjp-bdk97</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>BJP President Banner: भाजप प्रदेशाध्यक्षांच्या निवडीचे बॅनर फाडले... - देशोन्नती</t>
+          <t>डोंबिवलीचे आमदार झाले भाजपाचे नवे प्रदेशाध्यक्ष! कल्याण डोंबिवलीत यंदा महापौर कोणाचा?</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
+          <t>https://www.lokmat.com/kalyan-dombivli/dombivli-mla-becomes-bjps-new-state-president-who-will-be-the-mayor-of-kalyan-dombivli-this-year-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>रविंद्र शिंदेंचा भाजपमध्ये धडाकेबाज प्रवेश; चंद्रपूरच्या राजकारणाला कलाटणी!</t>
+          <t>महाराष्ट्रात मराठीचीच सक्ती, पण हिंदीचाही अभिमान, दबावाला बळी न पडता विद्यार्थ्यांच्या</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
+          <t>https://marathi.abplive.com/news/maharashtra/chief-minister-devendra-fadnavis-reaction-regarding-marathi-language-criticism-on-uddhav-thackeray-in-mumbai-1367354</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण; अधिकृत घोषणा आज होणार</t>
+          <t>खान्देशची बुलंद तोफ भाजपात जाणार? पडद्यामागच्या घडामोडींनी काँग्रेसची चिंता वाढली</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>https://marathi.freepressjournal.in/maharashtra/ravindra-chavan-to-be-bjp-maharashtra-president-announcement-soon</t>
+          <t>https://marathi.indiatimes.com/photogallery/news/congress-leader-kunal-patil-may-be-join-bjp-soon/photoshow/122030946.cms</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>Ravindra Chavan MaTa Katta : ठाकरे बंधूंची युती निश्चित, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण म्हणाले, भावनात्मक मुद्द्यांवर कुणाला...</t>
+          <t>Maharashtra Politics: महाविकास आघाडीला मोठं खिंडार, अनेक बडे नेते, संरपंचांसह पदाधिकाऱ्यांचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-major-blow-to-mva-as-key-leaders-sarpanch-join-bjp-in-shahapur-pvm91</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>डोंबिवलीत बुधवारी भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचा जनता दरबार</t>
+          <t>वाचाळवीरांवर कारवाईसाठी भाजप प्रदेशाध्यक्षांचे मौन का ?</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-janta-darbar-in-dombivli-on-wednesday-ssb-93-5314946/</t>
+          <t>https://www.lokmat.com/nagpur/why-is-the-bjp-state-president-silent-on-taking-action-against-bitter-speakers-a-a1000/</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण, १ जुलैला घोषणा; किरण रिजिजू निरीक्षक</t>
+          <t>Dombivali Politics : भाजप प्रदेश कार्याध्यक्षांच्या मतदारसंघातच भाजपला खिंडार; दोन नगरसेवकांचा राजीनामा</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/mumbai/ravindra-chavan-to-be-bjp-maharashtra-state-president-announcement-on-july-1-kiren-rijiju-observer-a-a571/</t>
+          <t>https://www.esakal.com/mumbai/setback-for-bjp-in-state-vice-presidents-constituency-ravindra-chavan-as-two-corporators-vikas-mhatre-and-kavita-mhatre-resign-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: भाजपमध्ये आता चव्हाणपर्व, रवींद्र चव्हाण बनले नवे भाजपचे प्रदेशाध्यक्ष!</t>
+          <t>Mumbai BJP President : अमित साटम मुंबई भाजपचे नवे अध्यक्ष! प्रदेशाध्यक्ष रविंद्र चव्हाण यांची मोठी घोषणा...</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/mumbai/ravindra-chavan-has-become-the-new-bjp-maharashtra-president-1426306.html</t>
+          <t>https://www.esakal.com/mumbai/amit-satam-appointed-new-mumbai-bjp-president-devendra-fadnavis-announcement-spb94</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>डोंंबिवलीच्या विकासाला ग्रहण लावणाऱ्या ‘चाँदभाई’चे नाव घ्या; राजू पाटील यांचे भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांना आवाहन</t>
+          <t>ऑनलाइन हाजिरी लगा रहे भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण, अघाड़ी सम्मेलन में की जीत दिलाने की मांग</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/mns-leader-raju-patil-slams-bjp-state-chief-ravindra-chavan-for-his-bjp-mayor-in-kdmc-remark-zws-70-5279498/</t>
+          <t>https://navbharatlive.com/maharashtra/akola/aim-provide-health-services-vaidya-aghadi-conference-bjp-mahayuti-ravindra-chavan-1329683.html</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>BJP Politics : भाजप प्रदेशाध्यक्षांच्या ठाकरेंना दे धक्का! बालेकिल्ल्यात 'डॅमेज कंट्रोल', विकास म्हात्रेंचे मन वळवले</t>
+          <t>भाजपा के कोर कमेटी बैठक में रवींद्र चव्हाण ने दिए निर्देश, चुनावी रणनीति और संगठन मजबूती पर की चर्चा</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/bjp-ravindra-chavan-successfully-resolves-vikas-mhatre-disconten-shivsen-ubt-rm89</t>
+          <t>https://navbharatlive.com/maharashtra/garchiroli/election-strategy-strengthening-organization-ravindra-chavan-instructions-bjp-1326133.html</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>Photo : प्रदेशाध्यक्ष पदाची सूत्रे स्वीकारताच रवींद्र चव्हाण अ‍ॅक्टिव्ह; म्हणाले…</t>
+          <t>Chandrashekhar Bawankule, Ravindra Chavan BJP State President</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
+          <t>https://www.khabar24.tv/2025/07/02/after-the-brilliant-tenure-of-chandrashekhar-bawankule-the-command-of-maharashtra-bjp-is-now-in-the-hands-of-ravindra-chavan/</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>अधिवेशन, कायदा-सुव्यवस्था राखण्यासाठी हिंदीची सक्ती रद्द, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
+          <t>डोंबिवली में पहलगाम हमले में मारे गए नागरिकों की स्मृति में बनेगा शहीद स्मारक, विधायक रविंद्र चव्हाण ने लिखा पत्र</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/mumbai/bjp-ravindra-chavan-says-hindi-compulsion-decision-withdrawn-due-to-assembly-session-and-law-and-order-mumbai-print-news-css-98-5217714/</t>
+          <t>https://www.newsnationtv.com/--20250502182005/</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>BJP State President Election | भाजपकडून प्रदेशाध्यक्ष पदासाठी निवडणूक कार्यक्रम जाहीर</t>
+          <t>भाजपला लवकरच मिळणार नवा प्रदेशाध्यक्ष; रविंद्र चव्हाण यांच्यावर सोपवणार जबाबदारी</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
+          <t>https://www.dainikprabhat.com/bjp-will-soon-get-a-new-state-president-ravindra-chavan-will-be-entrusted-with-the-responsibility/</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>मालवणमधील 'उबाठा'च्या चार माजी नगरसेवकांचा समर्थकांसह भाजपामध्ये प्रवेश, भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांनी केले स्वागत</t>
+          <t>Ravindra Chavan Appointed New BJP Maharashtra President : रविंद्र चव्हाण ठरले भाजपचे नवे कप्तान, महाराष्ट्राच्या संघटनाला नवे नेतृत्व</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/four-former-corporators-of-ubt-in-malvan-join-bjp-along-with-their-supporters-welcomed-by-bjp-state-president-ravindra-chavan-maharashtra-news-mhs25071403115</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-new-bjp-maharashtra-president/articleshow-x7qax8g</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>Sindhudurg Politics | सिंधुदुर्ग जिल्हा व भाजपसाठी आज आनंदाचा दिवस!</t>
+          <t>वसई-विरारच्या ‘बविआ’ च्या माजी नगसेवक आणि कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-bjp-state-president-sindhudurg-politics-sp96</t>
+          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>Devendra Fadnavis |महाराष्‍ट्र विकसित करुन दाखवू : मुख्यमंत्री देवेंद्र फडणवीस</t>
+          <t>Ravindra Chavan होणार महाराष्ट्र भाजपचे नवे प्रदेशाध्यक्ष, ठाकरेंच्या गडात होणार पहिलं शक्तिप्रदर्शन!</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/lets-develop-maharashtra-chief-minister-devendra-fadnavis-ng81</t>
+          <t>https://marathi.asianetnews.com/maharashtra/ravindra-chavan-to-become-maharashtra-bjp-president/articleshow-bv2gf6u</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>वसई-विरारच्या ‘बविआ’ च्या माजी नगसेवक आणि कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
+          <t>भोर, मुळशी तालुक्यातील विविध पक्षातील कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/former-nagsevaks-and-activists-of-bva-of-vasai-virar-join-bjp/</t>
+          <t>https://www.marathiebatmya.com/political/bhor-mulshi-taluka-workers-from-various-parties-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांच्या हस्ते ‘ध्येयवादी देवेंद्रजी’ कॉफी टेबल बुकचे प्रकाशन</t>
+          <t>शहापूर तालुक्यातील उबाठा, शरद पवार गट व काँग्रेसच्या अनेक कार्यकर्त्यांचा भाजपामध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
+          <t>https://www.marathiebatmya.com/political/activist-of-ubt-sharad-pawar-group-and-congress-in-shahapur-taluka-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>Kedar Jadhav makes bold prediction about India playing Pakistan in Asia Cup</t>
+          <t>कल्याण – डोंबिवली , चंद्रपूर जिल्ह्यातील अनेक माजी नगरसेवकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
+          <t>https://www.marathiebatmya.com/political/many-former-corporators-from-kalyan-dombivli-chandrapur-districts-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>4 ex-Congress corporators join BJP in Kalyan-Dombivli</t>
+          <t>मोठी बातमी : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
+          <t>https://www.timemaharashtra.com/maharashtra/big-news-ravindra-chavan-elected-as-bjps-working-regional-president/108447/</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
+          <t>BJP President Banner: भाजप प्रदेशाध्यक्षांच्या निवडीचे बॅनर फाडले... - देशोन्नती</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
+          <t>https://deshonnati.com/bjp-president-banner-tore-the-of-state-election/</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>BJP inducts key PWP leaders before local body elections</t>
+          <t>रविंद्र शिंदेंचा भाजपमध्ये धडाकेबाज प्रवेश; चंद्रपूरच्या राजकारणाला कलाटणी!</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
+          <t>https://news34.in/2025/07/ravindra-shinde-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>Former Congress MLA Kunal Patil joins BJP</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण; अधिकृत घोषणा आज होणार</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/former-congress-mla-kunal-patil-joins-bjp-10100556/</t>
+          <t>https://marathi.freepressjournal.in/maharashtra/ravindra-chavan-to-be-bjp-maharashtra-president-announcement-soon</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
+          <t>Ravindra Chavan MaTa Katta : ठाकरे बंधूंची युती निश्चित, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण म्हणाले, भावनात्मक मुद्द्यांवर कुणाला...</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-ravindra-chavan-talks-on-uddhav-thackeray-raj-thackeray-reunite-bmc-elections-2025/articleshow/123154745.cms</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>BJP picks new state chiefs, moves closer to electing JP Nadda's successor</t>
+          <t>डोंबिवलीत बुधवारी भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचा जनता दरबार</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
         <is>
-          <t>https://www.indiatoday.in/india/story/with-new-state-presidents-bjp-gears-up-to-choose-jp-nadda-successor-2748768-2025-07-01</t>
+          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-janta-darbar-in-dombivli-on-wednesday-ssb-93-5314946/</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>Cong ex-corporator from Sangli &amp; Vishal Patil’s close aide joins BJP</t>
+          <t>BJP Politics : भाजप प्रदेशाध्यक्षांच्या ठाकरेंना दे धक्का! बालेकिल्ल्यात 'डॅमेज कंट्रोल', विकास म्हात्रेंचे मन वळवले</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/kolhapur/cong-ex-corporator-from-sangli-vishal-patils-close-aide-joins-bjp/articleshow/123244747.cms</t>
+          <t>https://sarkarnama.esakal.com/mumbai/bjp-ravindra-chavan-successfully-resolves-vikas-mhatre-disconten-shivsen-ubt-rm89</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
+          <t>Photo : प्रदेशाध्यक्ष पदाची सूत्रे स्वीकारताच रवींद्र चव्हाण अ‍ॅक्टिव्ह; म्हणाले…</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
+          <t>https://www.mymahanagar.com/photo-gallery/ravindra-chavan-appealed-to-the-workers-after-assuming-the-post-of-bjp-state-president/898007/</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>Maharashtra Cabinet Reshuffle: Fadnavis Meets Amit Shah, Nadda Amid Speculation</t>
+          <t>अधिवेशन, कायदा-सुव्यवस्था राखण्यासाठी हिंदीची सक्ती रद्द, भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
+          <t>https://www.loksatta.com/mumbai/bjp-ravindra-chavan-says-hindi-compulsion-decision-withdrawn-due-to-assembly-session-and-law-and-order-mumbai-print-news-css-98-5217714/</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>Mumbai Confidential: Brother trouble</t>
+          <t>BJP State President Election | भाजपकडून प्रदेशाध्यक्ष पदासाठी निवडणूक कार्यक्रम जाहीर</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/mumbai-confidential/mumbai-confidential-brother-trouble-10110311/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-maharashtra-state-president-election-nomination-process-begins-ravindra-chavhan-likely-to-secure-position-1367011</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>Pune Congress leader Sanjay Jagtap joins BJP</t>
+          <t>Sindhudurg Politics | सिंधुदुर्ग जिल्हा व भाजपसाठी आज आनंदाचा दिवस!</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/Pune-Congress-leader-Sanjay-Jagtap-joins-BJP/2733730</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/ravindra-chavan-bjp-state-president-sindhudurg-politics-sp96</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>NCP, Shiv Sena (UBT) members join BJP in Nashik</t>
+          <t>Who is Ravindra Chavan: भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण कोण आहेत? जाणून घ्या राजकीय कारकीर्द</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
+          <t>https://marathi.oneindia.com/maharashtra/who-is-ravindra-chavan-new-maharashtra-president-of-bjp-know-about-his-political-career-in-marathi-031665.html</t>
         </is>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>Congress’s 5 time Ex-MLA Suresh Warpudkar kin set to join BJP</t>
+          <t>भाजपा प्रदेशाध्यक्ष रवींद्र चव्हाण यांच्या हस्ते ‘ध्येयवादी देवेंद्रजी’ कॉफी टेबल बुकचे प्रकाशन</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
+          <t>https://pcbtoday.in/%E0%A4%AD%E0%A4%BE%E0%A4%9C%E0%A4%AA%E0%A4%BE-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6%E0%A4%BE%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%B0%E0%A4%B5%E0%A5%80%E0%A4%82/</t>
         </is>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>India Politics Highlights| Criminals, gangsters got right to rape, loot under TMC banner: CPI(M)'s Md Salim</t>
+          <t>Kedar Jadhav makes bold prediction about India playing Pakistan in Asia Cup</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
+          <t>https://www.msn.com/en-gb/news/world/kedar-jadhav-makes-bold-prediction-about-india-playing-pakistan-in-asia-cup/ar-AA1KJnU4</t>
         </is>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>Maharashtra BJP appoints 58 new district presidents ahead of local body polls</t>
+          <t>4 ex-Congress corporators join BJP in Kalyan-Dombivli</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
         <is>
-          <t>https://www.newindianexpress.com/nation/2025/May/13/maharashtra-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/4-ex-congress-corporators-join-bjp-in-kalyan-dombivli/articleshow/123447826.cms</t>
         </is>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>Emotional farewell: Outgoing BJP State President Bawankule pens heartfelt letter to party workers</t>
+          <t>Who Is Ravindra Chavan, New Maharashtra BJP Chief, Close Confidant Of CM Devendra Fadnavis?</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
         <is>
-          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
+          <t>https://zeenews.india.com/india/who-is-ravindra-chavan-new-maharashtra-bjp-chief-close-confidant-of-cm-devendra-fadnavis-2925029.html</t>
         </is>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>BJP inducts key PWP leaders before local body elections</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/national/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://www.hindustantimes.com/cities/mumbai-news/bjp-inducts-key-pwp-leaders-before-local-body-elections-101744831159344.html</t>
         </is>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>Ameet Satam Appointed As Mumbai BJP President Ahead of BMC Polls</t>
+          <t>3-term Ameet Satam replaces Ashish Shelar as Mumbai BJP President</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>https://www.lokmattimes.com/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls-a517/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/3-term-ameet-satam-replaces-ashish-shelar-as-mumbai-bjp-president-3695763</t>
         </is>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Ex-Congress MLA Sanjay Jagtap Joins BJP With Supporters In Pune; Congress Hits Out,</t>
+          <t>Ahead of local body polls, BJP finalises names of 22 district presidents</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ex-congress-mla-sanjay-jagtap-joins-bjp-with-supporters-in-pune-congress-hits-out-calls-bjp-witch-party-video</t>
+          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
         </is>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>Maharashtra News: Former Congress MLA Sangram Thopte From Punes Bhor Joins BJP After Setback In 2024 Assembly</t>
+          <t>‘No one becomes great by imposing themselves’: Nitin Gadkari flags arrogance in leadership, Congress reacts</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-former-congress-mla-sangram-thopte-from-punes-bhor-joins-bjp-after-setback-in-2024-assembly-elections</t>
+          <t>https://www.livemint.com/politics/news/no-one-becomes-great-by-imposing-themselves-nitin-gadkari-warns-against-arrogance-in-leadership-cong-reacts-11752387796290.html</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Anna Dange Returns To BJP After 23 Years; Fadnavis Slams Congress Over Operation</t>
+          <t>BJP picks new state chiefs, moves closer to electing JP Nadda's successor</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-anna-dange-returns-to-bjp-after-23-years-fadnavis-slams-congress-over-operation-sindoor-remark</t>
+          <t>https://www.indiatoday.in/india/story/with-new-state-presidents-bjp-gears-up-to-choose-jp-nadda-successor-2748768-2025-07-01</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: State Congress Secretary Dilip Bhalerao, Along With Hundreds Of Supporters, Joins BJP</t>
+          <t>BJP picks MLA Ameet Satam as party’s Mumbai chief</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-state-congress-secretary-dilip-bhalerao-along-with-hundreds-of-supporters-joins-bjp</t>
+          <t>https://www.newindianexpress.com/nation/2025/Aug/26/bjp-picks-mla-ameet-satam-as-partys-mumbai-chief</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
+          <t>Maha: Sudhakar Badgujar, who faced charges of 'links' with underworld, joins BJP</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
+          <t>https://www.thehansindia.com/news/national/maha-sudhakar-badgujar-who-faced-charges-of-links-with-underworld-joins-bjp-980585</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: Former Congress Minister Suresh Warpudkar Joins BJP With Key Supporters</t>
+          <t>After poll drubbing, Prithviraj Chavan may replace Patole in Maharashtra Congress rejig</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-minister-suresh-warpudkar-joins-bjp-with-key-supporters</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jan/14/after-poll-drubbing-prithviraj-chavan-may-replace-patole-in-maharashtra-congress-rejig</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>Congress Receives A Jolt After Former Dhule MLA Kunal Patil Joins BJP</t>
+          <t>Maharashtra Cabinet Reshuffle: Fadnavis Meets Amit Shah, Nadda Amid Speculation</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
+          <t>https://www.deccanherald.com/india/maharashtra/maharashtra-cabinet-reshuffle-on-cards-fadnavis-meets-shah-nadda-in-delhi-3648744</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>Maharashtra Politics: BJP Appoints 58 New District Presidents Ahead Of Local Body Polls</t>
+          <t>NCP, Shiv Sena (UBT) members join BJP in Nashik</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
+          <t>https://timesofindia.indiatimes.com/city/nashik/ncp-shiv-sena-ubt-members-join-bjp-in-nashik/articleshow/122233115.cms</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>Ramchander Rao appointed as T'gana BJP President despite opposition: MP gets new chief as Hemant Khandelwal...</t>
+          <t>Congress’s 5 time Ex-MLA Suresh Warpudkar kin set to join BJP</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
+          <t>https://timesofindia.indiatimes.com/city/aurangabad/congress-ex-mla-suresh-warpudkar-and-family-set-to-join-bjp/articleshow/122951927.cms</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>BJP announces new state chiefs in 7 states, 2 UTs; moves closer to elect national president</t>
+          <t>India Politics Highlights| Criminals, gangsters got right to rape, loot under TMC banner: CPI(M)'s Md Salim</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
+          <t>https://www.deccanherald.com/india/bjp-state-chiefs-kharges-high-command-remark-congress-bihar-elections-modi-sonia-rahul-gandhi-socialist-secular-rss-constitution-india-tamil-nadu-3610086</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>Pune MP Murlidhar Mohol Launches City’s First 24×7 Digital Citizen Service Office</t>
+          <t>Maharashtra BJP appoints 58 new district presidents ahead of local body polls</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>https://www.mypunepulse.com/pune-mp-murlidhar-mohol-launches-citys-first-24x7-digital-citizen-service-office/</t>
+          <t>https://www.newindianexpress.com/nation/2025/May/13/maharashtra-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>BJP Appoints New State Presidents in 9 States Including Maharashtra and Madhya Pradesh</t>
+          <t>"Public gave us landslide victory": Dy CM Eknath Shinde exerts confidence on win of Mahayuti in Maharashtra elections</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
         <is>
-          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
+          <t>https://www.aninews.in/news/national/general-news/public-gave-us-landslide-victory-dy-cm-eknath-shinde-exerts-confidence-on-win-of-mahayuti-in-maharashtra-elections20250702090322</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>Emotional farewell: Outgoing BJP State President Bawankule pens heartfelt letter to party workers</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
         <is>
-          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
+          <t>https://www.nagpurtoday.in/emotional-farewell-outgoing-bjp-state-president-bawankule-pens-heartfelt-letter-to-party-workers/07021355</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>Ex Minister Ravindra Chavan Files Nomination For Maharashtra BJP Chief Post</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
+          <t>https://www.lokmattimes.com/national/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>BJP leader Ravindra Chavan appointed as new state president of Maharashtra</t>
+          <t>Ameet Satam Appointed As Mumbai BJP President Ahead of BMC Polls</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
+          <t>https://www.lokmattimes.com/mumbai/ameet-satam-appointed-as-mumbai-bjp-president-ahead-of-bmc-polls-a517/</t>
         </is>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>Pune bridge collapse: Ex-minister seeks probe into delay in construction of new structure</t>
+          <t>Maharashtra Politics: Ex-Congress MLA Sanjay Jagtap Joins BJP With Supporters In Pune; Congress Hits Out,</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>https://m.economictimes.com/news/india/pune-bridge-collapse-ex-minister-seeks-probe-into-delay-in-construction-of-new-structure/articleshow/121904713.cms</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-ex-congress-mla-sanjay-jagtap-joins-bjp-with-supporters-in-pune-congress-hits-out-calls-bjp-witch-party-video</t>
         </is>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>Ravindra Chavan elected unopposed as Maha BJP chief</t>
+          <t>Maharashtra News: Former Congress MLA Sangram Thopte From Punes Bhor Joins BJP After Setback In 2024 Assembly</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>https://tennews.in/ravindra-chavan-elected-unopposed-as-maha-bjp-chief/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-former-congress-mla-sangram-thopte-from-punes-bhor-joins-bjp-after-setback-in-2024-assembly-elections</t>
         </is>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>Andheri MLA Ameet Satam to lead Mumbai unit as party gears up for high-stakes BMC battle</t>
+          <t>Maharashtra Politics: State Congress Secretary Dilip Bhalerao, Along With Hundreds Of Supporters, Joins BJP</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/andheri-mla-ameet-satam-to-lead-mumbai-unit-as-party-gears-up-for-high-stakes-bmc-battle-23591113</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-state-congress-secretary-dilip-bhalerao-along-with-hundreds-of-supporters-joins-bjp</t>
         </is>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>Kailas Gorantyal Set to Join BJP Today</t>
+          <t>Mumbai BJP Leadership Shake-Up: Pravin Darekar And Amit Satam In Contention For City President Post Ahead Of</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
         <is>
-          <t>https://english.lokshahi.com/politics/kailash-gorantyal-to-join-bjp-today</t>
+          <t>https://www.freepressjournal.in/mumbai/mumbai-bjp-leadership-shake-up-pravin-darekar-and-amit-satam-in-contention-for-city-president-post-ahead-of-bmc-elections</t>
         </is>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
+          <t>Who Is Prithviraj Patil? Former Sangli Congress Leader to Join BJP Tomorrow</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/06/30/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
+          <t>https://www.freepressjournal.in/pune/who-is-prithviraj-patil-former-sangli-congress-leader-to-join-bjp-tomorrow</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>Maharashtra News: BJP Sets Up 1,221 Mandals Across State, Appoints 963 Presidents Ahead Of Local Body Polls</t>
+          <t>Maharashtra Politics: Former Congress Minister Suresh Warpudkar Joins BJP With Key Supporters</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-news-bjp-sets-up-1221-mandals-across-state-appoints-963-presidents-ahead-of-local-body-polls</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-former-congress-minister-suresh-warpudkar-joins-bjp-with-key-supporters</t>
         </is>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>Ameet Satam Becomes BJP's New Mumbai Chief Ahead Of BMC Polls. Who Is He?</t>
+          <t>Congress Receives A Jolt After Former Dhule MLA Kunal Patil Joins BJP</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ameet-satam-becomes-bjp-new-mumbai-chief-ahead-of-bmc-polls-who-is-he-1796474</t>
+          <t>https://ommcomnews.com/india-news/congress-receives-a-jolt-after-former-dhule-mla-kunal-patil-joins-bjp/</t>
         </is>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
+          <t>Maharashtra Politics: BJP Appoints 58 New District Presidents Ahead Of Local Body Polls</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
         <is>
-          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-politics-bjp-appoints-58-new-district-presidents-ahead-of-local-body-polls</t>
         </is>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>सीएम फडणवीस के विश्वासपात्र...रवींद्र चव्हाण महाराष्ट्र भाजपा के नए प्रदेश अध्यक्ष</t>
+          <t>Ramchander Rao appointed as T'gana BJP President despite opposition: MP gets new chief as Hemant Khandelwal...</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
+          <t>https://www.bhaskarenglish.in/national/news/bjp-state-presidents-appointment-national-president-election-july-maharashtra-himachal-pm-modi-jp-nadda-135348404.html</t>
         </is>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>Maharashtra: बीजेपी ने महाराष्ट्र में बता दिया कौन बनेगा प्रदेश अध्यक्ष? BMC चुनावों से पहले मराठी दांव</t>
+          <t>BJP announces new state chiefs in 7 states, 2 UTs; moves closer to elect national president</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
+          <t>https://english.publictv.in/bjp-announces-new-state-chiefs-in-7-states-2-uts-moves-closer-to-elect-national-president/</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>Former Minister Ravindra Chavan Appointed Maharashtra BJP Working President</t>
+          <t>BJP Appoints New State Presidents in 9 States Including Maharashtra and Madhya Pradesh</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
         <is>
-          <t>https://www.news18.com/politics/former-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-9185878.html</t>
+          <t>https://kknlive.com/en/andhra-pradesh-en/bjp-appoints-new-state-presidents-in-9-states/</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>कौन बनेगा महाराष्ट्र भाजपा का अध्यक्ष? इस नाम का चुना जाना लगभग तय</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
+          <t>https://fox5sandiego.com/business/press-releases/ein-presswire/827256708/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>महाराष्ट्र बीजेपी की कमान अब नए हाथों में, जानिए कौन हैं पार्टी के नवनियुक्त प्रदेश अध्यक्ष रवींद्र चव्हाण</t>
+          <t>Ex Minister Ravindra Chavan Files Nomination For Maharashtra BJP Chief Post</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
+          <t>https://www.ndtv.com/india-news/ex-minister-ravindra-chavan-files-nomination-for-maharashtra-bjp-chief-post-8800476</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
+          <t>BJP leader Ravindra Chavan appointed as new state president of Maharashtra</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>https://www.asianage.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888548</t>
+          <t>https://www.newsonair.gov.in/bjp-leader-ravindra-chavan-appointed-as-new-state-president-of-maharashtra/</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>पूर्व मंत्री रवींद्र चव्हाण बने महाराष्ट्र BJP के कार्यकारी प्रदेश अध्यक्ष, बावनकुले की कुर्सी छिनी</t>
+          <t>Ravindra Chavan set to take over as Maharashtra unit BJP chief tomorrow</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
         <is>
-          <t>https://www.tv9hindi.com/state/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp-3054565.html</t>
+          <t>https://www.socialnews.xyz/2025/06/30/ravindra-chavan-set-to-take-over-as-maharashtra-unit-bjp-chief-tomorrow/</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपचे प्रदेश कार्यकारी अध्यक्ष होताच रवींद्र चव्हाण अनवाणी पायाने</t>
+          <t>Ravindra Chavan Appointed Maharashtra BJP President: A Grassroots Leader with Ideology and Strategy</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
+          <t>https://www.tribuneindia.com/news/business/ravindra-chavan-appointed-maharashtra-bjp-president-a-grassroots-leader-with-ideology-and-strategy/</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP को मिलेगा नया चेहरा; चंद्रशेखर बावनकुले के बाद रवींद्र चव्हाण का नाम सबसे आगे, रिजिजू की निगरानी में होगा ऐलान</t>
+          <t>सीएम फडणवीस के विश्वासपात्र...रवींद्र चव्हाण महाराष्ट्र भाजपा के नए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>https://sudarshannews.in/news-detail.aspx?id=129159</t>
+          <t>https://ndtv.in/india/who-is-ravindra-chavan-new-bjp-president-for-maharashtra-close-aide-of-cm-fadnavis-8810167</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>हेमंत खंडेलवाल होंगे मध्य प्रदेश बीजेपी के नए अध्यक्ष, रवींद्र चव्हाण को महाराष्ट्र की कमान</t>
+          <t>Maharashtra: बीजेपी ने महाराष्ट्र में बता दिया कौन बनेगा प्रदेश अध्यक्ष? BMC चुनावों से पहले मराठी दांव</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-to-appoints-ravindra-chavan-next-bjp-president-of-maharashtra-chandrashekhar-bawankule-amit-shah-visit-know-all/articleshow/121479121.cms</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>भारतीय जनता पार्टीचे नवे प्रदेशाध्यक्ष म्हणून रवींद्र चव्हाण यांची बिनविरोध निवड</t>
+          <t>कभी भी थाम सकते हैं बीजेपी का दामन! रवींद्र चव्हाण से मिले थे कांग्रेस नेता कुणाल पाटिल...</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
         <is>
-          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
+          <t>https://www.etvbharat.com/hi/!bharat/maharashtra-politics-congress-leader-kunal-patil-denied-rumors-of-joining-bjp-hindi-news-hin25062504020</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>Ravindra Chavan News : मंत्रिमंडळात मोठे फेरबदल, 8 जणांना डच्चू मिळणार का? अखेर रवींद्र चव्हाण यांनीच केलं क्लिअर</t>
+          <t>Former Minister Ravindra Chavan Appointed Maharashtra BJP Working President</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/maharashtra-cabinet-reshuffle-2025-ministers-remove-ravindra-chavan-clarification-rm82</t>
+          <t>https://www.news18.com/politics/former-minister-ravindra-chavan-appointed-maharashtra-bjp-working-president-9185878.html</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>महाराष्ट्र लोकल बॉडी चुनावों को लेकर बड़ा अपडेट, बीजेपी, शिंदे और अजित पवार में रहेगा गठबंधन या फिर टूटेगा, जानें</t>
+          <t>कौन बनेगा महाराष्ट्र भाजपा का अध्यक्ष? इस नाम का चुना जाना लगभग तय</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
+          <t>https://www.indiatv.in/maharashtra/maharashtra-ravindra-chavan-set-to-become-new-president-of-state-bjp-said-sources-2025-06-30-1146038</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपने प्रदेशाध्यक्षपद देऊन माझ्यावर उपकार केले, माझी ओळख...; रवींद्र चव्हाणांची पक्षावर स्तुतीसुमने</t>
+          <t>महाराष्ट्र बीजेपी की कमान अब नए हाथों में, जानिए कौन हैं पार्टी के नवनियुक्त प्रदेश अध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-bjp-ravindra-chavan-new-president-ravindra-chavan-speech-latest-marathi-news-pp0731</t>
+          <t>https://www.livemint.com/hindi/trends/maharashtra-bjp-gets-new-state-chief-heres-all-about-newly-appointed-party-president-ravindra-chavan-know-who-is-he-241751382375965.html</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>अशोक चव्हाण यांचा आत्मविश्वास ढासळला, नांदेडमधील काँग्रेस नेत्यांची भाजपावर टीका</t>
+          <t>Ravindra Chavan Set to Become New Chief of Maharashtra BJP</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/bjp-mp-ashok-chavan-meeting-leaders-shows-shaken-confidence-said-congress-mp-ravindra-chavan-sud-02-5112129/</t>
+          <t>https://www.asianage.com/nation/ravindra-chavan-set-to-become-new-chief-of-maharashtra-bjp-1888548</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>Kunal Patil News: शिवसेना उद्धव ठाकरे, काँग्रेसला धुळ्यात भाजप एकाच वेळी धक्का देण्याच्या तयारीत?</t>
+          <t>पूर्व मंत्री रवींद्र चव्हाण बने महाराष्ट्र BJP के कार्यकारी प्रदेश अध्यक्ष, बावनकुले की कुर्सी छिनी</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/kunal-patil-politics-congress-leader-kunal-patil-shiv-senas-shubhangi-patil-are-on-the-path-to-bjp-sd67</t>
+          <t>https://www.tv9hindi.com/state/maharashtra/former-minister-ravindra-chavan-appointed-working-president-of-maharashtra-bjp-3054565.html</t>
         </is>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>Kedar Jadhav : केदार जाधव क्रिकेटच्या मैदानातून राजकीय आखाड्यात, भाजपमध्ये प्रवेश करणार,</t>
+          <t>महाराष्ट्र BJP को मिलेगा नया चेहरा; चंद्रशेखर बावनकुले के बाद रवींद्र चव्हाण का नाम सबसे आगे, रिजिजू की निगरानी में होगा ऐलान</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
+          <t>https://sudarshannews.in/news-detail.aspx?id=129159</t>
         </is>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>कुंडमळा पुलासाठी आठ कोटी मंजूर, सही ८० हजाराच्या पत्रावर…, संजय राऊत यांचा रवींद्र चव्हाण...</t>
+          <t>हेमंत खंडेलवाल होंगे मध्य प्रदेश बीजेपी के नए अध्यक्ष, रवींद्र चव्हाण को महाराष्ट्र की कमान</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/maharashtra/mumbai/shiv-sena-ubt-leader-sanjay-raut-criticizes-minister-ravindra-chavan-1424686.html</t>
+          <t>https://ndtv.in/india/hemant-khandelwal-will-be-the-new-president-of-madhya-pradesh-bjp-8808221</t>
         </is>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>स्थानिक नेत्यांशी चर्चा करुन अन्य पक्षातील नेत्यांना प्रवेश देणार; सरकारला पक्षसंघटनेचे पाठबळ देणार,भाजप नवे प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
+          <t>भारतीय जनता पार्टीचे नवे प्रदेशाध्यक्ष म्हणून रवींद्र चव्हाण यांची बिनविरोध निवड</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/newly-appointed-state-president-ravindra-chavan-stated-while-talking-to-loksatta-print-politics-news-phm-00-5196663/</t>
+          <t>https://www.newsonair.gov.in/mr/ravindra-chavan-elected-unopposed-as-new-state-president-of-bharatiya-janata-party/</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>पुण्यासह पश्चिम महाराष्ट्रावर भाजपचे लक्ष; प्रदेशाध्यक्षांनी पदाधिकाऱ्यांना काय दिल्या सूचना?…</t>
+          <t>महाराष्ट्र लोकल बॉडी चुनावों को लेकर बड़ा अपडेट, बीजेपी, शिंदे और अजित पवार में रहेगा गठबंधन या फिर टूटेगा, जानें</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-local-body-elections-bjp-likely-to-contest-alone-amid-mumbai-bmc-polls-with-eknath-shinde-and-ajit-pawar-amit-shah-ravindra-chavan-meet/articleshow/122897869.cms</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President Announcement : भाजपचं ठरलं! प्रदेशाध्यक्षाची लवकरच घोषणा; मुंबई अध्यक्षपदासाठी 'ही' तीन नावे चर्चेत</t>
+          <t>Ravindra Chavan News : मंत्रिमंडळात मोठे फेरबदल, 8 जणांना डच्चू मिळणार का? अखेर रवींद्र चव्हाण यांनीच केलं क्लिअर</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/bjp-to-announce-maharashtra-president-soon-3-names-in-contention-for-mumbai-post-sw79</t>
+          <t>https://sarkarnama.esakal.com/mumbai/maharashtra-cabinet-reshuffle-2025-ministers-remove-ravindra-chavan-clarification-rm82</t>
         </is>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>मोदी सरकारच्या अकरा वर्षाच्या काळात २५ कोटी कुटुंबं दारिद्र्य रेषेबाहेर; रवींद्र चव्हाण यांची माहिती</t>
+          <t>Ravindra Chavan : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड, काय आहे समीकरण?</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
+          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
         </is>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>महापालिका निवडणूक स्वबळावर लढणार? रवींद्र चव्हाणांनी स्पष्टच सांगितलं; म्हणाले- देवेंद्र फडणवीसांच्या आदेशानुसारच...</t>
+          <t>Ravindra Chavan : भाजपने प्रदेशाध्यक्षपद देऊन माझ्यावर उपकार केले, माझी ओळख...; रवींद्र चव्हाणांची पक्षावर स्तुतीसुमने</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/ravindra-chavan-statement-on-maharashtra-municipal-elections-vru98</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-bjp-ravindra-chavan-new-president-ravindra-chavan-speech-latest-marathi-news-pp0731</t>
         </is>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>भाजपच्या संघटन बांधणीला नवे बळ 963 मंडळ अध्यक्षांच्या नियुक्त्या पूर्ण रवींद्र</t>
+          <t>अशोक चव्हाण यांचा आत्मविश्वास ढासळला, नांदेडमधील काँग्रेस नेत्यांची भाजपावर टीका</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
+          <t>https://www.loksatta.com/maharashtra/bjp-mp-ashok-chavan-meeting-leaders-shows-shaken-confidence-said-congress-mp-ravindra-chavan-sud-02-5112129/</t>
         </is>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>Sanjay Jagtap: संजय जगताप यांचा भाजपमध्ये पक्षप्रवेश आगामी निवडणुकीआधी काँग्रेसला</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण, १ जुलैला घोषणा; किरण रिजिजू निरीक्षक</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
+          <t>https://www.lokmat.com/mumbai/ravindra-chavan-to-be-bjp-maharashtra-state-president-announcement-on-july-1-kiren-rijiju-observer-a-a571/</t>
         </is>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: बीजेपी ने 58 जिला अध्यक्षों के नाम किए घोषित, अब मुंबई अध्यक्ष की बारी, देखें पूरी लिस्ट</t>
+          <t>Kunal Patil News: शिवसेना उद्धव ठाकरे, काँग्रेसला धुळ्यात भाजप एकाच वेळी धक्का देण्याच्या तयारीत?</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/kunal-patil-politics-congress-leader-kunal-patil-shiv-senas-shubhangi-patil-are-on-the-path-to-bjp-sd67</t>
         </is>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>चंद्रशेखर बावनकुळेंकडून स्वीकारली सूत्रे; महापालिका, जिल्हा परिषद निवडणुकीचे आव्हान: फडणवीसांचे निकटवर्तीय ...</t>
+          <t>Ravindra Chavan emotional story: फडणवीस मुख्यमंत्री होणार नसल्याने धक्का बसला, डोळ्यात पाणी आले अन् ...; रवींद्र चव्हाणांनी सांगितला 2022 सालचा किस्सा.....</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/fadnavis-close-aide-ravindra-chavan-becomes-bjp-state-president-accepts-responsibility-from-chandrashekhar-bawankule-challenge-for-municipal-zilla-parishad-elections-135355331.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ravindra-chavan-reveals-2022-twist-emotional-reaction-as-devendra-fadnavis-wasnt-named-cm-sw79</t>
         </is>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
+          <t>Kedar Jadhav : केदार जाधव क्रिकेटच्या मैदानातून राजकीय आखाड्यात, भाजपमध्ये प्रवेश करणार,</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
+          <t>https://marathi.abplive.com/news/maharashtra/kedar-jadhav-to-join-bjp-in-presence-maharashtra-cm-devendra-fadnavis-ravindra-chavan-mumbai-marathi-news-1353247</t>
         </is>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : प्रदेशाध्यक्ष बावनकुळेंच्या जागी रवींद्र चव्हाणांची वर्णी ?</t>
+          <t>कुंडमळा पुलासाठी आठ कोटी मंजूर, सही ८० हजाराच्या पत्रावर…, संजय राऊत यांचा रवींद्र चव्हाण...</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/news/leadership-change-in-maharashtra-bjp-ravindra-chavan-appointed-state-president</t>
+          <t>https://www.tv9marathi.com/maharashtra/mumbai/shiv-sena-ubt-leader-sanjay-raut-criticizes-minister-ravindra-chavan-1424686.html</t>
         </is>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>MCA Election | रवींद्र चव्हाण MCA च्या मैदानात? दिल्ली दौऱ्यानंतर चर्चांना उधाण</t>
+          <t>स्थानिक नेत्यांशी चर्चा करुन अन्य पक्षातील नेत्यांना प्रवेश देणार; सरकारला पक्षसंघटनेचे पाठबळ देणार,भाजप नवे प्रदेशाध्यक्ष रवींद्र चव्हाण यांचे प्रतिपादन</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
+          <t>https://www.loksatta.com/politics/newly-appointed-state-president-ravindra-chavan-stated-while-talking-to-loksatta-print-politics-news-phm-00-5196663/</t>
         </is>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>मुंबई भाजप अध्यक्षपदी अमित साटम: रवींद्र चव्हाण, फडणवीसांनी केली घोषणा; मुंबई महापालिका निवडणुकीच्या तोंडाव...</t>
+          <t>BJP Maharashtra President Announcement : भाजपचं ठरलं! प्रदेशाध्यक्षाची लवकरच घोषणा; मुंबई अध्यक्षपदासाठी 'ही' तीन नावे चर्चेत</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-president-amit-satam-appointed-ahead-bmc-election-135756496.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/bjp-to-announce-maharashtra-president-soon-3-names-in-contention-for-mumbai-post-sw79</t>
         </is>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>भाजपला घमेंडी म्हणणाऱ्यांना शिंदेसेनेचे नेते समज देतील: रवींद्र चव्हाण</t>
+          <t>पुण्यासह पश्चिम महाराष्ट्रावर भाजपचे लक्ष; प्रदेशाध्यक्षांनी पदाधिकाऱ्यांना काय दिल्या सूचना?…</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/chhatrapati-sambhajinagar/shinde-sena-leaders-will-explain-to-those-who-call-bjp-arrogant-ravindra-chavan-a-a320/</t>
+          <t>https://www.loksatta.com/pune/ravindra-chavan-instructed-the-partys-office-bearers-in-western-maharashtra-pune-print-news-phm-00-5234205/</t>
         </is>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>BJP State President | रवींद्र चव्हाण यांची उद्या महाराष्ट्र भाजप प्रदेशाध्यक्षपदी निवड होणार</t>
+          <t>मोदी सरकारच्या अकरा वर्षाच्या काळात २५ कोटी कुटुंबं दारिद्र्य रेषेबाहेर; रवींद्र चव्हाण यांची माहिती</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
+          <t>https://www.etvbharat.com/mr/!state/narendra-modis-government-has-lifted-25-crore-families-out-of-poverty-in-11-years-says-ravindra-chavan-in-press-conference-maharashtra-news-mhs25061203154</t>
         </is>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>मुंबई भाजप अध्यक्षपदाच्या निवडीत मराठी चेहऱ्याला प्राधान्य</t>
+          <t>भाजपच्या संघटन बांधणीला नवे बळ 963 मंडळ अध्यक्षांच्या नियुक्त्या पूर्ण रवींद्र</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/amit-satam-mumbai-bjp-president-devendra-fadnavis-ravindra-chavan-mumbai-municipal-corporation-print-politics-news-ssb-93-5329396/</t>
+          <t>https://marathi.abplive.com/news/politics/maharashtra-politics-new-strength-in-bjp-organizational-building-appointments-of-963-mandal-presidents-completed-by-ravindra-chavan-marathi-news-1355302</t>
         </is>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>Sthanik Swarajya Sanstha :स्थानिक स्वराज्य संस्था निवडणुकांनंतर Ravindra Chavan प्रदेशाध्यक्ष?</t>
+          <t>महापालिका निवडणूक स्वबळावर लढणार? रवींद्र चव्हाणांनी स्पष्टच सांगितलं; म्हणाले- देवेंद्र फडणवीसांच्या आदेशानुसारच...</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-bjp-party-maharashtra-state-president-after-sthanik-swarajya-sanstha-election-chandrashekhar-bawankule-maharashtra-news-12-jan-2025-abp-majha-1338092</t>
+          <t>https://www.esakal.com/maharashtra/ravindra-chavan-statement-on-maharashtra-municipal-elections-vru98</t>
         </is>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : चव्हाण पेलणार का आव्हान!</t>
+          <t>Sanjay Jagtap: संजय जगताप यांचा भाजपमध्ये पक्षप्रवेश आगामी निवडणुकीआधी काँग्रेसला</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
+          <t>https://marathi.abplive.com/news/pune/pune-news-sanjay-jagtap-joins-bjp-ravindra-chavan-s-presence-big-blow-to-congress-before-upcoming-elections-1370379</t>
         </is>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: अखेर प्रतीक्षा संपली! बावनकुळेंनंतर भाजपला नवा धडाकेबाज प्रदेशाध्यक्ष मिळाला</t>
+          <t>Ravindra Chavan BJP : मुंबईहून भाजप कार्याध्यक्षांचा फोन अन् मंडल अध्यक्षाच्या निवडीला स्थगिती; विखे समर्थकाची कोणी केली तक्रार?</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-appointed-bjp-maharashtra-new-president-dk88</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/ahilyanagar-bjp-shevgaon-president-appointment-stalled-ravindra-chavan-order-pp82</t>
         </is>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>प्रसिद्धीपासून दूर, कामगिरीवर भर; भाजप प्रदेशाध्यक्षांचा अनोखा नागपूर दौरा</t>
+          <t>BMC चुनाव से पहले भाजपा का बड़ा दांव, आशीष शेलार को मुंबई अध्यक्ष पद से हटाया, अमित साटम को सौंपी कमान</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/politics/ravindra-chavan-nagpur-visit-keeps-media-in-dark-highlights-bjps-new-low-key-strategy-skips-publicity-focuses-on-groundwork-print-political-news-vsd-99-5252822/</t>
+          <t>https://www.patrika.com/mumbai-news/bjp-remove-ashish-shelar-from-mumbai-president-post-amit-satam-new-chief-before-bmc-election-19891254</t>
         </is>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>Nitesh Rane : राणेंच्या वक्तव्याचा भाजपच्या कार्यकारी अध्यक्षांना फटका... पत्रकार परिषदच गुंडाळण्याची वेळ!</t>
+          <t>MCA Election | रवींद्र चव्हाण MCA च्या मैदानात? दिल्ली दौऱ्यानंतर चर्चांना उधाण</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/nagpur-nitesh-rane-remark-ravindra-chavan-press-conference-disruption-bjp-controversy-hn97-rc70</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-maharashtra-bjp-president-likely-to-contest-mumbai-cricket-association-mca-election-in-november-after-delhi-visit-1374335</t>
         </is>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : महाराष्ट्रात भाजपला मिळाला नवा कॅप्टन; प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची...</t>
+          <t>Ravindra Chavan : प्रदेशाध्यक्ष बावनकुळेंच्या जागी रवींद्र चव्हाणांची वर्णी ?</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
+          <t>https://www.lokshahi.com/news/leadership-change-in-maharashtra-bjp-ravindra-chavan-appointed-state-president</t>
         </is>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : रवींद्र चव्हाण यांचे नाव आज प्रदेशाध्यक्षपदी जाहीर</t>
+          <t>Maharashtra BJP: बीजेपी ने 58 जिला अध्यक्षों के नाम किए घोषित, अब मुंबई अध्यक्ष की बारी, देखें पूरी लिस्ट</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/ravindra-chavan-to-be-announced-as-bjp-maharashtra-state-president-vsb99</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/bjp-maharashtra-annouces-50-district-president-navi-mumbai-rajesh-patil-mira-bhayandar-dilip-jain-check-full-list/articleshow/121136990.cms</t>
         </is>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>Maharashtra BJP: भाजपची मोर्चेबांधणी; स्थानिक निवडणुकांसाठी माजी खासदार, आमदारांची महत्त्वपूर्ण बैठक</t>
+          <t>मुंबई भाजप अध्यक्षपदी अमित साटम: रवींद्र चव्हाण, फडणवीसांनी केली घोषणा; मुंबई महापालिका निवडणुकीच्या तोंडाव...</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-state-president-ravindra-chavan-held-meeting-former-mps-mlas-for-preparation-upcoming-local-body-elections/articleshow/123032835.cms</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/mumbai-bjp-president-amit-satam-appointed-ahead-bmc-election-135756496.html</t>
         </is>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>BJP President : भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण निश्चित; मुंबई अध्यक्षपदी दरेकर शक्य</t>
+          <t>BJP State President | रवींद्र चव्हाण यांची उद्या महाराष्ट्र भाजप प्रदेशाध्यक्षपदी निवड होणार</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-president-ravindra-chavan-and-pravin-darekar-mumbai-president-politics-pjp78</t>
+          <t>https://marathi.abplive.com/videos/news/bjp-maharashtra-ravindra-chavan-set-to-be-elected-as-state-president-unopposed-formal-announcement-expected-tomorrow-1367175</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>डोंबिवलीतील विकास म्हात्रे यांचा भाजपमध्येच मुक्काम; मुख्यमंत्री देवेंद्र फडणवीस, प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घेतली भेट</t>
+          <t>Sthanik Swarajya Sanstha :स्थानिक स्वराज्य संस्था निवडणुकांनंतर Ravindra Chavan प्रदेशाध्यक्ष?</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/vikas-mhatre-from-dombivli-met-chief-minister-devendra-fadnavis-and-state-president-ravindra-chavan-amy-95-5214180/</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavan-bjp-party-maharashtra-state-president-after-sthanik-swarajya-sanstha-election-chandrashekhar-bawankule-maharashtra-news-12-jan-2025-abp-majha-1338092</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>‘एमएमआर’ क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा, प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
+          <t>BJP President : भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण निश्चित; मुंबई अध्यक्षपदी दरेकर शक्य</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/bjps-ravindra-chavan-instructed-mumbai-officials-to-implement-slum-rehabilitation-scheme-effectively-sud-02-4933709/</t>
+          <t>https://www.esakal.com/maharashtra/bjp-president-ravindra-chavan-and-pravin-darekar-mumbai-president-politics-pjp78</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>Municipal Election: पालिका निवडणुकीसाठी भाजपची जय्यत तयारी सुरू, माजी खासदार आणि आमदारांवर सोपवली मोठी जबाबदारी</t>
+          <t>Ravindra Chavan : चव्हाण पेलणार का आव्हान!</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-has-entrusted-responsibility-of-municipal-elections-in-maharashtra-to-former-mps-and-mlas-vru98</t>
+          <t>https://www.mymahanagar.com/editorial/will-ravindra-chavan-meet-the-challenge-of-the-bjp-state-president-in-marathi/898320/</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : साधू महंतांसह भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण श्रीमलंगगडावर</t>
+          <t>प्रसिद्धीपासून दूर, कामगिरीवर भर; भाजप प्रदेशाध्यक्षांचा अनोखा नागपूर दौरा</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/raigad/ravindra-chavan-visits-malanggad-with-sadhus-and-bjp-leaders-ab96</t>
+          <t>https://www.loksatta.com/politics/ravindra-chavan-nagpur-visit-keeps-media-in-dark-highlights-bjps-new-low-key-strategy-skips-publicity-focuses-on-groundwork-print-political-news-vsd-99-5252822/</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>अतुल भोसले सातारा जिल्हा भाजपमय करतील, रवींद्र चव्हाण यांचा विश्वास</t>
+          <t>Maharashtra BJP: अखेर प्रतीक्षा संपली! बावनकुळेंनंतर भाजपला नवा धडाकेबाज प्रदेशाध्यक्ष मिळाला</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/karad-ravindra-chavan-atul-bhosale-satara-bjp-president-vsd-99-5121887/</t>
+          <t>https://sarkarnama.esakal.com/mumbai/ravindra-chavan-appointed-bjp-maharashtra-new-president-dk88</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>Thackeray Shiv Sena Setback | ठाकरे शिवसेनेला मालवण शहरात खिंडार</t>
+          <t>Nitesh Rane : राणेंच्या वक्तव्याचा भाजपच्या कार्यकारी अध्यक्षांना फटका... पत्रकार परिषदच गुंडाळण्याची वेळ!</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/malvan-shiv-sena-defection-bjp-joining-ravindra-chavan-sp96</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/nagpur-nitesh-rane-remark-ravindra-chavan-press-conference-disruption-bjp-controversy-hn97-rc70</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>Ravindra Chavan यांचा शिवसेना उबाठाला धक्का, कामगार संघटनेचे दीड हजार सदस्यांचा भाजपमध्ये प्रवेश..</t>
+          <t>Ravindra Chavan : महाराष्ट्रात भाजपला मिळाला नवा कॅप्टन; प्रदेशाध्यक्षपदी रवींद्र चव्हाण यांची...</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-s-shiv-sena-ubatha-is-in-trouble-1500-members-of-the-workers-union-join-bjp-1051360.html</t>
+          <t>https://www.tv9marathi.com/videos/ravindra-chavan-elected-bjp-maharashtra-president-1436164.html</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>Ravindra Chavan भाजपा हीच माझी ओळख म्हणणारे रवींद्र चव्हाण महाराष्ट्र भाजपच्या प्रदेशाध्यक्षपदी!!</t>
+          <t>Ravindra Chavan : रवींद्र चव्हाण यांचे नाव आज प्रदेशाध्यक्षपदी जाहीर</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
+          <t>https://www.esakal.com/mumbai/ravindra-chavan-to-be-announced-as-bjp-maharashtra-state-president-vsb99</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : पुण्यात भाजपची ताकद वाढली, काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश</t>
+          <t>Maharashtra BJP: भाजपची मोर्चेबांधणी; स्थानिक निवडणुकांसाठी माजी खासदार, आमदारांची महत्त्वपूर्ण बैठक</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/video/maharashtra-politics-congress-leader-sanjay-jagtap-joins-bjp-in-pune-in-presence-of-state-president-ravindra-chavan-latest-marathi-news-yps99</t>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/bjp-state-president-ravindra-chavan-held-meeting-former-mps-mlas-for-preparation-upcoming-local-body-elections/articleshow/123032835.cms</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: ऑपरेशन एकनाथ शिंदेंमध्ये मोठी जबाबदारी ते फडणवीस मुख्यमंत्री होणार नाहीत</t>
+          <t>‘एमएमआर’ क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा, प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
+          <t>https://www.loksatta.com/thane/bjps-ravindra-chavan-instructed-mumbai-officials-to-implement-slum-rehabilitation-scheme-effectively-sud-02-4933709/</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan: रवींद्र चव्हाण बनले महाराष्ट्र भाजपचे कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा यांची घोषणा Who is Ravindra Chavan Ravindra Chavan becomes the working president of Maharashtra BJP Natio</t>
+          <t>डोंबिवलीतील विकास म्हात्रे यांचा भाजपमध्येच मुक्काम; मुख्यमंत्री देवेंद्र फडणवीस, प्रदेशाध्यक्ष रवींद्र चव्हाण यांची घेतली भेट</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
+          <t>https://www.loksatta.com/thane/vikas-mhatre-from-dombivli-met-chief-minister-devendra-fadnavis-and-state-president-ravindra-chavan-amy-95-5214180/</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण ; सावंतवाडीत कार्यकर्त्यांचा जल्लोष</t>
+          <t>Municipal Election: पालिका निवडणुकीसाठी भाजपची जय्यत तयारी सुरू, माजी खासदार आणि आमदारांवर सोपवली मोठी जबाबदारी</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
+          <t>https://www.esakal.com/maharashtra/bjp-state-president-ravindra-chavan-has-entrusted-responsibility-of-municipal-elections-in-maharashtra-to-former-mps-and-mlas-vru98</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>Ravindra Chavan : भाजपच्या कार्यकारी प्रदेश अध्यक्षपदी रवींद्र चव्हाण यांची निवड, काय आहे समीकरण?</t>
+          <t>Ravindra Chavan : साधू महंतांसह भाजपा प्रदेश अध्यक्ष रवींद्र चव्हाण श्रीमलंगगडावर</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>https://marathi.hindustantimes.com/maharashtra/ravindra-chavan-elected-as-bjp-working-state-president-why-bjp-gave-responsibility-141736618335892.html</t>
+          <t>https://pudhari.news/maharashtra/raigad/ravindra-chavan-visits-malanggad-with-sadhus-and-bjp-leaders-ab96</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>Local elections | स्थानिक निवडणुका महायुतीत लढू, कार्यकर्त्यांचाही विचार : रवींद्र चव्हाण</t>
+          <t>Thackeray Shiv Sena Setback | ठाकरे शिवसेनेला मालवण शहरात खिंडार</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-mahayuti-to-contest-local-elections-ab96</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/malvan-shiv-sena-defection-bjp-joining-ravindra-chavan-sp96</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>Ravindra Chavan भाजपमध्ये पक्ष प्रवेशांचा धडाका, लातूर धाराशिव अमरावतीमधील पदाधिकाऱ्यांचा पक्षप्रवेश</t>
+          <t>अतुल भोसले सातारा जिल्हा भाजपमय करतील, रवींद्र चव्हाण यांचा विश्वास</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
+          <t>https://www.loksatta.com/maharashtra/karad-ravindra-chavan-atul-bhosale-satara-bjp-president-vsd-99-5121887/</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>BJP Expansion Strategy: पक्षविस्तार की सत्तेसाठीची तडजोड?</t>
+          <t>Ravindra Chavan यांचा शिवसेना उबाठाला धक्का, कामगार संघटनेचे दीड हजार सदस्यांचा भाजपमध्ये प्रवेश..</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/bjp-expansion-or-power-compromise-maharashtra-politics-chandrasekhar-bawankule-ravindra-chavan-devendra-fadnavis-mm76</t>
+          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-s-shiv-sena-ubatha-is-in-trouble-1500-members-of-the-workers-union-join-bjp-1051360.html</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>Nitesh Rane Statement | नितेश राणे यांच्या विधानामुळे भाजपची कोंडी, रवींद्र चव्हाण यांनी गुंडाळली पत्रकार परिषद</t>
+          <t>Maharashtra Politics : पुण्यात भाजपची ताकद वाढली, काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nitesh-rane-statement-puts-bjp-in-spotlight-ravindra-chavan-cancels-press-meet-sk95</t>
+          <t>https://saamtv.esakal.com/video/maharashtra-politics-congress-leader-sanjay-jagtap-joins-bjp-in-pune-in-presence-of-state-president-ravindra-chavan-latest-marathi-news-yps99</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
+          <t>Ravindra Chavan भाजपा हीच माझी ओळख म्हणणारे रवींद्र चव्हाण महाराष्ट्र भाजपच्या प्रदेशाध्यक्षपदी!!</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
+          <t>https://thefocusindia.com/maharashtra-news/ravindra-chavan-state-president-of-maharashtra-bjp-who-says-bjp-is-my-identity-276739/amp/</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>Nanded News : जिल्ह्यातील शेतकऱ्यांच्या खात्यावर विम्याची रक्कम लवकरच जमा होणार</t>
+          <t>Ravindra Chavan: ऑपरेशन एकनाथ शिंदेंमध्ये मोठी जबाबदारी ते फडणवीस मुख्यमंत्री होणार नाहीत</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/insurance-amount-will-be-deposited-in-the-accounts-of-farmers-in-the-district-soon-np88</t>
+          <t>https://marathi.abplive.com/news/politics/operation-eknath-shinde-had-a-big-responsibility-he-said-that-fadnavis-would-not-become-the-chief-minister-so-he-had-tears-in-his-eyes-story-told-by-ravindra-chavan-1369426</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>भाजपचे कार्याध्यक्ष रवींद्र चव्हाण शनिवारी बीड दौऱ्यावर</t>
+          <t>Who Is Ravindra Chavan: रवींद्र चव्हाण बनले महाराष्ट्र भाजपचे कार्याध्यक्ष, राष्ट्रीय अध्यक्ष जेपी नड्डा यांची घोषणा Who is Ravindra Chavan Ravindra Chavan becomes the working president of Maharashtra BJP Natio</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/aurangabad/bjp-leader-ravindra-chavan-beed-tour-condolence-visit-vsd-99-5123945/</t>
+          <t>https://www.marathijagran.com/maharashtra/mumbai/who-is-ravindra-chavan-ravindra-chavan-becomes-the-working-president-of-maharashtra-bjp-national-president-jp-nadda-announced-50716</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>Maharashtra Politics : काँग्रेसला राज्यात मोठा हादरा, बड्या नेत्याने केला भाजपमध्ये प्रवेश</t>
+          <t>भाजप प्रदेशाध्यक्षपदी रवींद्र चव्हाण ; सावंतवाडीत कार्यकर्त्यांचा जल्लोष</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-congress-leader-kailas-gorantyal-quits-party-and-joins-bjp-in-presence-of-ravindra-chavan-jalna-strongman-switches-sides-yps99</t>
+          <t>https://www.tarunbharat.com/ravindra-chavan-appointed-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>कल्याण डोंबिवली क्षेत्रात झोपडपट्टी पुनर्वसन योजना प्रभावीपणे राबवा – भाजप प्रदेश कार्याध्यक्ष रवींद्र चव्हाण</t>
+          <t>Sangli News: सांगलीत डिनर डिप्लोमोसी अन् बंद दाराआड चर्चा पृथ्वीराज पाटलांनी शेवटी</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>https://www.localnewsnetwork.in/implement-slum-rehabilitation-scheme-effectively-in-kalyan-dombivali-area-bjp-state-working-president-ravindra-chavan/</t>
+          <t>https://marathi.abplive.com/news/sangli/dinner-diplomacy-and-closed-door-discussions-in-sangli-pruthviraj-patil-finally-leaves-congress-city-district-president-position-he-will-joining-bjp-tomorrow-ravindra-chavan-chandrakant-patil-1376602</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>प्रत्येकाच्या मनात ‘कमळ’ रुजले पाहिजे</t>
+          <t>Local elections | स्थानिक निवडणुका महायुतीत लढू, कार्यकर्त्यांचाही विचार : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/pune/bjp-leader-ravindra-chavan-urges-lotus-must-bloom-in-every-heart-pune-print-news-ocd-94-5167946/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/ravindra-chavan-mahayuti-to-contest-local-elections-ab96</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President | रवींद्र चव्हाण भाजपचे बारावे महाराष्ट्र प्रदेशाध्यक्ष होणार</t>
+          <t>BJP Expansion Strategy: पक्षविस्तार की सत्तेसाठीची तडजोड?</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/bjp-expansion-or-power-compromise-maharashtra-politics-chandrasekhar-bawankule-ravindra-chavan-devendra-fadnavis-mm76</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>भाजप लोकल बॉडीची निवडणूक स्वबळावर लढणार: पण मुंबईसाठी घेणार शिंदे, दादांची मदत; रवींद्र चव्हाण यांनी घेतली ...</t>
+          <t>Ravindra Chavan भाजपमध्ये पक्ष प्रवेशांचा धडाका, लातूर धाराशिव अमरावतीमधील पदाधिकाऱ्यांचा पक्षप्रवेश</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
         <is>
-          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-bjp-local-body-election-strategy-mumbai-alliance-shinde-ajit-pawar-135526240.html</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-party-joining-key-congress-and-thackeray-shiv-sena-office-bearers-join-bjp-in-maharashtra-under-ravindra-chavan-s-leadership-1374978</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>BJP Maharashtra President | १ जुलैला रवींद्र चव्हाणांच्या नावाची घोषणा, भाजपचं जोरदार शक्तिप्रदर्शन</t>
+          <t>Nanded News : जिल्ह्यातील शेतकऱ्यांच्या खात्यावर विम्याची रक्कम लवकरच जमा होणार</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
+          <t>https://pudhari.news/maharashtra/marathwada/nanded/insurance-amount-will-be-deposited-in-the-accounts-of-farmers-in-the-district-soon-np88</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>Sanjay Raut : सही करताना झोपेत असतात का? राऊतांचा रवींद्र चव्हाणांवर घणाघात</t>
+          <t>Nitesh Rane Statement | नितेश राणे यांच्या विधानामुळे भाजपची कोंडी, रवींद्र चव्हाण यांनी गुंडाळली पत्रकार परिषद</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/sanjay-raut-slams-ravindra-chavan-over-indrayani-river-bridge-collapse-accident-1424794.html</t>
+          <t>https://pudhari.news/maharashtra/vidarbha/nagpur/nitesh-rane-statement-puts-bjp-in-spotlight-ravindra-chavan-cancels-press-meet-sk95</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाणांचे शुभेच्छा देणार बॅनर फाडले</t>
+          <t>भाजपचे कार्याध्यक्ष रवींद्र चव्हाण शनिवारी बीड दौऱ्यावर</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-banners-wishing-ravindra-chavan-were-torn-1062422.html</t>
+          <t>https://www.loksatta.com/aurangabad/bjp-leader-ravindra-chavan-beed-tour-condolence-visit-vsd-99-5123945/</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>Maharashtra BJP President: रवींद्र चव्हाण यांच्यासमोर स्थानिक स्वराज्य संस्थांच्या निवडणुकांचे आव्हान</t>
+          <t>Maharashtra Politics : काँग्रेसला राज्यात मोठा हादरा, बड्या नेत्याने केला भाजपमध्ये प्रवेश</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-congress-leader-kailas-gorantyal-quits-party-and-joins-bjp-in-presence-of-ravindra-chavan-jalna-strongman-switches-sides-yps99</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>Ratnagiri BJP election : रवींद्र चव्हाणांच्या शब्दाला मान; रत्नागिरीत निकटवर्तीयांना संधी, सावंतांची फेर निवड</t>
+          <t>BJP Maharashtra President | रवींद्र चव्हाण भाजपचे बारावे महाराष्ट्र प्रदेशाध्यक्ष होणार</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-appoints-rajesh-sawant-and-satish-more-close-aides-of-party-vice-president-ravindra-chavan-as-district-presidents-for-south-and-north-ratnagiri-as11</t>
+          <t>https://marathi.abplive.com/videos/news/maharashtra-ravindra-chavhan-to-become-12th-bjp-maharashtra-state-president-succeeding-a-long-line-of-leaders-in-party-s-45-year-history-1366862</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>Jan Suraksha Bill : ‘जनसुरक्षे’मुळे विकासमार्ग खुला; प्रकल्पांना विरोध डाव्यांकडून : भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
+          <t>भाजप लोकल बॉडीची निवडणूक स्वबळावर लढणार: पण मुंबईसाठी घेणार शिंदे, दादांची मदत; रवींद्र चव्हाण यांनी घेतली ...</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/maharashtra/jan-suraksha-bill-will-pave-way-for-development-ravindra-chavan-amp17</t>
+          <t>https://divyamarathi.bhaskar.com/local/maharashtra/mumbai/news/maharashtra-bjp-local-body-election-strategy-mumbai-alliance-shinde-ajit-pawar-135526240.html</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Exclusive : ठाकरे बंधूंची युती ते BMC मध्ये भाजपचा महापौर? भाजपच्या नव्या...</t>
+          <t>प्रत्येकाच्या मनात ‘कमळ’ रुजले पाहिजे</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
+          <t>https://www.loksatta.com/pune/bjp-leader-ravindra-chavan-urges-lotus-must-bloom-in-every-heart-pune-print-news-ocd-94-5167946/</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>‘कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाशाला बेघर होऊ देणार नाही’ - आमदार रवींद्र चव्हाण</t>
+          <t>BJP Maharashtra President | १ जुलैला रवींद्र चव्हाणांच्या नावाची घोषणा, भाजपचं जोरदार शक्तिप्रदर्शन</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/kalyan-dombivli/not-a-single-resident-of-the-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-says-mla-ravindra-chavan-a-a653/</t>
+          <t>https://marathi.abplive.com/videos/news/politics-bjp-to-announce-ravindra-chavan-as-maharashtra-state-president-on-july-1-massive-party-gathering-planned-1366858</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>महापालिका निवडणुका महायुती एकत्र लढणार? नवे प्रदेशाध्यक्ष काय म्हणाले?; महापौरपदाबाबतही मोठं विधान</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाणांचे शुभेच्छा देणार बॅनर फाडले</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/mahayuatis-election-strategy-bjps-chavan-announces-joint-municipal-polls-contests-1444009.html</t>
+          <t>https://lokmat.news18.com/videos/maharashtra/ravindra-chavan-banners-wishing-ravindra-chavan-were-torn-1062422.html</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
+          <t>Ratnagiri BJP election : रवींद्र चव्हाणांच्या शब्दाला मान; रत्नागिरीत निकटवर्तीयांना संधी, सावंतांची फेर निवड</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-appoints-rajesh-sawant-and-satish-more-close-aides-of-party-vice-president-ravindra-chavan-as-district-presidents-for-south-and-north-ratnagiri-as11</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
+          <t>Maharashtra BJP President: रवींद्र चव्हाण यांच्यासमोर स्थानिक स्वराज्य संस्थांच्या निवडणुकांचे आव्हान</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
+          <t>https://marathi.abplive.com/videos/news/ravindra-chavan-unanimously-elected-maharashtra-bjp-president-faces-local-body-election-challenges-1367369</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>मोठी बातमी: BMC निवडणुकीआधी फडणवीसांनी डाव टाकला; भाजपकडून मुंबईत नव्या अध्यक्षाची घोषणा</t>
+          <t>Jan Suraksha Bill : ‘जनसुरक्षे’मुळे विकासमार्ग खुला; प्रकल्पांना विरोध डाव्यांकडून : भाजप प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/devendra-fadnavis-big-announcement-from-bjp-amit-satam-elected-as-mumbai-city-president/articleshow/123494762.cms</t>
+          <t>https://www.esakal.com/maharashtra/jan-suraksha-bill-will-pave-way-for-development-ravindra-chavan-amp17</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>घराण्याची 75 वर्षाची निष्ठा संपली… अखेर काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश, खान्देशात...</t>
+          <t>Ravindra Chavan Exclusive : ठाकरे बंधूंची युती ते BMC मध्ये भाजपचा महापौर? भाजपच्या नव्या...</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>https://www.tv9marathi.com/politics/big-blow-for-congress-in-khandesh-ex-mla-kunal-patil-join-bjp-1436092.html</t>
+          <t>https://www.tv9marathi.com/videos/bjp-ravindra-chavan-on-thackeray-brothers-alliance-mahayuti-bmc-election-strategy-hindi-marathi-controversy-1444066.html</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>BJP में शामिल हुए प्रदेश कांग्रेस सचिव दिलीप भालेराव, रवींद्र चव्हाण ने किया स्वागत</t>
+          <t>‘कल्याण-डोंबिवलीतील ६५ इमारतींमधील एकाही रहिवाशाला बेघर होऊ देणार नाही’ - आमदार रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/state-congress-secretary-dilip-bhalerao-joined-bjp-maharashtra-nikay-chunav-1308763.html</t>
+          <t>https://www.lokmat.com/kalyan-dombivli/not-a-single-resident-of-the-65-buildings-in-kalyan-dombivli-will-be-allowed-to-become-homeless-says-mla-ravindra-chavan-a-a653/</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>भाजपा संगठन चुनाव: महाराष्ट्र में रवींद्र चव्हाण , उत्तराखंड में महेंद्र भट्ट; जानें MP में कौन होगा BJP...</t>
+          <t>कल्याण-डोंबिवली परिसर भाजपमय करा, पालिकेवर भाजपचा महापौर बसवा, रवींद्र चव्हाण यांचे कार्यकर्त्यांना आवाहन</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/national/bjp-state-president-elections-ravindra-chavan-mahendra-bhatt-634968</t>
+          <t>https://www.loksatta.com/thane/bjp-state-president-ravindra-chavan-s-appeal-to-party-workers-to-work-for-bjp-mayor-in-kdmc-zws-70-5277354/</t>
         </is>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, जानें कौन हैं | Hari Bhoomi</t>
+          <t>महापालिका निवडणुका महायुती एकत्र लढणार? नवे प्रदेशाध्यक्ष काय म्हणाले?; महापौरपदाबाबतही मोठं विधान</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>https://www.haribhoomi.com/state-local/maharastra/ravindra-chavan-appointed-maharashtra-bjp-president-635140</t>
+          <t>https://www.tv9marathi.com/politics/mahayuatis-election-strategy-bjps-chavan-announces-joint-municipal-polls-contests-1444009.html</t>
         </is>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>कांग्रेस के पूर्व मंत्री वरपुडकर बने भाजपाई, रवींद्र चव्हाण ने किया स्वागत</t>
+          <t>स्थानिक स्वराज्य संस्था निवडणुकीत जनता भाजपसोबत राहील : रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/parbhani-senior-congress-leader-suresh-varpudkar-joined-bjp-1300751.html</t>
+          <t>https://pudhari.news/maharashtra/sangali/sangli-local-body-elections-ravindra-chavan-bjp-support-dc95</t>
         </is>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>Who Is Ravindra Chavan: देवेंद्र फडणवीसांचे विश्वासू रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष! एकमताने निवड</t>
+          <t>कोण आहेत भाजपचे नवे प्रदेशाध्यक्ष रवींद्र चव्हाण</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
+          <t>https://marathi.abplive.com/web-stories/politics/who-is-bharatiya-janata-party-state-president-of-maharashtra-ravindra-chavan-bjp-1367338</t>
         </is>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
+          <t>घराण्याची 75 वर्षाची निष्ठा संपली… अखेर काँग्रेसच्या बड्या नेत्याचा भाजपमध्ये प्रवेश, खान्देशात...</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
+          <t>https://www.tv9marathi.com/politics/big-blow-for-congress-in-khandesh-ex-mla-kunal-patil-join-bjp-1436092.html</t>
         </is>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
         <is>
-          <t>Maharashtra News Highlights : भाजपाला मिळणार नवा प्रदेशाध्यक्ष, रविंद्र चव्हाणांनी भरला अर्ज, मंगळवारी होणार अधिकृत घोषणा</t>
+          <t>महापालिका निवडणुकीआधी उद्धव ठाकरे गटाला भाजपाचा मोठा धक्का, कोकणातील नगरसेवकांसह शेकडो कार्यकर्त्यांचा...</t>
         </is>
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
+          <t>https://www.tv9marathi.com/maharashtra/uddhav-thackeray-shiv-sena-suffers-major-blow-key-malvan-councilors-join-bjp-political-landscape-1445255.html</t>
         </is>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
         <is>
-          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
+          <t>BJP में शामिल हुए प्रदेश कांग्रेस सचिव दिलीप भालेराव, रवींद्र चव्हाण ने किया स्वागत</t>
         </is>
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
+          <t>https://navbharatlive.com/maharashtra/state-congress-secretary-dilip-bhalerao-joined-bjp-maharashtra-nikay-chunav-1308763.html</t>
         </is>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
+          <t>भाजपा संगठन चुनाव: महाराष्ट्र में रवींद्र चव्हाण , उत्तराखंड में महेंद्र भट्ट; जानें MP में कौन होगा BJP...</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
+          <t>https://www.haribhoomi.com/national/bjp-state-president-elections-ravindra-chavan-mahendra-bhatt-634968</t>
         </is>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
+          <t>Ravindra Chavan: रवींद्र चव्हाण बने महाराष्ट्र बीजेपी अध्यक्ष, जानें कौन हैं | Hari Bhoomi</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>https://english.metrovaartha.com/news/states/ex-minister-ravindra-chavan-is-bjps-new-maharashtra-unit-chief</t>
+          <t>https://www.haribhoomi.com/state-local/maharastra/ravindra-chavan-appointed-maharashtra-bjp-president-635140</t>
         </is>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
         <is>
-          <t>Proud Of Hindi, No Red Carpet For English, Says Maharashtra CM Devendra Fadnavis (VIDEO)</t>
+          <t>कांग्रेस के पूर्व मंत्री वरपुडकर बने भाजपाई, रवींद्र चव्हाण ने किया स्वागत</t>
         </is>
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/proud-of-hindi-no-red-carpet-for-english-says-maharashtra-cm-devendra-fadnavis-video</t>
+          <t>https://navbharatlive.com/maharashtra/parbhani-senior-congress-leader-suresh-varpudkar-joined-bjp-1300751.html</t>
         </is>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>Ahmedabad Plane Crash: Air India Crew Member And Travel Influencer Roshni Songhare Among Victims</t>
+          <t>Who Is Ravindra Chavan: देवेंद्र फडणवीसांचे विश्वासू रवींद्र चव्हाण भाजपचे नवे प्रदेशाध्यक्ष! एकमताने निवड</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>https://www.thedailyjagran.com/entertainment/news/ahmedabad-plane-crash-air-india-crew-member-and-travel-influencer-roshni-songhare-among-victims-photos-videos-10244818</t>
+          <t>https://marathi.timesnownews.com/maharashtra/who-is-ravindra-chavan-devendra-fadnavis-confidant-ravindra-chavan-elected-as-bjps-new-state-president-article-152194052</t>
         </is>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>Bodies of Pahalgam terror attack victims reach Maharashtra: CM Fadnavis offers final respect to 6 victims b...</t>
+          <t>रवींद्र चव्हाण, चंद्रकांत पाटलांच्या उपस्थितीत निलेश देसाईंचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
+          <t>https://maharashtranews1.com/Nilesh-Desai-joins-BJP-in-the-presence-of-Ravindra-Chavhan-and-Chandrakant-Patil-</t>
         </is>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>महाराष्ट्र के शिरडी में BJP का दो दिवसीय अधिवेशन शुरू, अगले प्रदेश अध्यक्ष की हो सकती है घोषणा,जानें कौन आगे</t>
+          <t>Ravindra Chavan : भाजपचे प्रदेश कार्यकारी अध्यक्ष होताच रवींद्र चव्हाण अनवाणी पायाने</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
+          <t>https://marathi.abplive.com/news/politics/ravindra-chavan-visited-sai-baba-in-shirdi-after-being-appointed-as-state-executive-president-of-bjp-maharashtra-marathi-news-1338130</t>
         </is>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>जनवरी में UP-MP समेत 7 राज्यों में भाजपा अध्यक्ष बदलेंगे: नया राष्ट्रीय अध्यक्ष फरवरी तक, 15 जनवरी तक 50% र...</t>
+          <t>Maharashtra Breaking News LIVE : दिवसभरातील महत्त्वाच्या घडामोडी, ब्रेकिंग न्यूज एका क्लिकवर</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>https://www.bhaskar.com/national/news/bjp-organizational-election-meeting-2024-update-134203814.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-corona-update-rain-update-monsoon-ajchya-thalak-batmya-on-july-01-political-news-in-marathi-919652</t>
         </is>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>रविंद्र जडेजा का बिहार से क्या रिश्ता? 'क्रिकेट गुरु' महेंद्र सिंह चौहान से महेंद्र सिंह धोनी तक का सफर</t>
+          <t>Maharashtra News Highlights : भाजपाला मिळणार नवा प्रदेशाध्यक्ष, रविंद्र चव्हाणांनी भरला अर्ज, मंगळवारी होणार अधिकृत घोषणा</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
+          <t>https://www.loksatta.com/maharashtra/maharashtra-news-live-30-june-maharashtra-assembly-monsoon-session-2025-of-the-legislature-begins-today-mahayuti-government-devendra-fadanvis-ajit-pawar-eknath-shinde-gkt-96-5192359/</t>
         </is>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा के नए बॉस बने रवींद्र चौहान, जानिए कौन हैं निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
+          <t>Ashish Shelar : भाजपच्या शिलेदारांचा कोकणावर पकड मजबूत करण्याचा इरादा; रवींद्र चव्हाणांसह आशिष शेलारही सक्रिय</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/state/mumbai/politician-becomes-new-boss-of-maharashtra-bjp-know-who-is-the-president-ravindra-chauhan/1240488/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/ministers-ravindra-chavan-and-ashish-shelars-tour-of-konkan-to-strengthen-bjp-in-the-region-as11</t>
         </is>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>Air India Plane Crash: प्लेन की क्रू मेंबर का निधन, रोशनी सोंघरे की विमान हादसे में गई जान</t>
+          <t>मुंबई भाजप अध्यक्षपदाच्या निवडीत मराठी चेहऱ्याला प्राधान्य</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
+          <t>https://www.loksatta.com/politics/amit-satam-mumbai-bjp-president-devendra-fadnavis-ravindra-chavan-mumbai-municipal-corporation-print-politics-news-ssb-93-5329396/</t>
         </is>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>कौन हैं IAS अरविंद चौहान? इंसानियत की मिसाल पेश की, यूपी के इस डीएम की हर तरफ हो रही तारीफ</t>
+          <t>Maharashtra: Thousands to be homeless as KDMC plans to raze 51 buildings in Kalyan-Dombivli? Here’s what Fadnavis says</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/photo-gallery-who-is-ias-arvind-chauhan-shamli-dm-sat-on-ground-to-listen-70-year-old-woman-complaint/2813524</t>
+          <t>https://www.livemint.com/news/india/maharashtra-will-thousands-become-homeless-as-kdmc-to-raze-51-illegal-buildings-in-kalyan-dombivli-here-s-what-fadnavi-11739873948354.html</t>
         </is>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>महाराष्ट्र भाजपा अध्यक्ष के लिए रवींद्र चव्हाण का नाम तय! कल 5 बजे होगी घोषणा</t>
+          <t>Ravindra Chavan Named Maharashtra BJP Chief: Fadnavis Loyalist, Savarkar Follower – All About His Meteoric Rise</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/ravindra-chavan-maharashtra-bjp-president-announcement-devendra-fadnavis-1-july-1270075.html</t>
+          <t>https://news.abplive.com/cities/ravindra-chavan-named-maharashtra-bjp-president-fadnavis-loyalist-savarkar-follower-who-is-ravindra-chavan-profile-1784513</t>
         </is>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>तीन प्रदेशों के भाजपा अध्यक्ष तय - Naya India-Hindi News, Latest Hindi News, Breaking News, Hindi Samachar</t>
+          <t>Ex-minister Ravindra Chavan is BJP's new Maharashtra unit chief</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
+          <t>https://english.metrovaartha.com/news/states/ex-minister-ravindra-chavan-is-bjps-new-maharashtra-unit-chief</t>
         </is>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="inlineStr">
         <is>
-          <t>महाराष्ट्र BJP को मिला नया अध्यक्ष, रवींद्र चव्हाण बने प्रदेश प्रमुख</t>
+          <t>Ahmedabad Plane Crash: Air India Crew Member And Travel Influencer Roshni Songhare Among Victims</t>
         </is>
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
+          <t>https://www.thedailyjagran.com/entertainment/news/ahmedabad-plane-crash-air-india-crew-member-and-travel-influencer-roshni-songhare-among-victims-photos-videos-10244818</t>
         </is>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="inlineStr">
         <is>
-          <t>Maharashtra: BJP Leader Ravindra Chavan Appointed As New State President</t>
+          <t>Proud Of Hindi, No Red Carpet For English, Says Maharashtra CM Devendra Fadnavis (VIDEO)</t>
         </is>
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>https://globalgreenews.com/2025/07/02/maharashtra-bjp-leader-ravindra-chavan-appointed-as-new-state-president/</t>
+          <t>https://www.freepressjournal.in/mumbai/proud-of-hindi-no-red-carpet-for-english-says-maharashtra-cm-devendra-fadnavis-video</t>
         </is>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>Former Cricketer Kedar Jadhav Joins BJP</t>
+          <t>Bodies of Pahalgam terror attack victims reach Maharashtra: CM Fadnavis offers final respect to 6 victims b...</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
+          <t>https://www.bhaskarenglish.in/local/maharashtra/news/mumbai-receives-bodies-of-pahalgam-terror-attack-victims-134898349.html</t>
         </is>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>BJP chief in Maharashtra brings MNS union workers into party</t>
+          <t>महाराष्ट्र के शिरडी में BJP का दो दिवसीय अधिवेशन शुरू, अगले प्रदेश अध्यक्ष की हो सकती है घोषणा,जानें कौन आगे</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/bjp-chief-in-maharashtra-brings-mns-union-workers-into-party/articleshow/123367896.cms</t>
+          <t>https://navbharattimes.indiatimes.com/metro/mumbai/politics/maharashtra-bjp-convention-starts-in-shirdi-speculation-fumes-for-new-state-president-know-all/articleshow/117149931.cms</t>
         </is>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>Ahead of civic polls, Maharashtra BJP chief stakes claim for KDMC mayor's post</t>
+          <t>रविंद्र जडेजा का बिहार से क्या रिश्ता? 'क्रिकेट गुरु' महेंद्र सिंह चौहान से महेंद्र सिंह धोनी तक का सफर</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
+          <t>https://navbharattimes.indiatimes.com/state/bihar/patna/ravindra-jadeja-relation-with-bihar-journey-from-mahendra-singh-chauhan-to-dhoni/articleshow/121551590.cms</t>
         </is>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>Ahead of local body polls, BJP finalises names of 22 district presidents</t>
+          <t>महाराष्ट्र भाजपा के नए बॉस बने रवींद्र चौहान, जानिए कौन हैं निर्विरोध चुने गए प्रदेश अध्यक्ष</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/ahead-of-local-body-polls-bjp-finalises-names-of-22-district-presidents/articleshow/121549544.cms</t>
+          <t>https://hindi.news24online.com/state/mumbai/politician-becomes-new-boss-of-maharashtra-bjp-know-who-is-the-president-ravindra-chauhan/1240488/</t>
         </is>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>Former Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
+          <t>Air India Plane Crash: प्लेन की क्रू मेंबर का निधन, रोशनी सोंघरे की विमान हादसे में गई जान</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/mumbai-ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra-23587437</t>
+          <t>https://www.indiatv.in/maharashtra/crew-member-roshni-songhare-died-in-air-india-plane-crash-in-ahmedabad-2025-06-12-1142268</t>
         </is>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
         <is>
-          <t>Ex-Congress MLA Kailas Gorantyal joins BJP ahead of civic polls in Maharashtra</t>
+          <t>कौन हैं IAS अरविंद चौहान? इंसानियत की मिसाल पेश की, यूपी के इस डीएम की हर तरफ हो रही तारीफ</t>
         </is>
       </c>
       <c r="B460" t="inlineStr">
         <is>
-          <t>https://www.msn.com/en-in/news/India/ex-congress-mla-kailas-gorantyal-joins-bjp-ahead-of-civic-polls-in-maharashtra/ar-AA1JFbMn?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://zeenews.india.com/hindi/india/up-uttarakhand/photo-gallery-who-is-ias-arvind-chauhan-shamli-dm-sat-on-ground-to-listen-70-year-old-woman-complaint/2813524</t>
         </is>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="inlineStr">
         <is>
-          <t>BJP holds meeting of former MPs and MLAs ahead of local body polls in Maharashtra</t>
+          <t>महाराष्ट्र भाजपा अध्यक्ष के लिए रवींद्र चव्हाण का नाम तय! कल 5 बजे होगी घोषणा</t>
         </is>
       </c>
       <c r="B461" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/07/31/bes7-mh-bjp-meeting.html</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/ravindra-chavan-maharashtra-bjp-president-announcement-devendra-fadnavis-1-july-1270075.html</t>
         </is>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>Ahead of BMC polls 3-term MLA Ameet Satam named new Mumbai BJP chief</t>
+          <t>तीन प्रदेशों के भाजपा अध्यक्ष तय - Naya India-Hindi News, Latest Hindi News, Breaking News, Hindi Samachar</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/08/25/bom2-mh-mumbai-bjp-satam.html</t>
+          <t>https://www.nayaindia.com/news/bjp-presidents-of-three-states-decided/499890.html</t>
         </is>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>BJP MLA Amit Satam announced as president of Mumbai unit ahead of BMC polls</t>
+          <t>महाराष्ट्र BJP को मिला नया अध्यक्ष, रवींद्र चव्हाण बने प्रदेश प्रमुख</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>https://www.bignewsnetwork.com/news/278530942/bjp-mla-amit-satam-announced-as-president-of-mumbai-unit-ahead-of-bmc-polls</t>
+          <t>https://www.aajtak.in/india/maharashtra/video/maharashtra-bjp-has-a-new-president-ravindra-chavan-has-become-the-state-head-ytvd-2277534-2025-07-02</t>
         </is>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>Maha: Sudhakar Badgujar, who faced charges of 'links' with underworld, joins BJP</t>
+          <t>Maharashtra: BJP Leader Ravindra Chavan Appointed As New State President</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>https://www.thehawk.in/news/india/maha-sudhakar-badgujar-who-faced-charges-of-links-with-underworld-joins-bjp</t>
+          <t>https://globalgreenews.com/2025/07/02/maharashtra-bjp-leader-ravindra-chavan-appointed-as-new-state-president/</t>
         </is>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="inlineStr">
         <is>
-          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
+          <t>Ahead of civic polls, Maharashtra BJP chief stakes claim for KDMC mayor's post</t>
         </is>
       </c>
       <c r="B465" t="inlineStr">
         <is>
-          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
+          <t>https://timesofindia.indiatimes.com/city/thane/ahead-of-civic-polls-maharashtra-bjp-chief-stakes-claim-for-kdmc-mayors-post/articleshow/123077307.cms</t>
         </is>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="inlineStr">
         <is>
-          <t>Over 2,000 IndiGo employees join BJP ahead of BMC elections in Mumbai</t>
+          <t>Former Cricketer Kedar Jadhav Joins BJP</t>
         </is>
       </c>
       <c r="B466" t="inlineStr">
         <is>
-          <t>https://english.varthabharati.in/india/over-2000-indigo-employees-join-bjp-ahead-of-bmc-elections-in-mumbai</t>
+          <t>https://www.ndtv.com/india-news/former-cricketer-kedar-jadhav-joins-bjp-8118085</t>
         </is>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="inlineStr">
         <is>
-          <t>केडीएमसी- डॉ. नानासाहेब धर्माधिकारी प्रतिष्ठान कडून स्वच्छता अभियान</t>
+          <t>Ahead of Thackeray reunion, BJP’s Rane claims Uddhav harassed Raj, blames him for Shiv Sena’s downfall</t>
         </is>
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/3/KDMC-Dr-Nanasaheb-Dharmadhikari-Pratishthan-Cleanliness-Campaign.html</t>
+          <t>https://www.newindianexpress.com/nation/2025/Jul/01/ahead-of-thackeray-reunion-bjps-rane-claims-uddhav-harassed-raj-blames-him-for-shiv-senas-downfall</t>
         </is>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>Pandharpur Wari 2025 | डोंबिवलीहून पंढरपूरला निघाली सायकलने दिंडी</t>
+          <t>Ahead of BMC polls 3-term MLA Ameet Satam named new Mumbai BJP chief</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/thane/pandharpur-wari-2025-dindi-left-for-pandharpur-by-bicycle-from-dombivli-ar84</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/08/25/bom2-mh-mumbai-bjp-satam.html</t>
         </is>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>BJP Confusion Over Sudhakar Badgujar's Induction: Bawankule Unaware of Former Sena (UBT) Leader's Entry</t>
+          <t>BMC Elections 2025: BJP Appoints 3-Term MLA Ameet Satam To Lead Mumbai Unit Ahead of Civic Polls (Watch</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>https://www.deccanherald.com/india/maharashtra/confusion-in-bjp-over-induction-of-ex-sena-ubt-leader-bawankule-unaware-of-move-3589681</t>
+          <t>https://www.latestly.com/india/politics/bmc-elections-2025-bjp-appoints-3-term-mla-ameet-satam-to-lead-mumbai-unit-ahead-of-civic-polls-watch-video-7076183.html</t>
         </is>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>Pune bridge collapse: New bridge sanctioned a year ago but work order came on June 10 | Latest News India - Hindustan Times</t>
+          <t>मुंबईत ‘आयकॉनिक इमारती’ उभारण्यासाठी नवीन धोरण</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/pune-bridge-collapse-new-bridge-sanctioned-a-year-ago-but-work-order-came-on-june-10-101750128084734.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
         </is>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="inlineStr">
         <is>
-          <t>Centre removes Turkish firm Celebi from ground handling work at Mumbai and Delhi airports</t>
+          <t>Hindi language row : ‘हिंदी’वर नवा जीआर; ठाकरेंच्या दणक्यानंतर सरकार ताकही फुंकून पिणार, जाधव समितीला देश पालथा घालावा लागणार...</t>
         </is>
       </c>
       <c r="B471" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/centre-removes-turkish-firm-celebi-from-ground-handling-at-mumbai-airport/articleshow/122106708.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
         </is>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="inlineStr">
         <is>
-          <t>HC upholds BJP MLA’s victory, says ‘honest’ disclosure of second marriage permissible in his community won’t flout rules</t>
+          <t>कोकणात शरद पवारांच्या राष्ट्रवादीत भूकंप! उदय सामंतांना होमग्राऊंडवर नितेश राणेंचा दे धक्का, बडा नेता पळवला</t>
         </is>
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/cities/mumbai/rajendra-gavit-bjp-mla-second-marriage-hc-10086135/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-nitesh-rane-reveals-major-political-defection-in-ratnagiri-as11</t>
         </is>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="inlineStr">
         <is>
-          <t>मुंबईत ‘आयकॉनिक इमारती’ उभारण्यासाठी नवीन धोरण</t>
+          <t>Sharad Pawar NCP : तळ कोकणात राजकीय भूकंप? शरद पवारांना मोठा धक्का! एकमेव नेत्यानेही साथ सोडत केला भाजप प्रवेश</t>
         </is>
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/3/27/eknath-shinde-on-iconic-building-in-Mumbai.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-with-hundreds-of-supporters-major-blow-to-sharad-pawars-ncp-in-konkan-as11</t>
         </is>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>Hindi language row : ‘हिंदी’वर नवा जीआर; ठाकरेंच्या दणक्यानंतर सरकार ताकही फुंकून पिणार, जाधव समितीला देश पालथा घालावा लागणार...</t>
+          <t>उद्धव ठाकरे गटाला मालवणमध्ये भाजपचा मोठा धक्का; तीन नगरसेवकांचा भाजपात प्रवेश</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-trilingual-policy-narendra-jadhav-committee-raj-thackeray-opposition-language-review-rm82</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/thackeray-sena-setback-three-malvan-councilors-join-bjp-mk94</t>
         </is>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>कोकणात शरद पवारांच्या राष्ट्रवादीत भूकंप! उदय सामंतांना होमग्राऊंडवर नितेश राणेंचा दे धक्का, बडा नेता पळवला</t>
+          <t>BJP Politics : रत्नागिरी भाजप जिल्हाध्यक्षपदाच्या रेसमध्ये सावंतासह चौघे; कोणाला मिळणार संधी? नावे झाली पाकिट बंद,धाकधूकही वाढवली</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-nitesh-rane-reveals-major-political-defection-in-ratnagiri-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-south-ratnagiri-district-president-selection-by-state-office-as11</t>
         </is>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>Sharad Pawar NCP : तळ कोकणात राजकीय भूकंप? शरद पवारांना मोठा धक्का! एकमेव नेत्यानेही साथ सोडत केला भाजप प्रवेश</t>
+          <t>कोकणात राजकीय भूकंप! शरद पवारांना जबरदस्त धक्का, बडा नेता भाजपाच्या गळाला</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/prashant-yadav-joins-bjp-with-hundreds-of-supporters-major-blow-to-sharad-pawars-ncp-in-konkan-as11</t>
+          <t>https://saamtv.esakal.com/maharashtra/kokan-political-news-prashant-yadav-to-join-bjp-ahead-of-local-body-elections-says-nitesh-rane-bdk97</t>
         </is>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>उद्धव ठाकरे गटाला मालवणमध्ये भाजपचा मोठा धक्का; तीन नगरसेवकांचा भाजपात प्रवेश</t>
+          <t>BJP Politics : रायगड उत्तरमध्ये जुनाच चेहरा, दक्षिणमध्ये नव्याला संधी; अविनाश कोळी आणि धैर्यशील पाटलांच्या निवडीने भाजपला बळ</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/thackeray-sena-setback-three-malvan-councilors-join-bjp-mk94</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/avinash-koli-and-dhairyashil-patil-appointed-bjp-raigad-district-presidents-north-south</t>
         </is>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>BJP Politics : रत्नागिरी भाजप जिल्हाध्यक्षपदाच्या रेसमध्ये सावंतासह चौघे; कोणाला मिळणार संधी? नावे झाली पाकिट बंद,धाकधूकही वाढवली</t>
+          <t>Eknath Shinde : आजचा दिवस एकनाथ शिंदेंसाठी महत्त्वाचा; ठाण्यात भाजप मोठा धक्का देणार? युतीही तुटणार...</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/bjp-south-ratnagiri-district-president-selection-by-state-office-as11</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/bjp-strategy-meeting-thane-municipal-elections-eknath-shinde-rm89</t>
         </is>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>BJP Politics : रायगड उत्तरमध्ये जुनाच चेहरा, दक्षिणमध्ये नव्याला संधी; अविनाश कोळी आणि धैर्यशील पाटलांच्या निवडीने भाजपला बळ</t>
+          <t>निवडणुकांची तयारी, भाजपने भाकरी फिरवली राज्यात 58 जिल्हाध्यक्षांची नवी यादी</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/avinash-koli-and-dhairyashil-patil-appointed-bjp-raigad-district-presidents-north-south</t>
+          <t>https://marathi.abplive.com/news/politics/bjp-new-list-of-58-district-presidents-announced-in-the-state-with-mumbai-preparations-for-elections-devendra-fadnavis-chandrashekhar-bawankule-marathi-news-1358929</t>
         </is>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>Eknath Shinde : आजचा दिवस एकनाथ शिंदेंसाठी महत्त्वाचा; ठाण्यात भाजप मोठा धक्का देणार? युतीही तुटणार...</t>
+          <t>Ravindra Chavan यांची भाजपाच्या प्रदेशाध्यक्षपदी निवड</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/bjp-strategy-meeting-thane-municipal-elections-eknath-shinde-rm89</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
         </is>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>निवडणुकांची तयारी, भाजपने भाकरी फिरवली राज्यात 58 जिल्हाध्यक्षांची नवी यादी</t>
+          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>https://marathi.abplive.com/news/politics/bjp-new-list-of-58-district-presidents-announced-in-the-state-with-mumbai-preparations-for-elections-devendra-fadnavis-chandrashekhar-bawankule-marathi-news-1358929</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
         </is>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>Ravindra Chavan यांची भाजपाच्या प्रदेशाध्यक्षपदी निवड</t>
+          <t>25.03.2025: Governor Radhakrishnan, CM Devendra Fadnavis perform Bhumipujan of Tribute Wall</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/ravindra-chavan-elected-as-bjp-state-president/</t>
+          <t>https://rajbhavan-maharashtra.gov.in/en/25-03-2025-governor-radhakrishnan-cm-devendra-fadnavis-perform-bhumipujan-of-tribute-wall/</t>
         </is>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>Kokan Politics : शरद पवार गटाला धक्का; प्रदेश सरचिटणीस प्रशांत यादव भाजपाच्या वाटेवर</t>
+          <t>आगामी निवडणुकीत भाजपची नजर ५१ टक्के मतांवर!</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/kokan-politics-sharad-pawar-group-suffers-setback-state-general-secretary-prashant-yadav-on-bjps-path/</t>
+          <t>https://www.loksatta.com/sampadkiya/columns/new-bjp-state-president-ravindra-chavan-comments-on-upcoming-local-body-elections-in-loksatta-lok-samvad-program-ssb-93-5224541/</t>
         </is>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="inlineStr">
         <is>
-          <t>25.03.2025: Governor Radhakrishnan, CM Devendra Fadnavis perform Bhumipujan of Tribute Wall</t>
+          <t>कॉर्पोरेटमधील नोकरी ते मुंबई भाजपाच्या अध्यक्षपदी नियुक्ती, कोण आहेत अमित साटम?</t>
         </is>
       </c>
       <c r="B484" t="inlineStr">
         <is>
-          <t>https://rajbhavan-maharashtra.gov.in/en/25-03-2025-governor-radhakrishnan-cm-devendra-fadnavis-perform-bhumipujan-of-tribute-wall/</t>
+          <t>https://www.etvbharat.com/mr/!politics/bmc-election-2025-major-reshuffle-in-bjp-amit-satam-appointed-as-president-of-mumbai-bjp-know-political-reactions-his-profile-coroporate-job-to-politician-mhs25082501410</t>
         </is>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="inlineStr">
         <is>
-          <t>Ravindra Chavan BJP : मुंबईहून भाजप कार्याध्यक्षांचा फोन अन् मंडल अध्यक्षाच्या निवडीला स्थगिती; विखे समर्थकाची कोणी केली तक्रार?</t>
+          <t>अवजड वाहतूक करणाऱ्या वाहन चालकांचा संप मागे</t>
         </is>
       </c>
       <c r="B485" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/uttar-maharashtra/ahilyanagar-bjp-shevgaon-president-appointment-stalled-ravindra-chavan-order-pp82</t>
+          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
         </is>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="inlineStr">
         <is>
-          <t>Maharashtra Live Updates : 'फक्त निवडणूक डोळ्यासमोर ठेवून योजना आणल्या की..' ; रोहित पवारांचा टोला!</t>
+          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
         </is>
       </c>
       <c r="B486" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/headlines-maharashtra-breaking-news-maharashtra-news-maharashtra-politics-news-news-in-marathi-latest-marathi-news-30-may-2025-vaishnavi-hagawane-case-pune-court-update-police-custody-character-assassination-allegations-sharad-pawar-devendra-fadnavis-bjp-maharashtra-strategy-gram-panchayat-to-assembly-obc-movement-manoj-jarange-patil-laxman-hake</t>
+          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
         </is>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="inlineStr">
         <is>
-          <t>आगामी निवडणुकीत भाजपची नजर ५१ टक्के मतांवर!</t>
+          <t>BJP Gears Up for Maharashtra Civic Polls, Holds Meet with Former MPs, MLAs</t>
         </is>
       </c>
       <c r="B487" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/sampadkiya/columns/new-bjp-state-president-ravindra-chavan-comments-on-upcoming-local-body-elections-in-loksatta-lok-samvad-program-ssb-93-5224541/</t>
-        </is>
-      </c>
-    </row>
-    <row r="488">
-      <c r="A488" t="inlineStr">
-        <is>
-          <t>विधानसभा निवडणुकीत बंडखोरी करणाऱ्या नेत्याचे निलंबन भाजपकडून रद्द, राणेंची डोकेदुखी वाढणार?</t>
-        </is>
-      </c>
-      <c r="B488" t="inlineStr">
-        <is>
-          <t>https://www.lokmat.com/maharashtra/bjp-revokes-vishal-parabs-suspension-for-rebelling-in-assembly-elections-will-ranes-headache-increase-a-a301/</t>
-        </is>
-      </c>
-    </row>
-    <row r="489">
-      <c r="A489" t="inlineStr">
-        <is>
-          <t>अवजड वाहतूक करणाऱ्या वाहन चालकांचा संप मागे</t>
-        </is>
-      </c>
-      <c r="B489" t="inlineStr">
-        <is>
-          <t>https://marathi.ndtv.com/maharashtra/maharashtra-assembly-monsoon-session-2025-live-updates-mahayuti-vs-mva-cm-devendra-fadnavis-8804189</t>
-        </is>
-      </c>
-    </row>
-    <row r="490">
-      <c r="A490" t="inlineStr">
-        <is>
-          <t>Mumbai : भाजपा विधायक अमित साटम बने मुंबई भाजपा अध्यक्ष</t>
-        </is>
-      </c>
-      <c r="B490" t="inlineStr">
-        <is>
-          <t>https://indiagroundreport.com/mumbai-bjp-mla-amit-satam-becomes-mumbai-bjp-president/</t>
-        </is>
-      </c>
-    </row>
-    <row r="491">
-      <c r="A491" t="inlineStr">
-        <is>
-          <t>BJP Gears Up for Maharashtra Civic Polls, Holds Meet with Former MPs, MLAs</t>
-        </is>
-      </c>
-      <c r="B491" t="inlineStr">
         <is>
           <t>https://www.deccanherald.com/india/maharashtra/bjp-holds-meeting-of-former-mps-and-mlas-ahead-of-local-body-polls-in-maharashtra-3658754</t>
         </is>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A47"/>
+  <dimension ref="A1:A86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,322 +438,595 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/nda-candidates-win-in-vp-poll-testament-to-modis-leadership-chavan/articleshow/123816248.cms</t>
+          <t>http://www.msn.com/en-in/news/India/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez/ar-AA1HJbtF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://sahyadristartups.com/news/united-maharashtra-strengthens-marathi-community-collaboration-in-uae/</t>
+          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday?amp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/mumbai-illegal-building-demolition-halted-in-dombivli-as-urban-development-department-summons-kdmc-chief/articleshow/123789657.cms</t>
+          <t>https://www.socialnews.xyz/?p=6725428</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/2025/09/09/mumbai-devendra-fadnavis-flags-off-flood-relief-vehicles-to-jk-gallery/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/maharashtra-organizations-in-the-united-arab-emirates-discuss-collaborative-development/</t>
+          <t>https://www.newsdrum.in/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-10469533</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/ravindra-chavan-x-account-suspended/938586</t>
+          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://hindi.news24online.com/india/aaj-ki-taaza-khabar-live-updates-11-september-2025-today-breaking-news-news-24-hindi-samachar-up-mp-bihar-delhi-ncr-news-blog/1316028/</t>
+          <t>https://www.etvbharat.com/mr/!state/congress-mp-ravindra-chavan-criticized-bjp-mp-ashok-chavan-in-nanded-maharashtra-news-mhs25091506942</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/two-people-who-looted-a-petrol-pump-operator-in-chandur-were-caught-two-absconded/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%B8%E0%A5%87-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%A3-%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A4%A4%E0%A4%A6-%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B5%E0%A4%B3%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B0-%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%9F%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%B8-%E0%A4%A0-%E0%A4%A7-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%98%E0%A4%82%E0%A4%9F/ar-AA1v1SPv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.lokshahi.com/amp/story/desh-videsh/charlie-kirk-shot-dead-at-utah-college-event</t>
+          <t>https://www.lokmat.com/topics/ravindra-chavan/page/3/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://mandalnews.com/amravati/third-accused-in-robbery-case-arrested/</t>
+          <t>https://kokansadlive.com/kokan/vengurle/22961</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/hingoli-mp-nagesh-patil-wife-sushma-patil-passes-away-as80</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/thane/ulhasnagar-industrialist-sanjay-gupta-joins-bjp-again-2025-1353635.html</t>
+          <t>https://marathi.indiatimes.com/maharashtra/nanded/congress-mp-ravindra-chavan-from-nanded-criticize-bjp-mp-ashok-chavan/videoshow/123898698.cms</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://guhagarnews.com/jakhadi-festival-in-guhagar/</t>
+          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/amravati/amravati-crime-branch-arrested-2-criminals-for-looting-in-chandur-railway-petrol-pump-1350840.html/amp</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35408-txt-thane-20250921122606</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/bjp-provides-major-assistance-to-kashmir-flood-victims-first-wave-of-resource-trucks-depart/articleshow/123798265.cms</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/kokan/parag-mehta-elected-as-pali-nagaradhyaksh-bjp-scores-key-win-amp17</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://telugu.getlokalapp.com/amp/maharashtra-news/gadchiroli/gadchiroli/gadchiroli-mla-narote-meets-bjp-state-president-15383461</t>
+          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/kdmc-election-2025-kalyan-dombivli-ward-restructuring-political-equations-mm76</t>
+          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/77962/</t>
+          <t>https://pcbtoday.in/%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%AF%E0%A5%81%E0%A4%B5%E0%A4%BE-%E0%A4%B0%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%A6%E0%A5%8C%E0%A4%A1-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34557/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://www.timemaharashtra.com/maharashtra/thane/kalyan-dombivli-municipal-election-2025-new-political-equation-in-new-ward-system/132120/</t>
+          <t>https://ratnagirikhabardar.com/news/80153/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/78267/</t>
+          <t>https://ratnagirikhabardar.com/news/80063/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/maharashtra/ashok-chavan-nanded-lok-sabha-mp-prof-ravindra-chavan-had-political-discussion-during-flight-zws-70-5367966/</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/pm-modi-political-retirement-bjp-president-ravindra-chavan-reaction-dk88-rc70</t>
+          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/maharashtra/thane/page-9/</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/godhamgaon-ancholi-bridge-washed-away-in-heavy-rain-np88</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://news18marathi.com/videos/politics/madha-illegal-excavation-video-1476356.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/thane/ulhasnagar-industrialist-sanjay-gupta-joins-bjp-again-2025-1353635.html/amp</t>
+          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/short-videos/chhagan-bhujbal-priase-cm-fadnavis/938587</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://puneprahar.com/2025/09/maharashtra-organizations-in-the-united-arab-emirates-discuss-collaborative-development-2/</t>
+          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/internal-dispute-within-solapur-city-bjp-has-come-to-the-fore-988665.html/amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/madha-jai-malhar-kala-kendra-dispute-and-firing-one-injured-dk88</t>
+          <t>https://www.esakal.com/amp/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/rss-sarsanghchalak-mohan-bhagwat-statement-ticket-seekers-fear-dk88-rc70</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/cleanliness-drive-begins-in-kdmc-ward.html</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://krushival.in/even-after-independence-the-villagers-of-karanjwadi-remained-neglected/</t>
+          <t>https://www.esakal.com/amp/kokan/todays-latest-marathi-news-kop25d30398-txt-sindhudurg-20250920123949</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i33627-txt-raigad-today-20250910111537</t>
+          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/rlda-announces-tender-for-new-projects-while-csmt-station-redevelopment-remains-incomplete/articleshow/123798372.cms</t>
+          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i35408-txt-thane-20250921122606</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/conditional-bail-granted-by-special-court-in-25-kg-cannabis-case/articleshow/123800360.cms</t>
+          <t>https://maharashtramirror.com/mawal-breaking-news-ncp-congress-suffer-setback-in-mawal-bapu-bhegdes-supporters-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/65-homes-eligible-in-dharavi-redevelopment-project-including-322-families/articleshow/123798304.cms</t>
+          <t>https://mpbreakingnews.in/marathi/maharashtra/bjps-vijay-sankalp-rally-in-aditya-thackerays-constituency-today-bjp-will-break-the-coconut-of-municipal-election-campaign-05-697328</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/chlorine-gas-leak-at-bhivandi-water-purification-center-five-employees-affected/articleshow/123798337.cms</t>
+          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-uncut-speech-what-is-bjp-s-plan-for-bmc-elections-cm-fadnavis-thackeray-n18v-1074921.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/mumbai-to-develop-seven-sewage-treatment-plants-plan-to-discharge-treated-water-in-sea/articleshow/123798292.cms</t>
+          <t>https://www.newsdrum.in/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis-10471204</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/e-paper/malegaon-bomb-blast-case-victims-families-challenge-acquittal-of-sadhvi-pragya-singh-thakur/articleshow/123800199.cms</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/devendra-fadnavis-gst-reforms-second-phase-narendra-modi-event-1363060.html/amp</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://eduvarta.com/BJP-appoints-Rajesh-Pandey-as-Voter-Registration-Head</t>
+          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-unveils-rs-3268-cr-avgc-xr-policy-to-create-2-lakh-jobs-23594327</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/nagpur/india-must-be-force-for-global-good-rss-chief/articleshow/123816266.cms</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/amit-shah-at-lalbaugcha-raja-%E0%A4%97-%E0%A4%82%E0%A4%A1%E0%A4%B8-%E0%A4%A8-%E0%A4%A4%E0%A4%B5-%E0%A4%B2-%E0%A4%95%E0%A4%A1%E0%A5%87%E0%A4%B5%E0%A4%B0-%E0%A4%98%E0%A5%87%E0%A4%8A%E0%A4%A8-%E0%A4%85%E0%A4%AE-%E0%A4%A4-%E0%A4%B6-%E0%A4%B9-%E0%A4%B2-%E0%A4%B2%E0%A4%AC-%E0%A4%97%E0%A4%9A-%E0%A4%B0-%E0%A4%9C-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%A6%E0%A4%B0%E0%A5%8D%E0%A4%B6%E0%A4%A8-%E0%A4%B2/ar-AA1LwAZa?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://maharashtranews1.com/Amal-Mahadik-in-the-Self-reliant-India-Resolution-Campaign-Committee-</t>
+          <t>https://www.ptinews.com/detail/national/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.eaajkaanand.com/Encyc/2025/9/11/vote.html</t>
+          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/india/%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%A8%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A5%87%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A6-%E0%A4%A8-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B0-%E0%A4%88-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%95-%E0%A4%9C-%E0%A4%87%E0%A4%A8-%E0%A4%82%E0%A4%97/ar-AA1HO1X4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/one-lakh-cataract-operations-will-be-conducted-in-maharashtra-on-pm-modis-birthday-bjp/869293/?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%B7-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-bjp-%E0%A4%AE%E0%A4%B9-%E0%A4%A7-%E0%A4%B5%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%95%E0%A4%B9/ar-BB1rjuv7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>https://navbharatlive.com/maharashtra/pune/several-ncp-leaders-joined-the-bjp-in-mumbai-on-tuesday-1358034.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30123-txt-sindhudurg-today-20250919115725</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>https://www.esakal.com/amp/kokan/todays-latest-marathi-news-kop25d30489-txt-sindhudurg-20250920015648</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>https://statetimes.in/deportation-a-practical-approach-of-bringing-criminals-from-abroad-amit-shah/</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday?utm_campaign=Bundle&amp;utm_medium=referral&amp;utm_source=Bundle</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>https://www.devdiscourse.com/article/health/3629623-crisis-in-khyber-pakhtunkhwa-polio-team-kidnapped-amid-new-cases?amp</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/79519/</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>https://deshonnati.com/response-to-namo-yuva-run-marathon-in-parbhani/?amp=1</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>https://ratnagirikhabardar.com/news/79428/</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>https://hindi.theprint.in/india/one-lakh-cataract-operations-will-be-conducted-in-maharashtra-on-pm-modis-birthday-bjp/869293/</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>https://www.moneycontrol.com/news/india/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp-13550545.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/amp_articleshow/124001969.cms</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>https://www.etvbharat.com/mr/!state/bjp-to-start-mumbai-municipal-election-campaign-tomorrow-maharashtra-news-mhs25091506101</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A86"/>
+  <dimension ref="A1:A75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,14 +438,14 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>http://www.msn.com/en-in/news/India/dombivli-mla-ravindra-chavan-to-be-appointed-maharashtra-bjp-prez/ar-AA1HJbtF?apiversion=v2&amp;domshim=1&amp;noservercache=1&amp;noservertelemetry=1&amp;batchservertelemetry=1&amp;renderwebcomponents=1&amp;wcseo=1</t>
+          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday?amp</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom10-mh-bjp-modi-drive.html</t>
         </is>
       </c>
     </row>
@@ -466,392 +466,392 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-10469533</t>
+          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
+          <t>https://www.etvbharat.com/mr/!state/congress-mp-ravindra-chavan-criticized-bjp-mp-ashok-chavan-in-nanded-maharashtra-news-mhs25091506942</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/congress-mp-ravindra-chavan-criticized-bjp-mp-ashok-chavan-in-nanded-maharashtra-news-mhs25091506942</t>
+          <t>https://www.tarunbharat.com/spontaneous-response-to-telemedicine-clinic-camp-in-sangeli/</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%82%E0%A4%A8-%E0%A4%AB-%E0%A4%B8%E0%A5%87-%E0%A4%9F-%E0%A4%95%E0%A4%B2%E0%A5%87-%E0%A4%95-%E0%A4%95%E0%A4%A3-%E0%A4%A4-%E0%A4%B2-%E0%A4%AE%E0%A4%A4%E0%A4%A6-%E0%A4%B0-%E0%A4%AE%E0%A4%B9-%E0%A4%AF%E0%A5%81%E0%A4%A4-%E0%A4%95%E0%A4%A1%E0%A5%87-%E0%A4%B5%E0%A4%B3%E0%A4%B2%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%8D%E0%A4%AF-%E0%A4%A8%E0%A5%87%E0%A4%A4%E0%A5%83%E0%A4%A4%E0%A5%8D%E0%A4%B5-%E0%A4%AE%E0%A5%81%E0%A4%B3%E0%A5%87-%E0%A4%B0-%E0%A4%A3%E0%A5%87-%E0%A4%95%E0%A5%81%E0%A4%9F%E0%A5%81%E0%A4%82%E0%A4%AC-%E0%A4%B8-%E0%A4%A0-%E0%A4%A7-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%9A-%E0%A4%98%E0%A4%82%E0%A4%9F/ar-AA1v1SPv?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://www.lokmat.com/topics/ravindra-chavan/page/3/</t>
+          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-big-blow-to-mahavikas-aghadi-as-sarpanch-leaders-join-bjp-in-vidarbha-pvm91</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://kokansadlive.com/kokan/vengurle/22961</t>
+          <t>https://www.navakal.in/news/vaibhav-khedekar-to-join-bjp-news/</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
+          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/nanded/congress-mp-ravindra-chavan-from-nanded-criticize-bjp-mp-ashok-chavan/videoshow/123898698.cms</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35408-txt-thane-20250921122606</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35408-txt-thane-20250921122606</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34569/</t>
+          <t>https://www.marathi.hindusthanpost.com/social/bjps-big-announcement-grand-activities-will-be-held-across-the-state/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
+          <t>https://dainikmaval.com/supporters-from-maval-taluka-under-leadership-of-bapusaheb-bhegde-will-join-bjp-today/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
+          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://pcbtoday.in/%E0%A4%A8%E0%A4%AE%E0%A5%8B-%E0%A4%AF%E0%A5%81%E0%A4%B5%E0%A4%BE-%E0%A4%B0%E0%A4%A8-%E0%A4%8F%E0%A4%95-%E0%A4%A6%E0%A5%8C%E0%A4%A1-%E0%A4%AE%E0%A5%8B%E0%A4%A6%E0%A5%80/</t>
+          <t>https://ratnagirikhabardar.com/news/80063/</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/80153/</t>
+          <t>https://ratnagirikhabardar.com/news/79519/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/80063/</t>
+          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://www.uniindia.com/news/west/event-mah-modi-birthday-celebration/3580965.html</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://www.msn.com/mr-in/news/other/%E0%A4%A6%E0%A5%87%E0%A4%B5%E0%A5%87%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%AB%E0%A4%A1%E0%A4%A3%E0%A4%B5-%E0%A4%B8-%E0%A4%82%E0%A4%9A%E0%A5%87-%E0%A4%B5-%E0%A4%B6%E0%A5%8D%E0%A4%B5-%E0%A4%B8%E0%A5%82-%E0%A4%85%E0%A4%A8%E0%A5%8D-rss-%E0%A4%9A%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A4%B0%E0%A5%8D%E0%A4%9C-%E0%A4%A4%E0%A4%B2%E0%A5%87-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%AD-%E0%A4%9C%E0%A4%AA%E0%A4%9A%E0%A5%87-%E0%A4%A8%E0%A4%B5%E0%A5%87-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AE%E0%A5%81%E0%A4%82%E0%A4%AC%E0%A4%88%E0%A4%A4-%E0%A4%98-%E0%A4%B7%E0%A4%A3/ar-AA1HLd3n?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://pudhari.news/maharashtra/marathwada/nanded/nanded-ashok-chavan-political-news-np88</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
+          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/cleanliness-drive-begins-in-kdmc-ward.html</t>
+          <t>https://puneprimenews.com/pune/pune-news-ajit-pawar-gets-a-shock-in-pune-34-ncp-leaders-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/kokan/todays-latest-marathi-news-kop25d30398-txt-sindhudurg-20250920123949</t>
+          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/mumbai/todays-latest-marathi-news-mum25i35408-txt-thane-20250921122606</t>
+          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://maharashtramirror.com/mawal-breaking-news-ncp-congress-suffer-setback-in-mawal-bapu-bhegdes-supporters-join-bjp/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://mpbreakingnews.in/marathi/maharashtra/bjps-vijay-sankalp-rally-in-aditya-thackerays-constituency-today-bjp-will-break-the-coconut-of-municipal-election-campaign-05-697328</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://lokmat.news18.com/videos/video/ravindra-chavan-uncut-speech-what-is-bjp-s-plan-for-bmc-elections-cm-fadnavis-thackeray-n18v-1074921.html</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis-10471204</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/devendra-fadnavis-gst-reforms-second-phase-narendra-modi-event-1363060.html/amp</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/amp/mumbai/mumbai-news/article/maharashtra-unveils-rs-3268-cr-avgc-xr-policy-to-create-2-lakh-jobs-23594327</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
+          <t>https://www.newsdrum.in/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis-10471204</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
+          <t>https://www.moneycontrol.com/news/india/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp-13550545.html</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/detail/national/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
+          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/india/%E0%A4%AC-%E0%A4%9C%E0%A5%87%E0%A4%AA-%E0%A4%AA%E0%A5%8D%E0%A4%B0%E0%A4%A6%E0%A5%87%E0%A4%B6-%E0%A4%85%E0%A4%A7%E0%A5%8D%E0%A4%AF%E0%A4%95%E0%A5%8D%E0%A4%B7-%E0%A4%AC%E0%A4%A8%E0%A4%A4%E0%A5%87-%E0%A4%B9-%E0%A4%95-%E0%A4%82%E0%A4%97%E0%A5%8D%E0%A4%B0%E0%A5%87%E0%A4%B8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%B8%E0%A5%87%E0%A4%82%E0%A4%A7-%E0%A4%AA%E0%A4%B9%E0%A4%B2%E0%A5%87-%E0%A4%B9-%E0%A4%A6-%E0%A4%A8-%E0%A4%B0%E0%A4%B5-%E0%A4%82%E0%A4%A6%E0%A5%8D%E0%A4%B0-%E0%A4%9A%E0%A4%B5%E0%A5%8D%E0%A4%B9-%E0%A4%A3-%E0%A4%A8%E0%A5%87-%E0%A4%95%E0%A4%B0-%E0%A4%88-%E0%A4%95%E0%A5%81%E0%A4%A3-%E0%A4%B2-%E0%A4%AA-%E0%A4%9F-%E0%A4%B2-%E0%A4%95-%E0%A4%9C-%E0%A4%87%E0%A4%A8-%E0%A4%82%E0%A4%97/ar-AA1HO1X4?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
+          <t>https://ratnagirikhabardar.com/news/79210/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
+          <t>https://ratnagirikhabardar.com/news/79993/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/one-lakh-cataract-operations-will-be-conducted-in-maharashtra-on-pm-modis-birthday-bjp/869293/?amp</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.msn.com/hi-in/news/other/%E0%A4%B0-%E0%A4%9C%E0%A5%8D%E0%A4%AF-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%9C-%E0%A4%A4-%E0%A4%95-%E0%A4%B0-%E0%A4%9C%E0%A4%A8-%E0%A4%A4-%E0%A4%95%E0%A4%B0-%E0%A4%B5-%E0%A4%A6%E0%A5%8D%E0%A4%B5%E0%A5%87%E0%A4%B7-%E0%A4%AE%E0%A4%B9-%E0%A4%B0-%E0%A4%B7%E0%A5%8D%E0%A4%9F%E0%A5%8D%E0%A4%B0-bjp-%E0%A4%AE%E0%A4%B9-%E0%A4%A7-%E0%A4%B5%E0%A5%87%E0%A4%B6%E0%A4%A8-%E0%A4%AE%E0%A5%87%E0%A4%82-%E0%A4%AC-%E0%A4%B2%E0%A5%87-%E0%A4%A8-%E0%A4%A4-%E0%A4%A8-%E0%A4%97%E0%A4%A1%E0%A4%95%E0%A4%B0-%E0%A4%95%E0%A5%8D%E0%A4%AF-%E0%A4%95%E0%A5%81%E0%A4%9B-%E0%A4%95%E0%A4%B9/ar-BB1rjuv7?apiversion=v2&amp;noservercache=1&amp;domshim=1&amp;renderwebcomponents=1&amp;wcseo=1&amp;batchservertelemetry=1&amp;noservertelemetry=1</t>
+          <t>https://www.jaimaharashtranews.com/latest-news/mns-leader-vaibhav-khedekar-joins-bjp-maharashtra-ratnagiri-politics-shakes-up-ahead-of-local-elections/41550</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
+          <t>https://mahasamvad.in/179272/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/pune/several-ncp-leaders-joined-the-bjp-in-mumbai-on-tuesday-1358034.html</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
+          <t>https://www.saamana.com/maharashtra-20-lakhs-spent-from-government-treasury-in-the-name-of-washing-sheets-and-curtains-in-a-worli-rest-house/</t>
         </is>
       </c>
     </row>
@@ -865,166 +865,89 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/amp/kokan/todays-latest-marathi-news-kop25d30489-txt-sindhudurg-20250920015648</t>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>https://statetimes.in/deportation-a-practical-approach-of-bringing-criminals-from-abroad-amit-shah/</t>
+          <t>https://www.tv9marathi.com/maharashtra/vaibhav-khedekar-joins-bjp-maharashtra-ratnagiri-politics-shakes-up-ahead-of-local-elections-1498492.html</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
+          <t>https://mahasamvad.in/179534/</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday?utm_campaign=Bundle&amp;utm_medium=referral&amp;utm_source=Bundle</t>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://www.devdiscourse.com/article/health/3629623-crisis-in-khyber-pakhtunkhwa-polio-team-kidnapped-amid-new-cases?amp</t>
+          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79519/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/</t>
+          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://marathi.indiatimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>https://deshonnati.com/response-to-namo-yuva-run-marathon-in-parbhani/?amp=1</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79428/</t>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>https://hindi.theprint.in/india/one-lakh-cataract-operations-will-be-conducted-in-maharashtra-on-pm-modis-birthday-bjp/869293/</t>
+          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>https://www.moneycontrol.com/news/india/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp-13550545.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/amp_articleshow/124001969.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
         <is>
           <t>https://www.etvbharat.com/mr/!state/bjp-to-start-mumbai-municipal-election-campaign-tomorrow-maharashtra-news-mhs25091506101</t>
         </is>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A75"/>
+  <dimension ref="A1:A63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,21 +438,21 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/editor-detail/One-lakh-cataract-surgeries-in-Maharashtra-to-mark-Modi-s-birthday-BJP/2919522</t>
+          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom10-mh-bjp-modi-drive.html</t>
+          <t>https://www.indianwitness.com/news/national/bjp-launches-one-lakh-cataract-surgeries-to-mark-pm-mod</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.socialnews.xyz/?p=6725428</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom10-mh-bjp-modi-drive.amp.html</t>
         </is>
       </c>
     </row>
@@ -466,42 +466,42 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/congress-mp-ravindra-chavan-criticized-bjp-mp-ashok-chavan-in-nanded-maharashtra-news-mhs25091506942</t>
+          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.tarunbharat.com/spontaneous-response-to-telemedicine-clinic-camp-in-sangeli/</t>
+          <t>https://www.etvbharat.com/mr/!state/congress-mp-ravindra-chavan-criticized-bjp-mp-ashok-chavan-in-nanded-maharashtra-news-mhs25091506942</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/maharashtra-politics-big-blow-to-mahavikas-aghadi-as-sarpanch-leaders-join-bjp-in-vidarbha-pvm91</t>
+          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/vaibhav-khedekar-to-join-bjp-news/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
         </is>
       </c>
     </row>
@@ -543,14 +543,14 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/social/bjps-big-announcement-grand-activities-will-be-held-across-the-state/</t>
+          <t>https://dainikmaval.com/supporters-from-maval-taluka-under-leadership-of-bapusaheb-bhegde-will-join-bjp-today/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/supporters-from-maval-taluka-under-leadership-of-bapusaheb-bhegde-will-join-bjp-today/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
@@ -564,35 +564,35 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/80063/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://www.dainikprabhat.com/maval-political-shift-big-blow-to-maval-congress-hundreds-of-congress-workers-join-bjp/</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79519/</t>
+          <t>https://ratnagirikhabardar.com/news/80063/</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
+          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
         </is>
       </c>
     </row>
@@ -620,336 +620,252 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://newsarenaindia.com/nation/marking-pm-s-b-day-maha-bjp-plans-1-lakh-cataract-surgeries/56550</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.uniindia.com/news/west/event-mah-modi-birthday-celebration/3580965.html</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://pudhari.news/maharashtra/marathwada/nanded/nanded-ashok-chavan-political-news-np88</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/nanded-ashok-chavan-political-news-np88</t>
+          <t>https://puneprimenews.com/pune/pune-news-ajit-pawar-gets-a-shock-in-pune-34-ncp-leaders-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
+          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/pune-news-ajit-pawar-gets-a-shock-in-pune-34-ncp-leaders-join-bjp/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
+          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/ashish-shelar-inaugurates-the-exhibition-new-india-cultural-superpower.html</t>
+          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
+          <t>https://ratnagirikhabardar.com/news/79210/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/bjp-gave-up-claim-for-mumbai-mayors-post-in-2017-at-request-of-shinde-narvekar-says-cm-fadnavis-10471204</t>
+          <t>https://ratnagirikhabardar.com/news/79993/</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.moneycontrol.com/news/india/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp-13550545.html</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
+          <t>https://mahasamvad.in/179272/</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
+          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79210/</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79993/</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
+          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30123-txt-sindhudurg-today-20250919115725</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522</t>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://www.jaimaharashtranews.com/latest-news/mns-leader-vaibhav-khedekar-joins-bjp-maharashtra-ratnagiri-politics-shakes-up-ahead-of-local-elections/41550</t>
+          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179272/</t>
+          <t>https://civicmirror.in/maharashtra/new-gst-reforms-will-give-new-impetus-to-indias-economic-development-chief-minister-devendra-fadnavis/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://www.saamana.com/maharashtra-20-lakhs-spent-from-government-treasury-in-the-name-of-washing-sheets-and-curtains-in-a-worli-rest-house/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30123-txt-sindhudurg-today-20250919115725</t>
+          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>https://www.tv9marathi.com/maharashtra/vaibhav-khedekar-joins-bjp-maharashtra-ratnagiri-politics-shakes-up-ahead-of-local-elections-1498492.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>https://mahasamvad.in/179534/</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>https://www.devdiscourse.com/article/health/3629547-maharashtras-mega-health-drive-for-pm-modis-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-to-start-mumbai-municipal-election-campaign-tomorrow-maharashtra-news-mhs25091506101</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A63"/>
+  <dimension ref="A1:A62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -438,84 +438,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/story/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modi-s-birthday-bjp/2919522</t>
+          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.indianwitness.com/news/national/bjp-launches-one-lakh-cataract-surgeries-to-mark-pm-mod</t>
+          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/bom10-mh-bjp-modi-drive.amp.html</t>
+          <t>https://www.indianwitness.com/news/national/bjp-launches-one-lakh-cataract-surgeries-to-mark-pm-mod</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
+          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/congress-mp-ravindra-chavan-criticized-bjp-mp-ashok-chavan-in-nanded-maharashtra-news-mhs25091506942</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
+          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
+          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
+          <t>https://www.navakal.in/news/vaibhav-khedekar-to-join-bjp-news/</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35408-txt-thane-20250921122606</t>
+          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
         </is>
       </c>
     </row>
@@ -529,14 +529,14 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34569/</t>
+          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
@@ -557,7 +557,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
@@ -585,119 +585,119 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
+          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
+          <t>https://www.newsdrum.in/national/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday-10469982</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
+          <t>https://pudhari.news/maharashtra/marathwada/nanded/nanded-ashok-chavan-political-news-np88</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://puneprimenews.com/pune/pune-news-ajit-pawar-gets-a-shock-in-pune-34-ncp-leaders-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
+          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/nanded-ashok-chavan-political-news-np88</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/pune-news-ajit-pawar-gets-a-shock-in-pune-34-ncp-leaders-join-bjp/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30640-txt-sindhudurg-today-20250921112402</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
+          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/vidarbha/ajit-pawar-reacts-to-bhujbal-criticism-avoid-divide-in-society-sw79-rc70</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
+          <t>https://marathi.ndtv.com/videos/how-will-raj-thackeray-ambarnath-and-kalyan-daura-be-ndtv-report-996461</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://marathi.ndtv.com/videos/obc-elgar-morcha-in-hingoli-laxman-hake-warm-welcome-995642</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
         </is>
       </c>
     </row>
@@ -711,35 +711,35 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.ptinews.com/stories-detail/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp/2919522/1</t>
+          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
+          <t>https://ratnagirikhabardar.com/news/79210/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79210/</t>
+          <t>https://ratnagirikhabardar.com/news/79993/</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79993/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
@@ -753,7 +753,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/devendra-fadnavis-gst-reforms-second-phase-narendra-modi-event-1363060.html</t>
         </is>
       </c>
     </row>
@@ -767,105 +767,98 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/mumbai/todays-latest-marathi-news-mum25i35482-txt-today-20250921114037</t>
+          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://www.esakal.com/kokan/todays-latest-marathi-news-kop25d30123-txt-sindhudurg-today-20250919115725</t>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
+          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
+          <t>https://www.nagpurtoday.in/modi-is-the-biggest-brand-in-the-world-chief-minister-fadnavis-statement/09171621</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://civicmirror.in/maharashtra/new-gst-reforms-will-give-new-impetus-to-indias-economic-development-chief-minister-devendra-fadnavis/</t>
+          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
+          <t>https://www.etvbharat.com/mr/!state/bjp-to-start-mumbai-municipal-election-campaign-tomorrow-maharashtra-news-mhs25091506101</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
+          <t>https://www.theweek.in/wire-updates/national/2025/09/16/del42-pm-birthday.html</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A62"/>
+  <dimension ref="A1:A52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,7 +445,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
@@ -459,406 +459,336 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
+          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
+          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
+          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
+          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
+          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
+          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>https://www.navakal.in/news/vaibhav-khedekar-to-join-bjp-news/</t>
+          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
+          <t>https://deshdoot.com/container-hit-vehicles-loss-ahilyanagar/</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
+          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://aaplaawajnews.com/2025/34569/</t>
+          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://dainikmaval.com/supporters-from-maval-taluka-under-leadership-of-bapusaheb-bhegde-will-join-bjp-today/</t>
+          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
+          <t>https://aaplaawajnews.com/2025/34569/</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
+          <t>https://dainikmaval.com/supporters-from-maval-taluka-under-leadership-of-bapusaheb-bhegde-will-join-bjp-today/</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/80063/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://www.greaterkashmir.com/national/1-lakh-cataract-surgeries-in-maharashtra-to-mark-pms-birthday-bjp/</t>
+          <t>https://ratnagirikhabardar.com/news/80063/</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.newsdrum.in/national/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday-10469982</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/marathwada/nanded/nanded-ashok-chavan-political-news-np88</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://puneprimenews.com/pune/pune-news-ajit-pawar-gets-a-shock-in-pune-34-ncp-leaders-join-bjp/</t>
+          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
+          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/jayant-patil-ncp-sangli-padalkar-sw79-rg93</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://ratnagirikhabardar.com/news/79210/</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/18/dadar-matunga-cultural-center-organizes-spiritual-color-festival.html</t>
+          <t>https://ratnagirikhabardar.com/news/79993/</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/how-will-raj-thackeray-ambarnath-and-kalyan-daura-be-ndtv-report-996461</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://marathi.ndtv.com/videos/obc-elgar-morcha-in-hingoli-laxman-hake-warm-welcome-995642</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://navbharatlive.com/maharashtra/mumbai/devendra-fadnavis-gst-reforms-second-phase-narendra-modi-event-1363060.html</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79210/</t>
+          <t>https://deshdoot.com/mp-supriya-sule-visited-trimbakeshwar-and-take-darshan-trimbakraj-temple/</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79993/</t>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
+          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://www.mumbailive.com/hi/politics/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-and-demands-90035</t>
+          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/devendra-fadnavis-gst-reforms-second-phase-narendra-modi-event-1363060.html</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://mahasamvad.in/179272/</t>
+          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/kokan/sindhudurg/nitesh-rane-warning-dodamarg-event-guardian-minister-sp96</t>
+          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>https://www.nagpurtoday.in/modi-is-the-biggest-brand-in-the-world-chief-minister-fadnavis-statement/09171621</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>https://www.marathi.hindusthanpost.com/politics/mumbais-mayor-will-be-for-mumbaikars-not-for-the-chair-cm-devendra-fadnavis-attack/</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/bjp-to-start-mumbai-municipal-election-campaign-tomorrow-maharashtra-news-mhs25091506101</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>https://www.theweek.in/wire-updates/national/2025/09/16/del42-pm-birthday.html</t>
+          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A52"/>
+  <dimension ref="A1:A50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,14 +445,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
+          <t>https://www.indianwitness.com/news/national/bjp-launches-one-lakh-cataract-surgeries-to-mark-pm-mod</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://www.indianwitness.com/news/national/bjp-launches-one-lakh-cataract-surgeries-to-mark-pm-mod</t>
+          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
         </is>
       </c>
     </row>
@@ -466,7 +466,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
+          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
         </is>
       </c>
     </row>
@@ -480,7 +480,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://udayavani.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-131344?lang=en</t>
+          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
         </is>
       </c>
     </row>
@@ -515,21 +515,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
+          <t>https://www.navakal.in/news/vaibhav-khedekar-to-join-bjp-news/</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/container-hit-vehicles-loss-ahilyanagar/</t>
+          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
+          <t>https://deshdoot.com/container-hit-vehicles-loss-ahilyanagar/</t>
         </is>
       </c>
     </row>
@@ -578,14 +578,14 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
+          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/80063/</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
         </is>
       </c>
     </row>
@@ -599,28 +599,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
+          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
+          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
+          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
+          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
         </is>
       </c>
     </row>
@@ -634,161 +634,147 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-bmc-elections-mahayuti-alliance-but-bjp-plans-solo-contest-in-deputy-cm-strongholds-sw79</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/thackeray-brothers-meeting-fixed-on-dussehra-shivaji-park-alliance-buzz-sw79</t>
+          <t>https://maharashtramirror.com/mawal-breaking-news-ncp-congress-suffer-setback-in-mawal-bapu-bhegdes-supporters-join-bjp/</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
+          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
+          <t>https://ratnagirikhabardar.com/news/79210/</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://ratnagirikhabardar.com/news/79993/</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79210/</t>
+          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>https://ratnagirikhabardar.com/news/79993/</t>
+          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
+          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
+          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
+          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>https://navbharatlive.com/maharashtra/mumbai/devendra-fadnavis-gst-reforms-second-phase-narendra-modi-event-1363060.html</t>
+          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
+          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://deshdoot.com/mp-supriya-sule-visited-trimbakeshwar-and-take-darshan-trimbakraj-temple/</t>
+          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
+          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
+          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>https://thefocusindia.com/maharashtra-news/fadnavis-slams-thackeray-brothers-at-bjp-rally-284342/amp/</t>
+          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
+          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
+          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
+          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
+          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
+          <t>https://www.newsdanka.com/vishesh/state-bjp-to-organize-a-seva-pandharwada-for-pm-modis-75th-birthday/167436/</t>
         </is>
       </c>
     </row>

--- a/Output/Ravindra Chavan/extracted_links.xlsx
+++ b/Output/Ravindra Chavan/extracted_links.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A50"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,349 +435,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>https://timesofindia.indiatimes.com/city/mumbai/political-chess-underway-in-ulhasnagar-as-shiv-sena-allies-with-sai-party/articleshow/124001969.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>https://www.indianwitness.com/news/national/bjp-launches-one-lakh-cataract-surgeries-to-mark-pm-mod</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/maharashtra-bjp-launches-seva-pandharwada-to-mark-pm-modis-75th-birthday</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>https://indianexpress.com/article/political-pulse/a-prime-minister-has-his-birthday-a-party-throws-parties-10253607/</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>https://www.thehitavada.com/Encyc/2025/9/19/tatkare-terms-rahul-gandhis-vote-theft-allegation-childish.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>https://www.dtnext.in/news/national/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-846754</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>https://www.mid-day.com/mumbai/mumbai-news/article/maharashtra-to-conduct-over-1-lakh-cataract-surgeries-during-fortnight-long-health-drive-marking-pm-modis-birthday-23594304</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>https://www.freepressjournal.in/mumbai/bmc-election-mumbai-bjp-launches-platform-for-citizens-to-register-their-issues-demands</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>https://www.loksatta.com/thane/birthday-of-dombivli-mla-ravindra-chavan-phm-00-5386678/</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>https://navbharattimes.indiatimes.com/epaper/nbt-mumbai-epaper/shiv-sena-jolts-bjp-in-ulhasnagar-allies-with-sai-party/articleshow/124046213.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>https://kokansadlive.com/kokan/vengurle/22794</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>https://www.navakal.in/news/vaibhav-khedekar-to-join-bjp-news/</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/maharashtra/vaibhav-khedekar-to-lead-former-mns-leaders-into-bjp-in-mumbai-ceremony-latest-politics-bdk97</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>https://deshdoot.com/container-hit-vehicles-loss-ahilyanagar/</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>https://www.marathiebatmya.com/political/ravindra-chavan-said-service-fortnight-on-the-occasion-of-narendra-modis-birthda/</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>https://dainikmaval.com/hundreds-of-bapu-bhegde-supporters-join-bjp-in-maval-taluka-ravindra-chavan-bala-bhegde-ramdas-kakade/</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>https://aaplaawajnews.com/2025/34569/</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>https://dainikmaval.com/supporters-from-maval-taluka-under-leadership-of-bapusaheb-bhegde-will-join-bjp-today/</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/maharashtra-bjp-chandrashekhar-bawankule-magic-continues-ravindra-chavan-big-decision-15-days-sw79</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>https://www.mahamtb.com/Encyc/2025/9/16/seva-pandharvada-organized-across-the-state-on-the-occasion-of-prime-minister-modis-birthday-information-from-.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>https://www.navarashtra.com/maharashtra/on-the-occasion-of-modi-birthday-a-cleanliness-and-tree-plantation-campaign-was-organized-by-the-old-bjp-kalyan-city-committee-993381.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/paschim-maharashtra/maharashtra-politics-ajit-pawar-rival-bapu-bhegade-bjp-entry-but-this-joining-delayed-as11-sm89</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>https://www.deccanchronicle.com/nation/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp-1904130</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/en/!bharat/pm-modi-to-lay-foundation-of-pm-mitra-park-launch-sewa-pakhwada-in-madhya-pradesh-on-september-17-enn25091602243</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>https://www.bhaskarhindi.com/city/mumbai/mumbai-news-mahaaraashtr-mein-ek-laakh-mupht-motiyaabind-sarjaree-karavaegee-bhaajapa-1187636</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/pune/political-news-ncp-leaders-from-maval-join-bjp-sb97</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>https://zeenews.india.com/marathi/maharashtra/live-updates/maharashtra-breaking-news-today-maharashtra-politics-rain-update-ajchya-thalak-batmya-on-septembar-16-political-news-in-marathi-939577</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>https://www.etvbharat.com/mr/!state/sewa-pakhwada-in-the-maharashtra-on-the-occasion-of-prime-minister-narendra-modis-75th-birthday-iti-students-to-carry-out-cleanliness-drive-in-750-villages-maharashtra-news-mhs25091603490</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/former-khed-nagaradhyaksh-vaibhav-khedekar-to-join-bjp-in-ratnagiri-tomorrow-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>https://maharashtramirror.com/mawal-breaking-news-ncp-congress-suffer-setback-in-mawal-bapu-bhegdes-supporters-join-bjp/</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>https://statetimes.in/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>https://ratnagirikhabardar.com/news/79210/</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>https://ratnagirikhabardar.com/news/79993/</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/vishleshan/mumbai-civic-polls-uddhav-raj-thackeray-alliance-vs-shinde-sena-sw79</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/mumbai-pune/kalyan-dombivli-elections-eknath-shinde-vs-uddhav-thackeray-who-will-win-the-battle-vvg94</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>https://maharashtratimes.com/maharashtra/thane/bjp-leader-ganesh-naik-taking-shiv-sena-chief-and-dcm-eknath-shinde-head-on-in-thane-and-navi-mumbai/articleshow/124013451.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>https://www.patrika.com/mumbai-news/bal-thackeray-was-brand-not-you-fadnavis-took-a-dig-at-uddhav-thackeray-and-raj-thackeray-19953281</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/maharashtra/konkan/eknath-shinde-shivsena-deepak-kesarkar-may-get-bigger-responsibility-and-position-beyond-ministry-hints-by-minister-yogesh-kadam-at-sindhudurg-as11</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>https://www.mymahanagar.com/maharashtra/a-scam-worth-lakhs-of-rupees-has-been-revealed-in-the-name-of-laundry-at-visava-a-government-rest-house-in-worli/924082/</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>https://maharashtratimes.com/maharashtra/mumbai-news/cm-devendra-fadnavis-criticizes-thackeray-brothers-at-bjp-rally-mumbai/articleshow/123932945.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>https://pudhari.news/maharashtra/mumbai/devendra-fadnavis-mahayuti-saffron-flag-mumbai-bmc-ab96</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>https://www.easternmirrornagaland.com/one-lakh-cataract-surgeries-in-maharashtra-to-mark-modis-birthday-bjp</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>https://sarkarnama.esakal.com/desh/bihar-update-amit-shah-maharashtra-pattern-nitish-kumar-60-day-master-plan-dk88</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>https://saamtv.esakal.com/maharashtra/local-elections-2025-34-leaders-of-rashtrawadi-congress-join-bjp-in-pune-ahead-of-elections-bdk97</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>https://www.hindustantimes.com/india-news/how-bjp-is-celebrating-pm-narendra-modis-75th-birthday-across-states-today-details-of-events-101758067171247.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>https://www.livemint.com/news/india/pm-modi-turns-75-today-from-drone-shows-to-blood-donation-camps-bjps-grand-celebration-plans-for-the-day-11758069800439.html</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>https://m.economictimes.com/news/india/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/articleshow/123921237.cms</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>https://www.dailyexcelsior.com/pm-modi-to-launch-development-initiatives-as-part-of-sewa-pakhwada-to-mark-his-birthday/</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>https://www.newsdanka.com/vishesh/state-bjp-to-organize-a-seva-pandharwada-for-pm-modis-75th-birthday/167436/</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
